--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8146EF3-375A-43CA-AC34-668AEE37391E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" tabRatio="711" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -15,12 +21,23 @@
     <sheet name="GameDefine" sheetId="3" r:id="rId6"/>
     <sheet name="TextData" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="474">
   <si>
     <t>Id</t>
   </si>
@@ -837,9 +854,6 @@
     <t>Boot</t>
   </si>
   <si>
-    <t>ひびかけ色のキセキ</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -853,15 +867,6 @@
   </si>
   <si>
     <t>プレイヤーID:</t>
-  </si>
-  <si>
-    <t>NewGame</t>
-  </si>
-  <si>
-    <t>Continue</t>
-  </si>
-  <si>
-    <t>Option</t>
   </si>
   <si>
     <t>データを初期化しますか？</t>
@@ -1442,19 +1447,52 @@
   </si>
   <si>
     <t>収集率</t>
+  </si>
+  <si>
+    <t>Norm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TUTORIAL</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>新しくゲームを始める</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>オプションを設定する</t>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>チュートリアルをプレイする</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以前の続きからプレイする</t>
+    <rPh sb="0" eb="2">
+      <t>イゼン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1470,344 +1508,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1815,255 +1538,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2076,62 +1557,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2418,16 +1858,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="11.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2486,19 +1926,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="3" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="11.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2538,26 +1977,36 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C4">
+        <v>13240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>13230</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="15.9090909090909" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2616,19 +2065,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="23.8181818181818" customWidth="1"/>
-    <col min="6" max="9" width="12.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
+    <col min="6" max="9" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3048,18 +2496,1651 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D117"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="22.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>130</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>140</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>140</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>111</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>140</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>140</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>111</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>190</v>
+      </c>
+      <c r="D31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>140</v>
+      </c>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>140</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38">
+        <v>12</v>
+      </c>
+      <c r="C38">
+        <v>101</v>
+      </c>
+      <c r="D38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>200</v>
+      </c>
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <v>230</v>
+      </c>
+      <c r="D40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>240</v>
+      </c>
+      <c r="D41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42">
+        <v>210</v>
+      </c>
+      <c r="D42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>170</v>
+      </c>
+      <c r="D43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>160</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45">
+        <v>200</v>
+      </c>
+      <c r="D45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>230</v>
+      </c>
+      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47">
+        <v>11</v>
+      </c>
+      <c r="C47">
+        <v>240</v>
+      </c>
+      <c r="D47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48">
+        <v>210</v>
+      </c>
+      <c r="D48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>170</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50">
+        <v>6</v>
+      </c>
+      <c r="C50">
+        <v>160</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>802</v>
+      </c>
+      <c r="D51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>102</v>
+      </c>
+      <c r="D52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>802</v>
+      </c>
+      <c r="D62" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64">
+        <v>250</v>
+      </c>
+      <c r="D64" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
+      </c>
+      <c r="C66">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>260</v>
+      </c>
+      <c r="D70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+      <c r="C71">
+        <v>111</v>
+      </c>
+      <c r="D71" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72">
+        <v>9</v>
+      </c>
+      <c r="C72">
+        <v>150</v>
+      </c>
+      <c r="D72" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>140</v>
+      </c>
+      <c r="D74" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76">
+        <v>11</v>
+      </c>
+      <c r="C76">
+        <v>180</v>
+      </c>
+      <c r="D76" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77">
+        <v>7</v>
+      </c>
+      <c r="C77">
+        <v>170</v>
+      </c>
+      <c r="D77" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78">
+        <v>6</v>
+      </c>
+      <c r="C78">
+        <v>160</v>
+      </c>
+      <c r="D78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
+      <c r="C79">
+        <v>111</v>
+      </c>
+      <c r="D79" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>71</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>140</v>
+      </c>
+      <c r="D80" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>71</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>72</v>
+      </c>
+      <c r="B82">
+        <v>4</v>
+      </c>
+      <c r="C82">
+        <v>170</v>
+      </c>
+      <c r="D82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>100</v>
+      </c>
+      <c r="D83" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84">
+        <v>9</v>
+      </c>
+      <c r="C84">
+        <v>150</v>
+      </c>
+      <c r="D84" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85">
+        <v>8</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86">
+        <v>3</v>
+      </c>
+      <c r="C86">
+        <v>140</v>
+      </c>
+      <c r="D86" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B88">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>180</v>
+      </c>
+      <c r="D88" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>75</v>
+      </c>
+      <c r="B89">
+        <v>5</v>
+      </c>
+      <c r="C89">
+        <v>804</v>
+      </c>
+      <c r="D89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90">
+        <v>9</v>
+      </c>
+      <c r="C90">
+        <v>813</v>
+      </c>
+      <c r="D90" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>75</v>
+      </c>
+      <c r="B91">
+        <v>8</v>
+      </c>
+      <c r="C91">
+        <v>800</v>
+      </c>
+      <c r="D91" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>75</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>801</v>
+      </c>
+      <c r="D92" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>800</v>
+      </c>
+      <c r="D93" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>77</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
+      </c>
+      <c r="C94">
+        <v>804</v>
+      </c>
+      <c r="D94" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>77</v>
+      </c>
+      <c r="B95">
+        <v>9</v>
+      </c>
+      <c r="C95">
+        <v>814</v>
+      </c>
+      <c r="D95" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>77</v>
+      </c>
+      <c r="B96">
+        <v>8</v>
+      </c>
+      <c r="C96">
+        <v>800</v>
+      </c>
+      <c r="D96" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>77</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>801</v>
+      </c>
+      <c r="D97" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>77</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>800</v>
+      </c>
+      <c r="D98" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>78</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+      <c r="C99">
+        <v>804</v>
+      </c>
+      <c r="D99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>78</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>801</v>
+      </c>
+      <c r="D100" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>78</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>800</v>
+      </c>
+      <c r="D101" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+      <c r="C102">
+        <v>818</v>
+      </c>
+      <c r="D102" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>79</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103">
+        <v>800</v>
+      </c>
+      <c r="D103" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>79</v>
+      </c>
+      <c r="B104">
+        <v>6</v>
+      </c>
+      <c r="C104">
+        <v>825</v>
+      </c>
+      <c r="D104" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>80</v>
+      </c>
+      <c r="B105">
+        <v>9</v>
+      </c>
+      <c r="C105">
+        <v>817</v>
+      </c>
+      <c r="D105" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>80</v>
+      </c>
+      <c r="B106">
+        <v>8</v>
+      </c>
+      <c r="C106">
+        <v>816</v>
+      </c>
+      <c r="D106" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>81</v>
+      </c>
+      <c r="B107">
+        <v>8</v>
+      </c>
+      <c r="C107">
+        <v>817</v>
+      </c>
+      <c r="D107" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>82</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108">
+        <v>802</v>
+      </c>
+      <c r="D108" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>82</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="C109">
+        <v>801</v>
+      </c>
+      <c r="D109" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>82</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>800</v>
+      </c>
+      <c r="D110" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>83</v>
+      </c>
+      <c r="B111">
+        <v>5</v>
+      </c>
+      <c r="C111">
+        <v>804</v>
+      </c>
+      <c r="D111" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>801</v>
+      </c>
+      <c r="D112" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>83</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>800</v>
+      </c>
+      <c r="D113" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>84</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114">
+        <v>804</v>
+      </c>
+      <c r="D114" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>84</v>
+      </c>
+      <c r="B115">
+        <v>4</v>
+      </c>
+      <c r="C115">
+        <v>802</v>
+      </c>
+      <c r="D115" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>84</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>801</v>
+      </c>
+      <c r="D116" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>84</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>800</v>
+      </c>
+      <c r="D117" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3067,1641 +4148,6 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>120</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>130</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>140</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10">
-        <v>111</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>140</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>141</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>140</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18">
-        <v>111</v>
-      </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="C19">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>140</v>
-      </c>
-      <c r="D20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>120</v>
-      </c>
-      <c r="D23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24">
-        <v>140</v>
-      </c>
-      <c r="D24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>140</v>
-      </c>
-      <c r="D27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29">
-        <v>5</v>
-      </c>
-      <c r="C29">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>190</v>
-      </c>
-      <c r="D31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32">
-        <v>3</v>
-      </c>
-      <c r="C32">
-        <v>140</v>
-      </c>
-      <c r="D32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34">
-        <v>5</v>
-      </c>
-      <c r="C34">
-        <v>111</v>
-      </c>
-      <c r="D34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35">
-        <v>5</v>
-      </c>
-      <c r="C35">
-        <v>111</v>
-      </c>
-      <c r="D35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>140</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38">
-        <v>12</v>
-      </c>
-      <c r="C38">
-        <v>101</v>
-      </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39">
-        <v>4</v>
-      </c>
-      <c r="C39">
-        <v>200</v>
-      </c>
-      <c r="D39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40">
-        <v>9</v>
-      </c>
-      <c r="C40">
-        <v>230</v>
-      </c>
-      <c r="D40" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41">
-        <v>8</v>
-      </c>
-      <c r="C41">
-        <v>240</v>
-      </c>
-      <c r="D41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42">
-        <v>11</v>
-      </c>
-      <c r="C42">
-        <v>210</v>
-      </c>
-      <c r="D42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43">
-        <v>7</v>
-      </c>
-      <c r="C43">
-        <v>170</v>
-      </c>
-      <c r="D43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44">
-        <v>6</v>
-      </c>
-      <c r="C44">
-        <v>160</v>
-      </c>
-      <c r="D44" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>62</v>
-      </c>
-      <c r="B45">
-        <v>4</v>
-      </c>
-      <c r="C45">
-        <v>200</v>
-      </c>
-      <c r="D45" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46">
-        <v>9</v>
-      </c>
-      <c r="C46">
-        <v>230</v>
-      </c>
-      <c r="D46" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47">
-        <v>11</v>
-      </c>
-      <c r="C47">
-        <v>240</v>
-      </c>
-      <c r="D47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48">
-        <v>8</v>
-      </c>
-      <c r="C48">
-        <v>210</v>
-      </c>
-      <c r="D48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>62</v>
-      </c>
-      <c r="B49">
-        <v>7</v>
-      </c>
-      <c r="C49">
-        <v>170</v>
-      </c>
-      <c r="D49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50">
-        <v>6</v>
-      </c>
-      <c r="C50">
-        <v>160</v>
-      </c>
-      <c r="D50" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51">
-        <v>12</v>
-      </c>
-      <c r="C51">
-        <v>802</v>
-      </c>
-      <c r="D51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52">
-        <v>4</v>
-      </c>
-      <c r="C52">
-        <v>102</v>
-      </c>
-      <c r="D52" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53">
-        <v>6</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54">
-        <v>7</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57">
-        <v>4</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>67</v>
-      </c>
-      <c r="B58">
-        <v>3</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62">
-        <v>4</v>
-      </c>
-      <c r="C62">
-        <v>802</v>
-      </c>
-      <c r="D62" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63">
-        <v>4</v>
-      </c>
-      <c r="C63">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64">
-        <v>250</v>
-      </c>
-      <c r="D64" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>69</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
-      </c>
-      <c r="C66">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>69</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>12</v>
-      </c>
-      <c r="C70">
-        <v>260</v>
-      </c>
-      <c r="D70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71">
-        <v>5</v>
-      </c>
-      <c r="C71">
-        <v>111</v>
-      </c>
-      <c r="D71" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
-        <v>10</v>
-      </c>
-      <c r="B72">
-        <v>9</v>
-      </c>
-      <c r="C72">
-        <v>150</v>
-      </c>
-      <c r="D72" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
-        <v>10</v>
-      </c>
-      <c r="B73">
-        <v>8</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-      <c r="D73" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74">
-        <v>3</v>
-      </c>
-      <c r="C74">
-        <v>140</v>
-      </c>
-      <c r="D74" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>70</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76">
-        <v>11</v>
-      </c>
-      <c r="C76">
-        <v>180</v>
-      </c>
-      <c r="D76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77">
-        <v>7</v>
-      </c>
-      <c r="C77">
-        <v>170</v>
-      </c>
-      <c r="D77" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78">
-        <v>6</v>
-      </c>
-      <c r="C78">
-        <v>160</v>
-      </c>
-      <c r="D78" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>71</v>
-      </c>
-      <c r="B79">
-        <v>5</v>
-      </c>
-      <c r="C79">
-        <v>111</v>
-      </c>
-      <c r="D79" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>71</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80">
-        <v>140</v>
-      </c>
-      <c r="D80" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>71</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-      <c r="D81" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>72</v>
-      </c>
-      <c r="B82">
-        <v>4</v>
-      </c>
-      <c r="C82">
-        <v>170</v>
-      </c>
-      <c r="D82" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>73</v>
-      </c>
-      <c r="B83">
-        <v>12</v>
-      </c>
-      <c r="C83">
-        <v>100</v>
-      </c>
-      <c r="D83" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>73</v>
-      </c>
-      <c r="B84">
-        <v>9</v>
-      </c>
-      <c r="C84">
-        <v>150</v>
-      </c>
-      <c r="D84" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>73</v>
-      </c>
-      <c r="B85">
-        <v>8</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>74</v>
-      </c>
-      <c r="B86">
-        <v>3</v>
-      </c>
-      <c r="C86">
-        <v>140</v>
-      </c>
-      <c r="D86" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>74</v>
-      </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>73</v>
-      </c>
-      <c r="B88">
-        <v>11</v>
-      </c>
-      <c r="C88">
-        <v>180</v>
-      </c>
-      <c r="D88" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>75</v>
-      </c>
-      <c r="B89">
-        <v>5</v>
-      </c>
-      <c r="C89">
-        <v>804</v>
-      </c>
-      <c r="D89" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>75</v>
-      </c>
-      <c r="B90">
-        <v>9</v>
-      </c>
-      <c r="C90">
-        <v>813</v>
-      </c>
-      <c r="D90" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>75</v>
-      </c>
-      <c r="B91">
-        <v>8</v>
-      </c>
-      <c r="C91">
-        <v>800</v>
-      </c>
-      <c r="D91" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>75</v>
-      </c>
-      <c r="B92">
-        <v>1</v>
-      </c>
-      <c r="C92">
-        <v>801</v>
-      </c>
-      <c r="D92" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>75</v>
-      </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="C93">
-        <v>800</v>
-      </c>
-      <c r="D93" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>77</v>
-      </c>
-      <c r="B94">
-        <v>5</v>
-      </c>
-      <c r="C94">
-        <v>804</v>
-      </c>
-      <c r="D94" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>77</v>
-      </c>
-      <c r="B95">
-        <v>9</v>
-      </c>
-      <c r="C95">
-        <v>814</v>
-      </c>
-      <c r="D95" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96">
-        <v>8</v>
-      </c>
-      <c r="C96">
-        <v>800</v>
-      </c>
-      <c r="D96" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>77</v>
-      </c>
-      <c r="B97">
-        <v>1</v>
-      </c>
-      <c r="C97">
-        <v>801</v>
-      </c>
-      <c r="D97" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
-        <v>77</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="C98">
-        <v>800</v>
-      </c>
-      <c r="D98" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>78</v>
-      </c>
-      <c r="B99">
-        <v>5</v>
-      </c>
-      <c r="C99">
-        <v>804</v>
-      </c>
-      <c r="D99" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
-        <v>78</v>
-      </c>
-      <c r="B100">
-        <v>1</v>
-      </c>
-      <c r="C100">
-        <v>801</v>
-      </c>
-      <c r="D100" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
-        <v>78</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-      <c r="C101">
-        <v>800</v>
-      </c>
-      <c r="D101" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" t="s">
-        <v>79</v>
-      </c>
-      <c r="B102">
-        <v>5</v>
-      </c>
-      <c r="C102">
-        <v>818</v>
-      </c>
-      <c r="D102" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" t="s">
-        <v>79</v>
-      </c>
-      <c r="B103">
-        <v>4</v>
-      </c>
-      <c r="C103">
-        <v>800</v>
-      </c>
-      <c r="D103" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" t="s">
-        <v>79</v>
-      </c>
-      <c r="B104">
-        <v>6</v>
-      </c>
-      <c r="C104">
-        <v>825</v>
-      </c>
-      <c r="D104" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" t="s">
-        <v>80</v>
-      </c>
-      <c r="B105">
-        <v>9</v>
-      </c>
-      <c r="C105">
-        <v>817</v>
-      </c>
-      <c r="D105" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" t="s">
-        <v>80</v>
-      </c>
-      <c r="B106">
-        <v>8</v>
-      </c>
-      <c r="C106">
-        <v>816</v>
-      </c>
-      <c r="D106" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" t="s">
-        <v>81</v>
-      </c>
-      <c r="B107">
-        <v>8</v>
-      </c>
-      <c r="C107">
-        <v>817</v>
-      </c>
-      <c r="D107" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" t="s">
-        <v>82</v>
-      </c>
-      <c r="B108">
-        <v>4</v>
-      </c>
-      <c r="C108">
-        <v>802</v>
-      </c>
-      <c r="D108" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" t="s">
-        <v>82</v>
-      </c>
-      <c r="B109">
-        <v>3</v>
-      </c>
-      <c r="C109">
-        <v>801</v>
-      </c>
-      <c r="D109" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" t="s">
-        <v>82</v>
-      </c>
-      <c r="B110">
-        <v>2</v>
-      </c>
-      <c r="C110">
-        <v>800</v>
-      </c>
-      <c r="D110" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" t="s">
-        <v>83</v>
-      </c>
-      <c r="B111">
-        <v>5</v>
-      </c>
-      <c r="C111">
-        <v>804</v>
-      </c>
-      <c r="D111" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" t="s">
-        <v>83</v>
-      </c>
-      <c r="B112">
-        <v>1</v>
-      </c>
-      <c r="C112">
-        <v>801</v>
-      </c>
-      <c r="D112" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" t="s">
-        <v>83</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-      <c r="C113">
-        <v>800</v>
-      </c>
-      <c r="D113" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" t="s">
-        <v>84</v>
-      </c>
-      <c r="B114">
-        <v>5</v>
-      </c>
-      <c r="C114">
-        <v>804</v>
-      </c>
-      <c r="D114" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" t="s">
-        <v>84</v>
-      </c>
-      <c r="B115">
-        <v>4</v>
-      </c>
-      <c r="C115">
-        <v>802</v>
-      </c>
-      <c r="D115" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" t="s">
-        <v>84</v>
-      </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116">
-        <v>801</v>
-      </c>
-      <c r="D116" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" t="s">
-        <v>84</v>
-      </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-      <c r="C117">
-        <v>800</v>
-      </c>
-      <c r="D117" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="14.5454545454545" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4727,7 +4173,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -4735,7 +4181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -4743,7 +4189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -4751,7 +4197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -4792,7 +4238,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -4801,22 +4247,21 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G374"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:G375"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="34.1818181818182" customWidth="1"/>
+    <col min="2" max="2" width="52.90625" customWidth="1"/>
+    <col min="3" max="3" width="34.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4827,7 +4272,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4838,7 +4283,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:7">
+    <row r="3" spans="1:7" ht="14">
       <c r="A3">
         <v>51</v>
       </c>
@@ -4850,7 +4295,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>100</v>
       </c>
@@ -4861,7 +4306,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>101</v>
       </c>
@@ -4872,7 +4317,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>102</v>
       </c>
@@ -4883,7 +4328,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>110</v>
       </c>
@@ -4894,7 +4339,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>111</v>
       </c>
@@ -4905,7 +4350,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>120</v>
       </c>
@@ -4916,7 +4361,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>130</v>
       </c>
@@ -4927,7 +4372,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>140</v>
       </c>
@@ -4938,7 +4383,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>141</v>
       </c>
@@ -4949,7 +4394,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>150</v>
       </c>
@@ -4960,7 +4405,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>160</v>
       </c>
@@ -4971,7 +4416,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>170</v>
       </c>
@@ -4982,7 +4427,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>180</v>
       </c>
@@ -4993,7 +4438,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>190</v>
       </c>
@@ -5004,7 +4449,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>200</v>
       </c>
@@ -5015,7 +4460,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>210</v>
       </c>
@@ -5026,7 +4471,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>220</v>
       </c>
@@ -5037,7 +4482,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>230</v>
       </c>
@@ -5048,7 +4493,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>240</v>
       </c>
@@ -5059,7 +4504,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>250</v>
       </c>
@@ -5070,7 +4515,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>260</v>
       </c>
@@ -5081,7 +4526,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>270</v>
       </c>
@@ -5092,7 +4537,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>312</v>
       </c>
@@ -5103,7 +4548,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>313</v>
       </c>
@@ -5114,7 +4559,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>314</v>
       </c>
@@ -5125,7 +4570,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>315</v>
       </c>
@@ -5136,7 +4581,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>341</v>
       </c>
@@ -5147,7 +4592,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>342</v>
       </c>
@@ -5242,7 +4687,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>401</v>
       </c>
@@ -5253,7 +4698,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>402</v>
       </c>
@@ -5264,7 +4709,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>403</v>
       </c>
@@ -5275,7 +4720,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>404</v>
       </c>
@@ -5286,7 +4731,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>405</v>
       </c>
@@ -5297,7 +4742,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>420</v>
       </c>
@@ -5308,7 +4753,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>421</v>
       </c>
@@ -5319,7 +4764,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>422</v>
       </c>
@@ -5330,7 +4775,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>600</v>
       </c>
@@ -5341,7 +4786,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>601</v>
       </c>
@@ -5352,7 +4797,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>602</v>
       </c>
@@ -5715,7 +5160,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>820</v>
       </c>
@@ -5726,7 +5171,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>821</v>
       </c>
@@ -5737,7 +5182,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>822</v>
       </c>
@@ -5748,7 +5193,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>823</v>
       </c>
@@ -5759,7 +5204,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>824</v>
       </c>
@@ -5770,7 +5215,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>825</v>
       </c>
@@ -5781,7 +5226,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>826</v>
       </c>
@@ -5792,7 +5237,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>827</v>
       </c>
@@ -5803,7 +5248,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>1000</v>
       </c>
@@ -5814,7 +5259,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>1001</v>
       </c>
@@ -5825,7 +5270,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>1010</v>
       </c>
@@ -5836,7 +5281,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>1020</v>
       </c>
@@ -5847,7 +5292,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="93" customFormat="1" spans="1:3">
+    <row r="93" spans="1:4">
       <c r="A93">
         <v>1060</v>
       </c>
@@ -5858,7 +5303,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="94" customFormat="1" spans="1:3">
+    <row r="94" spans="1:4">
       <c r="A94">
         <v>1110</v>
       </c>
@@ -5869,7 +5314,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="95" customFormat="1" spans="1:3">
+    <row r="95" spans="1:4">
       <c r="A95">
         <v>1120</v>
       </c>
@@ -5894,7 +5339,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:4">
       <c r="A97">
         <v>2001</v>
       </c>
@@ -5905,7 +5350,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:4">
       <c r="A98">
         <v>2002</v>
       </c>
@@ -5916,7 +5361,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:4">
       <c r="A99">
         <v>2003</v>
       </c>
@@ -5927,7 +5372,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:4">
       <c r="A100">
         <v>2004</v>
       </c>
@@ -5938,7 +5383,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:4">
       <c r="A101">
         <v>2005</v>
       </c>
@@ -5949,7 +5394,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:4">
       <c r="A102">
         <v>2006</v>
       </c>
@@ -5960,7 +5405,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:4">
       <c r="A103">
         <v>2007</v>
       </c>
@@ -6027,7 +5472,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="108" customFormat="1" spans="1:4">
+    <row r="108" spans="1:4">
       <c r="A108">
         <v>2100</v>
       </c>
@@ -6041,7 +5486,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:4">
       <c r="A109">
         <v>2101</v>
       </c>
@@ -6052,7 +5497,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:4">
       <c r="A110">
         <v>2102</v>
       </c>
@@ -6063,7 +5508,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:4">
       <c r="A111">
         <v>2103</v>
       </c>
@@ -6074,7 +5519,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:4">
       <c r="A112">
         <v>2104</v>
       </c>
@@ -6113,7 +5558,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="115" ht="29" customHeight="1" spans="1:4">
+    <row r="115" spans="1:4" ht="29" customHeight="1">
       <c r="A115">
         <v>2220</v>
       </c>
@@ -6211,7 +5656,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:4">
       <c r="A122">
         <v>3000</v>
       </c>
@@ -6222,7 +5667,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:4">
       <c r="A123">
         <v>3010</v>
       </c>
@@ -6233,7 +5678,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:4">
       <c r="A124">
         <v>3011</v>
       </c>
@@ -6244,7 +5689,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:4">
       <c r="A125">
         <v>3040</v>
       </c>
@@ -6255,7 +5700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:4">
       <c r="A126">
         <v>3050</v>
       </c>
@@ -6266,7 +5711,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:4">
       <c r="A127">
         <v>3051</v>
       </c>
@@ -6277,7 +5722,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:4">
       <c r="A128">
         <v>3052</v>
       </c>
@@ -6640,7 +6085,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:4">
       <c r="A161">
         <v>6840</v>
       </c>
@@ -6651,7 +6096,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:4">
       <c r="A162">
         <v>6850</v>
       </c>
@@ -6662,7 +6107,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:4">
       <c r="A163">
         <v>6860</v>
       </c>
@@ -6673,7 +6118,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:4">
       <c r="A164">
         <v>6870</v>
       </c>
@@ -6684,7 +6129,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:4">
       <c r="A165">
         <v>6880</v>
       </c>
@@ -6695,7 +6140,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:4">
       <c r="A166">
         <v>6890</v>
       </c>
@@ -6706,7 +6151,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="167" ht="130" spans="1:4">
+    <row r="167" spans="1:4" ht="130">
       <c r="A167">
         <v>12010</v>
       </c>
@@ -6724,17 +6169,17 @@
       <c r="A168">
         <v>13010</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C168" t="s">
+        <v>103</v>
+      </c>
+      <c r="D168" t="s">
         <v>270</v>
       </c>
-      <c r="C168" t="s">
-        <v>103</v>
-      </c>
-      <c r="D168" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
+    </row>
+    <row r="169" spans="1:4">
       <c r="A169">
         <v>13020</v>
       </c>
@@ -6742,373 +6187,373 @@
         <v>103</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:4">
       <c r="A170">
         <v>13110</v>
       </c>
       <c r="B170" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C170" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:4">
       <c r="A171">
         <v>13120</v>
       </c>
       <c r="B171" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C171" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:4">
       <c r="A172">
         <v>13130</v>
       </c>
       <c r="B172" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C172" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:4">
       <c r="A173">
         <v>13140</v>
       </c>
       <c r="B173" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C173" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:4">
       <c r="A174">
         <v>13210</v>
       </c>
-      <c r="B174" t="s">
-        <v>276</v>
+      <c r="B174" s="4" t="s">
+        <v>470</v>
       </c>
       <c r="C174" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:4">
       <c r="A175">
         <v>13220</v>
       </c>
-      <c r="B175" t="s">
-        <v>277</v>
+      <c r="B175" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="C175" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:4">
       <c r="A176">
         <v>13230</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C176" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177">
+        <v>13240</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C177" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178">
+        <v>13300</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C178" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179">
+        <v>13301</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180">
+        <v>13310</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C180" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181">
+        <v>13320</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C176" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177">
-        <v>13300</v>
-      </c>
-      <c r="B177" s="2" t="s">
+      <c r="C181" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="26">
+      <c r="A182">
+        <v>13330</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C177" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178">
-        <v>13301</v>
-      </c>
-      <c r="B178" s="2" t="s">
+      <c r="C182" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183">
+        <v>13400</v>
+      </c>
+      <c r="B183" t="s">
         <v>280</v>
       </c>
-      <c r="C178" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179">
-        <v>13310</v>
-      </c>
-      <c r="B179" s="2" t="s">
+      <c r="C183" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184">
+        <v>13410</v>
+      </c>
+      <c r="B184" t="s">
+        <v>38</v>
+      </c>
+      <c r="C184" t="s">
         <v>281</v>
       </c>
-      <c r="C179" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180">
-        <v>13320</v>
-      </c>
-      <c r="B180" s="2" t="s">
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185">
+        <v>13420</v>
+      </c>
+      <c r="B185" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C180" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="181" ht="26" spans="1:3">
-      <c r="A181">
-        <v>13330</v>
-      </c>
-      <c r="B181" s="2" t="s">
+      <c r="C185" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186">
+        <v>13421</v>
+      </c>
+      <c r="B186" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C181" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182">
-        <v>13400</v>
-      </c>
-      <c r="B182" t="s">
+      <c r="C186" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187">
+        <v>13430</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C182" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183">
-        <v>13410</v>
-      </c>
-      <c r="B183" t="s">
-        <v>38</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="C187" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188">
+        <v>14090</v>
+      </c>
+      <c r="B188" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184">
-        <v>13420</v>
-      </c>
-      <c r="B184" s="2" t="s">
+      <c r="C188" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189">
+        <v>14110</v>
+      </c>
+      <c r="B189" t="s">
         <v>286</v>
       </c>
-      <c r="C184" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185">
-        <v>13421</v>
-      </c>
-      <c r="B185" s="2" t="s">
+      <c r="C189" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="14">
+      <c r="A190">
+        <v>15010</v>
+      </c>
+      <c r="B190" t="s">
         <v>287</v>
       </c>
-      <c r="C185" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186">
-        <v>13430</v>
-      </c>
-      <c r="B186" s="2" t="s">
+      <c r="C190" t="s">
+        <v>103</v>
+      </c>
+      <c r="D190" t="s">
         <v>288</v>
       </c>
-      <c r="C186" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187">
-        <v>14090</v>
-      </c>
-      <c r="B187" t="s">
+      <c r="G190" s="1"/>
+    </row>
+    <row r="191" spans="1:7" ht="14">
+      <c r="A191">
+        <v>16010</v>
+      </c>
+      <c r="B191" t="s">
         <v>289</v>
       </c>
-      <c r="C187" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188">
-        <v>14110</v>
-      </c>
-      <c r="B188" t="s">
+      <c r="C191" t="s">
+        <v>103</v>
+      </c>
+      <c r="D191" t="s">
         <v>290</v>
       </c>
-      <c r="C188" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="189" ht="15" spans="1:7">
-      <c r="A189">
-        <v>15010</v>
-      </c>
-      <c r="B189" t="s">
+      <c r="G191" s="1"/>
+    </row>
+    <row r="192" spans="1:7" ht="14">
+      <c r="A192">
+        <v>16020</v>
+      </c>
+      <c r="B192" t="s">
         <v>291</v>
       </c>
-      <c r="C189" t="s">
-        <v>103</v>
-      </c>
-      <c r="D189" t="s">
+      <c r="C192" t="s">
+        <v>103</v>
+      </c>
+      <c r="G192" s="1"/>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193">
+        <v>16100</v>
+      </c>
+      <c r="B193" t="s">
         <v>292</v>
       </c>
-      <c r="G189" s="1"/>
-    </row>
-    <row r="190" ht="15" spans="1:7">
-      <c r="A190">
-        <v>16010</v>
-      </c>
-      <c r="B190" t="s">
+      <c r="C193" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194">
+        <v>16110</v>
+      </c>
+      <c r="B194" t="s">
         <v>293</v>
       </c>
-      <c r="C190" t="s">
-        <v>103</v>
-      </c>
-      <c r="D190" t="s">
+      <c r="C194" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195">
+        <v>16200</v>
+      </c>
+      <c r="B195" t="s">
         <v>294</v>
       </c>
-      <c r="G190" s="1"/>
-    </row>
-    <row r="191" ht="15" spans="1:7">
-      <c r="A191">
-        <v>16020</v>
-      </c>
-      <c r="B191" t="s">
+      <c r="C195" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196">
+        <v>16210</v>
+      </c>
+      <c r="B196" t="s">
         <v>295</v>
       </c>
-      <c r="C191" t="s">
-        <v>103</v>
-      </c>
-      <c r="G191" s="1"/>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192">
-        <v>16100</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="C196" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197">
+        <v>16220</v>
+      </c>
+      <c r="B197" t="s">
         <v>296</v>
       </c>
-      <c r="C192" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193">
-        <v>16110</v>
-      </c>
-      <c r="B193" t="s">
+      <c r="C197" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198">
+        <v>16230</v>
+      </c>
+      <c r="B198" t="s">
         <v>297</v>
       </c>
-      <c r="C193" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194">
-        <v>16200</v>
-      </c>
-      <c r="B194" t="s">
+      <c r="C198" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199">
+        <v>16300</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C194" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195">
-        <v>16210</v>
-      </c>
-      <c r="B195" t="s">
+      <c r="C199" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200">
+        <v>16310</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C195" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196">
-        <v>16220</v>
-      </c>
-      <c r="B196" t="s">
+      <c r="C200" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201">
+        <v>16320</v>
+      </c>
+      <c r="B201" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C196" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197">
-        <v>16230</v>
-      </c>
-      <c r="B197" t="s">
+      <c r="C201" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202">
+        <v>16400</v>
+      </c>
+      <c r="B202" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="C197" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198">
-        <v>16300</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C198" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199">
-        <v>16310</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C199" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200">
-        <v>16320</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C200" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201">
-        <v>16400</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C201" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202">
-        <v>16410</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="C202" t="s">
         <v>103</v>
@@ -7116,265 +6561,265 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203">
-        <v>16800</v>
-      </c>
-      <c r="B203" t="s">
-        <v>189</v>
+        <v>16410</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="C203" t="s">
         <v>103</v>
-      </c>
-      <c r="D203" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204">
-        <v>16801</v>
+        <v>16800</v>
       </c>
       <c r="B204" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C204" t="s">
         <v>103</v>
       </c>
       <c r="D204" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B205" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C205" t="s">
         <v>103</v>
       </c>
       <c r="D205" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B206" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C206" t="s">
         <v>103</v>
       </c>
       <c r="D206" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B207" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C207" t="s">
         <v>103</v>
       </c>
       <c r="D207" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B208" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C208" t="s">
         <v>103</v>
       </c>
       <c r="D208" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209">
+        <v>16805</v>
+      </c>
+      <c r="B209" t="s">
+        <v>194</v>
+      </c>
+      <c r="C209" t="s">
+        <v>103</v>
+      </c>
+      <c r="D209" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210">
         <v>16806</v>
       </c>
-      <c r="B209" t="s">
+      <c r="B210" t="s">
         <v>195</v>
       </c>
-      <c r="C209" t="s">
-        <v>103</v>
-      </c>
-      <c r="D209" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210">
-        <v>17010</v>
-      </c>
-      <c r="B210" t="s">
-        <v>308</v>
-      </c>
       <c r="C210" t="s">
         <v>103</v>
+      </c>
+      <c r="D210" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211">
+        <v>17010</v>
+      </c>
+      <c r="B211" t="s">
+        <v>304</v>
+      </c>
+      <c r="C211" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212">
         <v>18010</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B212" t="s">
+        <v>305</v>
+      </c>
+      <c r="C212" t="s">
+        <v>103</v>
+      </c>
+      <c r="D212" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213">
+        <v>18020</v>
+      </c>
+      <c r="B213" t="s">
+        <v>307</v>
+      </c>
+      <c r="C213" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214">
+        <v>18100</v>
+      </c>
+      <c r="B214" t="s">
+        <v>200</v>
+      </c>
+      <c r="C214" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215">
+        <v>18110</v>
+      </c>
+      <c r="B215" t="s">
+        <v>308</v>
+      </c>
+      <c r="C215" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216">
+        <v>18120</v>
+      </c>
+      <c r="B216" t="s">
         <v>309</v>
       </c>
-      <c r="C211" t="s">
-        <v>103</v>
-      </c>
-      <c r="D211" t="s">
+      <c r="C216" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217">
+        <v>18130</v>
+      </c>
+      <c r="B217" t="s">
+        <v>231</v>
+      </c>
+      <c r="C217" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218">
+        <v>18200</v>
+      </c>
+      <c r="B218" t="s">
+        <v>111</v>
+      </c>
+      <c r="C218" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219">
+        <v>18210</v>
+      </c>
+      <c r="B219" t="s">
+        <v>112</v>
+      </c>
+      <c r="C219" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220">
+        <v>18220</v>
+      </c>
+      <c r="B220" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212">
-        <v>18020</v>
-      </c>
-      <c r="B212" t="s">
+      <c r="C220" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221">
+        <v>18300</v>
+      </c>
+      <c r="B221" t="s">
         <v>311</v>
       </c>
-      <c r="C212" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3">
-      <c r="A213">
-        <v>18100</v>
-      </c>
-      <c r="B213" t="s">
-        <v>200</v>
-      </c>
-      <c r="C213" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214">
-        <v>18110</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="C221" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222">
+        <v>18310</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C214" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3">
-      <c r="A215">
-        <v>18120</v>
-      </c>
-      <c r="B215" t="s">
+      <c r="C222" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223">
+        <v>18320</v>
+      </c>
+      <c r="B223" t="s">
         <v>313</v>
       </c>
-      <c r="C215" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3">
-      <c r="A216">
-        <v>18130</v>
-      </c>
-      <c r="B216" t="s">
-        <v>231</v>
-      </c>
-      <c r="C216" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3">
-      <c r="A217">
-        <v>18200</v>
-      </c>
-      <c r="B217" t="s">
-        <v>111</v>
-      </c>
-      <c r="C217" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3">
-      <c r="A218">
-        <v>18210</v>
-      </c>
-      <c r="B218" t="s">
-        <v>112</v>
-      </c>
-      <c r="C218" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
-      <c r="A219">
-        <v>18220</v>
-      </c>
-      <c r="B219" t="s">
+      <c r="C223" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224">
+        <v>18340</v>
+      </c>
+      <c r="B224" t="s">
         <v>314</v>
-      </c>
-      <c r="C219" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3">
-      <c r="A220">
-        <v>18300</v>
-      </c>
-      <c r="B220" t="s">
-        <v>315</v>
-      </c>
-      <c r="C220" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3">
-      <c r="A221">
-        <v>18310</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C221" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3">
-      <c r="A222">
-        <v>18320</v>
-      </c>
-      <c r="B222" t="s">
-        <v>317</v>
-      </c>
-      <c r="C222" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
-      <c r="A223">
-        <v>18340</v>
-      </c>
-      <c r="B223" t="s">
-        <v>318</v>
-      </c>
-      <c r="C223" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
-      <c r="A224">
-        <v>18400</v>
-      </c>
-      <c r="B224" t="s">
-        <v>319</v>
       </c>
       <c r="C224" t="s">
         <v>103</v>
@@ -7382,10 +6827,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B225" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C225" t="s">
         <v>103</v>
@@ -7393,10 +6838,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B226" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C226" t="s">
         <v>103</v>
@@ -7404,10 +6849,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B227" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C227" t="s">
         <v>103</v>
@@ -7415,10 +6860,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B228" t="s">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="C228" t="s">
         <v>103</v>
@@ -7426,10 +6871,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B229" t="s">
-        <v>323</v>
+        <v>104</v>
       </c>
       <c r="C229" t="s">
         <v>103</v>
@@ -7437,10 +6882,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B230" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C230" t="s">
         <v>103</v>
@@ -7448,10 +6893,10 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18510</v>
+        <v>18500</v>
       </c>
       <c r="B231" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C231" t="s">
         <v>103</v>
@@ -7459,10 +6904,10 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18800</v>
+        <v>18510</v>
       </c>
       <c r="B232" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C232" t="s">
         <v>103</v>
@@ -7470,10 +6915,10 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B233" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C233" t="s">
         <v>103</v>
@@ -7481,10 +6926,10 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B234" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C234" t="s">
         <v>103</v>
@@ -7492,10 +6937,10 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B235" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C235" t="s">
         <v>103</v>
@@ -7503,10 +6948,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B236" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C236" t="s">
         <v>103</v>
@@ -7514,10 +6959,10 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B237" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C237" t="s">
         <v>103</v>
@@ -7525,10 +6970,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B238" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C238" t="s">
         <v>103</v>
@@ -7536,10 +6981,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B239" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C239" t="s">
         <v>103</v>
@@ -7547,191 +6992,191 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
+        <v>18811</v>
+      </c>
+      <c r="B240" t="s">
+        <v>329</v>
+      </c>
+      <c r="C240" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241">
         <v>18812</v>
       </c>
-      <c r="B240" t="s">
+      <c r="B241" t="s">
+        <v>330</v>
+      </c>
+      <c r="C241" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="14">
+      <c r="A242">
+        <v>19010</v>
+      </c>
+      <c r="B242" t="s">
+        <v>331</v>
+      </c>
+      <c r="C242" t="s">
+        <v>332</v>
+      </c>
+      <c r="D242" t="s">
+        <v>333</v>
+      </c>
+      <c r="G242" s="1"/>
+    </row>
+    <row r="243" spans="1:7" ht="14">
+      <c r="A243">
+        <v>19011</v>
+      </c>
+      <c r="B243" t="s">
         <v>334</v>
       </c>
-      <c r="C240" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="241" ht="15" spans="1:7">
-      <c r="A241">
-        <v>19010</v>
-      </c>
-      <c r="B241" t="s">
+      <c r="C243" t="s">
+        <v>332</v>
+      </c>
+      <c r="G243" s="1"/>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244">
+        <v>19020</v>
+      </c>
+      <c r="B244" t="s">
+        <v>111</v>
+      </c>
+      <c r="C244" t="s">
         <v>335</v>
       </c>
-      <c r="C241" t="s">
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245">
+        <v>19030</v>
+      </c>
+      <c r="B245" t="s">
+        <v>112</v>
+      </c>
+      <c r="C245" t="s">
         <v>336</v>
       </c>
-      <c r="D241" t="s">
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246">
+        <v>19040</v>
+      </c>
+      <c r="B246" t="s">
         <v>337</v>
       </c>
-      <c r="G241" s="1"/>
-    </row>
-    <row r="242" ht="15" spans="1:7">
-      <c r="A242">
-        <v>19011</v>
-      </c>
-      <c r="B242" t="s">
+      <c r="C246" t="s">
         <v>338</v>
       </c>
-      <c r="C242" t="s">
-        <v>336</v>
-      </c>
-      <c r="G242" s="1"/>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243">
-        <v>19020</v>
-      </c>
-      <c r="B243" t="s">
-        <v>111</v>
-      </c>
-      <c r="C243" t="s">
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247">
+        <v>19050</v>
+      </c>
+      <c r="B247" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>19030</v>
-      </c>
-      <c r="B244" t="s">
-        <v>112</v>
-      </c>
-      <c r="C244" t="s">
+      <c r="C247" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>19040</v>
-      </c>
-      <c r="B245" t="s">
+    <row r="248" spans="1:7">
+      <c r="A248">
+        <v>19060</v>
+      </c>
+      <c r="B248" t="s">
         <v>341</v>
       </c>
-      <c r="C245" t="s">
+      <c r="C248" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="246" spans="1:3">
-      <c r="A246">
-        <v>19050</v>
-      </c>
-      <c r="B246" t="s">
+    <row r="249" spans="1:7">
+      <c r="A249">
+        <v>19070</v>
+      </c>
+      <c r="B249" t="s">
         <v>343</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C249" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
-      <c r="A247">
-        <v>19060</v>
-      </c>
-      <c r="B247" t="s">
+    <row r="250" spans="1:7">
+      <c r="A250">
+        <v>19100</v>
+      </c>
+      <c r="B250" t="s">
         <v>345</v>
       </c>
-      <c r="C247" t="s">
+      <c r="C250" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251">
+        <v>19110</v>
+      </c>
+      <c r="B251" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248">
-        <v>19070</v>
-      </c>
-      <c r="B248" t="s">
+      <c r="C251" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252">
+        <v>19200</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C252" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253">
+        <v>19210</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249">
-        <v>19100</v>
-      </c>
-      <c r="B249" t="s">
+      <c r="C253" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254">
+        <v>19220</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C249" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250">
-        <v>19110</v>
-      </c>
-      <c r="B250" t="s">
+      <c r="C254" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255">
+        <v>19230</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C250" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251">
-        <v>19200</v>
-      </c>
-      <c r="B251" s="2" t="s">
+      <c r="C255" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256">
+        <v>19240</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="C251" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252">
-        <v>19210</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C252" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253">
-        <v>19220</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C253" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254">
-        <v>19230</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C254" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3">
-      <c r="A255">
-        <v>19240</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C255" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256">
-        <v>19250</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="C256" t="s">
         <v>103</v>
@@ -7739,10 +7184,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C257" t="s">
         <v>103</v>
@@ -7750,10 +7195,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C258" t="s">
         <v>103</v>
@@ -7761,10 +7206,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C259" t="s">
         <v>103</v>
@@ -7772,32 +7217,32 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
+        <v>19280</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C260" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261">
         <v>19300</v>
       </c>
-      <c r="B260" t="s">
-        <v>360</v>
-      </c>
-      <c r="C260" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="261" ht="26" spans="1:3">
-      <c r="A261">
+      <c r="B261" t="s">
+        <v>356</v>
+      </c>
+      <c r="C261" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="26">
+      <c r="A262">
         <v>19310</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C261" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3">
-      <c r="A262">
-        <v>19320</v>
-      </c>
       <c r="B262" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C262" t="s">
         <v>103</v>
@@ -7805,10 +7250,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19330</v>
-      </c>
-      <c r="B263" t="s">
-        <v>363</v>
+        <v>19320</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="C263" t="s">
         <v>103</v>
@@ -7816,10 +7261,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B264" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C264" t="s">
         <v>103</v>
@@ -7827,10 +7272,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B265" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C265" t="s">
         <v>103</v>
@@ -7838,10 +7283,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B266" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C266" t="s">
         <v>103</v>
@@ -7849,10 +7294,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19400</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>367</v>
+        <v>19360</v>
+      </c>
+      <c r="B267" t="s">
+        <v>362</v>
       </c>
       <c r="C267" t="s">
         <v>103</v>
@@ -7860,10 +7305,10 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C268" t="s">
         <v>103</v>
@@ -7871,10 +7316,10 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C269" t="s">
         <v>103</v>
@@ -7882,10 +7327,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C270" t="s">
         <v>103</v>
@@ -7893,10 +7338,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19500</v>
-      </c>
-      <c r="B271" t="s">
-        <v>371</v>
+        <v>19420</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="C271" t="s">
         <v>103</v>
@@ -7904,380 +7349,380 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
+        <v>19500</v>
+      </c>
+      <c r="B272" t="s">
+        <v>367</v>
+      </c>
+      <c r="C272" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273">
         <v>19510</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C272" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3">
-      <c r="A273">
+      <c r="B273" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C273" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274">
         <v>19520</v>
       </c>
-      <c r="B273" s="2" t="s">
+      <c r="B274" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C274" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275">
+        <v>19600</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C275" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276">
+        <v>19601</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C276" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277">
+        <v>19602</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C277" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278">
+        <v>19603</v>
+      </c>
+      <c r="B278" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C273" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3">
-      <c r="A274">
-        <v>19600</v>
-      </c>
-      <c r="B274" s="2" t="s">
+      <c r="C278" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279">
+        <v>19604</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C274" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275">
-        <v>19601</v>
-      </c>
-      <c r="B275" s="2" t="s">
+      <c r="C279" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="14">
+      <c r="A280">
+        <v>19611</v>
+      </c>
+      <c r="B280" t="s">
         <v>374</v>
       </c>
-      <c r="C275" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276">
-        <v>19602</v>
-      </c>
-      <c r="B276" s="2" t="s">
+      <c r="C280" t="s">
+        <v>103</v>
+      </c>
+      <c r="D280" t="s">
         <v>375</v>
       </c>
-      <c r="C276" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277">
-        <v>19603</v>
-      </c>
-      <c r="B277" s="2" t="s">
+      <c r="G280" s="1"/>
+    </row>
+    <row r="281" spans="1:7" ht="14">
+      <c r="A281">
+        <v>19612</v>
+      </c>
+      <c r="B281" t="s">
         <v>376</v>
       </c>
-      <c r="C277" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278">
-        <v>19604</v>
-      </c>
-      <c r="B278" s="2" t="s">
+      <c r="C281" t="s">
+        <v>103</v>
+      </c>
+      <c r="G281" s="1"/>
+    </row>
+    <row r="282" spans="1:7" ht="14">
+      <c r="A282">
+        <v>19613</v>
+      </c>
+      <c r="B282" t="s">
         <v>377</v>
       </c>
-      <c r="C278" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="279" ht="15" spans="1:7">
-      <c r="A279">
-        <v>19611</v>
-      </c>
-      <c r="B279" t="s">
+      <c r="C282" t="s">
+        <v>103</v>
+      </c>
+      <c r="G282" s="1"/>
+    </row>
+    <row r="283" spans="1:7" ht="14">
+      <c r="A283">
+        <v>19614</v>
+      </c>
+      <c r="B283" t="s">
         <v>378</v>
       </c>
-      <c r="C279" t="s">
-        <v>103</v>
-      </c>
-      <c r="D279" t="s">
+      <c r="C283" t="s">
+        <v>103</v>
+      </c>
+      <c r="G283" s="1"/>
+    </row>
+    <row r="284" spans="1:7" ht="14">
+      <c r="A284">
+        <v>19615</v>
+      </c>
+      <c r="B284" t="s">
         <v>379</v>
       </c>
-      <c r="G279" s="1"/>
-    </row>
-    <row r="280" ht="15" spans="1:7">
-      <c r="A280">
-        <v>19612</v>
-      </c>
-      <c r="B280" t="s">
+      <c r="C284" t="s">
+        <v>103</v>
+      </c>
+      <c r="G284" s="1"/>
+    </row>
+    <row r="285" spans="1:7" ht="14">
+      <c r="A285">
+        <v>19616</v>
+      </c>
+      <c r="B285" t="s">
         <v>380</v>
       </c>
-      <c r="C280" t="s">
-        <v>103</v>
-      </c>
-      <c r="G280" s="1"/>
-    </row>
-    <row r="281" ht="15" spans="1:7">
-      <c r="A281">
-        <v>19613</v>
-      </c>
-      <c r="B281" t="s">
+      <c r="C285" t="s">
+        <v>103</v>
+      </c>
+      <c r="G285" s="1"/>
+    </row>
+    <row r="286" spans="1:7" ht="14">
+      <c r="A286">
+        <v>19617</v>
+      </c>
+      <c r="B286" t="s">
         <v>381</v>
       </c>
-      <c r="C281" t="s">
-        <v>103</v>
-      </c>
-      <c r="G281" s="1"/>
-    </row>
-    <row r="282" ht="15" spans="1:7">
-      <c r="A282">
-        <v>19614</v>
-      </c>
-      <c r="B282" t="s">
+      <c r="C286" t="s">
+        <v>103</v>
+      </c>
+      <c r="G286" s="1"/>
+    </row>
+    <row r="287" spans="1:7" ht="14">
+      <c r="A287">
+        <v>19618</v>
+      </c>
+      <c r="B287" t="s">
         <v>382</v>
       </c>
-      <c r="C282" t="s">
-        <v>103</v>
-      </c>
-      <c r="G282" s="1"/>
-    </row>
-    <row r="283" ht="15" spans="1:7">
-      <c r="A283">
-        <v>19615</v>
-      </c>
-      <c r="B283" t="s">
+      <c r="C287" t="s">
+        <v>103</v>
+      </c>
+      <c r="G287" s="1"/>
+    </row>
+    <row r="288" spans="1:7" ht="14">
+      <c r="A288">
+        <v>19619</v>
+      </c>
+      <c r="B288" t="s">
         <v>383</v>
       </c>
-      <c r="C283" t="s">
-        <v>103</v>
-      </c>
-      <c r="G283" s="1"/>
-    </row>
-    <row r="284" ht="15" spans="1:7">
-      <c r="A284">
-        <v>19616</v>
-      </c>
-      <c r="B284" t="s">
+      <c r="C288" t="s">
+        <v>103</v>
+      </c>
+      <c r="G288" s="1"/>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289">
+        <v>19631</v>
+      </c>
+      <c r="B289" t="s">
         <v>384</v>
       </c>
-      <c r="C284" t="s">
-        <v>103</v>
-      </c>
-      <c r="G284" s="1"/>
-    </row>
-    <row r="285" ht="15" spans="1:7">
-      <c r="A285">
-        <v>19617</v>
-      </c>
-      <c r="B285" t="s">
+      <c r="C289" t="s">
+        <v>103</v>
+      </c>
+      <c r="D289" t="s">
         <v>385</v>
       </c>
-      <c r="C285" t="s">
-        <v>103</v>
-      </c>
-      <c r="G285" s="1"/>
-    </row>
-    <row r="286" ht="15" spans="1:7">
-      <c r="A286">
-        <v>19618</v>
-      </c>
-      <c r="B286" t="s">
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290">
+        <v>19632</v>
+      </c>
+      <c r="B290" t="s">
         <v>386</v>
       </c>
-      <c r="C286" t="s">
-        <v>103</v>
-      </c>
-      <c r="G286" s="1"/>
-    </row>
-    <row r="287" ht="15" spans="1:7">
-      <c r="A287">
-        <v>19619</v>
-      </c>
-      <c r="B287" t="s">
+      <c r="C290" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291">
+        <v>19633</v>
+      </c>
+      <c r="B291" t="s">
         <v>387</v>
       </c>
-      <c r="C287" t="s">
-        <v>103</v>
-      </c>
-      <c r="G287" s="1"/>
-    </row>
-    <row r="288" spans="1:4">
-      <c r="A288">
-        <v>19631</v>
-      </c>
-      <c r="B288" t="s">
+      <c r="C291" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292">
+        <v>19634</v>
+      </c>
+      <c r="B292" t="s">
         <v>388</v>
       </c>
-      <c r="C288" t="s">
-        <v>103</v>
-      </c>
-      <c r="D288" t="s">
+      <c r="C292" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293">
+        <v>19700</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289">
-        <v>19632</v>
-      </c>
-      <c r="B289" t="s">
+      <c r="C293" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294">
+        <v>19710</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C294" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295">
+        <v>19720</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C289" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
-      <c r="A290">
-        <v>19633</v>
-      </c>
-      <c r="B290" t="s">
+      <c r="C295" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296">
+        <v>19730</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C290" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291">
-        <v>19634</v>
-      </c>
-      <c r="B291" t="s">
+      <c r="C296" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297">
+        <v>19740</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C291" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292">
-        <v>19700</v>
-      </c>
-      <c r="B292" s="2" t="s">
+      <c r="C297" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298">
+        <v>19800</v>
+      </c>
+      <c r="B298" t="s">
         <v>393</v>
       </c>
-      <c r="C292" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293">
-        <v>19710</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C293" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294">
-        <v>19720</v>
-      </c>
-      <c r="B294" s="2" t="s">
+      <c r="C298" t="s">
         <v>394</v>
-      </c>
-      <c r="C294" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3">
-      <c r="A295">
-        <v>19730</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C295" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3">
-      <c r="A296">
-        <v>19740</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C296" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3">
-      <c r="A297">
-        <v>19800</v>
-      </c>
-      <c r="B297" t="s">
-        <v>397</v>
-      </c>
-      <c r="C297" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3">
-      <c r="A298">
-        <v>19810</v>
-      </c>
-      <c r="B298" t="s">
-        <v>399</v>
-      </c>
-      <c r="C298" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299">
+        <v>19810</v>
+      </c>
+      <c r="B299" t="s">
+        <v>395</v>
+      </c>
+      <c r="C299" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300">
         <v>20010</v>
       </c>
-      <c r="B299" t="s">
+      <c r="B300" t="s">
+        <v>396</v>
+      </c>
+      <c r="C300" t="s">
+        <v>103</v>
+      </c>
+      <c r="D300" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301">
+        <v>20020</v>
+      </c>
+      <c r="B301" t="s">
+        <v>398</v>
+      </c>
+      <c r="C301" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302">
+        <v>20030</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C302" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303">
+        <v>20040</v>
+      </c>
+      <c r="B303" t="s">
         <v>400</v>
       </c>
-      <c r="C299" t="s">
-        <v>103</v>
-      </c>
-      <c r="D299" t="s">
+      <c r="C303" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304">
+        <v>20050</v>
+      </c>
+      <c r="B304" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
-      <c r="A300">
-        <v>20020</v>
-      </c>
-      <c r="B300" t="s">
-        <v>402</v>
-      </c>
-      <c r="C300" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
-      <c r="A301">
-        <v>20030</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C301" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3">
-      <c r="A302">
-        <v>20040</v>
-      </c>
-      <c r="B302" t="s">
-        <v>404</v>
-      </c>
-      <c r="C302" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3">
-      <c r="A303">
-        <v>20050</v>
-      </c>
-      <c r="B303" t="s">
-        <v>405</v>
-      </c>
-      <c r="C303" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
-      <c r="A304">
-        <v>20100</v>
-      </c>
-      <c r="B304" t="s">
-        <v>406</v>
       </c>
       <c r="C304" t="s">
         <v>103</v>
@@ -8285,10 +7730,10 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B305" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C305" t="s">
         <v>103</v>
@@ -8296,10 +7741,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B306" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C306" t="s">
         <v>103</v>
@@ -8307,10 +7752,10 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B307" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C307" t="s">
         <v>103</v>
@@ -8318,10 +7763,10 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B308" t="s">
-        <v>323</v>
+        <v>405</v>
       </c>
       <c r="C308" t="s">
         <v>103</v>
@@ -8329,10 +7774,10 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B309" t="s">
-        <v>410</v>
+        <v>319</v>
       </c>
       <c r="C309" t="s">
         <v>103</v>
@@ -8340,10 +7785,10 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B310" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C310" t="s">
         <v>103</v>
@@ -8351,10 +7796,10 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20230</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>412</v>
+        <v>20220</v>
+      </c>
+      <c r="B311" t="s">
+        <v>407</v>
       </c>
       <c r="C311" t="s">
         <v>103</v>
@@ -8362,10 +7807,10 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C312" t="s">
         <v>103</v>
@@ -8373,10 +7818,10 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C313" t="s">
         <v>103</v>
@@ -8384,10 +7829,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20260</v>
-      </c>
-      <c r="B314" t="s">
-        <v>415</v>
+        <v>20250</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>410</v>
       </c>
       <c r="C314" t="s">
         <v>103</v>
@@ -8395,10 +7840,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B315" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C315" t="s">
         <v>103</v>
@@ -8406,10 +7851,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B316" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C316" t="s">
         <v>103</v>
@@ -8417,10 +7862,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B317" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C317" t="s">
         <v>103</v>
@@ -8428,10 +7873,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B318" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C318" t="s">
         <v>103</v>
@@ -8439,10 +7884,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B319" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C319" t="s">
         <v>103</v>
@@ -8450,10 +7895,10 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B320" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C320" t="s">
         <v>103</v>
@@ -8461,10 +7906,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B321" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C321" t="s">
         <v>103</v>
@@ -8472,10 +7917,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B322" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C322" t="s">
         <v>103</v>
@@ -8483,10 +7928,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B323" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C323" t="s">
         <v>103</v>
@@ -8494,10 +7939,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B324" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C324" t="s">
         <v>103</v>
@@ -8505,10 +7950,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B325" t="s">
-        <v>107</v>
+        <v>421</v>
       </c>
       <c r="C325" t="s">
         <v>103</v>
@@ -8516,10 +7961,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B326" t="s">
-        <v>426</v>
+        <v>107</v>
       </c>
       <c r="C326" t="s">
         <v>103</v>
@@ -8527,10 +7972,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B327" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C327" t="s">
         <v>103</v>
@@ -8538,10 +7983,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B328" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C328" t="s">
         <v>103</v>
@@ -8549,10 +7994,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B329" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C329" t="s">
         <v>103</v>
@@ -8560,10 +8005,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B330" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C330" t="s">
         <v>103</v>
@@ -8571,10 +8016,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B331" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C331" t="s">
         <v>103</v>
@@ -8582,10 +8027,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B332" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C332" t="s">
         <v>103</v>
@@ -8593,10 +8038,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B333" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C333" t="s">
         <v>103</v>
@@ -8604,10 +8049,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B334" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C334" t="s">
         <v>103</v>
@@ -8615,10 +8060,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B335" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C335" t="s">
         <v>103</v>
@@ -8626,10 +8071,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B336" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C336" t="s">
         <v>103</v>
@@ -8637,10 +8082,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B337" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C337" t="s">
         <v>103</v>
@@ -8648,10 +8093,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B338" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C338" t="s">
         <v>103</v>
@@ -8659,10 +8104,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B339" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C339" t="s">
         <v>103</v>
@@ -8670,10 +8115,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B340" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C340" t="s">
         <v>103</v>
@@ -8681,10 +8126,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B341" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C341" t="s">
         <v>103</v>
@@ -8692,10 +8137,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B342" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C342" t="s">
         <v>103</v>
@@ -8703,10 +8148,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B343" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C343" t="s">
         <v>103</v>
@@ -8714,10 +8159,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B344" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C344" t="s">
         <v>103</v>
@@ -8725,10 +8170,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B345" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C345" t="s">
         <v>103</v>
@@ -8736,10 +8181,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B346" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C346" t="s">
         <v>103</v>
@@ -8747,10 +8192,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B347" t="s">
-        <v>338</v>
+        <v>442</v>
       </c>
       <c r="C347" t="s">
         <v>103</v>
@@ -8758,10 +8203,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B348" t="s">
-        <v>447</v>
+        <v>334</v>
       </c>
       <c r="C348" t="s">
         <v>103</v>
@@ -8769,10 +8214,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B349" t="s">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="C349" t="s">
         <v>103</v>
@@ -8780,10 +8225,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B350" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C350" t="s">
         <v>103</v>
@@ -8791,10 +8236,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B351" t="s">
-        <v>448</v>
+        <v>128</v>
       </c>
       <c r="C351" t="s">
         <v>103</v>
@@ -8802,21 +8247,21 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
+        <v>30040</v>
+      </c>
+      <c r="B352" t="s">
+        <v>444</v>
+      </c>
+      <c r="C352" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
+      <c r="A353">
         <v>31010</v>
       </c>
-      <c r="B352" t="s">
-        <v>449</v>
-      </c>
-      <c r="C352" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
-      <c r="A353">
-        <v>31020</v>
-      </c>
       <c r="B353" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C353" t="s">
         <v>103</v>
@@ -8824,46 +8269,46 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
+        <v>31020</v>
+      </c>
+      <c r="B354" t="s">
+        <v>446</v>
+      </c>
+      <c r="C354" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
+      <c r="A355">
         <v>102000</v>
       </c>
-      <c r="B354" t="s">
-        <v>451</v>
-      </c>
-      <c r="C354" t="s">
-        <v>103</v>
-      </c>
-      <c r="D354" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3">
-      <c r="A355">
+      <c r="B355" t="s">
+        <v>447</v>
+      </c>
+      <c r="C355" t="s">
+        <v>103</v>
+      </c>
+      <c r="D355" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
+      <c r="A356">
         <v>102010</v>
       </c>
-      <c r="B355" t="s">
-        <v>345</v>
-      </c>
-      <c r="C355" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3">
-      <c r="A356">
+      <c r="B356" t="s">
+        <v>341</v>
+      </c>
+      <c r="C356" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
+      <c r="A357">
         <v>102020</v>
       </c>
-      <c r="B356" t="s">
-        <v>378</v>
-      </c>
-      <c r="C356" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3">
-      <c r="A357">
-        <v>102030</v>
-      </c>
       <c r="B357" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="C357" t="s">
         <v>103</v>
@@ -8871,57 +8316,57 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
+        <v>102030</v>
+      </c>
+      <c r="B358" t="s">
+        <v>337</v>
+      </c>
+      <c r="C358" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
+      <c r="A359">
         <v>113000</v>
       </c>
-      <c r="B358" t="s">
+      <c r="B359" t="s">
+        <v>449</v>
+      </c>
+      <c r="C359" t="s">
+        <v>103</v>
+      </c>
+      <c r="D359" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
+      <c r="A360">
+        <v>113010</v>
+      </c>
+      <c r="B360" t="s">
+        <v>451</v>
+      </c>
+      <c r="C360" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
+      <c r="A361">
+        <v>113020</v>
+      </c>
+      <c r="B361" t="s">
+        <v>452</v>
+      </c>
+      <c r="C361" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
+      <c r="A362">
+        <v>113030</v>
+      </c>
+      <c r="B362" t="s">
         <v>453</v>
-      </c>
-      <c r="C358" t="s">
-        <v>103</v>
-      </c>
-      <c r="D358" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3">
-      <c r="A359">
-        <v>113010</v>
-      </c>
-      <c r="B359" t="s">
-        <v>455</v>
-      </c>
-      <c r="C359" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3">
-      <c r="A360">
-        <v>113020</v>
-      </c>
-      <c r="B360" t="s">
-        <v>456</v>
-      </c>
-      <c r="C360" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3">
-      <c r="A361">
-        <v>113030</v>
-      </c>
-      <c r="B361" t="s">
-        <v>457</v>
-      </c>
-      <c r="C361" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3">
-      <c r="A362">
-        <v>113040</v>
-      </c>
-      <c r="B362" t="s">
-        <v>458</v>
       </c>
       <c r="C362" t="s">
         <v>103</v>
@@ -8929,68 +8374,68 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
+        <v>113040</v>
+      </c>
+      <c r="B363" t="s">
+        <v>454</v>
+      </c>
+      <c r="C363" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
+      <c r="A364">
         <v>121010</v>
       </c>
-      <c r="B363" t="s">
+      <c r="B364" t="s">
+        <v>455</v>
+      </c>
+      <c r="C364" t="s">
+        <v>103</v>
+      </c>
+      <c r="D364" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365">
+        <v>121011</v>
+      </c>
+      <c r="B365" t="s">
+        <v>457</v>
+      </c>
+      <c r="C365" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366">
+        <v>121012</v>
+      </c>
+      <c r="B366" t="s">
+        <v>458</v>
+      </c>
+      <c r="C366" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367">
+        <v>121013</v>
+      </c>
+      <c r="B367" t="s">
         <v>459</v>
       </c>
-      <c r="C363" t="s">
-        <v>103</v>
-      </c>
-      <c r="D363" t="s">
+      <c r="C367" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368">
+        <v>121014</v>
+      </c>
+      <c r="B368" t="s">
         <v>460</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3">
-      <c r="A364">
-        <v>121011</v>
-      </c>
-      <c r="B364" t="s">
-        <v>461</v>
-      </c>
-      <c r="C364" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3">
-      <c r="A365">
-        <v>121012</v>
-      </c>
-      <c r="B365" t="s">
-        <v>462</v>
-      </c>
-      <c r="C365" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3">
-      <c r="A366">
-        <v>121013</v>
-      </c>
-      <c r="B366" t="s">
-        <v>463</v>
-      </c>
-      <c r="C366" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3">
-      <c r="A367">
-        <v>121014</v>
-      </c>
-      <c r="B367" t="s">
-        <v>464</v>
-      </c>
-      <c r="C367" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3">
-      <c r="A368">
-        <v>121015</v>
-      </c>
-      <c r="B368" t="s">
-        <v>465</v>
       </c>
       <c r="C368" t="s">
         <v>103</v>
@@ -8998,10 +8443,10 @@
     </row>
     <row r="369" spans="1:3">
       <c r="A369">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B369" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C369" t="s">
         <v>103</v>
@@ -9009,10 +8454,10 @@
     </row>
     <row r="370" spans="1:3">
       <c r="A370">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B370" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C370" t="s">
         <v>103</v>
@@ -9020,10 +8465,10 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B371" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C371" t="s">
         <v>103</v>
@@ -9031,10 +8476,10 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B372" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C372" t="s">
         <v>103</v>
@@ -9042,10 +8487,10 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B373" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C373" t="s">
         <v>103</v>
@@ -9053,17 +8498,28 @@
     </row>
     <row r="374" spans="1:3">
       <c r="A374">
+        <v>121020</v>
+      </c>
+      <c r="B374" t="s">
+        <v>466</v>
+      </c>
+      <c r="C374" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375">
         <v>121030</v>
       </c>
-      <c r="B374" t="s">
-        <v>471</v>
-      </c>
-      <c r="C374" t="s">
+      <c r="B375" t="s">
+        <v>467</v>
+      </c>
+      <c r="C375" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8146EF3-375A-43CA-AC34-668AEE37391E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67BE7EE-D63E-4BB9-AC2A-0F2281A726AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="481">
   <si>
     <t>Id</t>
   </si>
@@ -46,18 +46,6 @@
   </si>
   <si>
     <t>NameTextId</t>
-  </si>
-  <si>
-    <t>PARADIGM</t>
-  </si>
-  <si>
-    <t>MENU</t>
-  </si>
-  <si>
-    <t>EDIT</t>
-  </si>
-  <si>
-    <t>SAVE</t>
   </si>
   <si>
     <t>NEWGAME</t>
@@ -1037,9 +1025,6 @@
     <t>ボス</t>
   </si>
   <si>
-    <t>探索</t>
-  </si>
-  <si>
     <t>ステージを探索します</t>
   </si>
   <si>
@@ -1059,9 +1044,6 @@
   </si>
   <si>
     <t>キャラのステータスや魔法を確認します</t>
-  </si>
-  <si>
-    <t>回復</t>
   </si>
   <si>
     <t>Numinosを使用してキャラを回復します</t>
@@ -1484,6 +1466,73 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Departure</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TurnEnd</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MoveBattler</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Wait</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>UnitActEnd</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Battle</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Units</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>出撃</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ターン終了</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>移動</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>待機</t>
+    <rPh sb="0" eb="2">
+      <t>タイキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バトル</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>部隊</t>
+    <rPh sb="0" eb="2">
+      <t>ブタイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1864,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -1885,8 +1934,8 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="4" t="s">
+        <v>468</v>
       </c>
       <c r="C2">
         <v>19010</v>
@@ -1896,32 +1945,65 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="B3" s="4" t="s">
+        <v>469</v>
       </c>
       <c r="C3">
-        <v>19740</v>
+        <v>19020</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B4" s="4" t="s">
+        <v>470</v>
       </c>
       <c r="C4">
-        <v>19011</v>
+        <v>19030</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C5">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C6">
+        <v>19050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="B7" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C7">
+        <v>19060</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C8">
         <v>19070</v>
       </c>
     </row>
@@ -1956,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>13210</v>
@@ -1967,7 +2049,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>13220</v>
@@ -1978,7 +2060,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -1989,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>13230</v>
@@ -2025,7 +2107,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2036,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>18110</v>
@@ -2047,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>18120</v>
@@ -2058,7 +2140,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>18130</v>
@@ -2090,25 +2172,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2116,7 +2198,7 @@
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>6010</v>
@@ -2148,7 +2230,7 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>6020</v>
@@ -2180,7 +2262,7 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>6030</v>
@@ -2212,7 +2294,7 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>6040</v>
@@ -2244,7 +2326,7 @@
         <v>2030</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>6210</v>
@@ -2276,7 +2358,7 @@
         <v>2040</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>6220</v>
@@ -2308,7 +2390,7 @@
         <v>2050</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>6230</v>
@@ -2340,7 +2422,7 @@
         <v>2060</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>6240</v>
@@ -2372,7 +2454,7 @@
         <v>2070</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>6250</v>
@@ -2404,7 +2486,7 @@
         <v>2080</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>6260</v>
@@ -2436,7 +2518,7 @@
         <v>2090</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>6270</v>
@@ -2468,7 +2550,7 @@
         <v>2100</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>6280</v>
@@ -2514,15 +2596,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -2531,12 +2613,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -2545,12 +2627,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -2559,12 +2641,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2573,12 +2655,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -2587,12 +2669,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2601,12 +2683,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -2615,12 +2697,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -2629,12 +2711,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -2643,12 +2725,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2657,12 +2739,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2671,12 +2753,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -2685,12 +2767,12 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -2699,12 +2781,12 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -2713,12 +2795,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -2727,12 +2809,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2741,12 +2823,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2755,12 +2837,12 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -2769,12 +2851,12 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -2783,12 +2865,12 @@
         <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -2797,12 +2879,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -2811,12 +2893,12 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -2825,12 +2907,12 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -2839,12 +2921,12 @@
         <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -2853,12 +2935,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -2867,12 +2949,12 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -2881,12 +2963,12 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2895,12 +2977,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -2909,12 +2991,12 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -2923,12 +3005,12 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -2937,12 +3019,12 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -2951,12 +3033,12 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -2965,12 +3047,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -2979,12 +3061,12 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -2993,12 +3075,12 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3007,12 +3089,12 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3021,12 +3103,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -3035,12 +3117,12 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -3049,12 +3131,12 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -3063,12 +3145,12 @@
         <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -3077,12 +3159,12 @@
         <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -3091,12 +3173,12 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -3105,12 +3187,12 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3119,12 +3201,12 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -3133,12 +3215,12 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -3147,12 +3229,12 @@
         <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>11</v>
@@ -3161,12 +3243,12 @@
         <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -3175,12 +3257,12 @@
         <v>210</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -3189,12 +3271,12 @@
         <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -3203,12 +3285,12 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -3217,12 +3299,12 @@
         <v>802</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -3231,12 +3313,12 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -3245,12 +3327,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -3259,12 +3341,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -3273,12 +3355,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3287,12 +3369,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -3301,12 +3383,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -3315,12 +3397,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -3329,12 +3411,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -3343,12 +3425,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3357,12 +3439,12 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -3371,12 +3453,12 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -3387,7 +3469,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -3396,12 +3478,12 @@
         <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -3410,12 +3492,12 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -3426,7 +3508,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -3437,7 +3519,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -3448,7 +3530,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -3459,7 +3541,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -3468,12 +3550,12 @@
         <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -3482,12 +3564,12 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -3496,12 +3578,12 @@
         <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B73">
         <v>8</v>
@@ -3510,12 +3592,12 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -3524,12 +3606,12 @@
         <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -3538,12 +3620,12 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B76">
         <v>11</v>
@@ -3552,12 +3634,12 @@
         <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B77">
         <v>7</v>
@@ -3566,12 +3648,12 @@
         <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -3580,12 +3662,12 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -3594,12 +3676,12 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -3608,12 +3690,12 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -3622,12 +3704,12 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -3636,12 +3718,12 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -3650,12 +3732,12 @@
         <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B84">
         <v>9</v>
@@ -3664,12 +3746,12 @@
         <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B85">
         <v>8</v>
@@ -3678,12 +3760,12 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -3692,12 +3774,12 @@
         <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -3706,12 +3788,12 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -3720,12 +3802,12 @@
         <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -3734,12 +3816,12 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B90">
         <v>9</v>
@@ -3748,12 +3830,12 @@
         <v>813</v>
       </c>
       <c r="D90" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -3762,12 +3844,12 @@
         <v>800</v>
       </c>
       <c r="D91" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -3776,12 +3858,12 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -3790,12 +3872,12 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -3804,12 +3886,12 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B95">
         <v>9</v>
@@ -3818,12 +3900,12 @@
         <v>814</v>
       </c>
       <c r="D95" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -3832,12 +3914,12 @@
         <v>800</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -3846,12 +3928,12 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -3860,12 +3942,12 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -3874,12 +3956,12 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -3888,12 +3970,12 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3902,12 +3984,12 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -3916,12 +3998,12 @@
         <v>818</v>
       </c>
       <c r="D102" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -3930,12 +4012,12 @@
         <v>800</v>
       </c>
       <c r="D103" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -3944,12 +4026,12 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B105">
         <v>9</v>
@@ -3958,12 +4040,12 @@
         <v>817</v>
       </c>
       <c r="D105" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -3972,12 +4054,12 @@
         <v>816</v>
       </c>
       <c r="D106" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -3986,12 +4068,12 @@
         <v>817</v>
       </c>
       <c r="D107" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B108">
         <v>4</v>
@@ -4000,12 +4082,12 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -4014,12 +4096,12 @@
         <v>801</v>
       </c>
       <c r="D109" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -4028,12 +4110,12 @@
         <v>800</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -4042,12 +4124,12 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -4056,12 +4138,12 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -4070,12 +4152,12 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -4084,12 +4166,12 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -4098,12 +4180,12 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -4112,12 +4194,12 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -4126,7 +4208,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -4148,34 +4230,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -4183,7 +4265,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -4191,7 +4273,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -4199,7 +4281,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -4207,40 +4289,40 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B10">
         <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -4266,10 +4348,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4277,10 +4359,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14">
@@ -4288,10 +4370,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -4300,10 +4382,10 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4311,10 +4393,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4322,10 +4404,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4333,10 +4415,10 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4344,10 +4426,10 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4355,10 +4437,10 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4366,10 +4448,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4377,10 +4459,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4388,10 +4470,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4399,10 +4481,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4410,10 +4492,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4421,10 +4503,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4432,10 +4514,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4443,10 +4525,10 @@
         <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4454,10 +4536,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4465,10 +4547,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4476,10 +4558,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4487,10 +4569,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4498,10 +4580,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4509,10 +4591,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4520,10 +4602,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4531,10 +4613,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4542,10 +4624,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4553,10 +4635,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4564,10 +4646,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4575,10 +4657,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4586,10 +4668,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -4597,10 +4679,10 @@
         <v>342</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -4608,13 +4690,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -4622,13 +4704,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -4636,13 +4718,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -4650,13 +4732,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -4664,13 +4746,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -4678,13 +4760,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -4692,10 +4774,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -4703,10 +4785,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -4714,10 +4796,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -4725,10 +4807,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -4736,10 +4818,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -4747,10 +4829,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -4758,10 +4840,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -4769,10 +4851,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -4780,10 +4862,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -4791,10 +4873,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -4802,10 +4884,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -4813,10 +4895,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -4824,10 +4906,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -4835,10 +4917,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4846,10 +4928,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -4857,10 +4939,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -4868,10 +4950,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4879,10 +4961,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4890,10 +4972,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4901,10 +4983,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4912,10 +4994,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4923,10 +5005,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4934,10 +5016,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -4945,10 +5027,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4956,10 +5038,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -4967,10 +5049,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -4978,10 +5060,10 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -4989,10 +5071,10 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5000,10 +5082,10 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5011,10 +5093,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5022,10 +5104,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5033,10 +5115,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5044,10 +5126,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5055,10 +5137,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5066,10 +5148,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5077,10 +5159,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5088,10 +5170,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5099,10 +5181,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5110,10 +5192,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C76" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5121,10 +5203,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5132,10 +5214,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5143,10 +5225,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5154,10 +5236,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C80" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -5165,10 +5247,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -5176,10 +5258,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -5187,10 +5269,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -5198,10 +5280,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -5209,10 +5291,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -5220,10 +5302,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -5231,10 +5313,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -5242,10 +5324,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -5253,10 +5335,10 @@
         <v>1000</v>
       </c>
       <c r="B89" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -5264,10 +5346,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -5275,10 +5357,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -5286,10 +5368,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -5297,10 +5379,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -5308,10 +5390,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -5319,10 +5401,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C95" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -5330,13 +5412,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D96" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -5344,10 +5426,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C97" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -5355,10 +5437,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C98" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -5366,10 +5448,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -5377,10 +5459,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C100" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -5388,10 +5470,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C101" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -5399,10 +5481,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C102" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -5410,10 +5492,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -5421,13 +5503,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C104" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D104" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -5435,13 +5517,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D105" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -5449,13 +5531,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C106" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D106" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -5463,13 +5545,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D107" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -5477,13 +5559,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C108" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D108" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -5491,10 +5573,10 @@
         <v>2101</v>
       </c>
       <c r="B109" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -5502,10 +5584,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C110" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -5513,10 +5595,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -5524,10 +5606,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -5535,13 +5617,13 @@
         <v>2200</v>
       </c>
       <c r="B113" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C113" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D113" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -5549,13 +5631,13 @@
         <v>2210</v>
       </c>
       <c r="B114" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D114" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="29" customHeight="1">
@@ -5563,13 +5645,13 @@
         <v>2220</v>
       </c>
       <c r="B115" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D115" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -5577,13 +5659,13 @@
         <v>2300</v>
       </c>
       <c r="B116" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D116" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -5591,13 +5673,13 @@
         <v>2310</v>
       </c>
       <c r="B117" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D117" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -5605,13 +5687,13 @@
         <v>2320</v>
       </c>
       <c r="B118" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D118" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -5619,13 +5701,13 @@
         <v>2330</v>
       </c>
       <c r="B119" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C119" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D119" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -5633,13 +5715,13 @@
         <v>2340</v>
       </c>
       <c r="B120" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D120" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -5647,13 +5729,13 @@
         <v>2400</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D121" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -5661,10 +5743,10 @@
         <v>3000</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -5672,10 +5754,10 @@
         <v>3010</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -5683,10 +5765,10 @@
         <v>3011</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -5694,10 +5776,10 @@
         <v>3040</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -5705,10 +5787,10 @@
         <v>3050</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -5716,10 +5798,10 @@
         <v>3051</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -5727,10 +5809,10 @@
         <v>3052</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -5738,10 +5820,10 @@
         <v>3053</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -5749,10 +5831,10 @@
         <v>3054</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -5760,10 +5842,10 @@
         <v>3070</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -5771,10 +5853,10 @@
         <v>3071</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C132" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -5782,10 +5864,10 @@
         <v>3072</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -5793,10 +5875,10 @@
         <v>3073</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -5804,10 +5886,10 @@
         <v>3090</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -5815,10 +5897,10 @@
         <v>3211</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -5826,10 +5908,10 @@
         <v>3230</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -5837,10 +5919,10 @@
         <v>5000</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C138" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -5848,10 +5930,10 @@
         <v>5001</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -5859,10 +5941,10 @@
         <v>5002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C140" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -5870,10 +5952,10 @@
         <v>6001</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C141" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -5881,10 +5963,10 @@
         <v>6002</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -5892,10 +5974,10 @@
         <v>6100</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C143" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -5903,10 +5985,10 @@
         <v>6010</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C144" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -5914,10 +5996,10 @@
         <v>6011</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -5925,10 +6007,10 @@
         <v>6012</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C146" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -5936,10 +6018,10 @@
         <v>6020</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C147" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -5947,10 +6029,10 @@
         <v>6030</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C148" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -5958,10 +6040,10 @@
         <v>6040</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C149" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -5969,10 +6051,10 @@
         <v>6210</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C150" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -5980,10 +6062,10 @@
         <v>6220</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C151" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -5991,10 +6073,10 @@
         <v>6230</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C152" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6002,10 +6084,10 @@
         <v>6240</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C153" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6013,10 +6095,10 @@
         <v>6250</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C154" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6024,10 +6106,10 @@
         <v>6260</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C155" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6035,10 +6117,10 @@
         <v>6270</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C156" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6046,10 +6128,10 @@
         <v>6280</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C157" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6057,10 +6139,10 @@
         <v>6810</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6068,10 +6150,10 @@
         <v>6820</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C159" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6079,10 +6161,10 @@
         <v>6830</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C160" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -6090,10 +6172,10 @@
         <v>6840</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -6101,10 +6183,10 @@
         <v>6850</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C162" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -6112,10 +6194,10 @@
         <v>6860</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -6123,10 +6205,10 @@
         <v>6870</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C164" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -6134,10 +6216,10 @@
         <v>6880</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -6145,10 +6227,10 @@
         <v>6890</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C166" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="130">
@@ -6156,13 +6238,13 @@
         <v>12010</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C167" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -6170,13 +6252,13 @@
         <v>13010</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D168" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -6184,7 +6266,7 @@
         <v>13020</v>
       </c>
       <c r="C169" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -6192,10 +6274,10 @@
         <v>13110</v>
       </c>
       <c r="B170" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C170" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -6203,10 +6285,10 @@
         <v>13120</v>
       </c>
       <c r="B171" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -6214,10 +6296,10 @@
         <v>13130</v>
       </c>
       <c r="B172" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -6225,10 +6307,10 @@
         <v>13140</v>
       </c>
       <c r="B173" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C173" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -6236,10 +6318,10 @@
         <v>13210</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -6247,10 +6329,10 @@
         <v>13220</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C175" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -6258,10 +6340,10 @@
         <v>13230</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C176" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -6269,10 +6351,10 @@
         <v>13240</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C177" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -6280,10 +6362,10 @@
         <v>13300</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C178" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6291,10 +6373,10 @@
         <v>13301</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C179" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6302,10 +6384,10 @@
         <v>13310</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C180" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6313,10 +6395,10 @@
         <v>13320</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C181" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="26">
@@ -6324,10 +6406,10 @@
         <v>13330</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C182" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6335,10 +6417,10 @@
         <v>13400</v>
       </c>
       <c r="B183" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C183" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6346,10 +6428,10 @@
         <v>13410</v>
       </c>
       <c r="B184" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C184" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6357,10 +6439,10 @@
         <v>13420</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6368,10 +6450,10 @@
         <v>13421</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C186" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6379,10 +6461,10 @@
         <v>13430</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C187" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6390,10 +6472,10 @@
         <v>14090</v>
       </c>
       <c r="B188" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6401,10 +6483,10 @@
         <v>14110</v>
       </c>
       <c r="B189" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C189" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="14">
@@ -6412,13 +6494,13 @@
         <v>15010</v>
       </c>
       <c r="B190" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C190" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D190" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G190" s="1"/>
     </row>
@@ -6427,13 +6509,13 @@
         <v>16010</v>
       </c>
       <c r="B191" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C191" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D191" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G191" s="1"/>
     </row>
@@ -6442,10 +6524,10 @@
         <v>16020</v>
       </c>
       <c r="B192" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C192" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -6454,10 +6536,10 @@
         <v>16100</v>
       </c>
       <c r="B193" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C193" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -6465,10 +6547,10 @@
         <v>16110</v>
       </c>
       <c r="B194" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C194" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -6476,10 +6558,10 @@
         <v>16200</v>
       </c>
       <c r="B195" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C195" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -6487,10 +6569,10 @@
         <v>16210</v>
       </c>
       <c r="B196" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C196" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -6498,10 +6580,10 @@
         <v>16220</v>
       </c>
       <c r="B197" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C197" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -6509,10 +6591,10 @@
         <v>16230</v>
       </c>
       <c r="B198" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C198" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -6520,10 +6602,10 @@
         <v>16300</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C199" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -6531,10 +6613,10 @@
         <v>16310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C200" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -6542,10 +6624,10 @@
         <v>16320</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C201" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -6553,10 +6635,10 @@
         <v>16400</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C202" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -6564,10 +6646,10 @@
         <v>16410</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C203" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -6575,13 +6657,13 @@
         <v>16800</v>
       </c>
       <c r="B204" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C204" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D204" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -6589,13 +6671,13 @@
         <v>16801</v>
       </c>
       <c r="B205" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C205" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D205" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -6603,13 +6685,13 @@
         <v>16802</v>
       </c>
       <c r="B206" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C206" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D206" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -6617,13 +6699,13 @@
         <v>16803</v>
       </c>
       <c r="B207" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C207" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D207" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -6631,13 +6713,13 @@
         <v>16804</v>
       </c>
       <c r="B208" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C208" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D208" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -6645,13 +6727,13 @@
         <v>16805</v>
       </c>
       <c r="B209" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C209" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D209" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -6659,13 +6741,13 @@
         <v>16806</v>
       </c>
       <c r="B210" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C210" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D210" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -6673,10 +6755,10 @@
         <v>17010</v>
       </c>
       <c r="B211" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C211" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -6684,13 +6766,13 @@
         <v>18010</v>
       </c>
       <c r="B212" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C212" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D212" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -6698,10 +6780,10 @@
         <v>18020</v>
       </c>
       <c r="B213" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C213" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -6709,10 +6791,10 @@
         <v>18100</v>
       </c>
       <c r="B214" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C214" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -6720,10 +6802,10 @@
         <v>18110</v>
       </c>
       <c r="B215" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C215" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -6731,10 +6813,10 @@
         <v>18120</v>
       </c>
       <c r="B216" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C216" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -6742,10 +6824,10 @@
         <v>18130</v>
       </c>
       <c r="B217" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C217" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -6753,10 +6835,10 @@
         <v>18200</v>
       </c>
       <c r="B218" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C218" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -6764,10 +6846,10 @@
         <v>18210</v>
       </c>
       <c r="B219" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C219" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -6775,10 +6857,10 @@
         <v>18220</v>
       </c>
       <c r="B220" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C220" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -6786,10 +6868,10 @@
         <v>18300</v>
       </c>
       <c r="B221" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C221" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -6797,10 +6879,10 @@
         <v>18310</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C222" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -6808,10 +6890,10 @@
         <v>18320</v>
       </c>
       <c r="B223" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C223" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -6819,10 +6901,10 @@
         <v>18340</v>
       </c>
       <c r="B224" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C224" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -6830,10 +6912,10 @@
         <v>18400</v>
       </c>
       <c r="B225" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C225" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -6841,10 +6923,10 @@
         <v>18410</v>
       </c>
       <c r="B226" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C226" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -6852,10 +6934,10 @@
         <v>18420</v>
       </c>
       <c r="B227" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C227" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -6863,10 +6945,10 @@
         <v>18430</v>
       </c>
       <c r="B228" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C228" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -6874,10 +6956,10 @@
         <v>18440</v>
       </c>
       <c r="B229" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C229" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -6885,10 +6967,10 @@
         <v>18450</v>
       </c>
       <c r="B230" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C230" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -6896,10 +6978,10 @@
         <v>18500</v>
       </c>
       <c r="B231" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C231" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -6907,10 +6989,10 @@
         <v>18510</v>
       </c>
       <c r="B232" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C232" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -6918,10 +7000,10 @@
         <v>18800</v>
       </c>
       <c r="B233" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C233" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -6929,10 +7011,10 @@
         <v>18801</v>
       </c>
       <c r="B234" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C234" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -6940,10 +7022,10 @@
         <v>18802</v>
       </c>
       <c r="B235" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C235" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -6951,10 +7033,10 @@
         <v>18803</v>
       </c>
       <c r="B236" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C236" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -6962,10 +7044,10 @@
         <v>18804</v>
       </c>
       <c r="B237" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C237" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -6973,10 +7055,10 @@
         <v>18805</v>
       </c>
       <c r="B238" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C238" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -6984,10 +7066,10 @@
         <v>18806</v>
       </c>
       <c r="B239" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C239" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -6995,10 +7077,10 @@
         <v>18811</v>
       </c>
       <c r="B240" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C240" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7006,24 +7088,24 @@
         <v>18812</v>
       </c>
       <c r="B241" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C241" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="242" spans="1:7" ht="14">
       <c r="A242">
         <v>19010</v>
       </c>
-      <c r="B242" t="s">
-        <v>331</v>
+      <c r="B242" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="C242" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D242" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G242" s="1"/>
     </row>
@@ -7032,10 +7114,10 @@
         <v>19011</v>
       </c>
       <c r="B243" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C243" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G243" s="1"/>
     </row>
@@ -7043,66 +7125,66 @@
       <c r="A244">
         <v>19020</v>
       </c>
-      <c r="B244" t="s">
-        <v>111</v>
+      <c r="B244" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="C244" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245">
         <v>19030</v>
       </c>
-      <c r="B245" t="s">
-        <v>112</v>
+      <c r="B245" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="C245" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246">
         <v>19040</v>
       </c>
-      <c r="B246" t="s">
-        <v>337</v>
+      <c r="B246" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C246" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247">
         <v>19050</v>
       </c>
-      <c r="B247" t="s">
-        <v>339</v>
+      <c r="B247" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C247" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248">
         <v>19060</v>
       </c>
-      <c r="B248" t="s">
-        <v>341</v>
+      <c r="B248" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="C248" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249">
         <v>19070</v>
       </c>
-      <c r="B249" t="s">
-        <v>343</v>
+      <c r="B249" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="C249" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7110,10 +7192,10 @@
         <v>19100</v>
       </c>
       <c r="B250" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C250" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7121,10 +7203,10 @@
         <v>19110</v>
       </c>
       <c r="B251" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C251" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7132,10 +7214,10 @@
         <v>19200</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C252" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7143,10 +7225,10 @@
         <v>19210</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C253" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7154,10 +7236,10 @@
         <v>19220</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C254" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7165,10 +7247,10 @@
         <v>19230</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C255" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7176,10 +7258,10 @@
         <v>19240</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C256" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -7187,10 +7269,10 @@
         <v>19250</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C257" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -7198,10 +7280,10 @@
         <v>19260</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C258" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -7209,10 +7291,10 @@
         <v>19270</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C259" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -7220,10 +7302,10 @@
         <v>19280</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C260" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -7231,10 +7313,10 @@
         <v>19300</v>
       </c>
       <c r="B261" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C261" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="26">
@@ -7242,10 +7324,10 @@
         <v>19310</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C262" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -7253,10 +7335,10 @@
         <v>19320</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C263" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -7264,10 +7346,10 @@
         <v>19330</v>
       </c>
       <c r="B264" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C264" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -7275,10 +7357,10 @@
         <v>19340</v>
       </c>
       <c r="B265" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C265" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -7286,10 +7368,10 @@
         <v>19350</v>
       </c>
       <c r="B266" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C266" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -7297,10 +7379,10 @@
         <v>19360</v>
       </c>
       <c r="B267" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C267" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -7308,10 +7390,10 @@
         <v>19400</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C268" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -7319,10 +7401,10 @@
         <v>19401</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C269" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -7330,10 +7412,10 @@
         <v>19410</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C270" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -7341,10 +7423,10 @@
         <v>19420</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C271" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -7352,10 +7434,10 @@
         <v>19500</v>
       </c>
       <c r="B272" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C272" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7363,10 +7445,10 @@
         <v>19510</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C273" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7374,10 +7456,10 @@
         <v>19520</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C274" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7385,10 +7467,10 @@
         <v>19600</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C275" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7396,10 +7478,10 @@
         <v>19601</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C276" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7407,10 +7489,10 @@
         <v>19602</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C277" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7418,10 +7500,10 @@
         <v>19603</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C278" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7429,10 +7511,10 @@
         <v>19604</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C279" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14">
@@ -7440,13 +7522,13 @@
         <v>19611</v>
       </c>
       <c r="B280" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C280" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D280" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G280" s="1"/>
     </row>
@@ -7455,10 +7537,10 @@
         <v>19612</v>
       </c>
       <c r="B281" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C281" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G281" s="1"/>
     </row>
@@ -7467,10 +7549,10 @@
         <v>19613</v>
       </c>
       <c r="B282" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C282" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G282" s="1"/>
     </row>
@@ -7479,10 +7561,10 @@
         <v>19614</v>
       </c>
       <c r="B283" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C283" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G283" s="1"/>
     </row>
@@ -7491,10 +7573,10 @@
         <v>19615</v>
       </c>
       <c r="B284" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C284" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G284" s="1"/>
     </row>
@@ -7503,10 +7585,10 @@
         <v>19616</v>
       </c>
       <c r="B285" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C285" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G285" s="1"/>
     </row>
@@ -7515,10 +7597,10 @@
         <v>19617</v>
       </c>
       <c r="B286" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C286" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G286" s="1"/>
     </row>
@@ -7527,10 +7609,10 @@
         <v>19618</v>
       </c>
       <c r="B287" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C287" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G287" s="1"/>
     </row>
@@ -7539,10 +7621,10 @@
         <v>19619</v>
       </c>
       <c r="B288" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C288" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G288" s="1"/>
     </row>
@@ -7551,13 +7633,13 @@
         <v>19631</v>
       </c>
       <c r="B289" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C289" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D289" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -7565,10 +7647,10 @@
         <v>19632</v>
       </c>
       <c r="B290" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C290" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -7576,10 +7658,10 @@
         <v>19633</v>
       </c>
       <c r="B291" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C291" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -7587,10 +7669,10 @@
         <v>19634</v>
       </c>
       <c r="B292" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C292" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -7598,10 +7680,10 @@
         <v>19700</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C293" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -7609,10 +7691,10 @@
         <v>19710</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C294" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -7620,10 +7702,10 @@
         <v>19720</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C295" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -7631,10 +7713,10 @@
         <v>19730</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C296" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -7642,10 +7724,10 @@
         <v>19740</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C297" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -7653,10 +7735,10 @@
         <v>19800</v>
       </c>
       <c r="B298" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C298" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -7664,10 +7746,10 @@
         <v>19810</v>
       </c>
       <c r="B299" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C299" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -7675,13 +7757,13 @@
         <v>20010</v>
       </c>
       <c r="B300" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C300" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D300" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -7689,10 +7771,10 @@
         <v>20020</v>
       </c>
       <c r="B301" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C301" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -7700,10 +7782,10 @@
         <v>20030</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C302" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -7711,10 +7793,10 @@
         <v>20040</v>
       </c>
       <c r="B303" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C303" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -7722,10 +7804,10 @@
         <v>20050</v>
       </c>
       <c r="B304" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C304" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -7733,10 +7815,10 @@
         <v>20100</v>
       </c>
       <c r="B305" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C305" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -7744,10 +7826,10 @@
         <v>20110</v>
       </c>
       <c r="B306" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C306" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -7755,10 +7837,10 @@
         <v>20120</v>
       </c>
       <c r="B307" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C307" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -7766,10 +7848,10 @@
         <v>20200</v>
       </c>
       <c r="B308" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C308" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -7777,10 +7859,10 @@
         <v>20201</v>
       </c>
       <c r="B309" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C309" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -7788,10 +7870,10 @@
         <v>20210</v>
       </c>
       <c r="B310" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C310" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -7799,10 +7881,10 @@
         <v>20220</v>
       </c>
       <c r="B311" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C311" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -7810,10 +7892,10 @@
         <v>20230</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C312" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -7821,10 +7903,10 @@
         <v>20240</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C313" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -7832,10 +7914,10 @@
         <v>20250</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C314" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -7843,10 +7925,10 @@
         <v>20260</v>
       </c>
       <c r="B315" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C315" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -7854,10 +7936,10 @@
         <v>20270</v>
       </c>
       <c r="B316" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C316" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -7865,10 +7947,10 @@
         <v>20280</v>
       </c>
       <c r="B317" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C317" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -7876,10 +7958,10 @@
         <v>20290</v>
       </c>
       <c r="B318" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C318" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -7887,10 +7969,10 @@
         <v>20300</v>
       </c>
       <c r="B319" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C319" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -7898,10 +7980,10 @@
         <v>20310</v>
       </c>
       <c r="B320" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C320" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -7909,10 +7991,10 @@
         <v>20320</v>
       </c>
       <c r="B321" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C321" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -7920,10 +8002,10 @@
         <v>20330</v>
       </c>
       <c r="B322" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C322" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -7931,10 +8013,10 @@
         <v>20340</v>
       </c>
       <c r="B323" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C323" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -7942,10 +8024,10 @@
         <v>20350</v>
       </c>
       <c r="B324" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C324" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -7953,10 +8035,10 @@
         <v>23010</v>
       </c>
       <c r="B325" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C325" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -7964,10 +8046,10 @@
         <v>23020</v>
       </c>
       <c r="B326" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C326" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -7975,10 +8057,10 @@
         <v>23030</v>
       </c>
       <c r="B327" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C327" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -7986,10 +8068,10 @@
         <v>23031</v>
       </c>
       <c r="B328" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C328" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -7997,10 +8079,10 @@
         <v>23032</v>
       </c>
       <c r="B329" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C329" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -8008,10 +8090,10 @@
         <v>23040</v>
       </c>
       <c r="B330" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C330" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -8019,10 +8101,10 @@
         <v>24010</v>
       </c>
       <c r="B331" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C331" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -8030,10 +8112,10 @@
         <v>24020</v>
       </c>
       <c r="B332" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C332" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -8041,10 +8123,10 @@
         <v>24030</v>
       </c>
       <c r="B333" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C333" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -8052,10 +8134,10 @@
         <v>24040</v>
       </c>
       <c r="B334" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C334" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -8063,10 +8145,10 @@
         <v>24110</v>
       </c>
       <c r="B335" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C335" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -8074,10 +8156,10 @@
         <v>24111</v>
       </c>
       <c r="B336" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C336" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -8085,10 +8167,10 @@
         <v>24112</v>
       </c>
       <c r="B337" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C337" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -8096,10 +8178,10 @@
         <v>24113</v>
       </c>
       <c r="B338" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C338" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -8107,10 +8189,10 @@
         <v>24114</v>
       </c>
       <c r="B339" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C339" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -8118,10 +8200,10 @@
         <v>24115</v>
       </c>
       <c r="B340" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C340" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -8129,10 +8211,10 @@
         <v>24116</v>
       </c>
       <c r="B341" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C341" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -8140,10 +8222,10 @@
         <v>24117</v>
       </c>
       <c r="B342" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C342" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -8151,10 +8233,10 @@
         <v>24118</v>
       </c>
       <c r="B343" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C343" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -8162,10 +8244,10 @@
         <v>24119</v>
       </c>
       <c r="B344" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C344" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -8173,10 +8255,10 @@
         <v>24120</v>
       </c>
       <c r="B345" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C345" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -8184,10 +8266,10 @@
         <v>24121</v>
       </c>
       <c r="B346" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C346" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -8195,10 +8277,10 @@
         <v>24122</v>
       </c>
       <c r="B347" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C347" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -8206,10 +8288,10 @@
         <v>30000</v>
       </c>
       <c r="B348" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C348" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -8217,10 +8299,10 @@
         <v>30010</v>
       </c>
       <c r="B349" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C349" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -8228,10 +8310,10 @@
         <v>30020</v>
       </c>
       <c r="B350" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C350" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -8239,10 +8321,10 @@
         <v>30030</v>
       </c>
       <c r="B351" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C351" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -8250,10 +8332,10 @@
         <v>30040</v>
       </c>
       <c r="B352" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C352" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -8261,10 +8343,10 @@
         <v>31010</v>
       </c>
       <c r="B353" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C353" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -8272,10 +8354,10 @@
         <v>31020</v>
       </c>
       <c r="B354" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C354" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -8283,13 +8365,13 @@
         <v>102000</v>
       </c>
       <c r="B355" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C355" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D355" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -8297,10 +8379,10 @@
         <v>102010</v>
       </c>
       <c r="B356" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C356" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -8308,10 +8390,10 @@
         <v>102020</v>
       </c>
       <c r="B357" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C357" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -8319,10 +8401,10 @@
         <v>102030</v>
       </c>
       <c r="B358" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C358" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -8330,13 +8412,13 @@
         <v>113000</v>
       </c>
       <c r="B359" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C359" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D359" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -8344,10 +8426,10 @@
         <v>113010</v>
       </c>
       <c r="B360" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C360" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -8355,10 +8437,10 @@
         <v>113020</v>
       </c>
       <c r="B361" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C361" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -8366,10 +8448,10 @@
         <v>113030</v>
       </c>
       <c r="B362" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C362" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -8377,10 +8459,10 @@
         <v>113040</v>
       </c>
       <c r="B363" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C363" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -8388,13 +8470,13 @@
         <v>121010</v>
       </c>
       <c r="B364" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C364" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D364" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -8402,10 +8484,10 @@
         <v>121011</v>
       </c>
       <c r="B365" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C365" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -8413,10 +8495,10 @@
         <v>121012</v>
       </c>
       <c r="B366" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C366" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -8424,10 +8506,10 @@
         <v>121013</v>
       </c>
       <c r="B367" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C367" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -8435,10 +8517,10 @@
         <v>121014</v>
       </c>
       <c r="B368" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C368" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -8446,10 +8528,10 @@
         <v>121015</v>
       </c>
       <c r="B369" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C369" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -8457,10 +8539,10 @@
         <v>121016</v>
       </c>
       <c r="B370" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C370" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -8468,10 +8550,10 @@
         <v>121017</v>
       </c>
       <c r="B371" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C371" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -8479,10 +8561,10 @@
         <v>121018</v>
       </c>
       <c r="B372" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C372" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -8490,10 +8572,10 @@
         <v>121019</v>
       </c>
       <c r="B373" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C373" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -8501,10 +8583,10 @@
         <v>121020</v>
       </c>
       <c r="B374" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C374" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -8512,10 +8594,10 @@
         <v>121030</v>
       </c>
       <c r="B375" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C375" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67BE7EE-D63E-4BB9-AC2A-0F2281A726AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AD7380-589C-4973-96EA-D724AE5B2BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="478">
   <si>
     <t>Id</t>
   </si>
@@ -1025,40 +1025,19 @@
     <t>ボス</t>
   </si>
   <si>
-    <t>ステージを探索します</t>
-  </si>
-  <si>
     <t>Tactics</t>
   </si>
   <si>
     <t>編成</t>
   </si>
   <si>
-    <t>Numinosを使用してキャラのLvをアップします</t>
-  </si>
-  <si>
-    <t>キャラに魔法を習得させます</t>
-  </si>
-  <si>
     <t>キャラ</t>
   </si>
   <si>
-    <t>キャラのステータスや魔法を確認します</t>
-  </si>
-  <si>
-    <t>Numinosを使用してキャラを回復します</t>
-  </si>
-  <si>
     <t>ステージ</t>
   </si>
   <si>
-    <t>ステージの構成を確認します</t>
-  </si>
-  <si>
     <t>セーブ</t>
-  </si>
-  <si>
-    <t>ゲームの進行状態を保存します</t>
   </si>
   <si>
     <t>バトル評価値</t>
@@ -1533,6 +1512,25 @@
     <t>部隊</t>
     <rPh sb="0" eb="2">
       <t>ブタイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Save</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>セーブ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Conquer</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>制圧</t>
+    <rPh sb="0" eb="2">
+      <t>セイアツ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1913,7 +1911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -1935,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C2">
         <v>19010</v>
@@ -1946,7 +1944,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C3">
         <v>19020</v>
@@ -1957,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C4">
         <v>19030</v>
@@ -1968,7 +1966,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C5">
         <v>19040</v>
@@ -1979,7 +1977,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C6">
         <v>19050</v>
@@ -1990,7 +1988,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C7">
         <v>19060</v>
@@ -2001,10 +1999,32 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C8">
         <v>19070</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C9">
+        <v>19080</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C10">
+        <v>19090</v>
       </c>
     </row>
   </sheetData>
@@ -2060,7 +2080,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -4336,7 +4356,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G377"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -6252,7 +6272,7 @@
         <v>13010</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C168" t="s">
         <v>99</v>
@@ -6318,7 +6338,7 @@
         <v>13210</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C174" t="s">
         <v>99</v>
@@ -6329,7 +6349,7 @@
         <v>13220</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C175" t="s">
         <v>99</v>
@@ -6340,7 +6360,7 @@
         <v>13230</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="C176" t="s">
         <v>99</v>
@@ -6351,7 +6371,7 @@
         <v>13240</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C177" t="s">
         <v>99</v>
@@ -7099,13 +7119,13 @@
         <v>19010</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C242" t="s">
+        <v>99</v>
+      </c>
+      <c r="D242" t="s">
         <v>327</v>
-      </c>
-      <c r="D242" t="s">
-        <v>328</v>
       </c>
       <c r="G242" s="1"/>
     </row>
@@ -7114,10 +7134,10 @@
         <v>19011</v>
       </c>
       <c r="B243" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C243" t="s">
-        <v>327</v>
+        <v>99</v>
       </c>
       <c r="G243" s="1"/>
     </row>
@@ -7126,10 +7146,10 @@
         <v>19020</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C244" t="s">
-        <v>330</v>
+        <v>99</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7137,10 +7157,10 @@
         <v>19030</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C245" t="s">
-        <v>331</v>
+        <v>99</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7148,10 +7168,10 @@
         <v>19040</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="C246" t="s">
-        <v>333</v>
+        <v>99</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7159,10 +7179,10 @@
         <v>19050</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="C247" t="s">
-        <v>334</v>
+        <v>99</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7170,10 +7190,10 @@
         <v>19060</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C248" t="s">
-        <v>336</v>
+        <v>99</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7181,18 +7201,18 @@
         <v>19070</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C249" t="s">
-        <v>338</v>
+        <v>99</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250">
-        <v>19100</v>
-      </c>
-      <c r="B250" t="s">
-        <v>339</v>
+        <v>19080</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>475</v>
       </c>
       <c r="C250" t="s">
         <v>99</v>
@@ -7200,10 +7220,10 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251">
-        <v>19110</v>
-      </c>
-      <c r="B251" t="s">
-        <v>340</v>
+        <v>19090</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="C251" t="s">
         <v>99</v>
@@ -7211,10 +7231,10 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252">
-        <v>19200</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>341</v>
+        <v>19100</v>
+      </c>
+      <c r="B252" t="s">
+        <v>332</v>
       </c>
       <c r="C252" t="s">
         <v>99</v>
@@ -7222,10 +7242,10 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253">
-        <v>19210</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>342</v>
+        <v>19110</v>
+      </c>
+      <c r="B253" t="s">
+        <v>333</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7233,10 +7253,10 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254">
-        <v>19220</v>
+        <v>19200</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7244,10 +7264,10 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255">
-        <v>19230</v>
+        <v>19210</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7255,10 +7275,10 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256">
-        <v>19240</v>
+        <v>19220</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7266,10 +7286,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19250</v>
+        <v>19230</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7277,10 +7297,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19260</v>
+        <v>19240</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7288,10 +7308,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19270</v>
+        <v>19250</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7299,10 +7319,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19280</v>
+        <v>19260</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7310,21 +7330,21 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19300</v>
-      </c>
-      <c r="B261" t="s">
-        <v>350</v>
+        <v>19270</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="26">
+    <row r="262" spans="1:3">
       <c r="A262">
-        <v>19310</v>
+        <v>19280</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7332,21 +7352,21 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19320</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>352</v>
+        <v>19300</v>
+      </c>
+      <c r="B263" t="s">
+        <v>343</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" ht="26">
       <c r="A264">
-        <v>19330</v>
-      </c>
-      <c r="B264" t="s">
-        <v>353</v>
+        <v>19310</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C264" t="s">
         <v>99</v>
@@ -7354,10 +7374,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19340</v>
-      </c>
-      <c r="B265" t="s">
-        <v>354</v>
+        <v>19320</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C265" t="s">
         <v>99</v>
@@ -7365,10 +7385,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19350</v>
+        <v>19330</v>
       </c>
       <c r="B266" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C266" t="s">
         <v>99</v>
@@ -7376,10 +7396,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19360</v>
+        <v>19340</v>
       </c>
       <c r="B267" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C267" t="s">
         <v>99</v>
@@ -7387,10 +7407,10 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19400</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>357</v>
+        <v>19350</v>
+      </c>
+      <c r="B268" t="s">
+        <v>348</v>
       </c>
       <c r="C268" t="s">
         <v>99</v>
@@ -7398,10 +7418,10 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19401</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>358</v>
+        <v>19360</v>
+      </c>
+      <c r="B269" t="s">
+        <v>349</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7409,10 +7429,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19410</v>
+        <v>19400</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7420,10 +7440,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19420</v>
+        <v>19401</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7431,10 +7451,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19500</v>
-      </c>
-      <c r="B272" t="s">
-        <v>361</v>
+        <v>19410</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7442,10 +7462,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19510</v>
+        <v>19420</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7453,10 +7473,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19520</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>362</v>
+        <v>19500</v>
+      </c>
+      <c r="B274" t="s">
+        <v>354</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7464,10 +7484,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19600</v>
+        <v>19510</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7475,10 +7495,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19601</v>
+        <v>19520</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7486,10 +7506,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19602</v>
+        <v>19600</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7497,10 +7517,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19603</v>
+        <v>19601</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7508,60 +7528,58 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
+        <v>19602</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C279" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280">
+        <v>19603</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C280" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281">
         <v>19604</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C279" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="14">
-      <c r="A280">
-        <v>19611</v>
-      </c>
-      <c r="B280" t="s">
-        <v>368</v>
-      </c>
-      <c r="C280" t="s">
-        <v>99</v>
-      </c>
-      <c r="D280" t="s">
-        <v>369</v>
-      </c>
-      <c r="G280" s="1"/>
-    </row>
-    <row r="281" spans="1:7" ht="14">
-      <c r="A281">
-        <v>19612</v>
-      </c>
-      <c r="B281" t="s">
-        <v>370</v>
+      <c r="B281" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
       </c>
-      <c r="G281" s="1"/>
     </row>
     <row r="282" spans="1:7" ht="14">
       <c r="A282">
-        <v>19613</v>
+        <v>19611</v>
       </c>
       <c r="B282" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C282" t="s">
         <v>99</v>
+      </c>
+      <c r="D282" t="s">
+        <v>362</v>
       </c>
       <c r="G282" s="1"/>
     </row>
     <row r="283" spans="1:7" ht="14">
       <c r="A283">
-        <v>19614</v>
+        <v>19612</v>
       </c>
       <c r="B283" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C283" t="s">
         <v>99</v>
@@ -7570,10 +7588,10 @@
     </row>
     <row r="284" spans="1:7" ht="14">
       <c r="A284">
-        <v>19615</v>
+        <v>19613</v>
       </c>
       <c r="B284" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C284" t="s">
         <v>99</v>
@@ -7582,10 +7600,10 @@
     </row>
     <row r="285" spans="1:7" ht="14">
       <c r="A285">
-        <v>19616</v>
+        <v>19614</v>
       </c>
       <c r="B285" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C285" t="s">
         <v>99</v>
@@ -7594,10 +7612,10 @@
     </row>
     <row r="286" spans="1:7" ht="14">
       <c r="A286">
-        <v>19617</v>
+        <v>19615</v>
       </c>
       <c r="B286" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
@@ -7606,10 +7624,10 @@
     </row>
     <row r="287" spans="1:7" ht="14">
       <c r="A287">
-        <v>19618</v>
+        <v>19616</v>
       </c>
       <c r="B287" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
@@ -7618,193 +7636,195 @@
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
+        <v>19617</v>
+      </c>
+      <c r="B288" t="s">
+        <v>368</v>
+      </c>
+      <c r="C288" t="s">
+        <v>99</v>
+      </c>
+      <c r="G288" s="1"/>
+    </row>
+    <row r="289" spans="1:7" ht="14">
+      <c r="A289">
+        <v>19618</v>
+      </c>
+      <c r="B289" t="s">
+        <v>369</v>
+      </c>
+      <c r="C289" t="s">
+        <v>99</v>
+      </c>
+      <c r="G289" s="1"/>
+    </row>
+    <row r="290" spans="1:7" ht="14">
+      <c r="A290">
         <v>19619</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B290" t="s">
+        <v>370</v>
+      </c>
+      <c r="C290" t="s">
+        <v>99</v>
+      </c>
+      <c r="G290" s="1"/>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291">
+        <v>19631</v>
+      </c>
+      <c r="B291" t="s">
+        <v>371</v>
+      </c>
+      <c r="C291" t="s">
+        <v>99</v>
+      </c>
+      <c r="D291" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292">
+        <v>19632</v>
+      </c>
+      <c r="B292" t="s">
+        <v>373</v>
+      </c>
+      <c r="C292" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293">
+        <v>19633</v>
+      </c>
+      <c r="B293" t="s">
+        <v>374</v>
+      </c>
+      <c r="C293" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294">
+        <v>19634</v>
+      </c>
+      <c r="B294" t="s">
+        <v>375</v>
+      </c>
+      <c r="C294" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295">
+        <v>19700</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C295" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296">
+        <v>19710</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C296" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297">
+        <v>19720</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C288" t="s">
-        <v>99</v>
-      </c>
-      <c r="G288" s="1"/>
-    </row>
-    <row r="289" spans="1:4">
-      <c r="A289">
-        <v>19631</v>
-      </c>
-      <c r="B289" t="s">
+      <c r="C297" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298">
+        <v>19730</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C289" t="s">
-        <v>99</v>
-      </c>
-      <c r="D289" t="s">
+      <c r="C298" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299">
+        <v>19740</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="290" spans="1:4">
-      <c r="A290">
-        <v>19632</v>
-      </c>
-      <c r="B290" t="s">
+      <c r="C299" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300">
+        <v>19800</v>
+      </c>
+      <c r="B300" t="s">
         <v>380</v>
       </c>
-      <c r="C290" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4">
-      <c r="A291">
-        <v>19633</v>
-      </c>
-      <c r="B291" t="s">
+      <c r="C300" t="s">
         <v>381</v>
       </c>
-      <c r="C291" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
-      <c r="A292">
-        <v>19634</v>
-      </c>
-      <c r="B292" t="s">
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301">
+        <v>19810</v>
+      </c>
+      <c r="B301" t="s">
         <v>382</v>
       </c>
-      <c r="C292" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
-      <c r="A293">
-        <v>19700</v>
-      </c>
-      <c r="B293" s="2" t="s">
+      <c r="C301" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302">
+        <v>20010</v>
+      </c>
+      <c r="B302" t="s">
         <v>383</v>
       </c>
-      <c r="C293" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
-      <c r="A294">
-        <v>19710</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C294" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
-      <c r="A295">
-        <v>19720</v>
-      </c>
-      <c r="B295" s="2" t="s">
+      <c r="C302" t="s">
+        <v>99</v>
+      </c>
+      <c r="D302" t="s">
         <v>384</v>
       </c>
-      <c r="C295" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
-      <c r="A296">
-        <v>19730</v>
-      </c>
-      <c r="B296" s="2" t="s">
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303">
+        <v>20020</v>
+      </c>
+      <c r="B303" t="s">
         <v>385</v>
       </c>
-      <c r="C296" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4">
-      <c r="A297">
-        <v>19740</v>
-      </c>
-      <c r="B297" s="2" t="s">
+      <c r="C303" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304">
+        <v>20030</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="C297" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4">
-      <c r="A298">
-        <v>19800</v>
-      </c>
-      <c r="B298" t="s">
-        <v>387</v>
-      </c>
-      <c r="C298" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
-      <c r="A299">
-        <v>19810</v>
-      </c>
-      <c r="B299" t="s">
-        <v>389</v>
-      </c>
-      <c r="C299" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4">
-      <c r="A300">
-        <v>20010</v>
-      </c>
-      <c r="B300" t="s">
-        <v>390</v>
-      </c>
-      <c r="C300" t="s">
-        <v>99</v>
-      </c>
-      <c r="D300" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4">
-      <c r="A301">
-        <v>20020</v>
-      </c>
-      <c r="B301" t="s">
-        <v>392</v>
-      </c>
-      <c r="C301" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
-      <c r="A302">
-        <v>20030</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C302" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
-      <c r="A303">
-        <v>20040</v>
-      </c>
-      <c r="B303" t="s">
-        <v>394</v>
-      </c>
-      <c r="C303" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4">
-      <c r="A304">
-        <v>20050</v>
-      </c>
-      <c r="B304" t="s">
-        <v>395</v>
       </c>
       <c r="C304" t="s">
         <v>99</v>
@@ -7812,10 +7832,10 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20100</v>
+        <v>20040</v>
       </c>
       <c r="B305" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C305" t="s">
         <v>99</v>
@@ -7823,10 +7843,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20110</v>
+        <v>20050</v>
       </c>
       <c r="B306" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C306" t="s">
         <v>99</v>
@@ -7834,10 +7854,10 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20120</v>
+        <v>20100</v>
       </c>
       <c r="B307" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
@@ -7845,10 +7865,10 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20200</v>
+        <v>20110</v>
       </c>
       <c r="B308" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
@@ -7856,10 +7876,10 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20201</v>
+        <v>20120</v>
       </c>
       <c r="B309" t="s">
-        <v>315</v>
+        <v>391</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -7867,10 +7887,10 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20210</v>
+        <v>20200</v>
       </c>
       <c r="B310" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -7878,10 +7898,10 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20220</v>
+        <v>20201</v>
       </c>
       <c r="B311" t="s">
-        <v>401</v>
+        <v>315</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -7889,10 +7909,10 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20230</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>402</v>
+        <v>20210</v>
+      </c>
+      <c r="B312" t="s">
+        <v>393</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -7900,10 +7920,10 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20240</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>403</v>
+        <v>20220</v>
+      </c>
+      <c r="B313" t="s">
+        <v>394</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -7911,10 +7931,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20250</v>
+        <v>20230</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -7922,10 +7942,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20260</v>
-      </c>
-      <c r="B315" t="s">
-        <v>405</v>
+        <v>20240</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>396</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -7933,10 +7953,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20270</v>
-      </c>
-      <c r="B316" t="s">
-        <v>406</v>
+        <v>20250</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -7944,10 +7964,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>20280</v>
+        <v>20260</v>
       </c>
       <c r="B317" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -7955,10 +7975,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>20290</v>
+        <v>20270</v>
       </c>
       <c r="B318" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -7966,10 +7986,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>20300</v>
+        <v>20280</v>
       </c>
       <c r="B319" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -7977,10 +7997,10 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>20310</v>
+        <v>20290</v>
       </c>
       <c r="B320" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -7988,10 +8008,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20320</v>
+        <v>20300</v>
       </c>
       <c r="B321" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -7999,10 +8019,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20330</v>
+        <v>20310</v>
       </c>
       <c r="B322" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8010,10 +8030,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20340</v>
+        <v>20320</v>
       </c>
       <c r="B323" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8021,10 +8041,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20350</v>
+        <v>20330</v>
       </c>
       <c r="B324" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8032,10 +8052,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>23010</v>
+        <v>20340</v>
       </c>
       <c r="B325" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8043,10 +8063,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>23020</v>
+        <v>20350</v>
       </c>
       <c r="B326" t="s">
-        <v>103</v>
+        <v>407</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8054,10 +8074,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>23030</v>
+        <v>23010</v>
       </c>
       <c r="B327" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8065,10 +8085,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>23031</v>
+        <v>23020</v>
       </c>
       <c r="B328" t="s">
-        <v>417</v>
+        <v>103</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8076,10 +8096,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>23032</v>
+        <v>23030</v>
       </c>
       <c r="B329" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8087,10 +8107,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>23040</v>
+        <v>23031</v>
       </c>
       <c r="B330" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8098,10 +8118,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>24010</v>
+        <v>23032</v>
       </c>
       <c r="B331" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8109,10 +8129,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>24020</v>
+        <v>23040</v>
       </c>
       <c r="B332" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8120,10 +8140,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24030</v>
+        <v>24010</v>
       </c>
       <c r="B333" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8131,10 +8151,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24040</v>
+        <v>24020</v>
       </c>
       <c r="B334" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8142,10 +8162,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24110</v>
+        <v>24030</v>
       </c>
       <c r="B335" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8153,10 +8173,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24111</v>
+        <v>24040</v>
       </c>
       <c r="B336" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8164,10 +8184,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24112</v>
+        <v>24110</v>
       </c>
       <c r="B337" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8175,10 +8195,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24113</v>
+        <v>24111</v>
       </c>
       <c r="B338" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8186,10 +8206,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24114</v>
+        <v>24112</v>
       </c>
       <c r="B339" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8197,10 +8217,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24115</v>
+        <v>24113</v>
       </c>
       <c r="B340" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8208,10 +8228,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24116</v>
+        <v>24114</v>
       </c>
       <c r="B341" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8219,10 +8239,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24117</v>
+        <v>24115</v>
       </c>
       <c r="B342" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8230,10 +8250,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24118</v>
+        <v>24116</v>
       </c>
       <c r="B343" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8241,10 +8261,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24119</v>
+        <v>24117</v>
       </c>
       <c r="B344" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8252,10 +8272,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24120</v>
+        <v>24118</v>
       </c>
       <c r="B345" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8263,10 +8283,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24121</v>
+        <v>24119</v>
       </c>
       <c r="B346" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8274,10 +8294,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24122</v>
+        <v>24120</v>
       </c>
       <c r="B347" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8285,10 +8305,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>30000</v>
+        <v>24121</v>
       </c>
       <c r="B348" t="s">
-        <v>329</v>
+        <v>428</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8296,10 +8316,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>30010</v>
+        <v>24122</v>
       </c>
       <c r="B349" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8307,10 +8327,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>30020</v>
+        <v>30000</v>
       </c>
       <c r="B350" t="s">
-        <v>101</v>
+        <v>328</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8318,10 +8338,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>30030</v>
+        <v>30010</v>
       </c>
       <c r="B351" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8329,10 +8349,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>30040</v>
+        <v>30020</v>
       </c>
       <c r="B352" t="s">
-        <v>438</v>
+        <v>101</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8340,10 +8360,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>31010</v>
+        <v>30030</v>
       </c>
       <c r="B353" t="s">
-        <v>439</v>
+        <v>124</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8351,10 +8371,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>31020</v>
+        <v>30040</v>
       </c>
       <c r="B354" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8362,24 +8382,21 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>102000</v>
+        <v>31010</v>
       </c>
       <c r="B355" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
-      </c>
-      <c r="D355" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>102010</v>
+        <v>31020</v>
       </c>
       <c r="B356" t="s">
-        <v>335</v>
+        <v>433</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8387,21 +8404,24 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>102020</v>
+        <v>102000</v>
       </c>
       <c r="B357" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
+      </c>
+      <c r="D357" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>102030</v>
+        <v>102010</v>
       </c>
       <c r="B358" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
@@ -8409,24 +8429,21 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>113000</v>
+        <v>102020</v>
       </c>
       <c r="B359" t="s">
-        <v>443</v>
+        <v>361</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
-      </c>
-      <c r="D359" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>113010</v>
+        <v>102030</v>
       </c>
       <c r="B360" t="s">
-        <v>445</v>
+        <v>329</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
@@ -8434,21 +8451,24 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>113020</v>
+        <v>113000</v>
       </c>
       <c r="B361" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
+      </c>
+      <c r="D361" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>113030</v>
+        <v>113010</v>
       </c>
       <c r="B362" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
@@ -8456,10 +8476,10 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>113040</v>
+        <v>113020</v>
       </c>
       <c r="B363" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
@@ -8467,24 +8487,21 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>121010</v>
+        <v>113030</v>
       </c>
       <c r="B364" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
-      </c>
-      <c r="D364" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>121011</v>
+        <v>113040</v>
       </c>
       <c r="B365" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
@@ -8492,21 +8509,24 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>121012</v>
+        <v>121010</v>
       </c>
       <c r="B366" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
+      </c>
+      <c r="D366" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>121013</v>
+        <v>121011</v>
       </c>
       <c r="B367" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
@@ -8514,10 +8534,10 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>121014</v>
+        <v>121012</v>
       </c>
       <c r="B368" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
@@ -8525,10 +8545,10 @@
     </row>
     <row r="369" spans="1:3">
       <c r="A369">
-        <v>121015</v>
+        <v>121013</v>
       </c>
       <c r="B369" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
@@ -8536,10 +8556,10 @@
     </row>
     <row r="370" spans="1:3">
       <c r="A370">
-        <v>121016</v>
+        <v>121014</v>
       </c>
       <c r="B370" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
@@ -8547,10 +8567,10 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371">
-        <v>121017</v>
+        <v>121015</v>
       </c>
       <c r="B371" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
@@ -8558,10 +8578,10 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372">
-        <v>121018</v>
+        <v>121016</v>
       </c>
       <c r="B372" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
@@ -8569,10 +8589,10 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373">
-        <v>121019</v>
+        <v>121017</v>
       </c>
       <c r="B373" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8580,10 +8600,10 @@
     </row>
     <row r="374" spans="1:3">
       <c r="A374">
-        <v>121020</v>
+        <v>121018</v>
       </c>
       <c r="B374" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8591,12 +8611,34 @@
     </row>
     <row r="375" spans="1:3">
       <c r="A375">
+        <v>121019</v>
+      </c>
+      <c r="B375" t="s">
+        <v>452</v>
+      </c>
+      <c r="C375" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376">
+        <v>121020</v>
+      </c>
+      <c r="B376" t="s">
+        <v>453</v>
+      </c>
+      <c r="C376" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377">
         <v>121030</v>
       </c>
-      <c r="B375" t="s">
-        <v>461</v>
-      </c>
-      <c r="C375" t="s">
+      <c r="B377" t="s">
+        <v>454</v>
+      </c>
+      <c r="C377" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AD7380-589C-4973-96EA-D724AE5B2BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B9A47A-D09C-4092-B73E-4F75C5DBBEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="479">
   <si>
     <t>Id</t>
   </si>
@@ -1531,6 +1531,22 @@
     <t>制圧</t>
     <rPh sb="0" eb="2">
       <t>セイアツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>誰も至ることのない光の先へ</t>
+    <rPh sb="0" eb="1">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サキ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1591,7 +1607,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1606,6 +1622,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6285,6 +6304,9 @@
       <c r="A169">
         <v>13020</v>
       </c>
+      <c r="B169" s="5" t="s">
+        <v>478</v>
+      </c>
       <c r="C169" t="s">
         <v>99</v>
       </c>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B9A47A-D09C-4092-B73E-4F75C5DBBEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475D8ECF-BCDA-4197-98E4-E5A8E0982000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="481">
   <si>
     <t>Id</t>
   </si>
@@ -1548,6 +1548,17 @@
     <rPh sb="11" eb="12">
       <t>サキ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>編成</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>UnitEdit</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1930,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -1955,7 +1966,7 @@
         <v>461</v>
       </c>
       <c r="C2">
-        <v>19010</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1966,7 +1977,7 @@
         <v>462</v>
       </c>
       <c r="C3">
-        <v>19020</v>
+        <v>19001</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1977,7 +1988,7 @@
         <v>463</v>
       </c>
       <c r="C4">
-        <v>19030</v>
+        <v>19002</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1988,7 +1999,7 @@
         <v>464</v>
       </c>
       <c r="C5">
-        <v>19040</v>
+        <v>19003</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1999,7 +2010,7 @@
         <v>465</v>
       </c>
       <c r="C6">
-        <v>19050</v>
+        <v>19004</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2010,7 +2021,7 @@
         <v>466</v>
       </c>
       <c r="C7">
-        <v>19060</v>
+        <v>19005</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2021,7 +2032,7 @@
         <v>467</v>
       </c>
       <c r="C8">
-        <v>19070</v>
+        <v>19006</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2032,7 +2043,7 @@
         <v>474</v>
       </c>
       <c r="C9">
-        <v>19080</v>
+        <v>19007</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2043,7 +2054,18 @@
         <v>476</v>
       </c>
       <c r="C10">
-        <v>19090</v>
+        <v>19008</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C11">
+        <v>19009</v>
       </c>
     </row>
   </sheetData>
@@ -7138,7 +7160,7 @@
     </row>
     <row r="242" spans="1:7" ht="14">
       <c r="A242">
-        <v>19010</v>
+        <v>19000</v>
       </c>
       <c r="B242" s="4" t="s">
         <v>468</v>
@@ -7151,24 +7173,23 @@
       </c>
       <c r="G242" s="1"/>
     </row>
-    <row r="243" spans="1:7" ht="14">
+    <row r="243" spans="1:7">
       <c r="A243">
-        <v>19011</v>
-      </c>
-      <c r="B243" t="s">
-        <v>328</v>
+        <v>19001</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>469</v>
       </c>
       <c r="C243" t="s">
         <v>99</v>
       </c>
-      <c r="G243" s="1"/>
     </row>
     <row r="244" spans="1:7">
       <c r="A244">
-        <v>19020</v>
+        <v>19002</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C244" t="s">
         <v>99</v>
@@ -7176,10 +7197,10 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245">
-        <v>19030</v>
+        <v>19003</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C245" t="s">
         <v>99</v>
@@ -7187,7 +7208,7 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246">
-        <v>19040</v>
+        <v>19004</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>471</v>
@@ -7198,10 +7219,10 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247">
-        <v>19050</v>
+        <v>19005</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C247" t="s">
         <v>99</v>
@@ -7209,10 +7230,10 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248">
-        <v>19060</v>
+        <v>19006</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C248" t="s">
         <v>99</v>
@@ -7220,10 +7241,10 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249">
-        <v>19070</v>
+        <v>19007</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C249" t="s">
         <v>99</v>
@@ -7231,10 +7252,10 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250">
-        <v>19080</v>
+        <v>19008</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C250" t="s">
         <v>99</v>
@@ -7242,10 +7263,10 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251">
-        <v>19090</v>
+        <v>19009</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C251" t="s">
         <v>99</v>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475D8ECF-BCDA-4197-98E4-E5A8E0982000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EFCEE0-C1EB-43BE-923D-3D4D38C19FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="483">
   <si>
     <t>Id</t>
   </si>
@@ -1559,6 +1559,17 @@
   </si>
   <si>
     <t>UnitEdit</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Return</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>帰還</t>
+    <rPh sb="0" eb="2">
+      <t>キカン</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1941,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -2066,6 +2077,17 @@
       </c>
       <c r="C11">
         <v>19009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C12">
+        <v>19010</v>
       </c>
     </row>
   </sheetData>
@@ -4397,7 +4419,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G377"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -7274,10 +7296,10 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252">
-        <v>19100</v>
-      </c>
-      <c r="B252" t="s">
-        <v>332</v>
+        <v>19010</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>482</v>
       </c>
       <c r="C252" t="s">
         <v>99</v>
@@ -7285,10 +7307,10 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B253" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7296,10 +7318,10 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254">
-        <v>19200</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>334</v>
+        <v>19110</v>
+      </c>
+      <c r="B254" t="s">
+        <v>333</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7307,10 +7329,10 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7318,10 +7340,10 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7329,10 +7351,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7340,10 +7362,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7351,10 +7373,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19250</v>
+        <v>19240</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7362,10 +7384,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7373,10 +7395,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7384,10 +7406,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7395,32 +7417,32 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
+        <v>19280</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C263" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264">
         <v>19300</v>
       </c>
-      <c r="B263" t="s">
+      <c r="B264" t="s">
         <v>343</v>
       </c>
-      <c r="C263" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" ht="26">
-      <c r="A264">
+      <c r="C264" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="26">
+      <c r="A265">
         <v>19310</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="B265" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="C264" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3">
-      <c r="A265">
-        <v>19320</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C265" t="s">
         <v>99</v>
@@ -7428,10 +7450,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19330</v>
-      </c>
-      <c r="B266" t="s">
-        <v>346</v>
+        <v>19320</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C266" t="s">
         <v>99</v>
@@ -7439,10 +7461,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B267" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C267" t="s">
         <v>99</v>
@@ -7450,10 +7472,10 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B268" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C268" t="s">
         <v>99</v>
@@ -7461,10 +7483,10 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B269" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7472,10 +7494,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19400</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>350</v>
+        <v>19360</v>
+      </c>
+      <c r="B270" t="s">
+        <v>349</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7483,10 +7505,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7494,10 +7516,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7505,10 +7527,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7516,10 +7538,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19500</v>
-      </c>
-      <c r="B274" t="s">
-        <v>354</v>
+        <v>19420</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7527,10 +7549,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19510</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>340</v>
+        <v>19500</v>
+      </c>
+      <c r="B275" t="s">
+        <v>354</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7538,10 +7560,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19520</v>
+        <v>19510</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7549,10 +7571,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7560,10 +7582,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7571,10 +7593,10 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7582,10 +7604,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7593,48 +7615,47 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
+        <v>19603</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C281" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282">
         <v>19604</v>
       </c>
-      <c r="B281" s="2" t="s">
+      <c r="B282" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C281" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="14">
-      <c r="A282">
-        <v>19611</v>
-      </c>
-      <c r="B282" t="s">
-        <v>361</v>
-      </c>
       <c r="C282" t="s">
         <v>99</v>
       </c>
-      <c r="D282" t="s">
-        <v>362</v>
-      </c>
-      <c r="G282" s="1"/>
     </row>
     <row r="283" spans="1:7" ht="14">
       <c r="A283">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B283" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C283" t="s">
         <v>99</v>
+      </c>
+      <c r="D283" t="s">
+        <v>362</v>
       </c>
       <c r="G283" s="1"/>
     </row>
     <row r="284" spans="1:7" ht="14">
       <c r="A284">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B284" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C284" t="s">
         <v>99</v>
@@ -7643,10 +7664,10 @@
     </row>
     <row r="285" spans="1:7" ht="14">
       <c r="A285">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B285" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C285" t="s">
         <v>99</v>
@@ -7655,10 +7676,10 @@
     </row>
     <row r="286" spans="1:7" ht="14">
       <c r="A286">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B286" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
@@ -7667,10 +7688,10 @@
     </row>
     <row r="287" spans="1:7" ht="14">
       <c r="A287">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B287" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
@@ -7679,10 +7700,10 @@
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B288" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
@@ -7691,10 +7712,10 @@
     </row>
     <row r="289" spans="1:7" ht="14">
       <c r="A289">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B289" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7703,47 +7724,48 @@
     </row>
     <row r="290" spans="1:7" ht="14">
       <c r="A290">
+        <v>19618</v>
+      </c>
+      <c r="B290" t="s">
+        <v>369</v>
+      </c>
+      <c r="C290" t="s">
+        <v>99</v>
+      </c>
+      <c r="G290" s="1"/>
+    </row>
+    <row r="291" spans="1:7" ht="14">
+      <c r="A291">
         <v>19619</v>
       </c>
-      <c r="B290" t="s">
+      <c r="B291" t="s">
         <v>370</v>
       </c>
-      <c r="C290" t="s">
-        <v>99</v>
-      </c>
-      <c r="G290" s="1"/>
-    </row>
-    <row r="291" spans="1:7">
-      <c r="A291">
-        <v>19631</v>
-      </c>
-      <c r="B291" t="s">
-        <v>371</v>
-      </c>
       <c r="C291" t="s">
         <v>99</v>
       </c>
-      <c r="D291" t="s">
-        <v>372</v>
-      </c>
+      <c r="G291" s="1"/>
     </row>
     <row r="292" spans="1:7">
       <c r="A292">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="B292" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C292" t="s">
         <v>99</v>
+      </c>
+      <c r="D292" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B293" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C293" t="s">
         <v>99</v>
@@ -7751,10 +7773,10 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B294" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C294" t="s">
         <v>99</v>
@@ -7762,10 +7784,10 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295">
-        <v>19700</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>376</v>
+        <v>19634</v>
+      </c>
+      <c r="B295" t="s">
+        <v>375</v>
       </c>
       <c r="C295" t="s">
         <v>99</v>
@@ -7773,10 +7795,10 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="C296" t="s">
         <v>99</v>
@@ -7784,10 +7806,10 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
@@ -7795,10 +7817,10 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7806,10 +7828,10 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7817,57 +7839,57 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300">
-        <v>19800</v>
-      </c>
-      <c r="B300" t="s">
-        <v>380</v>
+        <v>19740</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="C300" t="s">
-        <v>381</v>
+        <v>99</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B301" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C301" t="s">
-        <v>99</v>
+        <v>381</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302">
-        <v>20010</v>
+        <v>19810</v>
       </c>
       <c r="B302" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C302" t="s">
         <v>99</v>
-      </c>
-      <c r="D302" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B303" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C303" t="s">
         <v>99</v>
+      </c>
+      <c r="D303" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304">
-        <v>20030</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>386</v>
+        <v>20020</v>
+      </c>
+      <c r="B304" t="s">
+        <v>385</v>
       </c>
       <c r="C304" t="s">
         <v>99</v>
@@ -7875,10 +7897,10 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20040</v>
-      </c>
-      <c r="B305" t="s">
-        <v>387</v>
+        <v>20030</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="C305" t="s">
         <v>99</v>
@@ -7886,10 +7908,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B306" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C306" t="s">
         <v>99</v>
@@ -7897,10 +7919,10 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B307" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
@@ -7908,10 +7930,10 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B308" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
@@ -7919,10 +7941,10 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B309" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -7930,10 +7952,10 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B310" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -7941,10 +7963,10 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B311" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -7952,10 +7974,10 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B312" t="s">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -7963,10 +7985,10 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B313" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -7974,10 +7996,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20230</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>395</v>
+        <v>20220</v>
+      </c>
+      <c r="B314" t="s">
+        <v>394</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -7985,10 +8007,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -7996,10 +8018,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -8007,10 +8029,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>20260</v>
-      </c>
-      <c r="B317" t="s">
-        <v>398</v>
+        <v>20250</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -8018,10 +8040,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B318" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -8029,10 +8051,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B319" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -8040,10 +8062,10 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B320" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8051,10 +8073,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B321" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8062,10 +8084,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B322" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8073,10 +8095,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B323" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8084,10 +8106,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B324" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8095,10 +8117,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B325" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8106,10 +8128,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B326" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8117,10 +8139,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B327" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8128,10 +8150,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B328" t="s">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8139,10 +8161,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B329" t="s">
-        <v>409</v>
+        <v>103</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8150,10 +8172,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B330" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8161,10 +8183,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B331" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8172,10 +8194,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B332" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8183,10 +8205,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B333" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8194,10 +8216,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B334" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8205,10 +8227,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B335" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8216,10 +8238,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8227,10 +8249,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B337" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8238,10 +8260,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B338" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8249,10 +8271,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B339" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8260,10 +8282,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B340" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8271,10 +8293,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B341" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8282,10 +8304,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B342" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8293,10 +8315,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B343" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8304,10 +8326,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B344" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8315,10 +8337,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B345" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8326,10 +8348,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B346" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8337,10 +8359,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B347" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8348,10 +8370,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B348" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8359,10 +8381,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B349" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8370,10 +8392,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B350" t="s">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8381,10 +8403,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B351" t="s">
-        <v>430</v>
+        <v>328</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8392,10 +8414,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B352" t="s">
-        <v>101</v>
+        <v>430</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8403,10 +8425,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B353" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8414,10 +8436,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B354" t="s">
-        <v>431</v>
+        <v>124</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8425,10 +8447,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B355" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8436,10 +8458,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B356" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8447,35 +8469,35 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B357" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
-      </c>
-      <c r="D357" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>102010</v>
+        <v>102000</v>
       </c>
       <c r="B358" t="s">
-        <v>330</v>
+        <v>434</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
+      </c>
+      <c r="D358" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B359" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
@@ -8483,10 +8505,10 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>102030</v>
+        <v>102020</v>
       </c>
       <c r="B360" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
@@ -8494,35 +8516,35 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>113000</v>
+        <v>102030</v>
       </c>
       <c r="B361" t="s">
-        <v>436</v>
+        <v>329</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
-      </c>
-      <c r="D361" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>113010</v>
+        <v>113000</v>
       </c>
       <c r="B362" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
+      </c>
+      <c r="D362" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B363" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
@@ -8530,10 +8552,10 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B364" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
@@ -8541,10 +8563,10 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B365" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
@@ -8552,35 +8574,35 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B366" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
-      </c>
-      <c r="D366" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>121011</v>
+        <v>121010</v>
       </c>
       <c r="B367" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
+      </c>
+      <c r="D367" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B368" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
@@ -8588,10 +8610,10 @@
     </row>
     <row r="369" spans="1:3">
       <c r="A369">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B369" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
@@ -8599,10 +8621,10 @@
     </row>
     <row r="370" spans="1:3">
       <c r="A370">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B370" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
@@ -8610,10 +8632,10 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B371" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
@@ -8621,10 +8643,10 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B372" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
@@ -8632,10 +8654,10 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B373" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8643,10 +8665,10 @@
     </row>
     <row r="374" spans="1:3">
       <c r="A374">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B374" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8654,10 +8676,10 @@
     </row>
     <row r="375" spans="1:3">
       <c r="A375">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B375" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C375" t="s">
         <v>99</v>
@@ -8665,10 +8687,10 @@
     </row>
     <row r="376" spans="1:3">
       <c r="A376">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B376" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C376" t="s">
         <v>99</v>
@@ -8676,12 +8698,23 @@
     </row>
     <row r="377" spans="1:3">
       <c r="A377">
+        <v>121020</v>
+      </c>
+      <c r="B377" t="s">
+        <v>453</v>
+      </c>
+      <c r="C377" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378">
         <v>121030</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B378" t="s">
         <v>454</v>
       </c>
-      <c r="C377" t="s">
+      <c r="C378" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EFCEE0-C1EB-43BE-923D-3D4D38C19FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D391B133-EA34-4015-BCC9-A7F6FBAA6956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="GameDefine" sheetId="3" r:id="rId6"/>
     <sheet name="TextData" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="485">
   <si>
     <t>Id</t>
   </si>
@@ -1570,6 +1570,14 @@
     <rPh sb="0" eb="2">
       <t>キカン</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Event</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>イベント</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1952,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -2088,6 +2096,17 @@
       </c>
       <c r="C12">
         <v>19010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C13">
+        <v>19011</v>
       </c>
     </row>
   </sheetData>
@@ -4419,7 +4438,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G379"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -7307,10 +7326,10 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253">
-        <v>19100</v>
-      </c>
-      <c r="B253" t="s">
-        <v>332</v>
+        <v>19011</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>484</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7318,10 +7337,10 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B254" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7329,10 +7348,10 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255">
-        <v>19200</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>334</v>
+        <v>19110</v>
+      </c>
+      <c r="B255" t="s">
+        <v>333</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7340,10 +7359,10 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7351,10 +7370,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7362,10 +7381,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7373,10 +7392,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19240</v>
+        <v>19230</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7384,10 +7403,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19250</v>
+        <v>19240</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7395,10 +7414,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19260</v>
+        <v>19250</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7406,10 +7425,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19270</v>
+        <v>19260</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7417,10 +7436,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19280</v>
+        <v>19270</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
@@ -7428,32 +7447,32 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
+        <v>19280</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C264" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265">
         <v>19300</v>
       </c>
-      <c r="B264" t="s">
+      <c r="B265" t="s">
         <v>343</v>
       </c>
-      <c r="C264" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="26">
-      <c r="A265">
+      <c r="C265" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="26">
+      <c r="A266">
         <v>19310</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="B266" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="C265" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3">
-      <c r="A266">
-        <v>19320</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C266" t="s">
         <v>99</v>
@@ -7461,10 +7480,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19330</v>
-      </c>
-      <c r="B267" t="s">
-        <v>346</v>
+        <v>19320</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C267" t="s">
         <v>99</v>
@@ -7472,10 +7491,10 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B268" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C268" t="s">
         <v>99</v>
@@ -7483,10 +7502,10 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B269" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7494,10 +7513,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B270" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7505,10 +7524,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19400</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>350</v>
+        <v>19360</v>
+      </c>
+      <c r="B271" t="s">
+        <v>349</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7516,10 +7535,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7527,10 +7546,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19410</v>
+        <v>19401</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7538,10 +7557,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19420</v>
+        <v>19410</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7549,10 +7568,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19500</v>
-      </c>
-      <c r="B275" t="s">
-        <v>354</v>
+        <v>19420</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7560,10 +7579,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19510</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>340</v>
+        <v>19500</v>
+      </c>
+      <c r="B276" t="s">
+        <v>354</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7571,10 +7590,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19520</v>
+        <v>19510</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7582,10 +7601,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7593,10 +7612,10 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7604,10 +7623,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7615,10 +7634,10 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
@@ -7626,48 +7645,47 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
+        <v>19603</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C282" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283">
         <v>19604</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="B283" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C282" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="14">
-      <c r="A283">
-        <v>19611</v>
-      </c>
-      <c r="B283" t="s">
-        <v>361</v>
-      </c>
       <c r="C283" t="s">
         <v>99</v>
       </c>
-      <c r="D283" t="s">
-        <v>362</v>
-      </c>
-      <c r="G283" s="1"/>
     </row>
     <row r="284" spans="1:7" ht="14">
       <c r="A284">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B284" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C284" t="s">
         <v>99</v>
+      </c>
+      <c r="D284" t="s">
+        <v>362</v>
       </c>
       <c r="G284" s="1"/>
     </row>
     <row r="285" spans="1:7" ht="14">
       <c r="A285">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B285" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C285" t="s">
         <v>99</v>
@@ -7676,10 +7694,10 @@
     </row>
     <row r="286" spans="1:7" ht="14">
       <c r="A286">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B286" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
@@ -7688,10 +7706,10 @@
     </row>
     <row r="287" spans="1:7" ht="14">
       <c r="A287">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B287" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
@@ -7700,10 +7718,10 @@
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B288" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
@@ -7712,10 +7730,10 @@
     </row>
     <row r="289" spans="1:7" ht="14">
       <c r="A289">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B289" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7724,10 +7742,10 @@
     </row>
     <row r="290" spans="1:7" ht="14">
       <c r="A290">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B290" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C290" t="s">
         <v>99</v>
@@ -7736,47 +7754,48 @@
     </row>
     <row r="291" spans="1:7" ht="14">
       <c r="A291">
+        <v>19618</v>
+      </c>
+      <c r="B291" t="s">
+        <v>369</v>
+      </c>
+      <c r="C291" t="s">
+        <v>99</v>
+      </c>
+      <c r="G291" s="1"/>
+    </row>
+    <row r="292" spans="1:7" ht="14">
+      <c r="A292">
         <v>19619</v>
       </c>
-      <c r="B291" t="s">
+      <c r="B292" t="s">
         <v>370</v>
       </c>
-      <c r="C291" t="s">
-        <v>99</v>
-      </c>
-      <c r="G291" s="1"/>
-    </row>
-    <row r="292" spans="1:7">
-      <c r="A292">
-        <v>19631</v>
-      </c>
-      <c r="B292" t="s">
-        <v>371</v>
-      </c>
       <c r="C292" t="s">
         <v>99</v>
       </c>
-      <c r="D292" t="s">
-        <v>372</v>
-      </c>
+      <c r="G292" s="1"/>
     </row>
     <row r="293" spans="1:7">
       <c r="A293">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="B293" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C293" t="s">
         <v>99</v>
+      </c>
+      <c r="D293" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B294" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C294" t="s">
         <v>99</v>
@@ -7784,10 +7803,10 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B295" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C295" t="s">
         <v>99</v>
@@ -7795,10 +7814,10 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296">
-        <v>19700</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>376</v>
+        <v>19634</v>
+      </c>
+      <c r="B296" t="s">
+        <v>375</v>
       </c>
       <c r="C296" t="s">
         <v>99</v>
@@ -7806,10 +7825,10 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
@@ -7817,10 +7836,10 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7828,10 +7847,10 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7839,10 +7858,10 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C300" t="s">
         <v>99</v>
@@ -7850,57 +7869,57 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301">
-        <v>19800</v>
-      </c>
-      <c r="B301" t="s">
-        <v>380</v>
+        <v>19740</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="C301" t="s">
-        <v>381</v>
+        <v>99</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B302" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C302" t="s">
-        <v>99</v>
+        <v>381</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303">
-        <v>20010</v>
+        <v>19810</v>
       </c>
       <c r="B303" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C303" t="s">
         <v>99</v>
-      </c>
-      <c r="D303" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B304" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C304" t="s">
         <v>99</v>
+      </c>
+      <c r="D304" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>20030</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>386</v>
+        <v>20020</v>
+      </c>
+      <c r="B305" t="s">
+        <v>385</v>
       </c>
       <c r="C305" t="s">
         <v>99</v>
@@ -7908,10 +7927,10 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>20040</v>
-      </c>
-      <c r="B306" t="s">
-        <v>387</v>
+        <v>20030</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="C306" t="s">
         <v>99</v>
@@ -7919,10 +7938,10 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B307" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
@@ -7930,10 +7949,10 @@
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B308" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
@@ -7941,10 +7960,10 @@
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B309" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -7952,10 +7971,10 @@
     </row>
     <row r="310" spans="1:3">
       <c r="A310">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B310" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -7963,10 +7982,10 @@
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B311" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -7974,10 +7993,10 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B312" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -7985,10 +8004,10 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B313" t="s">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -7996,10 +8015,10 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B314" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -8007,10 +8026,10 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20230</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>395</v>
+        <v>20220</v>
+      </c>
+      <c r="B315" t="s">
+        <v>394</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -8018,10 +8037,10 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -8029,10 +8048,10 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -8040,10 +8059,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>20260</v>
-      </c>
-      <c r="B318" t="s">
-        <v>398</v>
+        <v>20250</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -8051,10 +8070,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B319" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -8062,10 +8081,10 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B320" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8073,10 +8092,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B321" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8084,10 +8103,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B322" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8095,10 +8114,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B323" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8106,10 +8125,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B324" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8117,10 +8136,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B325" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8128,10 +8147,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B326" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8139,10 +8158,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B327" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8150,10 +8169,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B328" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8161,10 +8180,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B329" t="s">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8172,10 +8191,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B330" t="s">
-        <v>409</v>
+        <v>103</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8183,10 +8202,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B331" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8194,10 +8213,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B332" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8205,10 +8224,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B333" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8216,10 +8235,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B334" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8227,10 +8246,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B335" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8238,10 +8257,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8249,10 +8268,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B337" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8260,10 +8279,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B338" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8271,10 +8290,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B339" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8282,10 +8301,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B340" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8293,10 +8312,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B341" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8304,10 +8323,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B342" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8315,10 +8334,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B343" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8326,10 +8345,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B344" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8337,10 +8356,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B345" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8348,10 +8367,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B346" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8359,10 +8378,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B347" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8370,10 +8389,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B348" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8381,10 +8400,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B349" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8392,10 +8411,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B350" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8403,10 +8422,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B351" t="s">
-        <v>328</v>
+        <v>429</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8414,10 +8433,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B352" t="s">
-        <v>430</v>
+        <v>328</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8425,10 +8444,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B353" t="s">
-        <v>101</v>
+        <v>430</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8436,10 +8455,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B354" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8447,10 +8466,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B355" t="s">
-        <v>431</v>
+        <v>124</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8458,10 +8477,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B356" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8469,10 +8488,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B357" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
@@ -8480,35 +8499,35 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B358" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
-      </c>
-      <c r="D358" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>102010</v>
+        <v>102000</v>
       </c>
       <c r="B359" t="s">
-        <v>330</v>
+        <v>434</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
+      </c>
+      <c r="D359" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B360" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
@@ -8516,10 +8535,10 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>102030</v>
+        <v>102020</v>
       </c>
       <c r="B361" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
@@ -8527,35 +8546,35 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>113000</v>
+        <v>102030</v>
       </c>
       <c r="B362" t="s">
-        <v>436</v>
+        <v>329</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
-      </c>
-      <c r="D362" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>113010</v>
+        <v>113000</v>
       </c>
       <c r="B363" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
+      </c>
+      <c r="D363" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B364" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
@@ -8563,10 +8582,10 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B365" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
@@ -8574,10 +8593,10 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B366" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
@@ -8585,35 +8604,35 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B367" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
-      </c>
-      <c r="D367" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>121011</v>
+        <v>121010</v>
       </c>
       <c r="B368" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
+      </c>
+      <c r="D368" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B369" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
@@ -8621,10 +8640,10 @@
     </row>
     <row r="370" spans="1:3">
       <c r="A370">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B370" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
@@ -8632,10 +8651,10 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B371" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
@@ -8643,10 +8662,10 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B372" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
@@ -8654,10 +8673,10 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B373" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8665,10 +8684,10 @@
     </row>
     <row r="374" spans="1:3">
       <c r="A374">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B374" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8676,10 +8695,10 @@
     </row>
     <row r="375" spans="1:3">
       <c r="A375">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B375" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C375" t="s">
         <v>99</v>
@@ -8687,10 +8706,10 @@
     </row>
     <row r="376" spans="1:3">
       <c r="A376">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B376" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C376" t="s">
         <v>99</v>
@@ -8698,10 +8717,10 @@
     </row>
     <row r="377" spans="1:3">
       <c r="A377">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B377" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C377" t="s">
         <v>99</v>
@@ -8709,12 +8728,23 @@
     </row>
     <row r="378" spans="1:3">
       <c r="A378">
+        <v>121020</v>
+      </c>
+      <c r="B378" t="s">
+        <v>453</v>
+      </c>
+      <c r="C378" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379">
         <v>121030</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B379" t="s">
         <v>454</v>
       </c>
-      <c r="C378" t="s">
+      <c r="C379" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D391B133-EA34-4015-BCC9-A7F6FBAA6956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0BA198-D004-4503-98A2-7F5096DED942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -408,9 +408,6 @@
     <t>全回復まで</t>
   </si>
   <si>
-    <t>獲得(E)</t>
-  </si>
-  <si>
     <t>vs</t>
   </si>
   <si>
@@ -567,9 +564,6 @@
     <t>魔法切替</t>
   </si>
   <si>
-    <t>(E)</t>
-  </si>
-  <si>
     <t>Turn(s)</t>
   </si>
   <si>
@@ -628,9 +622,6 @@
   </si>
   <si>
     <t>ステータス</t>
-  </si>
-  <si>
-    <t>MP</t>
   </si>
   <si>
     <t>ATK</t>
@@ -968,9 +959,6 @@
     <t>\dのLvと魔法取得状態をリセットしますか？</t>
   </si>
   <si>
-    <t>Lvと魔法取得状態をリセットし\d(E)が還元されました</t>
-  </si>
-  <si>
     <t>\dを仲間にしますか？</t>
   </si>
   <si>
@@ -1058,19 +1046,10 @@
     <t>ショップを出ますか？</t>
   </si>
   <si>
-    <t>Rank.Nは10(E)、Rank.Rは20(E)で入手できます</t>
-  </si>
-  <si>
     <t>\dを入手しますか？</t>
   </si>
   <si>
-    <t>\d(E)を消費して</t>
-  </si>
-  <si>
     <t>\dを召喚しますか？</t>
-  </si>
-  <si>
-    <t>\d(E)を入手しますか？</t>
   </si>
   <si>
     <t>選択したステージからブランチを作りますか？</t>
@@ -1099,9 +1078,6 @@
   </si>
   <si>
     <t>バトル不参加のメンバーがいますがを開始しますか？</t>
-  </si>
-  <si>
-    <t>(E)が不足しています</t>
   </si>
   <si>
     <t>レベルリンク対象キャラはLvアップできません</t>
@@ -1578,6 +1554,38 @@
   </si>
   <si>
     <t>イベント</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SP</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Rank.Nは10(Nu)、Rank.Rは20(Nu)で入手できます</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>獲得(Nu)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>(Nu)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Lvと魔法取得状態をリセットし\d(Nu)が還元されました</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>\d(Nu)を消費して</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>\d(Nu)を入手しますか？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>(Nu)が不足しています</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1982,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C2">
         <v>19000</v>
@@ -1993,7 +2001,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C3">
         <v>19001</v>
@@ -2004,7 +2012,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C4">
         <v>19002</v>
@@ -2015,7 +2023,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C5">
         <v>19003</v>
@@ -2026,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C6">
         <v>19004</v>
@@ -2037,7 +2045,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C7">
         <v>19005</v>
@@ -2048,7 +2056,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C8">
         <v>19006</v>
@@ -2059,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C9">
         <v>19007</v>
@@ -2070,7 +2078,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C10">
         <v>19008</v>
@@ -2081,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C11">
         <v>19009</v>
@@ -2092,7 +2100,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C12">
         <v>19010</v>
@@ -2103,7 +2111,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C13">
         <v>19011</v>
@@ -2162,7 +2170,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -4780,8 +4788,8 @@
       <c r="A31">
         <v>342</v>
       </c>
-      <c r="B31" t="s">
-        <v>123</v>
+      <c r="B31" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
@@ -4792,13 +4800,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
         <v>124</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -4806,13 +4814,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" t="s">
         <v>126</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -4820,13 +4828,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
         <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -4834,13 +4842,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
         <v>129</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -4848,13 +4856,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
         <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -4868,7 +4876,7 @@
         <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -4876,7 +4884,7 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
@@ -4887,7 +4895,7 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
         <v>99</v>
@@ -4898,7 +4906,7 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
         <v>99</v>
@@ -4909,7 +4917,7 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
         <v>99</v>
@@ -4920,7 +4928,7 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s">
         <v>99</v>
@@ -4931,7 +4939,7 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
@@ -4942,7 +4950,7 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -4953,7 +4961,7 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
@@ -4964,7 +4972,7 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
         <v>99</v>
@@ -4975,7 +4983,7 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C47" t="s">
         <v>99</v>
@@ -4986,7 +4994,7 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
         <v>99</v>
@@ -4997,7 +5005,7 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
         <v>99</v>
@@ -5008,7 +5016,7 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
         <v>99</v>
@@ -5019,7 +5027,7 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
         <v>99</v>
@@ -5030,7 +5038,7 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -5041,7 +5049,7 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
         <v>99</v>
@@ -5052,7 +5060,7 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -5063,7 +5071,7 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s">
         <v>99</v>
@@ -5074,7 +5082,7 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C56" t="s">
         <v>99</v>
@@ -5085,7 +5093,7 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
         <v>99</v>
@@ -5096,7 +5104,7 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C58" t="s">
         <v>99</v>
@@ -5107,7 +5115,7 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
         <v>99</v>
@@ -5118,7 +5126,7 @@
         <v>702</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
         <v>99</v>
@@ -5129,7 +5137,7 @@
         <v>706</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
         <v>99</v>
@@ -5206,7 +5214,7 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
         <v>99</v>
@@ -5217,7 +5225,7 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
         <v>99</v>
@@ -5228,7 +5236,7 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C70" t="s">
         <v>99</v>
@@ -5239,7 +5247,7 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
         <v>99</v>
@@ -5250,7 +5258,7 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C72" t="s">
         <v>99</v>
@@ -5261,7 +5269,7 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C73" t="s">
         <v>99</v>
@@ -5272,7 +5280,7 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
         <v>99</v>
@@ -5294,7 +5302,7 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
         <v>99</v>
@@ -5305,7 +5313,7 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C77" t="s">
         <v>99</v>
@@ -5316,7 +5324,7 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
         <v>99</v>
@@ -5327,7 +5335,7 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
         <v>99</v>
@@ -5338,7 +5346,7 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
         <v>99</v>
@@ -5349,7 +5357,7 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
         <v>99</v>
@@ -5360,7 +5368,7 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
         <v>99</v>
@@ -5371,7 +5379,7 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
         <v>99</v>
@@ -5382,7 +5390,7 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
         <v>99</v>
@@ -5393,7 +5401,7 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
         <v>99</v>
@@ -5404,7 +5412,7 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
         <v>99</v>
@@ -5426,7 +5434,7 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
         <v>99</v>
@@ -5436,8 +5444,8 @@
       <c r="A89">
         <v>1000</v>
       </c>
-      <c r="B89" t="s">
-        <v>176</v>
+      <c r="B89" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="C89" t="s">
         <v>99</v>
@@ -5448,7 +5456,7 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C90" t="s">
         <v>99</v>
@@ -5459,7 +5467,7 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C91" t="s">
         <v>99</v>
@@ -5470,7 +5478,7 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C92" t="s">
         <v>99</v>
@@ -5481,7 +5489,7 @@
         <v>1060</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C93" t="s">
         <v>99</v>
@@ -5492,7 +5500,7 @@
         <v>1110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C94" t="s">
         <v>99</v>
@@ -5503,7 +5511,7 @@
         <v>1120</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C95" t="s">
         <v>99</v>
@@ -5514,13 +5522,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C96" t="s">
         <v>99</v>
       </c>
       <c r="D96" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -5528,7 +5536,7 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C97" t="s">
         <v>99</v>
@@ -5539,7 +5547,7 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C98" t="s">
         <v>99</v>
@@ -5550,7 +5558,7 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C99" t="s">
         <v>99</v>
@@ -5561,7 +5569,7 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C100" t="s">
         <v>99</v>
@@ -5572,7 +5580,7 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C101" t="s">
         <v>99</v>
@@ -5583,7 +5591,7 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C102" t="s">
         <v>99</v>
@@ -5594,7 +5602,7 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C103" t="s">
         <v>99</v>
@@ -5605,13 +5613,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C104" t="s">
         <v>99</v>
       </c>
       <c r="D104" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -5619,13 +5627,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C105" t="s">
         <v>99</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -5633,13 +5641,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C106" t="s">
         <v>99</v>
       </c>
       <c r="D106" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -5647,13 +5655,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C107" t="s">
         <v>99</v>
       </c>
       <c r="D107" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -5661,21 +5669,21 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C108" t="s">
         <v>99</v>
       </c>
       <c r="D108" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
         <v>2101</v>
       </c>
-      <c r="B109" t="s">
-        <v>197</v>
+      <c r="B109" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="C109" t="s">
         <v>99</v>
@@ -5686,7 +5694,7 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C110" t="s">
         <v>99</v>
@@ -5697,7 +5705,7 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C111" t="s">
         <v>99</v>
@@ -5708,7 +5716,7 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C112" t="s">
         <v>99</v>
@@ -5719,13 +5727,13 @@
         <v>2200</v>
       </c>
       <c r="B113" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C113" t="s">
         <v>99</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -5733,13 +5741,13 @@
         <v>2210</v>
       </c>
       <c r="B114" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C114" t="s">
         <v>99</v>
       </c>
       <c r="D114" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="29" customHeight="1">
@@ -5747,13 +5755,13 @@
         <v>2220</v>
       </c>
       <c r="B115" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C115" t="s">
         <v>99</v>
       </c>
       <c r="D115" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -5761,13 +5769,13 @@
         <v>2300</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C116" t="s">
         <v>99</v>
       </c>
       <c r="D116" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -5775,13 +5783,13 @@
         <v>2310</v>
       </c>
       <c r="B117" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C117" t="s">
         <v>99</v>
       </c>
       <c r="D117" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -5789,13 +5797,13 @@
         <v>2320</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C118" t="s">
         <v>99</v>
       </c>
       <c r="D118" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -5803,13 +5811,13 @@
         <v>2330</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C119" t="s">
         <v>99</v>
       </c>
       <c r="D119" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -5817,13 +5825,13 @@
         <v>2340</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C120" t="s">
         <v>99</v>
       </c>
       <c r="D120" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -5831,13 +5839,13 @@
         <v>2400</v>
       </c>
       <c r="B121" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C121" t="s">
         <v>99</v>
       </c>
       <c r="D121" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -5845,7 +5853,7 @@
         <v>3000</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C122" t="s">
         <v>99</v>
@@ -5856,7 +5864,7 @@
         <v>3010</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C123" t="s">
         <v>99</v>
@@ -5867,7 +5875,7 @@
         <v>3011</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C124" t="s">
         <v>99</v>
@@ -5878,7 +5886,7 @@
         <v>3040</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C125" t="s">
         <v>99</v>
@@ -5900,7 +5908,7 @@
         <v>3051</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C127" t="s">
         <v>99</v>
@@ -5911,7 +5919,7 @@
         <v>3052</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C128" t="s">
         <v>99</v>
@@ -5922,7 +5930,7 @@
         <v>3053</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C129" t="s">
         <v>99</v>
@@ -5933,7 +5941,7 @@
         <v>3054</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C130" t="s">
         <v>99</v>
@@ -5944,7 +5952,7 @@
         <v>3070</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C131" t="s">
         <v>99</v>
@@ -5955,7 +5963,7 @@
         <v>3071</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C132" t="s">
         <v>99</v>
@@ -5966,7 +5974,7 @@
         <v>3072</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C133" t="s">
         <v>99</v>
@@ -5977,7 +5985,7 @@
         <v>3073</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C134" t="s">
         <v>99</v>
@@ -5988,7 +5996,7 @@
         <v>3090</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C135" t="s">
         <v>99</v>
@@ -5999,7 +6007,7 @@
         <v>3211</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C136" t="s">
         <v>99</v>
@@ -6010,7 +6018,7 @@
         <v>3230</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C137" t="s">
         <v>99</v>
@@ -6021,7 +6029,7 @@
         <v>5000</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C138" t="s">
         <v>99</v>
@@ -6043,7 +6051,7 @@
         <v>5002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C140" t="s">
         <v>99</v>
@@ -6054,7 +6062,7 @@
         <v>6001</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C141" t="s">
         <v>99</v>
@@ -6065,7 +6073,7 @@
         <v>6002</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C142" t="s">
         <v>99</v>
@@ -6079,7 +6087,7 @@
         <v>99</v>
       </c>
       <c r="C143" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6087,10 +6095,10 @@
         <v>6010</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C144" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6098,7 +6106,7 @@
         <v>6011</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C145" t="s">
         <v>99</v>
@@ -6109,7 +6117,7 @@
         <v>6012</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C146" t="s">
         <v>99</v>
@@ -6120,10 +6128,10 @@
         <v>6020</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C147" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6131,10 +6139,10 @@
         <v>6030</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C148" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6142,10 +6150,10 @@
         <v>6040</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C149" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6153,10 +6161,10 @@
         <v>6210</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C150" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6164,10 +6172,10 @@
         <v>6220</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C151" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6175,10 +6183,10 @@
         <v>6230</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C152" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6186,10 +6194,10 @@
         <v>6240</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C153" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6197,10 +6205,10 @@
         <v>6250</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C154" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6208,10 +6216,10 @@
         <v>6260</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C155" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6219,10 +6227,10 @@
         <v>6270</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C156" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6230,10 +6238,10 @@
         <v>6280</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C157" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6241,7 +6249,7 @@
         <v>6810</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C158" t="s">
         <v>99</v>
@@ -6252,7 +6260,7 @@
         <v>6820</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C159" t="s">
         <v>99</v>
@@ -6263,7 +6271,7 @@
         <v>6830</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C160" t="s">
         <v>99</v>
@@ -6274,7 +6282,7 @@
         <v>6840</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C161" t="s">
         <v>99</v>
@@ -6285,7 +6293,7 @@
         <v>6850</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C162" t="s">
         <v>99</v>
@@ -6296,7 +6304,7 @@
         <v>6860</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C163" t="s">
         <v>99</v>
@@ -6307,7 +6315,7 @@
         <v>6870</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C164" t="s">
         <v>99</v>
@@ -6318,7 +6326,7 @@
         <v>6880</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C165" t="s">
         <v>99</v>
@@ -6329,7 +6337,7 @@
         <v>6890</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C166" t="s">
         <v>99</v>
@@ -6340,13 +6348,13 @@
         <v>12010</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C167" t="s">
         <v>99</v>
       </c>
       <c r="D167" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -6354,13 +6362,13 @@
         <v>13010</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C168" t="s">
         <v>99</v>
       </c>
       <c r="D168" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -6368,7 +6376,7 @@
         <v>13020</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="C169" t="s">
         <v>99</v>
@@ -6379,7 +6387,7 @@
         <v>13110</v>
       </c>
       <c r="B170" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C170" t="s">
         <v>99</v>
@@ -6390,7 +6398,7 @@
         <v>13120</v>
       </c>
       <c r="B171" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C171" t="s">
         <v>99</v>
@@ -6401,7 +6409,7 @@
         <v>13130</v>
       </c>
       <c r="B172" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C172" t="s">
         <v>99</v>
@@ -6412,7 +6420,7 @@
         <v>13140</v>
       </c>
       <c r="B173" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C173" t="s">
         <v>99</v>
@@ -6423,7 +6431,7 @@
         <v>13210</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C174" t="s">
         <v>99</v>
@@ -6434,7 +6442,7 @@
         <v>13220</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="C175" t="s">
         <v>99</v>
@@ -6445,7 +6453,7 @@
         <v>13230</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C176" t="s">
         <v>99</v>
@@ -6456,7 +6464,7 @@
         <v>13240</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C177" t="s">
         <v>99</v>
@@ -6467,7 +6475,7 @@
         <v>13300</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C178" t="s">
         <v>99</v>
@@ -6478,7 +6486,7 @@
         <v>13301</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C179" t="s">
         <v>99</v>
@@ -6489,7 +6497,7 @@
         <v>13310</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C180" t="s">
         <v>99</v>
@@ -6500,7 +6508,7 @@
         <v>13320</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C181" t="s">
         <v>99</v>
@@ -6511,7 +6519,7 @@
         <v>13330</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C182" t="s">
         <v>99</v>
@@ -6522,7 +6530,7 @@
         <v>13400</v>
       </c>
       <c r="B183" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C183" t="s">
         <v>99</v>
@@ -6536,7 +6544,7 @@
         <v>34</v>
       </c>
       <c r="C184" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6544,7 +6552,7 @@
         <v>13420</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C185" t="s">
         <v>99</v>
@@ -6555,7 +6563,7 @@
         <v>13421</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C186" t="s">
         <v>99</v>
@@ -6566,7 +6574,7 @@
         <v>13430</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C187" t="s">
         <v>99</v>
@@ -6577,7 +6585,7 @@
         <v>14090</v>
       </c>
       <c r="B188" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C188" t="s">
         <v>99</v>
@@ -6588,7 +6596,7 @@
         <v>14110</v>
       </c>
       <c r="B189" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C189" t="s">
         <v>99</v>
@@ -6599,13 +6607,13 @@
         <v>15010</v>
       </c>
       <c r="B190" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C190" t="s">
         <v>99</v>
       </c>
       <c r="D190" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G190" s="1"/>
     </row>
@@ -6614,13 +6622,13 @@
         <v>16010</v>
       </c>
       <c r="B191" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C191" t="s">
         <v>99</v>
       </c>
       <c r="D191" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G191" s="1"/>
     </row>
@@ -6629,7 +6637,7 @@
         <v>16020</v>
       </c>
       <c r="B192" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C192" t="s">
         <v>99</v>
@@ -6641,7 +6649,7 @@
         <v>16100</v>
       </c>
       <c r="B193" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C193" t="s">
         <v>99</v>
@@ -6652,7 +6660,7 @@
         <v>16110</v>
       </c>
       <c r="B194" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C194" t="s">
         <v>99</v>
@@ -6663,7 +6671,7 @@
         <v>16200</v>
       </c>
       <c r="B195" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C195" t="s">
         <v>99</v>
@@ -6674,7 +6682,7 @@
         <v>16210</v>
       </c>
       <c r="B196" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C196" t="s">
         <v>99</v>
@@ -6685,7 +6693,7 @@
         <v>16220</v>
       </c>
       <c r="B197" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C197" t="s">
         <v>99</v>
@@ -6696,7 +6704,7 @@
         <v>16230</v>
       </c>
       <c r="B198" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C198" t="s">
         <v>99</v>
@@ -6707,7 +6715,7 @@
         <v>16300</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C199" t="s">
         <v>99</v>
@@ -6718,7 +6726,7 @@
         <v>16310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C200" t="s">
         <v>99</v>
@@ -6729,7 +6737,7 @@
         <v>16320</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C201" t="s">
         <v>99</v>
@@ -6740,7 +6748,7 @@
         <v>16400</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C202" t="s">
         <v>99</v>
@@ -6751,7 +6759,7 @@
         <v>16410</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C203" t="s">
         <v>99</v>
@@ -6762,13 +6770,13 @@
         <v>16800</v>
       </c>
       <c r="B204" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C204" t="s">
         <v>99</v>
       </c>
       <c r="D204" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -6776,13 +6784,13 @@
         <v>16801</v>
       </c>
       <c r="B205" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C205" t="s">
         <v>99</v>
       </c>
       <c r="D205" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -6790,13 +6798,13 @@
         <v>16802</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C206" t="s">
         <v>99</v>
       </c>
       <c r="D206" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -6804,13 +6812,13 @@
         <v>16803</v>
       </c>
       <c r="B207" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C207" t="s">
         <v>99</v>
       </c>
       <c r="D207" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -6818,13 +6826,13 @@
         <v>16804</v>
       </c>
       <c r="B208" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C208" t="s">
         <v>99</v>
       </c>
       <c r="D208" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -6832,13 +6840,13 @@
         <v>16805</v>
       </c>
       <c r="B209" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C209" t="s">
         <v>99</v>
       </c>
       <c r="D209" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -6846,13 +6854,13 @@
         <v>16806</v>
       </c>
       <c r="B210" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C210" t="s">
         <v>99</v>
       </c>
       <c r="D210" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -6860,7 +6868,7 @@
         <v>17010</v>
       </c>
       <c r="B211" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C211" t="s">
         <v>99</v>
@@ -6871,13 +6879,13 @@
         <v>18010</v>
       </c>
       <c r="B212" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C212" t="s">
         <v>99</v>
       </c>
       <c r="D212" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -6885,7 +6893,7 @@
         <v>18020</v>
       </c>
       <c r="B213" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C213" t="s">
         <v>99</v>
@@ -6896,7 +6904,7 @@
         <v>18100</v>
       </c>
       <c r="B214" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C214" t="s">
         <v>99</v>
@@ -6907,7 +6915,7 @@
         <v>18110</v>
       </c>
       <c r="B215" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C215" t="s">
         <v>99</v>
@@ -6918,7 +6926,7 @@
         <v>18120</v>
       </c>
       <c r="B216" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C216" t="s">
         <v>99</v>
@@ -6929,7 +6937,7 @@
         <v>18130</v>
       </c>
       <c r="B217" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C217" t="s">
         <v>99</v>
@@ -6962,7 +6970,7 @@
         <v>18220</v>
       </c>
       <c r="B220" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C220" t="s">
         <v>99</v>
@@ -6973,7 +6981,7 @@
         <v>18300</v>
       </c>
       <c r="B221" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C221" t="s">
         <v>99</v>
@@ -6983,8 +6991,8 @@
       <c r="A222">
         <v>18310</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>308</v>
+      <c r="B222" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C222" t="s">
         <v>99</v>
@@ -6995,7 +7003,7 @@
         <v>18320</v>
       </c>
       <c r="B223" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C223" t="s">
         <v>99</v>
@@ -7006,7 +7014,7 @@
         <v>18340</v>
       </c>
       <c r="B224" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C224" t="s">
         <v>99</v>
@@ -7017,7 +7025,7 @@
         <v>18400</v>
       </c>
       <c r="B225" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C225" t="s">
         <v>99</v>
@@ -7028,7 +7036,7 @@
         <v>18410</v>
       </c>
       <c r="B226" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C226" t="s">
         <v>99</v>
@@ -7039,7 +7047,7 @@
         <v>18420</v>
       </c>
       <c r="B227" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C227" t="s">
         <v>99</v>
@@ -7050,7 +7058,7 @@
         <v>18430</v>
       </c>
       <c r="B228" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C228" t="s">
         <v>99</v>
@@ -7072,7 +7080,7 @@
         <v>18450</v>
       </c>
       <c r="B230" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C230" t="s">
         <v>99</v>
@@ -7083,7 +7091,7 @@
         <v>18500</v>
       </c>
       <c r="B231" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C231" t="s">
         <v>99</v>
@@ -7094,7 +7102,7 @@
         <v>18510</v>
       </c>
       <c r="B232" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C232" t="s">
         <v>99</v>
@@ -7105,7 +7113,7 @@
         <v>18800</v>
       </c>
       <c r="B233" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C233" t="s">
         <v>99</v>
@@ -7116,7 +7124,7 @@
         <v>18801</v>
       </c>
       <c r="B234" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C234" t="s">
         <v>99</v>
@@ -7127,7 +7135,7 @@
         <v>18802</v>
       </c>
       <c r="B235" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C235" t="s">
         <v>99</v>
@@ -7138,7 +7146,7 @@
         <v>18803</v>
       </c>
       <c r="B236" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C236" t="s">
         <v>99</v>
@@ -7149,7 +7157,7 @@
         <v>18804</v>
       </c>
       <c r="B237" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C237" t="s">
         <v>99</v>
@@ -7160,7 +7168,7 @@
         <v>18805</v>
       </c>
       <c r="B238" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C238" t="s">
         <v>99</v>
@@ -7171,7 +7179,7 @@
         <v>18806</v>
       </c>
       <c r="B239" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C239" t="s">
         <v>99</v>
@@ -7182,7 +7190,7 @@
         <v>18811</v>
       </c>
       <c r="B240" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C240" t="s">
         <v>99</v>
@@ -7193,7 +7201,7 @@
         <v>18812</v>
       </c>
       <c r="B241" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C241" t="s">
         <v>99</v>
@@ -7204,13 +7212,13 @@
         <v>19000</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C242" t="s">
         <v>99</v>
       </c>
       <c r="D242" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G242" s="1"/>
     </row>
@@ -7219,7 +7227,7 @@
         <v>19001</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C243" t="s">
         <v>99</v>
@@ -7230,7 +7238,7 @@
         <v>19002</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C244" t="s">
         <v>99</v>
@@ -7241,7 +7249,7 @@
         <v>19003</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C245" t="s">
         <v>99</v>
@@ -7252,7 +7260,7 @@
         <v>19004</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C246" t="s">
         <v>99</v>
@@ -7263,7 +7271,7 @@
         <v>19005</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C247" t="s">
         <v>99</v>
@@ -7274,7 +7282,7 @@
         <v>19006</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C248" t="s">
         <v>99</v>
@@ -7285,7 +7293,7 @@
         <v>19007</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C249" t="s">
         <v>99</v>
@@ -7296,7 +7304,7 @@
         <v>19008</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C250" t="s">
         <v>99</v>
@@ -7307,7 +7315,7 @@
         <v>19009</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C251" t="s">
         <v>99</v>
@@ -7318,7 +7326,7 @@
         <v>19010</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C252" t="s">
         <v>99</v>
@@ -7329,7 +7337,7 @@
         <v>19011</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7340,7 +7348,7 @@
         <v>19100</v>
       </c>
       <c r="B254" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7351,7 +7359,7 @@
         <v>19110</v>
       </c>
       <c r="B255" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7362,7 +7370,7 @@
         <v>19200</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7373,7 +7381,7 @@
         <v>19210</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7384,7 +7392,7 @@
         <v>19220</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7395,7 +7403,7 @@
         <v>19230</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7405,8 +7413,8 @@
       <c r="A260">
         <v>19240</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>338</v>
+      <c r="B260" s="5" t="s">
+        <v>478</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7417,7 +7425,7 @@
         <v>19250</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7427,8 +7435,8 @@
       <c r="A262">
         <v>19260</v>
       </c>
-      <c r="B262" s="2" t="s">
-        <v>340</v>
+      <c r="B262" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7439,7 +7447,7 @@
         <v>19270</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
@@ -7449,8 +7457,8 @@
       <c r="A264">
         <v>19280</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>342</v>
+      <c r="B264" s="5" t="s">
+        <v>483</v>
       </c>
       <c r="C264" t="s">
         <v>99</v>
@@ -7461,7 +7469,7 @@
         <v>19300</v>
       </c>
       <c r="B265" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C265" t="s">
         <v>99</v>
@@ -7472,7 +7480,7 @@
         <v>19310</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C266" t="s">
         <v>99</v>
@@ -7483,7 +7491,7 @@
         <v>19320</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C267" t="s">
         <v>99</v>
@@ -7494,7 +7502,7 @@
         <v>19330</v>
       </c>
       <c r="B268" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C268" t="s">
         <v>99</v>
@@ -7505,7 +7513,7 @@
         <v>19340</v>
       </c>
       <c r="B269" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7516,7 +7524,7 @@
         <v>19350</v>
       </c>
       <c r="B270" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7527,7 +7535,7 @@
         <v>19360</v>
       </c>
       <c r="B271" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7538,7 +7546,7 @@
         <v>19400</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7549,7 +7557,7 @@
         <v>19401</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7559,8 +7567,8 @@
       <c r="A274">
         <v>19410</v>
       </c>
-      <c r="B274" s="2" t="s">
-        <v>352</v>
+      <c r="B274" s="5" t="s">
+        <v>484</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7571,7 +7579,7 @@
         <v>19420</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7582,7 +7590,7 @@
         <v>19500</v>
       </c>
       <c r="B276" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7592,8 +7600,8 @@
       <c r="A277">
         <v>19510</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>340</v>
+      <c r="B277" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7604,7 +7612,7 @@
         <v>19520</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7615,7 +7623,7 @@
         <v>19600</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7626,7 +7634,7 @@
         <v>19601</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7637,7 +7645,7 @@
         <v>19602</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
@@ -7648,7 +7656,7 @@
         <v>19603</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C282" t="s">
         <v>99</v>
@@ -7659,7 +7667,7 @@
         <v>19604</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C283" t="s">
         <v>99</v>
@@ -7670,13 +7678,13 @@
         <v>19611</v>
       </c>
       <c r="B284" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C284" t="s">
         <v>99</v>
       </c>
       <c r="D284" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G284" s="1"/>
     </row>
@@ -7685,7 +7693,7 @@
         <v>19612</v>
       </c>
       <c r="B285" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C285" t="s">
         <v>99</v>
@@ -7697,7 +7705,7 @@
         <v>19613</v>
       </c>
       <c r="B286" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
@@ -7709,7 +7717,7 @@
         <v>19614</v>
       </c>
       <c r="B287" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
@@ -7721,7 +7729,7 @@
         <v>19615</v>
       </c>
       <c r="B288" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
@@ -7733,7 +7741,7 @@
         <v>19616</v>
       </c>
       <c r="B289" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7745,7 +7753,7 @@
         <v>19617</v>
       </c>
       <c r="B290" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C290" t="s">
         <v>99</v>
@@ -7757,7 +7765,7 @@
         <v>19618</v>
       </c>
       <c r="B291" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C291" t="s">
         <v>99</v>
@@ -7769,7 +7777,7 @@
         <v>19619</v>
       </c>
       <c r="B292" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C292" t="s">
         <v>99</v>
@@ -7781,13 +7789,13 @@
         <v>19631</v>
       </c>
       <c r="B293" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C293" t="s">
         <v>99</v>
       </c>
       <c r="D293" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -7795,7 +7803,7 @@
         <v>19632</v>
       </c>
       <c r="B294" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C294" t="s">
         <v>99</v>
@@ -7806,7 +7814,7 @@
         <v>19633</v>
       </c>
       <c r="B295" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C295" t="s">
         <v>99</v>
@@ -7817,7 +7825,7 @@
         <v>19634</v>
       </c>
       <c r="B296" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C296" t="s">
         <v>99</v>
@@ -7828,7 +7836,7 @@
         <v>19700</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
@@ -7839,7 +7847,7 @@
         <v>19710</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7850,7 +7858,7 @@
         <v>19720</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7861,7 +7869,7 @@
         <v>19730</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C300" t="s">
         <v>99</v>
@@ -7872,7 +7880,7 @@
         <v>19740</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C301" t="s">
         <v>99</v>
@@ -7883,10 +7891,10 @@
         <v>19800</v>
       </c>
       <c r="B302" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C302" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -7894,7 +7902,7 @@
         <v>19810</v>
       </c>
       <c r="B303" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C303" t="s">
         <v>99</v>
@@ -7905,13 +7913,13 @@
         <v>20010</v>
       </c>
       <c r="B304" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C304" t="s">
         <v>99</v>
       </c>
       <c r="D304" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -7919,7 +7927,7 @@
         <v>20020</v>
       </c>
       <c r="B305" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C305" t="s">
         <v>99</v>
@@ -7930,7 +7938,7 @@
         <v>20030</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C306" t="s">
         <v>99</v>
@@ -7941,7 +7949,7 @@
         <v>20040</v>
       </c>
       <c r="B307" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
@@ -7952,7 +7960,7 @@
         <v>20050</v>
       </c>
       <c r="B308" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
@@ -7963,7 +7971,7 @@
         <v>20100</v>
       </c>
       <c r="B309" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -7974,7 +7982,7 @@
         <v>20110</v>
       </c>
       <c r="B310" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -7985,7 +7993,7 @@
         <v>20120</v>
       </c>
       <c r="B311" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -7996,7 +8004,7 @@
         <v>20200</v>
       </c>
       <c r="B312" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -8007,7 +8015,7 @@
         <v>20201</v>
       </c>
       <c r="B313" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -8018,7 +8026,7 @@
         <v>20210</v>
       </c>
       <c r="B314" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -8029,7 +8037,7 @@
         <v>20220</v>
       </c>
       <c r="B315" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -8040,7 +8048,7 @@
         <v>20230</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -8051,7 +8059,7 @@
         <v>20240</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -8062,7 +8070,7 @@
         <v>20250</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -8073,7 +8081,7 @@
         <v>20260</v>
       </c>
       <c r="B319" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -8084,7 +8092,7 @@
         <v>20270</v>
       </c>
       <c r="B320" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8095,7 +8103,7 @@
         <v>20280</v>
       </c>
       <c r="B321" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8106,7 +8114,7 @@
         <v>20290</v>
       </c>
       <c r="B322" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8117,7 +8125,7 @@
         <v>20300</v>
       </c>
       <c r="B323" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8128,7 +8136,7 @@
         <v>20310</v>
       </c>
       <c r="B324" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8139,7 +8147,7 @@
         <v>20320</v>
       </c>
       <c r="B325" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8150,7 +8158,7 @@
         <v>20330</v>
       </c>
       <c r="B326" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8161,7 +8169,7 @@
         <v>20340</v>
       </c>
       <c r="B327" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8172,7 +8180,7 @@
         <v>20350</v>
       </c>
       <c r="B328" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8183,7 +8191,7 @@
         <v>23010</v>
       </c>
       <c r="B329" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8205,7 +8213,7 @@
         <v>23030</v>
       </c>
       <c r="B331" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8216,7 +8224,7 @@
         <v>23031</v>
       </c>
       <c r="B332" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8227,7 +8235,7 @@
         <v>23032</v>
       </c>
       <c r="B333" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8238,7 +8246,7 @@
         <v>23040</v>
       </c>
       <c r="B334" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8249,7 +8257,7 @@
         <v>24010</v>
       </c>
       <c r="B335" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8260,7 +8268,7 @@
         <v>24020</v>
       </c>
       <c r="B336" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8271,7 +8279,7 @@
         <v>24030</v>
       </c>
       <c r="B337" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8282,7 +8290,7 @@
         <v>24040</v>
       </c>
       <c r="B338" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8293,7 +8301,7 @@
         <v>24110</v>
       </c>
       <c r="B339" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8304,7 +8312,7 @@
         <v>24111</v>
       </c>
       <c r="B340" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8315,7 +8323,7 @@
         <v>24112</v>
       </c>
       <c r="B341" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8326,7 +8334,7 @@
         <v>24113</v>
       </c>
       <c r="B342" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8337,7 +8345,7 @@
         <v>24114</v>
       </c>
       <c r="B343" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8348,7 +8356,7 @@
         <v>24115</v>
       </c>
       <c r="B344" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8359,7 +8367,7 @@
         <v>24116</v>
       </c>
       <c r="B345" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8370,7 +8378,7 @@
         <v>24117</v>
       </c>
       <c r="B346" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8381,7 +8389,7 @@
         <v>24118</v>
       </c>
       <c r="B347" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8392,7 +8400,7 @@
         <v>24119</v>
       </c>
       <c r="B348" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8403,7 +8411,7 @@
         <v>24120</v>
       </c>
       <c r="B349" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8414,7 +8422,7 @@
         <v>24121</v>
       </c>
       <c r="B350" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8425,7 +8433,7 @@
         <v>24122</v>
       </c>
       <c r="B351" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8436,7 +8444,7 @@
         <v>30000</v>
       </c>
       <c r="B352" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8447,7 +8455,7 @@
         <v>30010</v>
       </c>
       <c r="B353" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8469,7 +8477,7 @@
         <v>30030</v>
       </c>
       <c r="B355" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8480,7 +8488,7 @@
         <v>30040</v>
       </c>
       <c r="B356" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8491,7 +8499,7 @@
         <v>31010</v>
       </c>
       <c r="B357" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
@@ -8502,7 +8510,7 @@
         <v>31020</v>
       </c>
       <c r="B358" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
@@ -8513,13 +8521,13 @@
         <v>102000</v>
       </c>
       <c r="B359" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
       </c>
       <c r="D359" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -8527,7 +8535,7 @@
         <v>102010</v>
       </c>
       <c r="B360" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
@@ -8538,7 +8546,7 @@
         <v>102020</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
@@ -8549,7 +8557,7 @@
         <v>102030</v>
       </c>
       <c r="B362" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
@@ -8560,13 +8568,13 @@
         <v>113000</v>
       </c>
       <c r="B363" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
       </c>
       <c r="D363" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -8574,7 +8582,7 @@
         <v>113010</v>
       </c>
       <c r="B364" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
@@ -8585,7 +8593,7 @@
         <v>113020</v>
       </c>
       <c r="B365" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
@@ -8596,7 +8604,7 @@
         <v>113030</v>
       </c>
       <c r="B366" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
@@ -8607,7 +8615,7 @@
         <v>113040</v>
       </c>
       <c r="B367" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
@@ -8618,13 +8626,13 @@
         <v>121010</v>
       </c>
       <c r="B368" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
       </c>
       <c r="D368" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -8632,7 +8640,7 @@
         <v>121011</v>
       </c>
       <c r="B369" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
@@ -8643,7 +8651,7 @@
         <v>121012</v>
       </c>
       <c r="B370" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
@@ -8654,7 +8662,7 @@
         <v>121013</v>
       </c>
       <c r="B371" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
@@ -8665,7 +8673,7 @@
         <v>121014</v>
       </c>
       <c r="B372" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
@@ -8676,7 +8684,7 @@
         <v>121015</v>
       </c>
       <c r="B373" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8687,7 +8695,7 @@
         <v>121016</v>
       </c>
       <c r="B374" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8698,7 +8706,7 @@
         <v>121017</v>
       </c>
       <c r="B375" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C375" t="s">
         <v>99</v>
@@ -8709,7 +8717,7 @@
         <v>121018</v>
       </c>
       <c r="B376" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C376" t="s">
         <v>99</v>
@@ -8720,7 +8728,7 @@
         <v>121019</v>
       </c>
       <c r="B377" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C377" t="s">
         <v>99</v>
@@ -8731,7 +8739,7 @@
         <v>121020</v>
       </c>
       <c r="B378" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C378" t="s">
         <v>99</v>
@@ -8742,7 +8750,7 @@
         <v>121030</v>
       </c>
       <c r="B379" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C379" t="s">
         <v>99</v>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0BA198-D004-4503-98A2-7F5096DED942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB1F6BF-623F-46A1-A948-CB0176300EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="GameDefine" sheetId="3" r:id="rId6"/>
     <sheet name="TextData" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="486">
   <si>
     <t>Id</t>
   </si>
@@ -1557,10 +1557,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>SP</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>Rank.Nは10(Nu)、Rank.Rは20(Nu)で入手できます</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1586,6 +1582,14 @@
   </si>
   <si>
     <t>(Nu)が不足しています</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>CP</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MOV</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -4446,7 +4450,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G379"/>
+  <dimension ref="A1:G380"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -4789,7 +4793,7 @@
         <v>342</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
@@ -5445,7 +5449,7 @@
         <v>1000</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C89" t="s">
         <v>99</v>
@@ -5683,7 +5687,7 @@
         <v>2101</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C109" t="s">
         <v>99</v>
@@ -5724,24 +5728,21 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>2200</v>
-      </c>
-      <c r="B113" t="s">
-        <v>198</v>
+        <v>2105</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>485</v>
       </c>
       <c r="C113" t="s">
         <v>99</v>
-      </c>
-      <c r="D113" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>2210</v>
+        <v>2200</v>
       </c>
       <c r="B114" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="C114" t="s">
         <v>99</v>
@@ -5750,12 +5751,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="29" customHeight="1">
+    <row r="115" spans="1:4">
       <c r="A115">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B115" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C115" t="s">
         <v>99</v>
@@ -5764,12 +5765,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" ht="29" customHeight="1">
       <c r="A116">
-        <v>2300</v>
+        <v>2220</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C116" t="s">
         <v>99</v>
@@ -5780,10 +5781,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117">
-        <v>2310</v>
+        <v>2300</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C117" t="s">
         <v>99</v>
@@ -5794,10 +5795,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="B118" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C118" t="s">
         <v>99</v>
@@ -5808,10 +5809,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B119" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C119" t="s">
         <v>99</v>
@@ -5822,10 +5823,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B120" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C120" t="s">
         <v>99</v>
@@ -5836,10 +5837,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>2400</v>
+        <v>2340</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C121" t="s">
         <v>99</v>
@@ -5850,21 +5851,24 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122">
-        <v>3000</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>207</v>
+        <v>2400</v>
+      </c>
+      <c r="B122" t="s">
+        <v>206</v>
       </c>
       <c r="C122" t="s">
         <v>99</v>
+      </c>
+      <c r="D122" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C123" t="s">
         <v>99</v>
@@ -5872,10 +5876,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C124" t="s">
         <v>99</v>
@@ -5883,10 +5887,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125">
-        <v>3040</v>
+        <v>3011</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C125" t="s">
         <v>99</v>
@@ -5894,10 +5898,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>32</v>
+        <v>210</v>
       </c>
       <c r="C126" t="s">
         <v>99</v>
@@ -5905,10 +5909,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="C127" t="s">
         <v>99</v>
@@ -5916,10 +5920,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C128" t="s">
         <v>99</v>
@@ -5927,10 +5931,10 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C129" t="s">
         <v>99</v>
@@ -5938,10 +5942,10 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C130" t="s">
         <v>99</v>
@@ -5949,10 +5953,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>3070</v>
+        <v>3054</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C131" t="s">
         <v>99</v>
@@ -5960,10 +5964,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C132" t="s">
         <v>99</v>
@@ -5971,10 +5975,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C133" t="s">
         <v>99</v>
@@ -5982,10 +5986,10 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C134" t="s">
         <v>99</v>
@@ -5993,10 +5997,10 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>3090</v>
+        <v>3073</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C135" t="s">
         <v>99</v>
@@ -6004,10 +6008,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>3211</v>
+        <v>3090</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C136" t="s">
         <v>99</v>
@@ -6015,10 +6019,10 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>3230</v>
+        <v>3211</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C137" t="s">
         <v>99</v>
@@ -6026,10 +6030,10 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>5000</v>
+        <v>3230</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C138" t="s">
         <v>99</v>
@@ -6037,10 +6041,10 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>99</v>
+        <v>221</v>
       </c>
       <c r="C139" t="s">
         <v>99</v>
@@ -6048,10 +6052,10 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="C140" t="s">
         <v>99</v>
@@ -6059,10 +6063,10 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>6001</v>
+        <v>5002</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C141" t="s">
         <v>99</v>
@@ -6070,10 +6074,10 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C142" t="s">
         <v>99</v>
@@ -6081,43 +6085,43 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>6100</v>
+        <v>6002</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="C143" t="s">
-        <v>225</v>
+        <v>99</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>6010</v>
+        <v>6100</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="C144" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C145" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C146" t="s">
         <v>99</v>
@@ -6125,142 +6129,142 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>6020</v>
+        <v>6012</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C147" t="s">
-        <v>231</v>
+        <v>99</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C149" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>6210</v>
+        <v>6040</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C150" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C151" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C152" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>6240</v>
+        <v>6230</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C153" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C154" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>6260</v>
+        <v>6250</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C155" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>6270</v>
+        <v>6260</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C156" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>6280</v>
+        <v>6270</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C157" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>6810</v>
+        <v>6280</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C158" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>6820</v>
+        <v>6810</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C159" t="s">
         <v>99</v>
@@ -6268,10 +6272,10 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>6830</v>
+        <v>6820</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C160" t="s">
         <v>99</v>
@@ -6279,10 +6283,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161">
-        <v>6840</v>
+        <v>6830</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C161" t="s">
         <v>99</v>
@@ -6290,10 +6294,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162">
-        <v>6850</v>
+        <v>6840</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C162" t="s">
         <v>99</v>
@@ -6301,10 +6305,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163">
-        <v>6860</v>
+        <v>6850</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C163" t="s">
         <v>99</v>
@@ -6312,10 +6316,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164">
-        <v>6870</v>
+        <v>6860</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C164" t="s">
         <v>99</v>
@@ -6323,10 +6327,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165">
-        <v>6880</v>
+        <v>6870</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C165" t="s">
         <v>99</v>
@@ -6334,60 +6338,60 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166">
+        <v>6880</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C166" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167">
         <v>6890</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B167" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C166" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="130">
-      <c r="A167">
+      <c r="C167" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="130">
+      <c r="A168">
         <v>12010</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B168" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C167" t="s">
-        <v>99</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="C168" t="s">
+        <v>99</v>
+      </c>
+      <c r="D168" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168">
-        <v>13010</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="C168" t="s">
-        <v>99</v>
-      </c>
-      <c r="D168" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169">
-        <v>13020</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>470</v>
+        <v>13010</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>447</v>
       </c>
       <c r="C169" t="s">
         <v>99</v>
+      </c>
+      <c r="D169" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170">
-        <v>13110</v>
-      </c>
-      <c r="B170" t="s">
-        <v>264</v>
+        <v>13020</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>470</v>
       </c>
       <c r="C170" t="s">
         <v>99</v>
@@ -6395,10 +6399,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171">
-        <v>13120</v>
+        <v>13110</v>
       </c>
       <c r="B171" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C171" t="s">
         <v>99</v>
@@ -6406,10 +6410,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172">
-        <v>13130</v>
+        <v>13120</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C172" t="s">
         <v>99</v>
@@ -6417,10 +6421,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173">
-        <v>13140</v>
+        <v>13130</v>
       </c>
       <c r="B173" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C173" t="s">
         <v>99</v>
@@ -6428,10 +6432,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174">
-        <v>13210</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>449</v>
+        <v>13140</v>
+      </c>
+      <c r="B174" t="s">
+        <v>267</v>
       </c>
       <c r="C174" t="s">
         <v>99</v>
@@ -6439,10 +6443,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175">
-        <v>13220</v>
+        <v>13210</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C175" t="s">
         <v>99</v>
@@ -6450,10 +6454,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176">
-        <v>13230</v>
+        <v>13220</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C176" t="s">
         <v>99</v>
@@ -6461,10 +6465,10 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>13240</v>
+        <v>13230</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C177" t="s">
         <v>99</v>
@@ -6472,10 +6476,10 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>13300</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>268</v>
+        <v>13240</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>451</v>
       </c>
       <c r="C178" t="s">
         <v>99</v>
@@ -6483,10 +6487,10 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>13301</v>
+        <v>13300</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C179" t="s">
         <v>99</v>
@@ -6494,10 +6498,10 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>13310</v>
+        <v>13301</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C180" t="s">
         <v>99</v>
@@ -6505,32 +6509,32 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
+        <v>13310</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C181" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182">
         <v>13320</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B182" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C181" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="26">
-      <c r="A182">
+      <c r="C182" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="26">
+      <c r="A183">
         <v>13330</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B183" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="C182" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
-      <c r="A183">
-        <v>13400</v>
-      </c>
-      <c r="B183" t="s">
-        <v>273</v>
       </c>
       <c r="C183" t="s">
         <v>99</v>
@@ -6538,32 +6542,32 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>13410</v>
+        <v>13400</v>
       </c>
       <c r="B184" t="s">
-        <v>34</v>
+        <v>273</v>
       </c>
       <c r="C184" t="s">
-        <v>274</v>
+        <v>99</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185">
-        <v>13420</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>275</v>
+        <v>13410</v>
+      </c>
+      <c r="B185" t="s">
+        <v>34</v>
       </c>
       <c r="C185" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>13421</v>
+        <v>13420</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C186" t="s">
         <v>99</v>
@@ -6571,10 +6575,10 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>13430</v>
+        <v>13421</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C187" t="s">
         <v>99</v>
@@ -6582,10 +6586,10 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>14090</v>
-      </c>
-      <c r="B188" t="s">
-        <v>278</v>
+        <v>13430</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="C188" t="s">
         <v>99</v>
@@ -6593,198 +6597,195 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
+        <v>14090</v>
+      </c>
+      <c r="B189" t="s">
+        <v>278</v>
+      </c>
+      <c r="C189" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190">
         <v>14110</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B190" t="s">
         <v>279</v>
       </c>
-      <c r="C189" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="14">
-      <c r="A190">
-        <v>15010</v>
-      </c>
-      <c r="B190" t="s">
-        <v>280</v>
-      </c>
       <c r="C190" t="s">
         <v>99</v>
       </c>
-      <c r="D190" t="s">
-        <v>281</v>
-      </c>
-      <c r="G190" s="1"/>
     </row>
     <row r="191" spans="1:7" ht="14">
       <c r="A191">
-        <v>16010</v>
+        <v>15010</v>
       </c>
       <c r="B191" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C191" t="s">
         <v>99</v>
       </c>
       <c r="D191" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G191" s="1"/>
     </row>
     <row r="192" spans="1:7" ht="14">
       <c r="A192">
+        <v>16010</v>
+      </c>
+      <c r="B192" t="s">
+        <v>282</v>
+      </c>
+      <c r="C192" t="s">
+        <v>99</v>
+      </c>
+      <c r="D192" t="s">
+        <v>283</v>
+      </c>
+      <c r="G192" s="1"/>
+    </row>
+    <row r="193" spans="1:7" ht="14">
+      <c r="A193">
         <v>16020</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B193" t="s">
         <v>284</v>
       </c>
-      <c r="C192" t="s">
-        <v>99</v>
-      </c>
-      <c r="G192" s="1"/>
-    </row>
-    <row r="193" spans="1:4">
-      <c r="A193">
+      <c r="C193" t="s">
+        <v>99</v>
+      </c>
+      <c r="G193" s="1"/>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194">
         <v>16100</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B194" t="s">
         <v>285</v>
       </c>
-      <c r="C193" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194">
+      <c r="C194" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195">
         <v>16110</v>
       </c>
-      <c r="B194" t="s">
+      <c r="B195" t="s">
         <v>286</v>
       </c>
-      <c r="C194" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195">
+      <c r="C195" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196">
         <v>16200</v>
       </c>
-      <c r="B195" t="s">
+      <c r="B196" t="s">
         <v>287</v>
       </c>
-      <c r="C195" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
-      <c r="A196">
+      <c r="C196" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197">
         <v>16210</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B197" t="s">
         <v>288</v>
       </c>
-      <c r="C196" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
-      <c r="A197">
+      <c r="C197" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198">
         <v>16220</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B198" t="s">
         <v>289</v>
       </c>
-      <c r="C197" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
-      <c r="A198">
+      <c r="C198" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199">
         <v>16230</v>
       </c>
-      <c r="B198" t="s">
+      <c r="B199" t="s">
         <v>290</v>
       </c>
-      <c r="C198" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
-      <c r="A199">
+      <c r="C199" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200">
         <v>16300</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B200" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C199" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4">
-      <c r="A200">
+      <c r="C200" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201">
         <v>16310</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="B201" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C200" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
-      <c r="A201">
+      <c r="C201" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202">
         <v>16320</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="B202" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C201" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
-      <c r="A202">
+      <c r="C202" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203">
         <v>16400</v>
       </c>
-      <c r="B202" s="2" t="s">
+      <c r="B203" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C202" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
-      <c r="A203">
+      <c r="C203" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204">
         <v>16410</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="B204" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C203" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
-      <c r="A204">
+      <c r="C204" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205">
         <v>16800</v>
       </c>
-      <c r="B204" t="s">
+      <c r="B205" t="s">
         <v>183</v>
-      </c>
-      <c r="C204" t="s">
-        <v>99</v>
-      </c>
-      <c r="D204" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
-      <c r="A205">
-        <v>16801</v>
-      </c>
-      <c r="B205" t="s">
-        <v>184</v>
       </c>
       <c r="C205" t="s">
         <v>99</v>
@@ -6793,12 +6794,12 @@
         <v>296</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:7">
       <c r="A206">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B206" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C206" t="s">
         <v>99</v>
@@ -6807,12 +6808,12 @@
         <v>296</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:7">
       <c r="A207">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B207" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C207" t="s">
         <v>99</v>
@@ -6821,12 +6822,12 @@
         <v>296</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:7">
       <c r="A208">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B208" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C208" t="s">
         <v>99</v>
@@ -6837,10 +6838,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B209" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C209" t="s">
         <v>99</v>
@@ -6851,10 +6852,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210">
-        <v>16806</v>
+        <v>16805</v>
       </c>
       <c r="B210" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C210" t="s">
         <v>99</v>
@@ -6865,46 +6866,49 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211">
-        <v>17010</v>
+        <v>16806</v>
       </c>
       <c r="B211" t="s">
-        <v>297</v>
+        <v>189</v>
       </c>
       <c r="C211" t="s">
         <v>99</v>
+      </c>
+      <c r="D211" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212">
-        <v>18010</v>
+        <v>17010</v>
       </c>
       <c r="B212" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C212" t="s">
         <v>99</v>
-      </c>
-      <c r="D212" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213">
-        <v>18020</v>
+        <v>18010</v>
       </c>
       <c r="B213" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C213" t="s">
         <v>99</v>
+      </c>
+      <c r="D213" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214">
-        <v>18100</v>
+        <v>18020</v>
       </c>
       <c r="B214" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="C214" t="s">
         <v>99</v>
@@ -6912,10 +6916,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215">
-        <v>18110</v>
+        <v>18100</v>
       </c>
       <c r="B215" t="s">
-        <v>301</v>
+        <v>194</v>
       </c>
       <c r="C215" t="s">
         <v>99</v>
@@ -6923,10 +6927,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216">
-        <v>18120</v>
+        <v>18110</v>
       </c>
       <c r="B216" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C216" t="s">
         <v>99</v>
@@ -6934,10 +6938,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217">
-        <v>18130</v>
+        <v>18120</v>
       </c>
       <c r="B217" t="s">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="C217" t="s">
         <v>99</v>
@@ -6945,10 +6949,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218">
-        <v>18200</v>
+        <v>18130</v>
       </c>
       <c r="B218" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="C218" t="s">
         <v>99</v>
@@ -6956,10 +6960,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219">
-        <v>18210</v>
+        <v>18200</v>
       </c>
       <c r="B219" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C219" t="s">
         <v>99</v>
@@ -6967,10 +6971,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220">
-        <v>18220</v>
+        <v>18210</v>
       </c>
       <c r="B220" t="s">
-        <v>303</v>
+        <v>108</v>
       </c>
       <c r="C220" t="s">
         <v>99</v>
@@ -6978,10 +6982,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221">
-        <v>18300</v>
+        <v>18220</v>
       </c>
       <c r="B221" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C221" t="s">
         <v>99</v>
@@ -6989,10 +6993,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222">
-        <v>18310</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>481</v>
+        <v>18300</v>
+      </c>
+      <c r="B222" t="s">
+        <v>304</v>
       </c>
       <c r="C222" t="s">
         <v>99</v>
@@ -7000,10 +7004,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223">
-        <v>18320</v>
-      </c>
-      <c r="B223" t="s">
-        <v>305</v>
+        <v>18310</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="C223" t="s">
         <v>99</v>
@@ -7011,10 +7015,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224">
-        <v>18340</v>
+        <v>18320</v>
       </c>
       <c r="B224" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C224" t="s">
         <v>99</v>
@@ -7022,10 +7026,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18400</v>
+        <v>18340</v>
       </c>
       <c r="B225" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C225" t="s">
         <v>99</v>
@@ -7033,10 +7037,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B226" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C226" t="s">
         <v>99</v>
@@ -7044,10 +7048,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B227" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C227" t="s">
         <v>99</v>
@@ -7055,10 +7059,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B228" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C228" t="s">
         <v>99</v>
@@ -7066,10 +7070,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B229" t="s">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="C229" t="s">
         <v>99</v>
@@ -7077,10 +7081,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B230" t="s">
-        <v>311</v>
+        <v>100</v>
       </c>
       <c r="C230" t="s">
         <v>99</v>
@@ -7088,10 +7092,10 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B231" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C231" t="s">
         <v>99</v>
@@ -7099,10 +7103,10 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18510</v>
+        <v>18500</v>
       </c>
       <c r="B232" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C232" t="s">
         <v>99</v>
@@ -7110,10 +7114,10 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>18800</v>
+        <v>18510</v>
       </c>
       <c r="B233" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C233" t="s">
         <v>99</v>
@@ -7121,10 +7125,10 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B234" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C234" t="s">
         <v>99</v>
@@ -7132,10 +7136,10 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B235" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C235" t="s">
         <v>99</v>
@@ -7143,10 +7147,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B236" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C236" t="s">
         <v>99</v>
@@ -7154,10 +7158,10 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B237" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C237" t="s">
         <v>99</v>
@@ -7165,10 +7169,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B238" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C238" t="s">
         <v>99</v>
@@ -7176,10 +7180,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B239" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C239" t="s">
         <v>99</v>
@@ -7187,10 +7191,10 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B240" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C240" t="s">
         <v>99</v>
@@ -7198,47 +7202,47 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241">
+        <v>18811</v>
+      </c>
+      <c r="B241" t="s">
+        <v>321</v>
+      </c>
+      <c r="C241" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242">
         <v>18812</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B242" t="s">
         <v>322</v>
       </c>
-      <c r="C241" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="14">
-      <c r="A242">
+      <c r="C242" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="14">
+      <c r="A243">
         <v>19000</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B243" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C242" t="s">
-        <v>99</v>
-      </c>
-      <c r="D242" t="s">
+      <c r="C243" t="s">
+        <v>99</v>
+      </c>
+      <c r="D243" t="s">
         <v>323</v>
       </c>
-      <c r="G242" s="1"/>
-    </row>
-    <row r="243" spans="1:7">
-      <c r="A243">
-        <v>19001</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C243" t="s">
-        <v>99</v>
-      </c>
+      <c r="G243" s="1"/>
     </row>
     <row r="244" spans="1:7">
       <c r="A244">
-        <v>19002</v>
+        <v>19001</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C244" t="s">
         <v>99</v>
@@ -7246,10 +7250,10 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245">
-        <v>19003</v>
+        <v>19002</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C245" t="s">
         <v>99</v>
@@ -7257,7 +7261,7 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246">
-        <v>19004</v>
+        <v>19003</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>463</v>
@@ -7268,10 +7272,10 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247">
-        <v>19005</v>
+        <v>19004</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C247" t="s">
         <v>99</v>
@@ -7279,10 +7283,10 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248">
-        <v>19006</v>
+        <v>19005</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C248" t="s">
         <v>99</v>
@@ -7290,10 +7294,10 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249">
-        <v>19007</v>
+        <v>19006</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C249" t="s">
         <v>99</v>
@@ -7301,10 +7305,10 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250">
-        <v>19008</v>
+        <v>19007</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C250" t="s">
         <v>99</v>
@@ -7312,10 +7316,10 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251">
-        <v>19009</v>
+        <v>19008</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C251" t="s">
         <v>99</v>
@@ -7323,10 +7327,10 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252">
-        <v>19010</v>
+        <v>19009</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C252" t="s">
         <v>99</v>
@@ -7334,10 +7338,10 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253">
-        <v>19011</v>
+        <v>19010</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7345,10 +7349,10 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254">
-        <v>19100</v>
-      </c>
-      <c r="B254" t="s">
-        <v>328</v>
+        <v>19011</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7356,10 +7360,10 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B255" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7367,10 +7371,10 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256">
-        <v>19200</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>330</v>
+        <v>19110</v>
+      </c>
+      <c r="B256" t="s">
+        <v>329</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7378,10 +7382,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7389,10 +7393,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7400,10 +7404,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7411,10 +7415,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19240</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>478</v>
+        <v>19230</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7422,10 +7426,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19250</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>334</v>
+        <v>19240</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>477</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7433,10 +7437,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19260</v>
-      </c>
-      <c r="B262" s="5" t="s">
-        <v>482</v>
+        <v>19250</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>334</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7444,10 +7448,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19270</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>335</v>
+        <v>19260</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
@@ -7455,10 +7459,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19280</v>
-      </c>
-      <c r="B264" s="5" t="s">
-        <v>483</v>
+        <v>19270</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="C264" t="s">
         <v>99</v>
@@ -7466,32 +7470,32 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
+        <v>19280</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C265" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266">
         <v>19300</v>
       </c>
-      <c r="B265" t="s">
+      <c r="B266" t="s">
         <v>336</v>
       </c>
-      <c r="C265" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" ht="26">
-      <c r="A266">
+      <c r="C266" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="26">
+      <c r="A267">
         <v>19310</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B267" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C266" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3">
-      <c r="A267">
-        <v>19320</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C267" t="s">
         <v>99</v>
@@ -7499,10 +7503,10 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19330</v>
-      </c>
-      <c r="B268" t="s">
-        <v>339</v>
+        <v>19320</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="C268" t="s">
         <v>99</v>
@@ -7510,10 +7514,10 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B269" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7521,10 +7525,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B270" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7532,10 +7536,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B271" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7543,10 +7547,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19400</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>343</v>
+        <v>19360</v>
+      </c>
+      <c r="B272" t="s">
+        <v>342</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7554,10 +7558,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7565,10 +7569,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19410</v>
-      </c>
-      <c r="B274" s="5" t="s">
-        <v>484</v>
+        <v>19401</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7576,10 +7580,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19420</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>345</v>
+        <v>19410</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>483</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7587,10 +7591,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19500</v>
-      </c>
-      <c r="B276" t="s">
-        <v>346</v>
+        <v>19420</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7598,10 +7602,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19510</v>
-      </c>
-      <c r="B277" s="5" t="s">
-        <v>482</v>
+        <v>19500</v>
+      </c>
+      <c r="B277" t="s">
+        <v>346</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7609,10 +7613,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19520</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>347</v>
+        <v>19510</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7620,10 +7624,10 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7631,10 +7635,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7642,10 +7646,10 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
@@ -7653,10 +7657,10 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C282" t="s">
         <v>99</v>
@@ -7664,48 +7668,47 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283">
+        <v>19603</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C283" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284">
         <v>19604</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="B284" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C283" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="14">
-      <c r="A284">
-        <v>19611</v>
-      </c>
-      <c r="B284" t="s">
-        <v>353</v>
-      </c>
       <c r="C284" t="s">
         <v>99</v>
       </c>
-      <c r="D284" t="s">
-        <v>354</v>
-      </c>
-      <c r="G284" s="1"/>
     </row>
     <row r="285" spans="1:7" ht="14">
       <c r="A285">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B285" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C285" t="s">
         <v>99</v>
+      </c>
+      <c r="D285" t="s">
+        <v>354</v>
       </c>
       <c r="G285" s="1"/>
     </row>
     <row r="286" spans="1:7" ht="14">
       <c r="A286">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B286" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
@@ -7714,10 +7717,10 @@
     </row>
     <row r="287" spans="1:7" ht="14">
       <c r="A287">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B287" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
@@ -7726,10 +7729,10 @@
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B288" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
@@ -7738,10 +7741,10 @@
     </row>
     <row r="289" spans="1:7" ht="14">
       <c r="A289">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B289" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7750,10 +7753,10 @@
     </row>
     <row r="290" spans="1:7" ht="14">
       <c r="A290">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B290" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C290" t="s">
         <v>99</v>
@@ -7762,10 +7765,10 @@
     </row>
     <row r="291" spans="1:7" ht="14">
       <c r="A291">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B291" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C291" t="s">
         <v>99</v>
@@ -7774,47 +7777,48 @@
     </row>
     <row r="292" spans="1:7" ht="14">
       <c r="A292">
+        <v>19618</v>
+      </c>
+      <c r="B292" t="s">
+        <v>361</v>
+      </c>
+      <c r="C292" t="s">
+        <v>99</v>
+      </c>
+      <c r="G292" s="1"/>
+    </row>
+    <row r="293" spans="1:7" ht="14">
+      <c r="A293">
         <v>19619</v>
       </c>
-      <c r="B292" t="s">
+      <c r="B293" t="s">
         <v>362</v>
       </c>
-      <c r="C292" t="s">
-        <v>99</v>
-      </c>
-      <c r="G292" s="1"/>
-    </row>
-    <row r="293" spans="1:7">
-      <c r="A293">
-        <v>19631</v>
-      </c>
-      <c r="B293" t="s">
-        <v>363</v>
-      </c>
       <c r="C293" t="s">
         <v>99</v>
       </c>
-      <c r="D293" t="s">
-        <v>364</v>
-      </c>
+      <c r="G293" s="1"/>
     </row>
     <row r="294" spans="1:7">
       <c r="A294">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="B294" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C294" t="s">
         <v>99</v>
+      </c>
+      <c r="D294" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="295" spans="1:7">
       <c r="A295">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B295" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C295" t="s">
         <v>99</v>
@@ -7822,10 +7826,10 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B296" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C296" t="s">
         <v>99</v>
@@ -7833,10 +7837,10 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297">
-        <v>19700</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>368</v>
+        <v>19634</v>
+      </c>
+      <c r="B297" t="s">
+        <v>367</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
@@ -7844,10 +7848,10 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7855,10 +7859,10 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7866,10 +7870,10 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C300" t="s">
         <v>99</v>
@@ -7877,10 +7881,10 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C301" t="s">
         <v>99</v>
@@ -7888,211 +7892,211 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302">
-        <v>19800</v>
-      </c>
-      <c r="B302" t="s">
-        <v>372</v>
+        <v>19740</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="C302" t="s">
-        <v>373</v>
+        <v>99</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B303" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C303" t="s">
-        <v>99</v>
+        <v>373</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304">
+        <v>19810</v>
+      </c>
+      <c r="B304" t="s">
+        <v>374</v>
+      </c>
+      <c r="C304" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305">
         <v>20010</v>
       </c>
-      <c r="B304" t="s">
+      <c r="B305" t="s">
         <v>375</v>
       </c>
-      <c r="C304" t="s">
-        <v>99</v>
-      </c>
-      <c r="D304" t="s">
+      <c r="C305" t="s">
+        <v>99</v>
+      </c>
+      <c r="D305" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
-      <c r="A305">
+    <row r="306" spans="1:4">
+      <c r="A306">
         <v>20020</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B306" t="s">
         <v>377</v>
       </c>
-      <c r="C305" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3">
-      <c r="A306">
+      <c r="C306" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307">
         <v>20030</v>
       </c>
-      <c r="B306" s="2" t="s">
+      <c r="B307" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C306" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
-      <c r="A307">
+      <c r="C307" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308">
         <v>20040</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B308" t="s">
         <v>379</v>
       </c>
-      <c r="C307" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3">
-      <c r="A308">
+      <c r="C308" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309">
         <v>20050</v>
       </c>
-      <c r="B308" t="s">
+      <c r="B309" t="s">
         <v>380</v>
       </c>
-      <c r="C308" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
-      <c r="A309">
+      <c r="C309" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310">
         <v>20100</v>
       </c>
-      <c r="B309" t="s">
+      <c r="B310" t="s">
         <v>381</v>
       </c>
-      <c r="C309" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
-      <c r="A310">
+      <c r="C310" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311">
         <v>20110</v>
       </c>
-      <c r="B310" t="s">
+      <c r="B311" t="s">
         <v>382</v>
       </c>
-      <c r="C310" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3">
-      <c r="A311">
+      <c r="C311" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312">
         <v>20120</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B312" t="s">
         <v>383</v>
       </c>
-      <c r="C311" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3">
-      <c r="A312">
+      <c r="C312" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313">
         <v>20200</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B313" t="s">
         <v>384</v>
       </c>
-      <c r="C312" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
-      <c r="A313">
+      <c r="C313" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314">
         <v>20201</v>
       </c>
-      <c r="B313" t="s">
+      <c r="B314" t="s">
         <v>311</v>
       </c>
-      <c r="C313" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3">
-      <c r="A314">
+      <c r="C314" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315">
         <v>20210</v>
       </c>
-      <c r="B314" t="s">
+      <c r="B315" t="s">
         <v>385</v>
       </c>
-      <c r="C314" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3">
-      <c r="A315">
+      <c r="C315" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316">
         <v>20220</v>
       </c>
-      <c r="B315" t="s">
+      <c r="B316" t="s">
         <v>386</v>
       </c>
-      <c r="C315" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3">
-      <c r="A316">
+      <c r="C316" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317">
         <v>20230</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="B317" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C316" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3">
-      <c r="A317">
+      <c r="C317" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318">
         <v>20240</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="B318" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C317" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3">
-      <c r="A318">
+      <c r="C318" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319">
         <v>20250</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="B319" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C318" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
-      <c r="A319">
+      <c r="C319" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320">
         <v>20260</v>
       </c>
-      <c r="B319" t="s">
+      <c r="B320" t="s">
         <v>390</v>
-      </c>
-      <c r="C319" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3">
-      <c r="A320">
-        <v>20270</v>
-      </c>
-      <c r="B320" t="s">
-        <v>391</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8100,10 +8104,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B321" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8111,10 +8115,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B322" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8122,10 +8126,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B323" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8133,10 +8137,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B324" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8144,10 +8148,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B325" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8155,10 +8159,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B326" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8166,10 +8170,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B327" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8177,10 +8181,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B328" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8188,10 +8192,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B329" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8199,10 +8203,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B330" t="s">
-        <v>103</v>
+        <v>400</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8210,10 +8214,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B331" t="s">
-        <v>401</v>
+        <v>103</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8221,10 +8225,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B332" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8232,10 +8236,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B333" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8243,10 +8247,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B334" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8254,10 +8258,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B335" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8265,10 +8269,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B336" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8276,10 +8280,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B337" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8287,10 +8291,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B338" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8298,10 +8302,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B339" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8309,10 +8313,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B340" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8320,10 +8324,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B341" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8331,10 +8335,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B342" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8342,10 +8346,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B343" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8353,10 +8357,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B344" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8364,10 +8368,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B345" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8375,10 +8379,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B346" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8386,10 +8390,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B347" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8397,10 +8401,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B348" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8408,10 +8412,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B349" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8419,10 +8423,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B350" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8430,10 +8434,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B351" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8441,10 +8445,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B352" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8452,10 +8456,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B353" t="s">
-        <v>422</v>
+        <v>324</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8463,10 +8467,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B354" t="s">
-        <v>101</v>
+        <v>422</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8474,10 +8478,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B355" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8485,10 +8489,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B356" t="s">
-        <v>423</v>
+        <v>123</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8496,10 +8500,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B357" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
@@ -8507,10 +8511,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B358" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
@@ -8518,35 +8522,35 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B359" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
-      </c>
-      <c r="D359" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>102010</v>
+        <v>102000</v>
       </c>
       <c r="B360" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
+      </c>
+      <c r="D360" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B361" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
@@ -8554,10 +8558,10 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>102030</v>
+        <v>102020</v>
       </c>
       <c r="B362" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
@@ -8565,35 +8569,35 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>113000</v>
+        <v>102030</v>
       </c>
       <c r="B363" t="s">
-        <v>428</v>
+        <v>325</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
-      </c>
-      <c r="D363" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>113010</v>
+        <v>113000</v>
       </c>
       <c r="B364" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
+      </c>
+      <c r="D364" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B365" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
@@ -8601,10 +8605,10 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B366" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
@@ -8612,10 +8616,10 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B367" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
@@ -8623,141 +8627,153 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
+        <v>113040</v>
+      </c>
+      <c r="B368" t="s">
+        <v>433</v>
+      </c>
+      <c r="C368" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369">
         <v>121010</v>
       </c>
-      <c r="B368" t="s">
+      <c r="B369" t="s">
         <v>434</v>
       </c>
-      <c r="C368" t="s">
-        <v>99</v>
-      </c>
-      <c r="D368" t="s">
+      <c r="C369" t="s">
+        <v>99</v>
+      </c>
+      <c r="D369" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
-      <c r="A369">
+    <row r="370" spans="1:4">
+      <c r="A370">
         <v>121011</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B370" t="s">
         <v>436</v>
       </c>
-      <c r="C369" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3">
-      <c r="A370">
+      <c r="C370" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371">
         <v>121012</v>
       </c>
-      <c r="B370" t="s">
+      <c r="B371" t="s">
         <v>437</v>
       </c>
-      <c r="C370" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3">
-      <c r="A371">
+      <c r="C371" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372">
         <v>121013</v>
       </c>
-      <c r="B371" t="s">
+      <c r="B372" t="s">
         <v>438</v>
       </c>
-      <c r="C371" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3">
-      <c r="A372">
+      <c r="C372" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373">
         <v>121014</v>
       </c>
-      <c r="B372" t="s">
+      <c r="B373" t="s">
         <v>439</v>
       </c>
-      <c r="C372" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3">
-      <c r="A373">
+      <c r="C373" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374">
         <v>121015</v>
       </c>
-      <c r="B373" t="s">
+      <c r="B374" t="s">
         <v>440</v>
       </c>
-      <c r="C373" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3">
-      <c r="A374">
+      <c r="C374" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375">
         <v>121016</v>
       </c>
-      <c r="B374" t="s">
+      <c r="B375" t="s">
         <v>441</v>
       </c>
-      <c r="C374" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3">
-      <c r="A375">
+      <c r="C375" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376">
         <v>121017</v>
       </c>
-      <c r="B375" t="s">
+      <c r="B376" t="s">
         <v>442</v>
       </c>
-      <c r="C375" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3">
-      <c r="A376">
+      <c r="C376" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377">
         <v>121018</v>
       </c>
-      <c r="B376" t="s">
+      <c r="B377" t="s">
         <v>443</v>
       </c>
-      <c r="C376" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3">
-      <c r="A377">
+      <c r="C377" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378">
         <v>121019</v>
       </c>
-      <c r="B377" t="s">
+      <c r="B378" t="s">
         <v>444</v>
       </c>
-      <c r="C377" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3">
-      <c r="A378">
+      <c r="C378" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379">
         <v>121020</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B379" t="s">
         <v>445</v>
       </c>
-      <c r="C378" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3">
-      <c r="A379">
+      <c r="C379" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380">
         <v>121030</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B380" t="s">
         <v>446</v>
       </c>
-      <c r="C379" t="s">
+      <c r="C380" t="s">
         <v>99</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB1F6BF-623F-46A1-A948-CB0176300EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D63740A-8DAA-4FD9-9231-5295656F1DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="487">
   <si>
     <t>Id</t>
   </si>
@@ -1590,6 +1590,13 @@
   </si>
   <si>
     <t>MOV</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>所持</t>
+    <rPh sb="0" eb="2">
+      <t>ショジ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -4450,7 +4457,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G380"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -6993,10 +7000,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222">
-        <v>18300</v>
-      </c>
-      <c r="B222" t="s">
-        <v>304</v>
+        <v>18230</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>486</v>
       </c>
       <c r="C222" t="s">
         <v>99</v>
@@ -7004,10 +7011,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223">
-        <v>18310</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>480</v>
+        <v>18300</v>
+      </c>
+      <c r="B223" t="s">
+        <v>304</v>
       </c>
       <c r="C223" t="s">
         <v>99</v>
@@ -7015,10 +7022,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224">
-        <v>18320</v>
-      </c>
-      <c r="B224" t="s">
-        <v>305</v>
+        <v>18310</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="C224" t="s">
         <v>99</v>
@@ -7026,10 +7033,10 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18340</v>
+        <v>18320</v>
       </c>
       <c r="B225" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C225" t="s">
         <v>99</v>
@@ -7037,10 +7044,10 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18400</v>
+        <v>18340</v>
       </c>
       <c r="B226" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C226" t="s">
         <v>99</v>
@@ -7048,10 +7055,10 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B227" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C227" t="s">
         <v>99</v>
@@ -7059,10 +7066,10 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B228" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C228" t="s">
         <v>99</v>
@@ -7070,10 +7077,10 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B229" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C229" t="s">
         <v>99</v>
@@ -7081,10 +7088,10 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B230" t="s">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="C230" t="s">
         <v>99</v>
@@ -7092,10 +7099,10 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B231" t="s">
-        <v>311</v>
+        <v>100</v>
       </c>
       <c r="C231" t="s">
         <v>99</v>
@@ -7103,10 +7110,10 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B232" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C232" t="s">
         <v>99</v>
@@ -7114,10 +7121,10 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>18510</v>
+        <v>18500</v>
       </c>
       <c r="B233" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C233" t="s">
         <v>99</v>
@@ -7125,10 +7132,10 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>18800</v>
+        <v>18510</v>
       </c>
       <c r="B234" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C234" t="s">
         <v>99</v>
@@ -7136,10 +7143,10 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B235" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C235" t="s">
         <v>99</v>
@@ -7147,10 +7154,10 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B236" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C236" t="s">
         <v>99</v>
@@ -7158,10 +7165,10 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B237" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C237" t="s">
         <v>99</v>
@@ -7169,10 +7176,10 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B238" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C238" t="s">
         <v>99</v>
@@ -7180,10 +7187,10 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B239" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C239" t="s">
         <v>99</v>
@@ -7191,10 +7198,10 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B240" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C240" t="s">
         <v>99</v>
@@ -7202,10 +7209,10 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B241" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C241" t="s">
         <v>99</v>
@@ -7213,47 +7220,47 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242">
+        <v>18811</v>
+      </c>
+      <c r="B242" t="s">
+        <v>321</v>
+      </c>
+      <c r="C242" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243">
         <v>18812</v>
       </c>
-      <c r="B242" t="s">
+      <c r="B243" t="s">
         <v>322</v>
       </c>
-      <c r="C242" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="14">
-      <c r="A243">
+      <c r="C243" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="14">
+      <c r="A244">
         <v>19000</v>
       </c>
-      <c r="B243" s="4" t="s">
+      <c r="B244" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C243" t="s">
-        <v>99</v>
-      </c>
-      <c r="D243" t="s">
+      <c r="C244" t="s">
+        <v>99</v>
+      </c>
+      <c r="D244" t="s">
         <v>323</v>
       </c>
-      <c r="G243" s="1"/>
-    </row>
-    <row r="244" spans="1:7">
-      <c r="A244">
-        <v>19001</v>
-      </c>
-      <c r="B244" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C244" t="s">
-        <v>99</v>
-      </c>
+      <c r="G244" s="1"/>
     </row>
     <row r="245" spans="1:7">
       <c r="A245">
-        <v>19002</v>
+        <v>19001</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C245" t="s">
         <v>99</v>
@@ -7261,10 +7268,10 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246">
-        <v>19003</v>
+        <v>19002</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C246" t="s">
         <v>99</v>
@@ -7272,7 +7279,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247">
-        <v>19004</v>
+        <v>19003</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>463</v>
@@ -7283,10 +7290,10 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248">
-        <v>19005</v>
+        <v>19004</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C248" t="s">
         <v>99</v>
@@ -7294,10 +7301,10 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249">
-        <v>19006</v>
+        <v>19005</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C249" t="s">
         <v>99</v>
@@ -7305,10 +7312,10 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250">
-        <v>19007</v>
+        <v>19006</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C250" t="s">
         <v>99</v>
@@ -7316,10 +7323,10 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251">
-        <v>19008</v>
+        <v>19007</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C251" t="s">
         <v>99</v>
@@ -7327,10 +7334,10 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252">
-        <v>19009</v>
+        <v>19008</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C252" t="s">
         <v>99</v>
@@ -7338,10 +7345,10 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253">
-        <v>19010</v>
+        <v>19009</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7349,10 +7356,10 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254">
-        <v>19011</v>
+        <v>19010</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7360,10 +7367,10 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255">
-        <v>19100</v>
-      </c>
-      <c r="B255" t="s">
-        <v>328</v>
+        <v>19011</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7371,10 +7378,10 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B256" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7382,10 +7389,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19200</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>330</v>
+        <v>19110</v>
+      </c>
+      <c r="B257" t="s">
+        <v>329</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7393,10 +7400,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7404,10 +7411,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7415,10 +7422,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7426,10 +7433,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19240</v>
-      </c>
-      <c r="B261" s="5" t="s">
-        <v>477</v>
+        <v>19230</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7437,10 +7444,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19250</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>334</v>
+        <v>19240</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>477</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7448,10 +7455,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19260</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>481</v>
+        <v>19250</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>334</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
@@ -7459,10 +7466,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19270</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>335</v>
+        <v>19260</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C264" t="s">
         <v>99</v>
@@ -7470,10 +7477,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19280</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>482</v>
+        <v>19270</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="C265" t="s">
         <v>99</v>
@@ -7481,32 +7488,32 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
+        <v>19280</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C266" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267">
         <v>19300</v>
       </c>
-      <c r="B266" t="s">
+      <c r="B267" t="s">
         <v>336</v>
       </c>
-      <c r="C266" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="26">
-      <c r="A267">
+      <c r="C267" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="26">
+      <c r="A268">
         <v>19310</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="B268" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C267" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3">
-      <c r="A268">
-        <v>19320</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C268" t="s">
         <v>99</v>
@@ -7514,10 +7521,10 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19330</v>
-      </c>
-      <c r="B269" t="s">
-        <v>339</v>
+        <v>19320</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7525,10 +7532,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B270" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7536,10 +7543,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B271" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7547,10 +7554,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B272" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7558,10 +7565,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19400</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>343</v>
+        <v>19360</v>
+      </c>
+      <c r="B273" t="s">
+        <v>342</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7569,10 +7576,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7580,10 +7587,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19410</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>483</v>
+        <v>19401</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7591,10 +7598,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19420</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>345</v>
+        <v>19410</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>483</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7602,10 +7609,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19500</v>
-      </c>
-      <c r="B277" t="s">
-        <v>346</v>
+        <v>19420</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7613,10 +7620,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19510</v>
-      </c>
-      <c r="B278" s="5" t="s">
-        <v>481</v>
+        <v>19500</v>
+      </c>
+      <c r="B278" t="s">
+        <v>346</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7624,10 +7631,10 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>19520</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>347</v>
+        <v>19510</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7635,10 +7642,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7646,10 +7653,10 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
@@ -7657,10 +7664,10 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C282" t="s">
         <v>99</v>
@@ -7668,10 +7675,10 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C283" t="s">
         <v>99</v>
@@ -7679,48 +7686,47 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284">
+        <v>19603</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C284" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285">
         <v>19604</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="B285" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C284" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="14">
-      <c r="A285">
-        <v>19611</v>
-      </c>
-      <c r="B285" t="s">
-        <v>353</v>
-      </c>
       <c r="C285" t="s">
         <v>99</v>
       </c>
-      <c r="D285" t="s">
-        <v>354</v>
-      </c>
-      <c r="G285" s="1"/>
     </row>
     <row r="286" spans="1:7" ht="14">
       <c r="A286">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B286" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
+      </c>
+      <c r="D286" t="s">
+        <v>354</v>
       </c>
       <c r="G286" s="1"/>
     </row>
     <row r="287" spans="1:7" ht="14">
       <c r="A287">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B287" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
@@ -7729,10 +7735,10 @@
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B288" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
@@ -7741,10 +7747,10 @@
     </row>
     <row r="289" spans="1:7" ht="14">
       <c r="A289">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B289" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7753,10 +7759,10 @@
     </row>
     <row r="290" spans="1:7" ht="14">
       <c r="A290">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B290" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C290" t="s">
         <v>99</v>
@@ -7765,10 +7771,10 @@
     </row>
     <row r="291" spans="1:7" ht="14">
       <c r="A291">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B291" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C291" t="s">
         <v>99</v>
@@ -7777,10 +7783,10 @@
     </row>
     <row r="292" spans="1:7" ht="14">
       <c r="A292">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B292" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C292" t="s">
         <v>99</v>
@@ -7789,47 +7795,48 @@
     </row>
     <row r="293" spans="1:7" ht="14">
       <c r="A293">
+        <v>19618</v>
+      </c>
+      <c r="B293" t="s">
+        <v>361</v>
+      </c>
+      <c r="C293" t="s">
+        <v>99</v>
+      </c>
+      <c r="G293" s="1"/>
+    </row>
+    <row r="294" spans="1:7" ht="14">
+      <c r="A294">
         <v>19619</v>
       </c>
-      <c r="B293" t="s">
+      <c r="B294" t="s">
         <v>362</v>
       </c>
-      <c r="C293" t="s">
-        <v>99</v>
-      </c>
-      <c r="G293" s="1"/>
-    </row>
-    <row r="294" spans="1:7">
-      <c r="A294">
-        <v>19631</v>
-      </c>
-      <c r="B294" t="s">
-        <v>363</v>
-      </c>
       <c r="C294" t="s">
         <v>99</v>
       </c>
-      <c r="D294" t="s">
-        <v>364</v>
-      </c>
+      <c r="G294" s="1"/>
     </row>
     <row r="295" spans="1:7">
       <c r="A295">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="B295" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C295" t="s">
         <v>99</v>
+      </c>
+      <c r="D295" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="296" spans="1:7">
       <c r="A296">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B296" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C296" t="s">
         <v>99</v>
@@ -7837,10 +7844,10 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B297" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
@@ -7848,10 +7855,10 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298">
-        <v>19700</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>368</v>
+        <v>19634</v>
+      </c>
+      <c r="B298" t="s">
+        <v>367</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7859,10 +7866,10 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7870,10 +7877,10 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="C300" t="s">
         <v>99</v>
@@ -7881,10 +7888,10 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C301" t="s">
         <v>99</v>
@@ -7892,10 +7899,10 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C302" t="s">
         <v>99</v>
@@ -7903,57 +7910,57 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303">
-        <v>19800</v>
-      </c>
-      <c r="B303" t="s">
-        <v>372</v>
+        <v>19740</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="C303" t="s">
-        <v>373</v>
+        <v>99</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B304" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C304" t="s">
-        <v>99</v>
+        <v>373</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305">
-        <v>20010</v>
+        <v>19810</v>
       </c>
       <c r="B305" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C305" t="s">
         <v>99</v>
-      </c>
-      <c r="D305" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B306" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C306" t="s">
         <v>99</v>
+      </c>
+      <c r="D306" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307">
-        <v>20030</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>378</v>
+        <v>20020</v>
+      </c>
+      <c r="B307" t="s">
+        <v>377</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
@@ -7961,10 +7968,10 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308">
-        <v>20040</v>
-      </c>
-      <c r="B308" t="s">
-        <v>379</v>
+        <v>20030</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
@@ -7972,10 +7979,10 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B309" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -7983,10 +7990,10 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B310" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -7994,10 +8001,10 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B311" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -8005,10 +8012,10 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B312" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -8016,10 +8023,10 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B313" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -8027,10 +8034,10 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B314" t="s">
-        <v>311</v>
+        <v>384</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -8038,10 +8045,10 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B315" t="s">
-        <v>385</v>
+        <v>311</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -8049,10 +8056,10 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B316" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -8060,10 +8067,10 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317">
-        <v>20230</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>387</v>
+        <v>20220</v>
+      </c>
+      <c r="B317" t="s">
+        <v>386</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -8071,10 +8078,10 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -8082,10 +8089,10 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -8093,10 +8100,10 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320">
-        <v>20260</v>
-      </c>
-      <c r="B320" t="s">
-        <v>390</v>
+        <v>20250</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8104,10 +8111,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B321" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8115,10 +8122,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B322" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8126,10 +8133,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B323" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8137,10 +8144,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B324" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8148,10 +8155,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B325" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8159,10 +8166,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B326" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8170,10 +8177,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B327" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8181,10 +8188,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B328" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8192,10 +8199,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B329" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8203,10 +8210,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B330" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8214,10 +8221,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B331" t="s">
-        <v>103</v>
+        <v>400</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8225,10 +8232,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B332" t="s">
-        <v>401</v>
+        <v>103</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8236,10 +8243,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B333" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8247,10 +8254,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B334" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8258,10 +8265,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B335" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8269,10 +8276,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B336" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8280,10 +8287,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B337" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8291,10 +8298,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B338" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8302,10 +8309,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B339" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8313,10 +8320,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B340" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8324,10 +8331,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B341" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8335,10 +8342,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B342" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8346,10 +8353,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B343" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8357,10 +8364,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B344" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8368,10 +8375,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B345" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8379,10 +8386,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B346" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8390,10 +8397,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B347" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8401,10 +8408,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B348" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8412,10 +8419,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B349" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8423,10 +8430,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B350" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8434,10 +8441,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B351" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8445,10 +8452,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B352" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8456,10 +8463,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B353" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8467,10 +8474,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B354" t="s">
-        <v>422</v>
+        <v>324</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8478,10 +8485,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B355" t="s">
-        <v>101</v>
+        <v>422</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8489,10 +8496,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B356" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8500,10 +8507,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B357" t="s">
-        <v>423</v>
+        <v>123</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
@@ -8511,10 +8518,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B358" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
@@ -8522,10 +8529,10 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B359" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
@@ -8533,35 +8540,35 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B360" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
-      </c>
-      <c r="D360" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>102010</v>
+        <v>102000</v>
       </c>
       <c r="B361" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
+      </c>
+      <c r="D361" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B362" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
@@ -8569,10 +8576,10 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>102030</v>
+        <v>102020</v>
       </c>
       <c r="B363" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
@@ -8580,35 +8587,35 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>113000</v>
+        <v>102030</v>
       </c>
       <c r="B364" t="s">
-        <v>428</v>
+        <v>325</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
-      </c>
-      <c r="D364" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>113010</v>
+        <v>113000</v>
       </c>
       <c r="B365" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
+      </c>
+      <c r="D365" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B366" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
@@ -8616,10 +8623,10 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B367" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
@@ -8627,10 +8634,10 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B368" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
@@ -8638,35 +8645,35 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B369" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
-      </c>
-      <c r="D369" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370">
-        <v>121011</v>
+        <v>121010</v>
       </c>
       <c r="B370" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
+      </c>
+      <c r="D370" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B371" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
@@ -8674,10 +8681,10 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B372" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
@@ -8685,10 +8692,10 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B373" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8696,10 +8703,10 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B374" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8707,10 +8714,10 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B375" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C375" t="s">
         <v>99</v>
@@ -8718,10 +8725,10 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B376" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C376" t="s">
         <v>99</v>
@@ -8729,10 +8736,10 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B377" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C377" t="s">
         <v>99</v>
@@ -8740,10 +8747,10 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B378" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C378" t="s">
         <v>99</v>
@@ -8751,10 +8758,10 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B379" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C379" t="s">
         <v>99</v>
@@ -8762,12 +8769,23 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380">
+        <v>121020</v>
+      </c>
+      <c r="B380" t="s">
+        <v>445</v>
+      </c>
+      <c r="C380" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381">
         <v>121030</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B381" t="s">
         <v>446</v>
       </c>
-      <c r="C380" t="s">
+      <c r="C381" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D63740A-8DAA-4FD9-9231-5295656F1DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5E6355-EC87-48D4-8001-2A07741A7F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="GameDefine" sheetId="3" r:id="rId6"/>
     <sheet name="TextData" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="489">
   <si>
     <t>Id</t>
   </si>
@@ -879,9 +879,6 @@
   </si>
   <si>
     <t>(初回のみ)</t>
-  </si>
-  <si>
-    <t>\dを入手！</t>
   </si>
   <si>
     <t>Stage.\d</t>
@@ -1597,6 +1594,21 @@
     <rPh sb="0" eb="2">
       <t>ショジ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GetItem</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アイテム入手</t>
+    <rPh sb="4" eb="6">
+      <t>ニュウシュ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>\d\cを入手！</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1979,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -2001,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C2">
         <v>19000</v>
@@ -2012,7 +2024,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C3">
         <v>19001</v>
@@ -2023,7 +2035,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C4">
         <v>19002</v>
@@ -2034,7 +2046,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C5">
         <v>19003</v>
@@ -2045,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C6">
         <v>19004</v>
@@ -2056,7 +2068,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C7">
         <v>19005</v>
@@ -2067,7 +2079,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C8">
         <v>19006</v>
@@ -2078,7 +2090,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C9">
         <v>19007</v>
@@ -2089,7 +2101,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C10">
         <v>19008</v>
@@ -2100,7 +2112,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C11">
         <v>19009</v>
@@ -2111,7 +2123,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C12">
         <v>19010</v>
@@ -2122,10 +2134,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C13">
         <v>19011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14">
+        <v>19012</v>
       </c>
     </row>
   </sheetData>
@@ -2181,7 +2204,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -4457,7 +4480,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G382"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -4800,7 +4823,7 @@
         <v>342</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
@@ -5456,7 +5479,7 @@
         <v>1000</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C89" t="s">
         <v>99</v>
@@ -5694,7 +5717,7 @@
         <v>2101</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C109" t="s">
         <v>99</v>
@@ -5738,7 +5761,7 @@
         <v>2105</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C113" t="s">
         <v>99</v>
@@ -6384,7 +6407,7 @@
         <v>13010</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C169" t="s">
         <v>99</v>
@@ -6398,7 +6421,7 @@
         <v>13020</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C170" t="s">
         <v>99</v>
@@ -6453,7 +6476,7 @@
         <v>13210</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C175" t="s">
         <v>99</v>
@@ -6464,7 +6487,7 @@
         <v>13220</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C176" t="s">
         <v>99</v>
@@ -6475,7 +6498,7 @@
         <v>13230</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C177" t="s">
         <v>99</v>
@@ -6486,7 +6509,7 @@
         <v>13240</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C178" t="s">
         <v>99</v>
@@ -6617,8 +6640,8 @@
       <c r="A190">
         <v>14110</v>
       </c>
-      <c r="B190" t="s">
-        <v>279</v>
+      <c r="B190" s="4" t="s">
+        <v>488</v>
       </c>
       <c r="C190" t="s">
         <v>99</v>
@@ -6629,13 +6652,13 @@
         <v>15010</v>
       </c>
       <c r="B191" t="s">
+        <v>279</v>
+      </c>
+      <c r="C191" t="s">
+        <v>99</v>
+      </c>
+      <c r="D191" t="s">
         <v>280</v>
-      </c>
-      <c r="C191" t="s">
-        <v>99</v>
-      </c>
-      <c r="D191" t="s">
-        <v>281</v>
       </c>
       <c r="G191" s="1"/>
     </row>
@@ -6644,13 +6667,13 @@
         <v>16010</v>
       </c>
       <c r="B192" t="s">
+        <v>281</v>
+      </c>
+      <c r="C192" t="s">
+        <v>99</v>
+      </c>
+      <c r="D192" t="s">
         <v>282</v>
-      </c>
-      <c r="C192" t="s">
-        <v>99</v>
-      </c>
-      <c r="D192" t="s">
-        <v>283</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -6659,7 +6682,7 @@
         <v>16020</v>
       </c>
       <c r="B193" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C193" t="s">
         <v>99</v>
@@ -6671,7 +6694,7 @@
         <v>16100</v>
       </c>
       <c r="B194" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C194" t="s">
         <v>99</v>
@@ -6682,7 +6705,7 @@
         <v>16110</v>
       </c>
       <c r="B195" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C195" t="s">
         <v>99</v>
@@ -6693,7 +6716,7 @@
         <v>16200</v>
       </c>
       <c r="B196" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C196" t="s">
         <v>99</v>
@@ -6704,7 +6727,7 @@
         <v>16210</v>
       </c>
       <c r="B197" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C197" t="s">
         <v>99</v>
@@ -6715,7 +6738,7 @@
         <v>16220</v>
       </c>
       <c r="B198" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C198" t="s">
         <v>99</v>
@@ -6726,7 +6749,7 @@
         <v>16230</v>
       </c>
       <c r="B199" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C199" t="s">
         <v>99</v>
@@ -6737,7 +6760,7 @@
         <v>16300</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C200" t="s">
         <v>99</v>
@@ -6748,7 +6771,7 @@
         <v>16310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C201" t="s">
         <v>99</v>
@@ -6759,7 +6782,7 @@
         <v>16320</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C202" t="s">
         <v>99</v>
@@ -6770,7 +6793,7 @@
         <v>16400</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C203" t="s">
         <v>99</v>
@@ -6781,7 +6804,7 @@
         <v>16410</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C204" t="s">
         <v>99</v>
@@ -6798,7 +6821,7 @@
         <v>99</v>
       </c>
       <c r="D205" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6812,7 +6835,7 @@
         <v>99</v>
       </c>
       <c r="D206" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6826,7 +6849,7 @@
         <v>99</v>
       </c>
       <c r="D207" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6840,7 +6863,7 @@
         <v>99</v>
       </c>
       <c r="D208" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -6854,7 +6877,7 @@
         <v>99</v>
       </c>
       <c r="D209" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -6868,7 +6891,7 @@
         <v>99</v>
       </c>
       <c r="D210" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -6882,7 +6905,7 @@
         <v>99</v>
       </c>
       <c r="D211" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -6890,7 +6913,7 @@
         <v>17010</v>
       </c>
       <c r="B212" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C212" t="s">
         <v>99</v>
@@ -6901,13 +6924,13 @@
         <v>18010</v>
       </c>
       <c r="B213" t="s">
+        <v>297</v>
+      </c>
+      <c r="C213" t="s">
+        <v>99</v>
+      </c>
+      <c r="D213" t="s">
         <v>298</v>
-      </c>
-      <c r="C213" t="s">
-        <v>99</v>
-      </c>
-      <c r="D213" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -6915,7 +6938,7 @@
         <v>18020</v>
       </c>
       <c r="B214" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C214" t="s">
         <v>99</v>
@@ -6937,7 +6960,7 @@
         <v>18110</v>
       </c>
       <c r="B216" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C216" t="s">
         <v>99</v>
@@ -6948,7 +6971,7 @@
         <v>18120</v>
       </c>
       <c r="B217" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C217" t="s">
         <v>99</v>
@@ -6992,7 +7015,7 @@
         <v>18220</v>
       </c>
       <c r="B221" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C221" t="s">
         <v>99</v>
@@ -7003,7 +7026,7 @@
         <v>18230</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C222" t="s">
         <v>99</v>
@@ -7014,7 +7037,7 @@
         <v>18300</v>
       </c>
       <c r="B223" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C223" t="s">
         <v>99</v>
@@ -7025,7 +7048,7 @@
         <v>18310</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C224" t="s">
         <v>99</v>
@@ -7036,7 +7059,7 @@
         <v>18320</v>
       </c>
       <c r="B225" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C225" t="s">
         <v>99</v>
@@ -7047,7 +7070,7 @@
         <v>18340</v>
       </c>
       <c r="B226" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C226" t="s">
         <v>99</v>
@@ -7058,7 +7081,7 @@
         <v>18400</v>
       </c>
       <c r="B227" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C227" t="s">
         <v>99</v>
@@ -7069,7 +7092,7 @@
         <v>18410</v>
       </c>
       <c r="B228" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C228" t="s">
         <v>99</v>
@@ -7080,7 +7103,7 @@
         <v>18420</v>
       </c>
       <c r="B229" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C229" t="s">
         <v>99</v>
@@ -7091,7 +7114,7 @@
         <v>18430</v>
       </c>
       <c r="B230" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C230" t="s">
         <v>99</v>
@@ -7113,7 +7136,7 @@
         <v>18450</v>
       </c>
       <c r="B232" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C232" t="s">
         <v>99</v>
@@ -7124,7 +7147,7 @@
         <v>18500</v>
       </c>
       <c r="B233" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C233" t="s">
         <v>99</v>
@@ -7135,7 +7158,7 @@
         <v>18510</v>
       </c>
       <c r="B234" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C234" t="s">
         <v>99</v>
@@ -7146,7 +7169,7 @@
         <v>18800</v>
       </c>
       <c r="B235" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C235" t="s">
         <v>99</v>
@@ -7157,7 +7180,7 @@
         <v>18801</v>
       </c>
       <c r="B236" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C236" t="s">
         <v>99</v>
@@ -7168,7 +7191,7 @@
         <v>18802</v>
       </c>
       <c r="B237" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C237" t="s">
         <v>99</v>
@@ -7179,7 +7202,7 @@
         <v>18803</v>
       </c>
       <c r="B238" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C238" t="s">
         <v>99</v>
@@ -7190,7 +7213,7 @@
         <v>18804</v>
       </c>
       <c r="B239" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C239" t="s">
         <v>99</v>
@@ -7201,7 +7224,7 @@
         <v>18805</v>
       </c>
       <c r="B240" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C240" t="s">
         <v>99</v>
@@ -7212,7 +7235,7 @@
         <v>18806</v>
       </c>
       <c r="B241" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C241" t="s">
         <v>99</v>
@@ -7223,7 +7246,7 @@
         <v>18811</v>
       </c>
       <c r="B242" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C242" t="s">
         <v>99</v>
@@ -7234,7 +7257,7 @@
         <v>18812</v>
       </c>
       <c r="B243" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C243" t="s">
         <v>99</v>
@@ -7245,13 +7268,13 @@
         <v>19000</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C244" t="s">
         <v>99</v>
       </c>
       <c r="D244" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G244" s="1"/>
     </row>
@@ -7260,7 +7283,7 @@
         <v>19001</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C245" t="s">
         <v>99</v>
@@ -7271,7 +7294,7 @@
         <v>19002</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C246" t="s">
         <v>99</v>
@@ -7282,7 +7305,7 @@
         <v>19003</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C247" t="s">
         <v>99</v>
@@ -7293,7 +7316,7 @@
         <v>19004</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C248" t="s">
         <v>99</v>
@@ -7304,7 +7327,7 @@
         <v>19005</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C249" t="s">
         <v>99</v>
@@ -7315,7 +7338,7 @@
         <v>19006</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C250" t="s">
         <v>99</v>
@@ -7326,7 +7349,7 @@
         <v>19007</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C251" t="s">
         <v>99</v>
@@ -7337,7 +7360,7 @@
         <v>19008</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C252" t="s">
         <v>99</v>
@@ -7348,7 +7371,7 @@
         <v>19009</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C253" t="s">
         <v>99</v>
@@ -7359,7 +7382,7 @@
         <v>19010</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C254" t="s">
         <v>99</v>
@@ -7370,7 +7393,7 @@
         <v>19011</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C255" t="s">
         <v>99</v>
@@ -7378,10 +7401,10 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256">
-        <v>19100</v>
-      </c>
-      <c r="B256" t="s">
-        <v>328</v>
+        <v>19012</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>487</v>
       </c>
       <c r="C256" t="s">
         <v>99</v>
@@ -7389,10 +7412,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B257" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7400,10 +7423,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19200</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>330</v>
+        <v>19110</v>
+      </c>
+      <c r="B258" t="s">
+        <v>328</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7411,10 +7434,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7422,10 +7445,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7433,10 +7456,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7444,10 +7467,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19240</v>
-      </c>
-      <c r="B262" s="5" t="s">
-        <v>477</v>
+        <v>19230</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7455,10 +7478,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19250</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>334</v>
+        <v>19240</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>476</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
@@ -7466,10 +7489,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19260</v>
-      </c>
-      <c r="B264" s="5" t="s">
-        <v>481</v>
+        <v>19250</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C264" t="s">
         <v>99</v>
@@ -7477,10 +7500,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19270</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>335</v>
+        <v>19260</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="C265" t="s">
         <v>99</v>
@@ -7488,10 +7511,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19280</v>
-      </c>
-      <c r="B266" s="5" t="s">
-        <v>482</v>
+        <v>19270</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>334</v>
       </c>
       <c r="C266" t="s">
         <v>99</v>
@@ -7499,32 +7522,32 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
+        <v>19280</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C267" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268">
         <v>19300</v>
       </c>
-      <c r="B267" t="s">
+      <c r="B268" t="s">
+        <v>335</v>
+      </c>
+      <c r="C268" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="26">
+      <c r="A269">
+        <v>19310</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="C267" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" ht="26">
-      <c r="A268">
-        <v>19310</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C268" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3">
-      <c r="A269">
-        <v>19320</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C269" t="s">
         <v>99</v>
@@ -7532,10 +7555,10 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
-        <v>19330</v>
-      </c>
-      <c r="B270" t="s">
-        <v>339</v>
+        <v>19320</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7543,10 +7566,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B271" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7554,10 +7577,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B272" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7565,10 +7588,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B273" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7576,10 +7599,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19400</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>343</v>
+        <v>19360</v>
+      </c>
+      <c r="B274" t="s">
+        <v>341</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7587,10 +7610,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7598,10 +7621,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19410</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>483</v>
+        <v>19401</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7609,10 +7632,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19420</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>345</v>
+        <v>19410</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7620,10 +7643,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19500</v>
-      </c>
-      <c r="B278" t="s">
-        <v>346</v>
+        <v>19420</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7631,10 +7654,10 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>19510</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>481</v>
+        <v>19500</v>
+      </c>
+      <c r="B279" t="s">
+        <v>345</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7642,10 +7665,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>19520</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>347</v>
+        <v>19510</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7653,10 +7676,10 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
@@ -7664,10 +7687,10 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C282" t="s">
         <v>99</v>
@@ -7675,10 +7698,10 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C283" t="s">
         <v>99</v>
@@ -7686,10 +7709,10 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C284" t="s">
         <v>99</v>
@@ -7697,48 +7720,47 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285">
+        <v>19603</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C285" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286">
         <v>19604</v>
       </c>
-      <c r="B285" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C285" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="14">
-      <c r="A286">
-        <v>19611</v>
-      </c>
-      <c r="B286" t="s">
-        <v>353</v>
+      <c r="B286" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="C286" t="s">
         <v>99</v>
       </c>
-      <c r="D286" t="s">
-        <v>354</v>
-      </c>
-      <c r="G286" s="1"/>
     </row>
     <row r="287" spans="1:7" ht="14">
       <c r="A287">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B287" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C287" t="s">
         <v>99</v>
+      </c>
+      <c r="D287" t="s">
+        <v>353</v>
       </c>
       <c r="G287" s="1"/>
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B288" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
@@ -7747,10 +7769,10 @@
     </row>
     <row r="289" spans="1:7" ht="14">
       <c r="A289">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B289" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7759,10 +7781,10 @@
     </row>
     <row r="290" spans="1:7" ht="14">
       <c r="A290">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B290" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C290" t="s">
         <v>99</v>
@@ -7771,10 +7793,10 @@
     </row>
     <row r="291" spans="1:7" ht="14">
       <c r="A291">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B291" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C291" t="s">
         <v>99</v>
@@ -7783,10 +7805,10 @@
     </row>
     <row r="292" spans="1:7" ht="14">
       <c r="A292">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B292" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C292" t="s">
         <v>99</v>
@@ -7795,10 +7817,10 @@
     </row>
     <row r="293" spans="1:7" ht="14">
       <c r="A293">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B293" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C293" t="s">
         <v>99</v>
@@ -7807,47 +7829,48 @@
     </row>
     <row r="294" spans="1:7" ht="14">
       <c r="A294">
+        <v>19618</v>
+      </c>
+      <c r="B294" t="s">
+        <v>360</v>
+      </c>
+      <c r="C294" t="s">
+        <v>99</v>
+      </c>
+      <c r="G294" s="1"/>
+    </row>
+    <row r="295" spans="1:7" ht="14">
+      <c r="A295">
         <v>19619</v>
       </c>
-      <c r="B294" t="s">
-        <v>362</v>
-      </c>
-      <c r="C294" t="s">
-        <v>99</v>
-      </c>
-      <c r="G294" s="1"/>
-    </row>
-    <row r="295" spans="1:7">
-      <c r="A295">
-        <v>19631</v>
-      </c>
       <c r="B295" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C295" t="s">
         <v>99</v>
       </c>
-      <c r="D295" t="s">
-        <v>364</v>
-      </c>
+      <c r="G295" s="1"/>
     </row>
     <row r="296" spans="1:7">
       <c r="A296">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="B296" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C296" t="s">
         <v>99</v>
+      </c>
+      <c r="D296" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B297" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
@@ -7855,10 +7878,10 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B298" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7866,10 +7889,10 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299">
-        <v>19700</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>368</v>
+        <v>19634</v>
+      </c>
+      <c r="B299" t="s">
+        <v>366</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7877,10 +7900,10 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>327</v>
+        <v>367</v>
       </c>
       <c r="C300" t="s">
         <v>99</v>
@@ -7888,10 +7911,10 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="C301" t="s">
         <v>99</v>
@@ -7899,10 +7922,10 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C302" t="s">
         <v>99</v>
@@ -7910,10 +7933,10 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C303" t="s">
         <v>99</v>
@@ -7921,57 +7944,57 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304">
-        <v>19800</v>
-      </c>
-      <c r="B304" t="s">
-        <v>372</v>
+        <v>19740</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>370</v>
       </c>
       <c r="C304" t="s">
-        <v>373</v>
+        <v>99</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B305" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C305" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306">
-        <v>20010</v>
+        <v>19810</v>
       </c>
       <c r="B306" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C306" t="s">
         <v>99</v>
-      </c>
-      <c r="D306" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B307" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
+      </c>
+      <c r="D307" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308">
-        <v>20030</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>378</v>
+        <v>20020</v>
+      </c>
+      <c r="B308" t="s">
+        <v>376</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
@@ -7979,10 +8002,10 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309">
-        <v>20040</v>
-      </c>
-      <c r="B309" t="s">
-        <v>379</v>
+        <v>20030</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -7990,10 +8013,10 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B310" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -8001,10 +8024,10 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B311" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -8012,10 +8035,10 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B312" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -8023,10 +8046,10 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B313" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -8034,10 +8057,10 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B314" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -8045,10 +8068,10 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B315" t="s">
-        <v>311</v>
+        <v>383</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -8056,10 +8079,10 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B316" t="s">
-        <v>385</v>
+        <v>310</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -8067,10 +8090,10 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B317" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -8078,10 +8101,10 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318">
-        <v>20230</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>387</v>
+        <v>20220</v>
+      </c>
+      <c r="B318" t="s">
+        <v>385</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -8089,10 +8112,10 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -8100,10 +8123,10 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8111,10 +8134,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20260</v>
-      </c>
-      <c r="B321" t="s">
-        <v>390</v>
+        <v>20250</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8122,10 +8145,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B322" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8133,10 +8156,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B323" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8144,10 +8167,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B324" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8155,10 +8178,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B325" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8166,10 +8189,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B326" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8177,10 +8200,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B327" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8188,10 +8211,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B328" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8199,10 +8222,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B329" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8210,10 +8233,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B330" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8221,10 +8244,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B331" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8232,10 +8255,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B332" t="s">
-        <v>103</v>
+        <v>399</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8243,10 +8266,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B333" t="s">
-        <v>401</v>
+        <v>103</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8254,10 +8277,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B334" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8265,10 +8288,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B335" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8276,10 +8299,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B336" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8287,10 +8310,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B337" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8298,10 +8321,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B338" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8309,10 +8332,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B339" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8320,10 +8343,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B340" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8331,10 +8354,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B341" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8342,10 +8365,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B342" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8353,10 +8376,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B343" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8364,10 +8387,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B344" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8375,10 +8398,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B345" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8386,10 +8409,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B346" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8397,10 +8420,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B347" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8408,10 +8431,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B348" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8419,10 +8442,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B349" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8430,10 +8453,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B350" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8441,10 +8464,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B351" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8452,10 +8475,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B352" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8463,10 +8486,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B353" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8474,10 +8497,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B354" t="s">
-        <v>324</v>
+        <v>420</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8485,10 +8508,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B355" t="s">
-        <v>422</v>
+        <v>323</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8496,10 +8519,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B356" t="s">
-        <v>101</v>
+        <v>421</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8507,10 +8530,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B357" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
@@ -8518,10 +8541,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B358" t="s">
-        <v>423</v>
+        <v>123</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
@@ -8529,10 +8552,10 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B359" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
@@ -8540,10 +8563,10 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B360" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
@@ -8551,35 +8574,35 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B361" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
-      </c>
-      <c r="D361" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>102010</v>
+        <v>102000</v>
       </c>
       <c r="B362" t="s">
-        <v>326</v>
+        <v>425</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
+      </c>
+      <c r="D362" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B363" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
@@ -8587,10 +8610,10 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>102030</v>
+        <v>102020</v>
       </c>
       <c r="B364" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
@@ -8598,35 +8621,35 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>113000</v>
+        <v>102030</v>
       </c>
       <c r="B365" t="s">
-        <v>428</v>
+        <v>324</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
-      </c>
-      <c r="D365" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>113010</v>
+        <v>113000</v>
       </c>
       <c r="B366" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
+      </c>
+      <c r="D366" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B367" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
@@ -8634,10 +8657,10 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B368" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
@@ -8645,10 +8668,10 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B369" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
@@ -8656,35 +8679,35 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B370" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
-      </c>
-      <c r="D370" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371">
-        <v>121011</v>
+        <v>121010</v>
       </c>
       <c r="B371" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
+      </c>
+      <c r="D371" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B372" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
@@ -8692,10 +8715,10 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B373" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8703,10 +8726,10 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B374" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8714,10 +8737,10 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B375" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C375" t="s">
         <v>99</v>
@@ -8725,10 +8748,10 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B376" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C376" t="s">
         <v>99</v>
@@ -8736,10 +8759,10 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B377" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C377" t="s">
         <v>99</v>
@@ -8747,10 +8770,10 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B378" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C378" t="s">
         <v>99</v>
@@ -8758,10 +8781,10 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B379" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C379" t="s">
         <v>99</v>
@@ -8769,10 +8792,10 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B380" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C380" t="s">
         <v>99</v>
@@ -8780,12 +8803,23 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381">
+        <v>121020</v>
+      </c>
+      <c r="B381" t="s">
+        <v>444</v>
+      </c>
+      <c r="C381" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382">
         <v>121030</v>
       </c>
-      <c r="B381" t="s">
-        <v>446</v>
-      </c>
-      <c r="C381" t="s">
+      <c r="B382" t="s">
+        <v>445</v>
+      </c>
+      <c r="C382" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5E6355-EC87-48D4-8001-2A07741A7F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1971C7-95A5-4589-9697-91B3ED8F1D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" tabRatio="711" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="491">
   <si>
     <t>Id</t>
   </si>
@@ -1609,6 +1609,17 @@
   </si>
   <si>
     <t>\d\cを入手！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Gacha</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>奇跡</t>
+    <rPh sb="0" eb="2">
+      <t>キセキ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1991,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.36328125" customWidth="1"/>
@@ -2149,6 +2160,17 @@
       </c>
       <c r="C14">
         <v>19012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C15">
+        <v>19013</v>
       </c>
     </row>
   </sheetData>
@@ -4480,7 +4502,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G382"/>
+  <dimension ref="A1:G383"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="52.90625" customWidth="1"/>
@@ -7412,10 +7434,10 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19100</v>
-      </c>
-      <c r="B257" t="s">
-        <v>327</v>
+        <v>19013</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>490</v>
       </c>
       <c r="C257" t="s">
         <v>99</v>
@@ -7423,10 +7445,10 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B258" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C258" t="s">
         <v>99</v>
@@ -7434,10 +7456,10 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19200</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>329</v>
+        <v>19110</v>
+      </c>
+      <c r="B259" t="s">
+        <v>328</v>
       </c>
       <c r="C259" t="s">
         <v>99</v>
@@ -7445,10 +7467,10 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C260" t="s">
         <v>99</v>
@@ -7456,10 +7478,10 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C261" t="s">
         <v>99</v>
@@ -7467,10 +7489,10 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C262" t="s">
         <v>99</v>
@@ -7478,10 +7500,10 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19240</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>476</v>
+        <v>19230</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="C263" t="s">
         <v>99</v>
@@ -7489,10 +7511,10 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19250</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>333</v>
+        <v>19240</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>476</v>
       </c>
       <c r="C264" t="s">
         <v>99</v>
@@ -7500,10 +7522,10 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19260</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>480</v>
+        <v>19250</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C265" t="s">
         <v>99</v>
@@ -7511,10 +7533,10 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19270</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>334</v>
+        <v>19260</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="C266" t="s">
         <v>99</v>
@@ -7522,10 +7544,10 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19280</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>481</v>
+        <v>19270</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>334</v>
       </c>
       <c r="C267" t="s">
         <v>99</v>
@@ -7533,32 +7555,32 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
+        <v>19280</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C268" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269">
         <v>19300</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B269" t="s">
         <v>335</v>
       </c>
-      <c r="C268" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" ht="26">
-      <c r="A269">
+      <c r="C269" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="26">
+      <c r="A270">
         <v>19310</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="B270" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="C269" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270">
-        <v>19320</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="C270" t="s">
         <v>99</v>
@@ -7566,10 +7588,10 @@
     </row>
     <row r="271" spans="1:3">
       <c r="A271">
-        <v>19330</v>
-      </c>
-      <c r="B271" t="s">
-        <v>338</v>
+        <v>19320</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="C271" t="s">
         <v>99</v>
@@ -7577,10 +7599,10 @@
     </row>
     <row r="272" spans="1:3">
       <c r="A272">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B272" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C272" t="s">
         <v>99</v>
@@ -7588,10 +7610,10 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B273" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C273" t="s">
         <v>99</v>
@@ -7599,10 +7621,10 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B274" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C274" t="s">
         <v>99</v>
@@ -7610,10 +7632,10 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>19400</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>342</v>
+        <v>19360</v>
+      </c>
+      <c r="B275" t="s">
+        <v>341</v>
       </c>
       <c r="C275" t="s">
         <v>99</v>
@@ -7621,10 +7643,10 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C276" t="s">
         <v>99</v>
@@ -7632,10 +7654,10 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>19410</v>
-      </c>
-      <c r="B277" s="5" t="s">
-        <v>482</v>
+        <v>19401</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="C277" t="s">
         <v>99</v>
@@ -7643,10 +7665,10 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>19420</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>344</v>
+        <v>19410</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C278" t="s">
         <v>99</v>
@@ -7654,10 +7676,10 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>19500</v>
-      </c>
-      <c r="B279" t="s">
-        <v>345</v>
+        <v>19420</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C279" t="s">
         <v>99</v>
@@ -7665,10 +7687,10 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>19510</v>
-      </c>
-      <c r="B280" s="5" t="s">
-        <v>480</v>
+        <v>19500</v>
+      </c>
+      <c r="B280" t="s">
+        <v>345</v>
       </c>
       <c r="C280" t="s">
         <v>99</v>
@@ -7676,10 +7698,10 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>19520</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>346</v>
+        <v>19510</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="C281" t="s">
         <v>99</v>
@@ -7687,10 +7709,10 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C282" t="s">
         <v>99</v>
@@ -7698,10 +7720,10 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C283" t="s">
         <v>99</v>
@@ -7709,10 +7731,10 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C284" t="s">
         <v>99</v>
@@ -7720,10 +7742,10 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C285" t="s">
         <v>99</v>
@@ -7731,48 +7753,47 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286">
+        <v>19603</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C286" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287">
         <v>19604</v>
       </c>
-      <c r="B286" s="2" t="s">
+      <c r="B287" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C286" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="14">
-      <c r="A287">
-        <v>19611</v>
-      </c>
-      <c r="B287" t="s">
-        <v>352</v>
-      </c>
       <c r="C287" t="s">
         <v>99</v>
       </c>
-      <c r="D287" t="s">
-        <v>353</v>
-      </c>
-      <c r="G287" s="1"/>
     </row>
     <row r="288" spans="1:7" ht="14">
       <c r="A288">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B288" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C288" t="s">
         <v>99</v>
+      </c>
+      <c r="D288" t="s">
+        <v>353</v>
       </c>
       <c r="G288" s="1"/>
     </row>
     <row r="289" spans="1:7" ht="14">
       <c r="A289">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B289" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C289" t="s">
         <v>99</v>
@@ -7781,10 +7802,10 @@
     </row>
     <row r="290" spans="1:7" ht="14">
       <c r="A290">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B290" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C290" t="s">
         <v>99</v>
@@ -7793,10 +7814,10 @@
     </row>
     <row r="291" spans="1:7" ht="14">
       <c r="A291">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B291" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C291" t="s">
         <v>99</v>
@@ -7805,10 +7826,10 @@
     </row>
     <row r="292" spans="1:7" ht="14">
       <c r="A292">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B292" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C292" t="s">
         <v>99</v>
@@ -7817,10 +7838,10 @@
     </row>
     <row r="293" spans="1:7" ht="14">
       <c r="A293">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B293" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C293" t="s">
         <v>99</v>
@@ -7829,10 +7850,10 @@
     </row>
     <row r="294" spans="1:7" ht="14">
       <c r="A294">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B294" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C294" t="s">
         <v>99</v>
@@ -7841,47 +7862,48 @@
     </row>
     <row r="295" spans="1:7" ht="14">
       <c r="A295">
+        <v>19618</v>
+      </c>
+      <c r="B295" t="s">
+        <v>360</v>
+      </c>
+      <c r="C295" t="s">
+        <v>99</v>
+      </c>
+      <c r="G295" s="1"/>
+    </row>
+    <row r="296" spans="1:7" ht="14">
+      <c r="A296">
         <v>19619</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B296" t="s">
         <v>361</v>
       </c>
-      <c r="C295" t="s">
-        <v>99</v>
-      </c>
-      <c r="G295" s="1"/>
-    </row>
-    <row r="296" spans="1:7">
-      <c r="A296">
-        <v>19631</v>
-      </c>
-      <c r="B296" t="s">
-        <v>362</v>
-      </c>
       <c r="C296" t="s">
         <v>99</v>
       </c>
-      <c r="D296" t="s">
-        <v>363</v>
-      </c>
+      <c r="G296" s="1"/>
     </row>
     <row r="297" spans="1:7">
       <c r="A297">
-        <v>19632</v>
+        <v>19631</v>
       </c>
       <c r="B297" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C297" t="s">
         <v>99</v>
+      </c>
+      <c r="D297" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B298" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C298" t="s">
         <v>99</v>
@@ -7889,10 +7911,10 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B299" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C299" t="s">
         <v>99</v>
@@ -7900,10 +7922,10 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300">
-        <v>19700</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>367</v>
+        <v>19634</v>
+      </c>
+      <c r="B300" t="s">
+        <v>366</v>
       </c>
       <c r="C300" t="s">
         <v>99</v>
@@ -7911,10 +7933,10 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="C301" t="s">
         <v>99</v>
@@ -7922,10 +7944,10 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>368</v>
+        <v>326</v>
       </c>
       <c r="C302" t="s">
         <v>99</v>
@@ -7933,10 +7955,10 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C303" t="s">
         <v>99</v>
@@ -7944,10 +7966,10 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C304" t="s">
         <v>99</v>
@@ -7955,57 +7977,57 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305">
-        <v>19800</v>
-      </c>
-      <c r="B305" t="s">
-        <v>371</v>
+        <v>19740</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>370</v>
       </c>
       <c r="C305" t="s">
-        <v>372</v>
+        <v>99</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306">
-        <v>19810</v>
+        <v>19800</v>
       </c>
       <c r="B306" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C306" t="s">
-        <v>99</v>
+        <v>372</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307">
-        <v>20010</v>
+        <v>19810</v>
       </c>
       <c r="B307" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C307" t="s">
         <v>99</v>
-      </c>
-      <c r="D307" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B308" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C308" t="s">
         <v>99</v>
+      </c>
+      <c r="D308" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309">
-        <v>20030</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>377</v>
+        <v>20020</v>
+      </c>
+      <c r="B309" t="s">
+        <v>376</v>
       </c>
       <c r="C309" t="s">
         <v>99</v>
@@ -8013,10 +8035,10 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310">
-        <v>20040</v>
-      </c>
-      <c r="B310" t="s">
-        <v>378</v>
+        <v>20030</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>377</v>
       </c>
       <c r="C310" t="s">
         <v>99</v>
@@ -8024,10 +8046,10 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B311" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C311" t="s">
         <v>99</v>
@@ -8035,10 +8057,10 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B312" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C312" t="s">
         <v>99</v>
@@ -8046,10 +8068,10 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B313" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C313" t="s">
         <v>99</v>
@@ -8057,10 +8079,10 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B314" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C314" t="s">
         <v>99</v>
@@ -8068,10 +8090,10 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B315" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C315" t="s">
         <v>99</v>
@@ -8079,10 +8101,10 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B316" t="s">
-        <v>310</v>
+        <v>383</v>
       </c>
       <c r="C316" t="s">
         <v>99</v>
@@ -8090,10 +8112,10 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B317" t="s">
-        <v>384</v>
+        <v>310</v>
       </c>
       <c r="C317" t="s">
         <v>99</v>
@@ -8101,10 +8123,10 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B318" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C318" t="s">
         <v>99</v>
@@ -8112,10 +8134,10 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319">
-        <v>20230</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>386</v>
+        <v>20220</v>
+      </c>
+      <c r="B319" t="s">
+        <v>385</v>
       </c>
       <c r="C319" t="s">
         <v>99</v>
@@ -8123,10 +8145,10 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C320" t="s">
         <v>99</v>
@@ -8134,10 +8156,10 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C321" t="s">
         <v>99</v>
@@ -8145,10 +8167,10 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20260</v>
-      </c>
-      <c r="B322" t="s">
-        <v>389</v>
+        <v>20250</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="C322" t="s">
         <v>99</v>
@@ -8156,10 +8178,10 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B323" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C323" t="s">
         <v>99</v>
@@ -8167,10 +8189,10 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B324" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C324" t="s">
         <v>99</v>
@@ -8178,10 +8200,10 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B325" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C325" t="s">
         <v>99</v>
@@ -8189,10 +8211,10 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B326" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C326" t="s">
         <v>99</v>
@@ -8200,10 +8222,10 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B327" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C327" t="s">
         <v>99</v>
@@ -8211,10 +8233,10 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B328" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C328" t="s">
         <v>99</v>
@@ -8222,10 +8244,10 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B329" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C329" t="s">
         <v>99</v>
@@ -8233,10 +8255,10 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B330" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C330" t="s">
         <v>99</v>
@@ -8244,10 +8266,10 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B331" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C331" t="s">
         <v>99</v>
@@ -8255,10 +8277,10 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B332" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C332" t="s">
         <v>99</v>
@@ -8266,10 +8288,10 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B333" t="s">
-        <v>103</v>
+        <v>399</v>
       </c>
       <c r="C333" t="s">
         <v>99</v>
@@ -8277,10 +8299,10 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B334" t="s">
-        <v>400</v>
+        <v>103</v>
       </c>
       <c r="C334" t="s">
         <v>99</v>
@@ -8288,10 +8310,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B335" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C335" t="s">
         <v>99</v>
@@ -8299,10 +8321,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B336" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C336" t="s">
         <v>99</v>
@@ -8310,10 +8332,10 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B337" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C337" t="s">
         <v>99</v>
@@ -8321,10 +8343,10 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B338" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C338" t="s">
         <v>99</v>
@@ -8332,10 +8354,10 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B339" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C339" t="s">
         <v>99</v>
@@ -8343,10 +8365,10 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B340" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C340" t="s">
         <v>99</v>
@@ -8354,10 +8376,10 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B341" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C341" t="s">
         <v>99</v>
@@ -8365,10 +8387,10 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B342" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C342" t="s">
         <v>99</v>
@@ -8376,10 +8398,10 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B343" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C343" t="s">
         <v>99</v>
@@ -8387,10 +8409,10 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B344" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C344" t="s">
         <v>99</v>
@@ -8398,10 +8420,10 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B345" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C345" t="s">
         <v>99</v>
@@ -8409,10 +8431,10 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B346" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C346" t="s">
         <v>99</v>
@@ -8420,10 +8442,10 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B347" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C347" t="s">
         <v>99</v>
@@ -8431,10 +8453,10 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B348" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C348" t="s">
         <v>99</v>
@@ -8442,10 +8464,10 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B349" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C349" t="s">
         <v>99</v>
@@ -8453,10 +8475,10 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B350" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C350" t="s">
         <v>99</v>
@@ -8464,10 +8486,10 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B351" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C351" t="s">
         <v>99</v>
@@ -8475,10 +8497,10 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B352" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C352" t="s">
         <v>99</v>
@@ -8486,10 +8508,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B353" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C353" t="s">
         <v>99</v>
@@ -8497,10 +8519,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B354" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C354" t="s">
         <v>99</v>
@@ -8508,10 +8530,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B355" t="s">
-        <v>323</v>
+        <v>420</v>
       </c>
       <c r="C355" t="s">
         <v>99</v>
@@ -8519,10 +8541,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B356" t="s">
-        <v>421</v>
+        <v>323</v>
       </c>
       <c r="C356" t="s">
         <v>99</v>
@@ -8530,10 +8552,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B357" t="s">
-        <v>101</v>
+        <v>421</v>
       </c>
       <c r="C357" t="s">
         <v>99</v>
@@ -8541,10 +8563,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B358" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C358" t="s">
         <v>99</v>
@@ -8552,10 +8574,10 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B359" t="s">
-        <v>422</v>
+        <v>123</v>
       </c>
       <c r="C359" t="s">
         <v>99</v>
@@ -8563,10 +8585,10 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B360" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C360" t="s">
         <v>99</v>
@@ -8574,10 +8596,10 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B361" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C361" t="s">
         <v>99</v>
@@ -8585,35 +8607,35 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B362" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C362" t="s">
         <v>99</v>
-      </c>
-      <c r="D362" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363">
-        <v>102010</v>
+        <v>102000</v>
       </c>
       <c r="B363" t="s">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="C363" t="s">
         <v>99</v>
+      </c>
+      <c r="D363" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B364" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="C364" t="s">
         <v>99</v>
@@ -8621,10 +8643,10 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>102030</v>
+        <v>102020</v>
       </c>
       <c r="B365" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="C365" t="s">
         <v>99</v>
@@ -8632,35 +8654,35 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>113000</v>
+        <v>102030</v>
       </c>
       <c r="B366" t="s">
-        <v>427</v>
+        <v>324</v>
       </c>
       <c r="C366" t="s">
         <v>99</v>
-      </c>
-      <c r="D366" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>113010</v>
+        <v>113000</v>
       </c>
       <c r="B367" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C367" t="s">
         <v>99</v>
+      </c>
+      <c r="D367" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B368" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C368" t="s">
         <v>99</v>
@@ -8668,10 +8690,10 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B369" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C369" t="s">
         <v>99</v>
@@ -8679,10 +8701,10 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B370" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C370" t="s">
         <v>99</v>
@@ -8690,35 +8712,35 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B371" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C371" t="s">
         <v>99</v>
-      </c>
-      <c r="D371" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372">
-        <v>121011</v>
+        <v>121010</v>
       </c>
       <c r="B372" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C372" t="s">
         <v>99</v>
+      </c>
+      <c r="D372" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B373" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C373" t="s">
         <v>99</v>
@@ -8726,10 +8748,10 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B374" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C374" t="s">
         <v>99</v>
@@ -8737,10 +8759,10 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B375" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C375" t="s">
         <v>99</v>
@@ -8748,10 +8770,10 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B376" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C376" t="s">
         <v>99</v>
@@ -8759,10 +8781,10 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B377" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C377" t="s">
         <v>99</v>
@@ -8770,10 +8792,10 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B378" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C378" t="s">
         <v>99</v>
@@ -8781,10 +8803,10 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B379" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C379" t="s">
         <v>99</v>
@@ -8792,10 +8814,10 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B380" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C380" t="s">
         <v>99</v>
@@ -8803,10 +8825,10 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B381" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C381" t="s">
         <v>99</v>
@@ -8814,12 +8836,23 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382">
+        <v>121020</v>
+      </c>
+      <c r="B382" t="s">
+        <v>444</v>
+      </c>
+      <c r="C382" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383">
         <v>121030</v>
       </c>
-      <c r="B382" t="s">
+      <c r="B383" t="s">
         <v>445</v>
       </c>
-      <c r="C382" t="s">
+      <c r="C383" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="487">
   <si>
     <t>Id</t>
   </si>
@@ -876,13 +876,10 @@
     <t>Boot</t>
   </si>
   <si>
-    <t>Norm</t>
+    <t>橋梁戦場のエインフェリア</t>
   </si>
   <si>
     <t>Title</t>
-  </si>
-  <si>
-    <t>誰も至ることのない光の先へ</t>
   </si>
   <si>
     <t>Version</t>
@@ -1497,10 +1494,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1524,13 +1521,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1539,9 +1529,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1554,15 +1550,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1570,7 +1583,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1591,23 +1611,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1615,30 +1621,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1654,15 +1652,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1677,19 +1674,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1707,19 +1776,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1731,61 +1818,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1797,25 +1836,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1827,37 +1848,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1882,30 +1879,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1917,6 +1890,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1940,21 +1928,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1968,6 +1941,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1976,145 +1973,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6942,9 +6939,7 @@
       <c r="A170">
         <v>13020</v>
       </c>
-      <c r="B170" s="4" t="s">
-        <v>285</v>
-      </c>
+      <c r="B170" s="4"/>
       <c r="C170" t="s">
         <v>115</v>
       </c>
@@ -6954,7 +6949,7 @@
         <v>13110</v>
       </c>
       <c r="B171" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C171" t="s">
         <v>115</v>
@@ -6965,7 +6960,7 @@
         <v>13120</v>
       </c>
       <c r="B172" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C172" t="s">
         <v>115</v>
@@ -6976,7 +6971,7 @@
         <v>13130</v>
       </c>
       <c r="B173" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C173" t="s">
         <v>115</v>
@@ -6987,7 +6982,7 @@
         <v>13140</v>
       </c>
       <c r="B174" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C174" t="s">
         <v>115</v>
@@ -6998,7 +6993,7 @@
         <v>13210</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C175" t="s">
         <v>115</v>
@@ -7009,7 +7004,7 @@
         <v>13220</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C176" t="s">
         <v>115</v>
@@ -7020,7 +7015,7 @@
         <v>13230</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C177" t="s">
         <v>115</v>
@@ -7031,7 +7026,7 @@
         <v>13240</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C178" t="s">
         <v>115</v>
@@ -7042,7 +7037,7 @@
         <v>13300</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C179" t="s">
         <v>115</v>
@@ -7053,7 +7048,7 @@
         <v>13301</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C180" t="s">
         <v>115</v>
@@ -7064,7 +7059,7 @@
         <v>13310</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C181" t="s">
         <v>115</v>
@@ -7075,7 +7070,7 @@
         <v>13320</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C182" t="s">
         <v>115</v>
@@ -7086,7 +7081,7 @@
         <v>13330</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C183" t="s">
         <v>115</v>
@@ -7097,7 +7092,7 @@
         <v>13400</v>
       </c>
       <c r="B184" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C184" t="s">
         <v>115</v>
@@ -7111,7 +7106,7 @@
         <v>50</v>
       </c>
       <c r="C185" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -7119,7 +7114,7 @@
         <v>13420</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C186" t="s">
         <v>115</v>
@@ -7130,7 +7125,7 @@
         <v>13421</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C187" t="s">
         <v>115</v>
@@ -7141,7 +7136,7 @@
         <v>13430</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C188" t="s">
         <v>115</v>
@@ -7152,7 +7147,7 @@
         <v>14090</v>
       </c>
       <c r="B189" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C189" t="s">
         <v>115</v>
@@ -7163,7 +7158,7 @@
         <v>14110</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C190" t="s">
         <v>115</v>
@@ -7174,13 +7169,13 @@
         <v>15010</v>
       </c>
       <c r="B191" t="s">
+        <v>305</v>
+      </c>
+      <c r="C191" t="s">
+        <v>115</v>
+      </c>
+      <c r="D191" t="s">
         <v>306</v>
-      </c>
-      <c r="C191" t="s">
-        <v>115</v>
-      </c>
-      <c r="D191" t="s">
-        <v>307</v>
       </c>
       <c r="G191" s="1"/>
     </row>
@@ -7189,7 +7184,7 @@
         <v>16010</v>
       </c>
       <c r="B192" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C192" t="s">
         <v>115</v>
@@ -7204,7 +7199,7 @@
         <v>16020</v>
       </c>
       <c r="B193" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C193" t="s">
         <v>115</v>
@@ -7216,7 +7211,7 @@
         <v>16100</v>
       </c>
       <c r="B194" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C194" t="s">
         <v>115</v>
@@ -7227,7 +7222,7 @@
         <v>16110</v>
       </c>
       <c r="B195" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C195" t="s">
         <v>115</v>
@@ -7238,7 +7233,7 @@
         <v>16200</v>
       </c>
       <c r="B196" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C196" t="s">
         <v>115</v>
@@ -7249,7 +7244,7 @@
         <v>16210</v>
       </c>
       <c r="B197" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C197" t="s">
         <v>115</v>
@@ -7260,7 +7255,7 @@
         <v>16220</v>
       </c>
       <c r="B198" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C198" t="s">
         <v>115</v>
@@ -7271,7 +7266,7 @@
         <v>16230</v>
       </c>
       <c r="B199" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C199" t="s">
         <v>115</v>
@@ -7282,7 +7277,7 @@
         <v>16300</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C200" t="s">
         <v>115</v>
@@ -7293,7 +7288,7 @@
         <v>16310</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C201" t="s">
         <v>115</v>
@@ -7304,7 +7299,7 @@
         <v>16320</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C202" t="s">
         <v>115</v>
@@ -7315,7 +7310,7 @@
         <v>16400</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C203" t="s">
         <v>115</v>
@@ -7326,7 +7321,7 @@
         <v>16410</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C204" t="s">
         <v>115</v>
@@ -7343,7 +7338,7 @@
         <v>115</v>
       </c>
       <c r="D205" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7357,7 +7352,7 @@
         <v>115</v>
       </c>
       <c r="D206" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7371,7 +7366,7 @@
         <v>115</v>
       </c>
       <c r="D207" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7385,7 +7380,7 @@
         <v>115</v>
       </c>
       <c r="D208" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7399,7 +7394,7 @@
         <v>115</v>
       </c>
       <c r="D209" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7413,7 +7408,7 @@
         <v>115</v>
       </c>
       <c r="D210" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7427,7 +7422,7 @@
         <v>115</v>
       </c>
       <c r="D211" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -7435,7 +7430,7 @@
         <v>17010</v>
       </c>
       <c r="B212" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C212" t="s">
         <v>115</v>
@@ -7446,13 +7441,13 @@
         <v>18010</v>
       </c>
       <c r="B213" t="s">
+        <v>322</v>
+      </c>
+      <c r="C213" t="s">
+        <v>115</v>
+      </c>
+      <c r="D213" t="s">
         <v>323</v>
-      </c>
-      <c r="C213" t="s">
-        <v>115</v>
-      </c>
-      <c r="D213" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -7460,7 +7455,7 @@
         <v>18020</v>
       </c>
       <c r="B214" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C214" t="s">
         <v>115</v>
@@ -7482,7 +7477,7 @@
         <v>18110</v>
       </c>
       <c r="B216" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C216" t="s">
         <v>115</v>
@@ -7493,7 +7488,7 @@
         <v>18120</v>
       </c>
       <c r="B217" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C217" t="s">
         <v>115</v>
@@ -7537,7 +7532,7 @@
         <v>18220</v>
       </c>
       <c r="B221" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C221" t="s">
         <v>115</v>
@@ -7548,7 +7543,7 @@
         <v>18230</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C222" t="s">
         <v>115</v>
@@ -7559,7 +7554,7 @@
         <v>18300</v>
       </c>
       <c r="B223" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C223" t="s">
         <v>115</v>
@@ -7570,7 +7565,7 @@
         <v>18310</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C224" t="s">
         <v>115</v>
@@ -7581,7 +7576,7 @@
         <v>18320</v>
       </c>
       <c r="B225" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C225" t="s">
         <v>115</v>
@@ -7592,7 +7587,7 @@
         <v>18340</v>
       </c>
       <c r="B226" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C226" t="s">
         <v>115</v>
@@ -7603,7 +7598,7 @@
         <v>18400</v>
       </c>
       <c r="B227" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C227" t="s">
         <v>115</v>
@@ -7614,7 +7609,7 @@
         <v>18410</v>
       </c>
       <c r="B228" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C228" t="s">
         <v>115</v>
@@ -7625,7 +7620,7 @@
         <v>18420</v>
       </c>
       <c r="B229" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C229" t="s">
         <v>115</v>
@@ -7636,7 +7631,7 @@
         <v>18430</v>
       </c>
       <c r="B230" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C230" t="s">
         <v>115</v>
@@ -7658,7 +7653,7 @@
         <v>18450</v>
       </c>
       <c r="B232" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C232" t="s">
         <v>115</v>
@@ -7669,7 +7664,7 @@
         <v>18500</v>
       </c>
       <c r="B233" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C233" t="s">
         <v>115</v>
@@ -7680,7 +7675,7 @@
         <v>18510</v>
       </c>
       <c r="B234" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C234" t="s">
         <v>115</v>
@@ -7691,7 +7686,7 @@
         <v>18800</v>
       </c>
       <c r="B235" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C235" t="s">
         <v>115</v>
@@ -7702,7 +7697,7 @@
         <v>18801</v>
       </c>
       <c r="B236" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C236" t="s">
         <v>115</v>
@@ -7713,7 +7708,7 @@
         <v>18802</v>
       </c>
       <c r="B237" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C237" t="s">
         <v>115</v>
@@ -7724,7 +7719,7 @@
         <v>18803</v>
       </c>
       <c r="B238" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C238" t="s">
         <v>115</v>
@@ -7735,7 +7730,7 @@
         <v>18804</v>
       </c>
       <c r="B239" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C239" t="s">
         <v>115</v>
@@ -7746,7 +7741,7 @@
         <v>18805</v>
       </c>
       <c r="B240" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C240" t="s">
         <v>115</v>
@@ -7757,7 +7752,7 @@
         <v>18806</v>
       </c>
       <c r="B241" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C241" t="s">
         <v>115</v>
@@ -7768,7 +7763,7 @@
         <v>18811</v>
       </c>
       <c r="B242" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C242" t="s">
         <v>115</v>
@@ -7779,7 +7774,7 @@
         <v>18812</v>
       </c>
       <c r="B243" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C243" t="s">
         <v>115</v>
@@ -7790,13 +7785,13 @@
         <v>19000</v>
       </c>
       <c r="B244" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C244" t="s">
+        <v>115</v>
+      </c>
+      <c r="D244" t="s">
         <v>350</v>
-      </c>
-      <c r="C244" t="s">
-        <v>115</v>
-      </c>
-      <c r="D244" t="s">
-        <v>351</v>
       </c>
       <c r="G244" s="1"/>
     </row>
@@ -7805,7 +7800,7 @@
         <v>19001</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C245" t="s">
         <v>115</v>
@@ -7816,7 +7811,7 @@
         <v>19002</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C246" t="s">
         <v>115</v>
@@ -7827,7 +7822,7 @@
         <v>19003</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C247" t="s">
         <v>115</v>
@@ -7838,7 +7833,7 @@
         <v>19004</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C248" t="s">
         <v>115</v>
@@ -7849,7 +7844,7 @@
         <v>19005</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C249" t="s">
         <v>115</v>
@@ -7860,7 +7855,7 @@
         <v>19006</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C250" t="s">
         <v>115</v>
@@ -7871,7 +7866,7 @@
         <v>19007</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C251" t="s">
         <v>115</v>
@@ -7882,7 +7877,7 @@
         <v>19008</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C252" t="s">
         <v>115</v>
@@ -7893,7 +7888,7 @@
         <v>19009</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C253" t="s">
         <v>115</v>
@@ -7904,7 +7899,7 @@
         <v>19010</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C254" t="s">
         <v>115</v>
@@ -7915,7 +7910,7 @@
         <v>19011</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C255" t="s">
         <v>115</v>
@@ -7926,7 +7921,7 @@
         <v>19012</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C256" t="s">
         <v>115</v>
@@ -7937,7 +7932,7 @@
         <v>19013</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C257" t="s">
         <v>115</v>
@@ -7948,7 +7943,7 @@
         <v>19014</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C258" t="s">
         <v>115</v>
@@ -7959,7 +7954,7 @@
         <v>19100</v>
       </c>
       <c r="B259" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C259" t="s">
         <v>115</v>
@@ -7970,7 +7965,7 @@
         <v>19110</v>
       </c>
       <c r="B260" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C260" t="s">
         <v>115</v>
@@ -7981,7 +7976,7 @@
         <v>19200</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C261" t="s">
         <v>115</v>
@@ -7992,7 +7987,7 @@
         <v>19210</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C262" t="s">
         <v>115</v>
@@ -8003,7 +7998,7 @@
         <v>19220</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C263" t="s">
         <v>115</v>
@@ -8014,7 +8009,7 @@
         <v>19230</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C264" t="s">
         <v>115</v>
@@ -8025,7 +8020,7 @@
         <v>19240</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C265" t="s">
         <v>115</v>
@@ -8036,7 +8031,7 @@
         <v>19250</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C266" t="s">
         <v>115</v>
@@ -8047,7 +8042,7 @@
         <v>19260</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C267" t="s">
         <v>115</v>
@@ -8058,7 +8053,7 @@
         <v>19270</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C268" t="s">
         <v>115</v>
@@ -8069,7 +8064,7 @@
         <v>19280</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C269" t="s">
         <v>115</v>
@@ -8080,7 +8075,7 @@
         <v>19300</v>
       </c>
       <c r="B270" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C270" t="s">
         <v>115</v>
@@ -8091,7 +8086,7 @@
         <v>19310</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C271" t="s">
         <v>115</v>
@@ -8102,7 +8097,7 @@
         <v>19320</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C272" t="s">
         <v>115</v>
@@ -8113,7 +8108,7 @@
         <v>19330</v>
       </c>
       <c r="B273" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C273" t="s">
         <v>115</v>
@@ -8124,7 +8119,7 @@
         <v>19340</v>
       </c>
       <c r="B274" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C274" t="s">
         <v>115</v>
@@ -8135,7 +8130,7 @@
         <v>19350</v>
       </c>
       <c r="B275" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C275" t="s">
         <v>115</v>
@@ -8146,7 +8141,7 @@
         <v>19360</v>
       </c>
       <c r="B276" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C276" t="s">
         <v>115</v>
@@ -8157,7 +8152,7 @@
         <v>19400</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C277" t="s">
         <v>115</v>
@@ -8168,7 +8163,7 @@
         <v>19401</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C278" t="s">
         <v>115</v>
@@ -8179,7 +8174,7 @@
         <v>19410</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C279" t="s">
         <v>115</v>
@@ -8190,7 +8185,7 @@
         <v>19420</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C280" t="s">
         <v>115</v>
@@ -8201,7 +8196,7 @@
         <v>19500</v>
       </c>
       <c r="B281" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C281" t="s">
         <v>115</v>
@@ -8212,7 +8207,7 @@
         <v>19510</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C282" t="s">
         <v>115</v>
@@ -8223,7 +8218,7 @@
         <v>19520</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C283" t="s">
         <v>115</v>
@@ -8234,7 +8229,7 @@
         <v>19600</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C284" t="s">
         <v>115</v>
@@ -8245,7 +8240,7 @@
         <v>19601</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C285" t="s">
         <v>115</v>
@@ -8256,7 +8251,7 @@
         <v>19602</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C286" t="s">
         <v>115</v>
@@ -8267,7 +8262,7 @@
         <v>19603</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C287" t="s">
         <v>115</v>
@@ -8278,7 +8273,7 @@
         <v>19604</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C288" t="s">
         <v>115</v>
@@ -8289,13 +8284,13 @@
         <v>19611</v>
       </c>
       <c r="B289" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C289" t="s">
         <v>115</v>
       </c>
       <c r="D289" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G289" s="1"/>
     </row>
@@ -8304,7 +8299,7 @@
         <v>19612</v>
       </c>
       <c r="B290" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C290" t="s">
         <v>115</v>
@@ -8316,7 +8311,7 @@
         <v>19613</v>
       </c>
       <c r="B291" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C291" t="s">
         <v>115</v>
@@ -8328,7 +8323,7 @@
         <v>19614</v>
       </c>
       <c r="B292" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C292" t="s">
         <v>115</v>
@@ -8340,7 +8335,7 @@
         <v>19615</v>
       </c>
       <c r="B293" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C293" t="s">
         <v>115</v>
@@ -8352,7 +8347,7 @@
         <v>19616</v>
       </c>
       <c r="B294" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C294" t="s">
         <v>115</v>
@@ -8364,7 +8359,7 @@
         <v>19617</v>
       </c>
       <c r="B295" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C295" t="s">
         <v>115</v>
@@ -8376,7 +8371,7 @@
         <v>19618</v>
       </c>
       <c r="B296" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C296" t="s">
         <v>115</v>
@@ -8388,7 +8383,7 @@
         <v>19619</v>
       </c>
       <c r="B297" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C297" t="s">
         <v>115</v>
@@ -8400,13 +8395,13 @@
         <v>19631</v>
       </c>
       <c r="B298" t="s">
+        <v>401</v>
+      </c>
+      <c r="C298" t="s">
+        <v>115</v>
+      </c>
+      <c r="D298" t="s">
         <v>402</v>
-      </c>
-      <c r="C298" t="s">
-        <v>115</v>
-      </c>
-      <c r="D298" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -8414,7 +8409,7 @@
         <v>19632</v>
       </c>
       <c r="B299" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C299" t="s">
         <v>115</v>
@@ -8425,7 +8420,7 @@
         <v>19633</v>
       </c>
       <c r="B300" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C300" t="s">
         <v>115</v>
@@ -8436,7 +8431,7 @@
         <v>19634</v>
       </c>
       <c r="B301" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C301" t="s">
         <v>115</v>
@@ -8447,7 +8442,7 @@
         <v>19700</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C302" t="s">
         <v>115</v>
@@ -8458,7 +8453,7 @@
         <v>19710</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C303" t="s">
         <v>115</v>
@@ -8469,7 +8464,7 @@
         <v>19720</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C304" t="s">
         <v>115</v>
@@ -8480,7 +8475,7 @@
         <v>19730</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C305" t="s">
         <v>115</v>
@@ -8491,7 +8486,7 @@
         <v>19740</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C306" t="s">
         <v>115</v>
@@ -8502,10 +8497,10 @@
         <v>19800</v>
       </c>
       <c r="B307" t="s">
+        <v>410</v>
+      </c>
+      <c r="C307" t="s">
         <v>411</v>
-      </c>
-      <c r="C307" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -8513,7 +8508,7 @@
         <v>19810</v>
       </c>
       <c r="B308" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C308" t="s">
         <v>115</v>
@@ -8524,13 +8519,13 @@
         <v>20010</v>
       </c>
       <c r="B309" t="s">
+        <v>413</v>
+      </c>
+      <c r="C309" t="s">
+        <v>115</v>
+      </c>
+      <c r="D309" t="s">
         <v>414</v>
-      </c>
-      <c r="C309" t="s">
-        <v>115</v>
-      </c>
-      <c r="D309" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -8538,7 +8533,7 @@
         <v>20020</v>
       </c>
       <c r="B310" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C310" t="s">
         <v>115</v>
@@ -8549,7 +8544,7 @@
         <v>20030</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C311" t="s">
         <v>115</v>
@@ -8560,7 +8555,7 @@
         <v>20040</v>
       </c>
       <c r="B312" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C312" t="s">
         <v>115</v>
@@ -8571,7 +8566,7 @@
         <v>20050</v>
       </c>
       <c r="B313" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C313" t="s">
         <v>115</v>
@@ -8582,7 +8577,7 @@
         <v>20100</v>
       </c>
       <c r="B314" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C314" t="s">
         <v>115</v>
@@ -8593,7 +8588,7 @@
         <v>20110</v>
       </c>
       <c r="B315" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C315" t="s">
         <v>115</v>
@@ -8604,7 +8599,7 @@
         <v>20120</v>
       </c>
       <c r="B316" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C316" t="s">
         <v>115</v>
@@ -8615,7 +8610,7 @@
         <v>20200</v>
       </c>
       <c r="B317" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C317" t="s">
         <v>115</v>
@@ -8626,7 +8621,7 @@
         <v>20201</v>
       </c>
       <c r="B318" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C318" t="s">
         <v>115</v>
@@ -8637,7 +8632,7 @@
         <v>20210</v>
       </c>
       <c r="B319" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C319" t="s">
         <v>115</v>
@@ -8648,7 +8643,7 @@
         <v>20220</v>
       </c>
       <c r="B320" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C320" t="s">
         <v>115</v>
@@ -8659,7 +8654,7 @@
         <v>20230</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C321" t="s">
         <v>115</v>
@@ -8670,7 +8665,7 @@
         <v>20240</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C322" t="s">
         <v>115</v>
@@ -8681,7 +8676,7 @@
         <v>20250</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C323" t="s">
         <v>115</v>
@@ -8692,7 +8687,7 @@
         <v>20260</v>
       </c>
       <c r="B324" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C324" t="s">
         <v>115</v>
@@ -8703,7 +8698,7 @@
         <v>20270</v>
       </c>
       <c r="B325" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C325" t="s">
         <v>115</v>
@@ -8714,7 +8709,7 @@
         <v>20280</v>
       </c>
       <c r="B326" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C326" t="s">
         <v>115</v>
@@ -8725,7 +8720,7 @@
         <v>20290</v>
       </c>
       <c r="B327" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C327" t="s">
         <v>115</v>
@@ -8736,7 +8731,7 @@
         <v>20300</v>
       </c>
       <c r="B328" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C328" t="s">
         <v>115</v>
@@ -8747,7 +8742,7 @@
         <v>20310</v>
       </c>
       <c r="B329" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C329" t="s">
         <v>115</v>
@@ -8758,7 +8753,7 @@
         <v>20320</v>
       </c>
       <c r="B330" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C330" t="s">
         <v>115</v>
@@ -8769,7 +8764,7 @@
         <v>20330</v>
       </c>
       <c r="B331" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C331" t="s">
         <v>115</v>
@@ -8780,7 +8775,7 @@
         <v>20340</v>
       </c>
       <c r="B332" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C332" t="s">
         <v>115</v>
@@ -8791,7 +8786,7 @@
         <v>20350</v>
       </c>
       <c r="B333" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C333" t="s">
         <v>115</v>
@@ -8802,7 +8797,7 @@
         <v>23010</v>
       </c>
       <c r="B334" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C334" t="s">
         <v>115</v>
@@ -8824,7 +8819,7 @@
         <v>23030</v>
       </c>
       <c r="B336" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C336" t="s">
         <v>115</v>
@@ -8835,7 +8830,7 @@
         <v>23031</v>
       </c>
       <c r="B337" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C337" t="s">
         <v>115</v>
@@ -8846,7 +8841,7 @@
         <v>23032</v>
       </c>
       <c r="B338" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C338" t="s">
         <v>115</v>
@@ -8857,7 +8852,7 @@
         <v>23040</v>
       </c>
       <c r="B339" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C339" t="s">
         <v>115</v>
@@ -8868,7 +8863,7 @@
         <v>24010</v>
       </c>
       <c r="B340" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C340" t="s">
         <v>115</v>
@@ -8879,7 +8874,7 @@
         <v>24020</v>
       </c>
       <c r="B341" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C341" t="s">
         <v>115</v>
@@ -8890,7 +8885,7 @@
         <v>24030</v>
       </c>
       <c r="B342" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C342" t="s">
         <v>115</v>
@@ -8901,7 +8896,7 @@
         <v>24040</v>
       </c>
       <c r="B343" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C343" t="s">
         <v>115</v>
@@ -8912,7 +8907,7 @@
         <v>24110</v>
       </c>
       <c r="B344" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C344" t="s">
         <v>115</v>
@@ -8923,7 +8918,7 @@
         <v>24111</v>
       </c>
       <c r="B345" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C345" t="s">
         <v>115</v>
@@ -8934,7 +8929,7 @@
         <v>24112</v>
       </c>
       <c r="B346" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C346" t="s">
         <v>115</v>
@@ -8945,7 +8940,7 @@
         <v>24113</v>
       </c>
       <c r="B347" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C347" t="s">
         <v>115</v>
@@ -8956,7 +8951,7 @@
         <v>24114</v>
       </c>
       <c r="B348" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C348" t="s">
         <v>115</v>
@@ -8967,7 +8962,7 @@
         <v>24115</v>
       </c>
       <c r="B349" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C349" t="s">
         <v>115</v>
@@ -8978,7 +8973,7 @@
         <v>24116</v>
       </c>
       <c r="B350" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C350" t="s">
         <v>115</v>
@@ -8989,7 +8984,7 @@
         <v>24117</v>
       </c>
       <c r="B351" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C351" t="s">
         <v>115</v>
@@ -9000,7 +8995,7 @@
         <v>24118</v>
       </c>
       <c r="B352" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C352" t="s">
         <v>115</v>
@@ -9011,7 +9006,7 @@
         <v>24119</v>
       </c>
       <c r="B353" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C353" t="s">
         <v>115</v>
@@ -9022,7 +9017,7 @@
         <v>24120</v>
       </c>
       <c r="B354" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C354" t="s">
         <v>115</v>
@@ -9033,7 +9028,7 @@
         <v>24121</v>
       </c>
       <c r="B355" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C355" t="s">
         <v>115</v>
@@ -9044,7 +9039,7 @@
         <v>24122</v>
       </c>
       <c r="B356" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C356" t="s">
         <v>115</v>
@@ -9055,7 +9050,7 @@
         <v>30000</v>
       </c>
       <c r="B357" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C357" t="s">
         <v>115</v>
@@ -9066,7 +9061,7 @@
         <v>30010</v>
       </c>
       <c r="B358" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C358" t="s">
         <v>115</v>
@@ -9099,7 +9094,7 @@
         <v>30040</v>
       </c>
       <c r="B361" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C361" t="s">
         <v>115</v>
@@ -9110,7 +9105,7 @@
         <v>31010</v>
       </c>
       <c r="B362" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C362" t="s">
         <v>115</v>
@@ -9121,7 +9116,7 @@
         <v>31020</v>
       </c>
       <c r="B363" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C363" t="s">
         <v>115</v>
@@ -9132,13 +9127,13 @@
         <v>102000</v>
       </c>
       <c r="B364" t="s">
+        <v>464</v>
+      </c>
+      <c r="C364" t="s">
+        <v>115</v>
+      </c>
+      <c r="D364" t="s">
         <v>465</v>
-      </c>
-      <c r="C364" t="s">
-        <v>115</v>
-      </c>
-      <c r="D364" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -9146,7 +9141,7 @@
         <v>102010</v>
       </c>
       <c r="B365" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C365" t="s">
         <v>115</v>
@@ -9157,7 +9152,7 @@
         <v>102020</v>
       </c>
       <c r="B366" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C366" t="s">
         <v>115</v>
@@ -9168,7 +9163,7 @@
         <v>102030</v>
       </c>
       <c r="B367" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C367" t="s">
         <v>115</v>
@@ -9179,13 +9174,13 @@
         <v>113000</v>
       </c>
       <c r="B368" t="s">
+        <v>468</v>
+      </c>
+      <c r="C368" t="s">
+        <v>115</v>
+      </c>
+      <c r="D368" t="s">
         <v>469</v>
-      </c>
-      <c r="C368" t="s">
-        <v>115</v>
-      </c>
-      <c r="D368" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -9193,7 +9188,7 @@
         <v>113010</v>
       </c>
       <c r="B369" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C369" t="s">
         <v>115</v>
@@ -9204,7 +9199,7 @@
         <v>113020</v>
       </c>
       <c r="B370" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C370" t="s">
         <v>115</v>
@@ -9215,7 +9210,7 @@
         <v>113030</v>
       </c>
       <c r="B371" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C371" t="s">
         <v>115</v>
@@ -9226,7 +9221,7 @@
         <v>113040</v>
       </c>
       <c r="B372" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C372" t="s">
         <v>115</v>
@@ -9237,13 +9232,13 @@
         <v>121010</v>
       </c>
       <c r="B373" t="s">
+        <v>474</v>
+      </c>
+      <c r="C373" t="s">
+        <v>115</v>
+      </c>
+      <c r="D373" t="s">
         <v>475</v>
-      </c>
-      <c r="C373" t="s">
-        <v>115</v>
-      </c>
-      <c r="D373" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -9251,7 +9246,7 @@
         <v>121011</v>
       </c>
       <c r="B374" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C374" t="s">
         <v>115</v>
@@ -9262,7 +9257,7 @@
         <v>121012</v>
       </c>
       <c r="B375" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C375" t="s">
         <v>115</v>
@@ -9273,7 +9268,7 @@
         <v>121013</v>
       </c>
       <c r="B376" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C376" t="s">
         <v>115</v>
@@ -9284,7 +9279,7 @@
         <v>121014</v>
       </c>
       <c r="B377" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C377" t="s">
         <v>115</v>
@@ -9295,7 +9290,7 @@
         <v>121015</v>
       </c>
       <c r="B378" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C378" t="s">
         <v>115</v>
@@ -9306,7 +9301,7 @@
         <v>121016</v>
       </c>
       <c r="B379" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C379" t="s">
         <v>115</v>
@@ -9317,7 +9312,7 @@
         <v>121017</v>
       </c>
       <c r="B380" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C380" t="s">
         <v>115</v>
@@ -9328,7 +9323,7 @@
         <v>121018</v>
       </c>
       <c r="B381" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C381" t="s">
         <v>115</v>
@@ -9339,7 +9334,7 @@
         <v>121019</v>
       </c>
       <c r="B382" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C382" t="s">
         <v>115</v>
@@ -9350,7 +9345,7 @@
         <v>121020</v>
       </c>
       <c r="B383" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C383" t="s">
         <v>115</v>
@@ -9361,7 +9356,7 @@
         <v>121030</v>
       </c>
       <c r="B384" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C384" t="s">
         <v>115</v>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="488">
   <si>
     <t>Id</t>
   </si>
@@ -661,19 +661,22 @@
     <t>ステータス</t>
   </si>
   <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>SPD</t>
+  </si>
+  <si>
+    <t>MOV</t>
+  </si>
+  <si>
     <t>CP</t>
-  </si>
-  <si>
-    <t>ATK</t>
-  </si>
-  <si>
-    <t>DEF</t>
-  </si>
-  <si>
-    <t>SPD</t>
-  </si>
-  <si>
-    <t>MOV</t>
   </si>
   <si>
     <t>Range.</t>
@@ -1494,10 +1497,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1521,16 +1524,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1544,15 +1546,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1560,51 +1554,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1619,9 +1568,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1635,24 +1630,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1660,6 +1647,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1674,13 +1677,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1698,13 +1797,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1716,109 +1845,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1830,31 +1857,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1870,11 +1873,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1894,6 +1895,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1909,11 +1930,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1922,7 +1949,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1941,30 +1968,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1973,49 +1976,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2024,94 +2000,121 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4999,7 +5002,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G384"/>
+  <dimension ref="A1:G385"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="52.9090909090909" customWidth="1"/>
@@ -6286,51 +6289,48 @@
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:3">
       <c r="A114">
-        <v>2200</v>
-      </c>
-      <c r="B114" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C114" t="s">
         <v>115</v>
-      </c>
-      <c r="D114" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
+        <v>2200</v>
+      </c>
+      <c r="B115" t="s">
+        <v>219</v>
+      </c>
+      <c r="C115" t="s">
+        <v>115</v>
+      </c>
+      <c r="D115" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116">
         <v>2210</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B116" t="s">
         <v>199</v>
       </c>
-      <c r="C115" t="s">
-        <v>115</v>
-      </c>
-      <c r="D115" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="116" ht="29" customHeight="1" spans="1:4">
-      <c r="A116">
+      <c r="C116" t="s">
+        <v>115</v>
+      </c>
+      <c r="D116" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="117" ht="29" customHeight="1" spans="1:4">
+      <c r="A117">
         <v>2220</v>
-      </c>
-      <c r="B116" t="s">
-        <v>220</v>
-      </c>
-      <c r="C116" t="s">
-        <v>115</v>
-      </c>
-      <c r="D116" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117">
-        <v>2300</v>
       </c>
       <c r="B117" t="s">
         <v>221</v>
@@ -6339,12 +6339,12 @@
         <v>115</v>
       </c>
       <c r="D117" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118">
-        <v>2310</v>
+        <v>2300</v>
       </c>
       <c r="B118" t="s">
         <v>222</v>
@@ -6353,12 +6353,12 @@
         <v>115</v>
       </c>
       <c r="D118" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="B119" t="s">
         <v>223</v>
@@ -6367,12 +6367,12 @@
         <v>115</v>
       </c>
       <c r="D119" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B120" t="s">
         <v>224</v>
@@ -6381,12 +6381,12 @@
         <v>115</v>
       </c>
       <c r="D120" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B121" t="s">
         <v>225</v>
@@ -6395,12 +6395,12 @@
         <v>115</v>
       </c>
       <c r="D121" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122">
-        <v>2400</v>
+        <v>2340</v>
       </c>
       <c r="B122" t="s">
         <v>226</v>
@@ -6409,23 +6409,26 @@
         <v>115</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123">
-        <v>3000</v>
-      </c>
-      <c r="B123" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B123" t="s">
         <v>227</v>
       </c>
       <c r="C123" t="s">
         <v>115</v>
+      </c>
+      <c r="D123" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>228</v>
@@ -6436,7 +6439,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>229</v>
@@ -6447,7 +6450,7 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>3040</v>
+        <v>3011</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>230</v>
@@ -6458,10 +6461,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>48</v>
+        <v>231</v>
       </c>
       <c r="C127" t="s">
         <v>115</v>
@@ -6469,10 +6472,10 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="C128" t="s">
         <v>115</v>
@@ -6480,7 +6483,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>232</v>
@@ -6491,7 +6494,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>233</v>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>234</v>
@@ -6513,10 +6516,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>3070</v>
+        <v>3054</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C132" t="s">
         <v>115</v>
@@ -6524,10 +6527,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C133" t="s">
         <v>115</v>
@@ -6535,7 +6538,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>236</v>
@@ -6546,7 +6549,7 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>237</v>
@@ -6557,7 +6560,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>3090</v>
+        <v>3073</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>238</v>
@@ -6568,7 +6571,7 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>3211</v>
+        <v>3090</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>239</v>
@@ -6579,7 +6582,7 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>3230</v>
+        <v>3211</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>240</v>
@@ -6590,7 +6593,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>5000</v>
+        <v>3230</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>241</v>
@@ -6601,10 +6604,10 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="C140" t="s">
         <v>115</v>
@@ -6612,10 +6615,10 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>242</v>
+        <v>115</v>
       </c>
       <c r="C141" t="s">
         <v>115</v>
@@ -6623,7 +6626,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>6001</v>
+        <v>5002</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>243</v>
@@ -6634,7 +6637,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>244</v>
@@ -6645,40 +6648,40 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>6100</v>
+        <v>6002</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="C144" t="s">
-        <v>245</v>
+        <v>115</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>6010</v>
+        <v>6100</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C145" t="s">
         <v>246</v>
-      </c>
-      <c r="C145" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C146" t="s">
         <v>248</v>
-      </c>
-      <c r="C146" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>249</v>
@@ -6689,139 +6692,139 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>6020</v>
+        <v>6012</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>250</v>
       </c>
       <c r="C148" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C149" t="s">
         <v>252</v>
-      </c>
-      <c r="C149" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C150" t="s">
         <v>254</v>
-      </c>
-      <c r="C150" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>6210</v>
+        <v>6040</v>
       </c>
       <c r="B151" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C151" t="s">
         <v>256</v>
-      </c>
-      <c r="C151" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C152" t="s">
         <v>258</v>
-      </c>
-      <c r="C152" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="B153" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C153" t="s">
         <v>260</v>
-      </c>
-      <c r="C153" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>6240</v>
+        <v>6230</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C154" t="s">
         <v>262</v>
-      </c>
-      <c r="C154" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="B155" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C155" t="s">
         <v>264</v>
-      </c>
-      <c r="C155" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>6260</v>
+        <v>6250</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C156" t="s">
         <v>266</v>
-      </c>
-      <c r="C156" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>6270</v>
+        <v>6260</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C157" t="s">
         <v>268</v>
-      </c>
-      <c r="C157" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>6280</v>
+        <v>6270</v>
       </c>
       <c r="B158" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C158" t="s">
         <v>270</v>
-      </c>
-      <c r="C158" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>6810</v>
+        <v>6280</v>
       </c>
       <c r="B159" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C159" t="s">
         <v>272</v>
-      </c>
-      <c r="C159" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>6820</v>
+        <v>6810</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>273</v>
@@ -6832,7 +6835,7 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>6830</v>
+        <v>6820</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>274</v>
@@ -6843,7 +6846,7 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>6840</v>
+        <v>6830</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>275</v>
@@ -6854,7 +6857,7 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>6850</v>
+        <v>6840</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>276</v>
@@ -6865,7 +6868,7 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>6860</v>
+        <v>6850</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>277</v>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>6870</v>
+        <v>6860</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>278</v>
@@ -6887,7 +6890,7 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>6880</v>
+        <v>6870</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>279</v>
@@ -6898,7 +6901,7 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>6890</v>
+        <v>6880</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>280</v>
@@ -6907,9 +6910,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="168" ht="130" spans="1:4">
+    <row r="168" spans="1:3">
       <c r="A168">
-        <v>12010</v>
+        <v>6890</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>281</v>
@@ -6917,47 +6920,47 @@
       <c r="C168" t="s">
         <v>115</v>
       </c>
-      <c r="D168" t="s">
+    </row>
+    <row r="169" ht="130" spans="1:4">
+      <c r="A169">
+        <v>12010</v>
+      </c>
+      <c r="B169" s="3" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169">
+      <c r="C169" t="s">
+        <v>115</v>
+      </c>
+      <c r="D169" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170">
         <v>13010</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C169" t="s">
-        <v>115</v>
-      </c>
-      <c r="D169" t="s">
+      <c r="B170" s="2" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170">
-        <v>13020</v>
-      </c>
-      <c r="B170" s="4"/>
       <c r="C170" t="s">
         <v>115</v>
+      </c>
+      <c r="D170" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>13110</v>
-      </c>
-      <c r="B171" t="s">
-        <v>285</v>
-      </c>
+        <v>13020</v>
+      </c>
+      <c r="B171" s="4"/>
       <c r="C171" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>13120</v>
+        <v>13110</v>
       </c>
       <c r="B172" t="s">
         <v>286</v>
@@ -6968,7 +6971,7 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>13130</v>
+        <v>13120</v>
       </c>
       <c r="B173" t="s">
         <v>287</v>
@@ -6979,7 +6982,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>13140</v>
+        <v>13130</v>
       </c>
       <c r="B174" t="s">
         <v>288</v>
@@ -6990,9 +6993,9 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>13210</v>
-      </c>
-      <c r="B175" s="2" t="s">
+        <v>13140</v>
+      </c>
+      <c r="B175" t="s">
         <v>289</v>
       </c>
       <c r="C175" t="s">
@@ -7001,7 +7004,7 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>13220</v>
+        <v>13210</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>290</v>
@@ -7012,7 +7015,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>13230</v>
+        <v>13220</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>291</v>
@@ -7023,7 +7026,7 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>13240</v>
+        <v>13230</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>292</v>
@@ -7034,9 +7037,9 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>13300</v>
-      </c>
-      <c r="B179" s="3" t="s">
+        <v>13240</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>293</v>
       </c>
       <c r="C179" t="s">
@@ -7045,7 +7048,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>13301</v>
+        <v>13300</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>294</v>
@@ -7056,7 +7059,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>13310</v>
+        <v>13301</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>295</v>
@@ -7067,7 +7070,7 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>13320</v>
+        <v>13310</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>296</v>
@@ -7076,9 +7079,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="183" ht="26" spans="1:3">
+    <row r="183" spans="1:3">
       <c r="A183">
-        <v>13330</v>
+        <v>13320</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>297</v>
@@ -7087,11 +7090,11 @@
         <v>115</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" ht="26" spans="1:3">
       <c r="A184">
-        <v>13400</v>
-      </c>
-      <c r="B184" t="s">
+        <v>13330</v>
+      </c>
+      <c r="B184" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C184" t="s">
@@ -7100,29 +7103,29 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>13410</v>
+        <v>13400</v>
       </c>
       <c r="B185" t="s">
-        <v>50</v>
+        <v>299</v>
       </c>
       <c r="C185" t="s">
-        <v>299</v>
+        <v>115</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>13420</v>
-      </c>
-      <c r="B186" s="3" t="s">
+        <v>13410</v>
+      </c>
+      <c r="B186" t="s">
+        <v>50</v>
+      </c>
+      <c r="C186" t="s">
         <v>300</v>
-      </c>
-      <c r="C186" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>13421</v>
+        <v>13420</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>301</v>
@@ -7133,7 +7136,7 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>13430</v>
+        <v>13421</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>302</v>
@@ -7144,9 +7147,9 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>14090</v>
-      </c>
-      <c r="B189" t="s">
+        <v>13430</v>
+      </c>
+      <c r="B189" s="3" t="s">
         <v>303</v>
       </c>
       <c r="C189" t="s">
@@ -7155,48 +7158,44 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
+        <v>14090</v>
+      </c>
+      <c r="B190" t="s">
+        <v>304</v>
+      </c>
+      <c r="C190" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191">
         <v>14110</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C190" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="191" ht="14" spans="1:7">
-      <c r="A191">
-        <v>15010</v>
-      </c>
-      <c r="B191" t="s">
+      <c r="B191" s="2" t="s">
         <v>305</v>
       </c>
       <c r="C191" t="s">
         <v>115</v>
       </c>
-      <c r="D191" t="s">
-        <v>306</v>
-      </c>
-      <c r="G191" s="1"/>
     </row>
     <row r="192" ht="14" spans="1:7">
       <c r="A192">
-        <v>16010</v>
+        <v>15010</v>
       </c>
       <c r="B192" t="s">
+        <v>306</v>
+      </c>
+      <c r="C192" t="s">
+        <v>115</v>
+      </c>
+      <c r="D192" t="s">
         <v>307</v>
-      </c>
-      <c r="C192" t="s">
-        <v>115</v>
-      </c>
-      <c r="D192" t="s">
-        <v>8</v>
       </c>
       <c r="G192" s="1"/>
     </row>
     <row r="193" ht="14" spans="1:7">
       <c r="A193">
-        <v>16020</v>
+        <v>16010</v>
       </c>
       <c r="B193" t="s">
         <v>308</v>
@@ -7204,11 +7203,14 @@
       <c r="C193" t="s">
         <v>115</v>
       </c>
+      <c r="D193" t="s">
+        <v>8</v>
+      </c>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" ht="14" spans="1:7">
       <c r="A194">
-        <v>16100</v>
+        <v>16020</v>
       </c>
       <c r="B194" t="s">
         <v>309</v>
@@ -7216,10 +7218,11 @@
       <c r="C194" t="s">
         <v>115</v>
       </c>
+      <c r="G194" s="1"/>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>16110</v>
+        <v>16100</v>
       </c>
       <c r="B195" t="s">
         <v>310</v>
@@ -7230,7 +7233,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>16200</v>
+        <v>16110</v>
       </c>
       <c r="B196" t="s">
         <v>311</v>
@@ -7241,7 +7244,7 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>16210</v>
+        <v>16200</v>
       </c>
       <c r="B197" t="s">
         <v>312</v>
@@ -7252,7 +7255,7 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>16220</v>
+        <v>16210</v>
       </c>
       <c r="B198" t="s">
         <v>313</v>
@@ -7263,7 +7266,7 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>16230</v>
+        <v>16220</v>
       </c>
       <c r="B199" t="s">
         <v>314</v>
@@ -7274,9 +7277,9 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>16300</v>
-      </c>
-      <c r="B200" s="3" t="s">
+        <v>16230</v>
+      </c>
+      <c r="B200" t="s">
         <v>315</v>
       </c>
       <c r="C200" t="s">
@@ -7285,7 +7288,7 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>16310</v>
+        <v>16300</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>316</v>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>16320</v>
+        <v>16310</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>317</v>
@@ -7307,7 +7310,7 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>16400</v>
+        <v>16320</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>318</v>
@@ -7318,7 +7321,7 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>16410</v>
+        <v>16400</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>319</v>
@@ -7327,118 +7330,118 @@
         <v>115</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:3">
       <c r="A205">
-        <v>16800</v>
-      </c>
-      <c r="B205" t="s">
-        <v>201</v>
+        <v>16410</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="C205" t="s">
         <v>115</v>
-      </c>
-      <c r="D205" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206">
-        <v>16801</v>
+        <v>16800</v>
       </c>
       <c r="B206" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C206" t="s">
         <v>115</v>
       </c>
       <c r="D206" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B207" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C207" t="s">
         <v>115</v>
       </c>
       <c r="D207" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B208" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C208" t="s">
         <v>115</v>
       </c>
       <c r="D208" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B209" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C209" t="s">
         <v>115</v>
       </c>
       <c r="D209" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B210" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C210" t="s">
         <v>115</v>
       </c>
       <c r="D210" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211">
+        <v>16805</v>
+      </c>
+      <c r="B211" t="s">
+        <v>206</v>
+      </c>
+      <c r="C211" t="s">
+        <v>115</v>
+      </c>
+      <c r="D211" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212">
         <v>16806</v>
       </c>
-      <c r="B211" t="s">
+      <c r="B212" t="s">
         <v>207</v>
       </c>
-      <c r="C211" t="s">
-        <v>115</v>
-      </c>
-      <c r="D211" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212">
+      <c r="C212" t="s">
+        <v>115</v>
+      </c>
+      <c r="D212" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213">
         <v>17010</v>
-      </c>
-      <c r="B212" t="s">
-        <v>321</v>
-      </c>
-      <c r="C212" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
-      <c r="A213">
-        <v>18010</v>
       </c>
       <c r="B213" t="s">
         <v>322</v>
@@ -7446,27 +7449,27 @@
       <c r="C213" t="s">
         <v>115</v>
       </c>
-      <c r="D213" t="s">
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214">
+        <v>18010</v>
+      </c>
+      <c r="B214" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214">
-        <v>18020</v>
-      </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
+        <v>115</v>
+      </c>
+      <c r="D214" t="s">
         <v>324</v>
-      </c>
-      <c r="C214" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>18100</v>
+        <v>18020</v>
       </c>
       <c r="B215" t="s">
-        <v>212</v>
+        <v>325</v>
       </c>
       <c r="C215" t="s">
         <v>115</v>
@@ -7474,10 +7477,10 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>18110</v>
+        <v>18100</v>
       </c>
       <c r="B216" t="s">
-        <v>325</v>
+        <v>212</v>
       </c>
       <c r="C216" t="s">
         <v>115</v>
@@ -7485,7 +7488,7 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>18120</v>
+        <v>18110</v>
       </c>
       <c r="B217" t="s">
         <v>326</v>
@@ -7496,10 +7499,10 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>18130</v>
+        <v>18120</v>
       </c>
       <c r="B218" t="s">
-        <v>244</v>
+        <v>327</v>
       </c>
       <c r="C218" t="s">
         <v>115</v>
@@ -7507,10 +7510,10 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>18200</v>
+        <v>18130</v>
       </c>
       <c r="B219" t="s">
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="C219" t="s">
         <v>115</v>
@@ -7518,10 +7521,10 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>18210</v>
+        <v>18200</v>
       </c>
       <c r="B220" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C220" t="s">
         <v>115</v>
@@ -7529,10 +7532,10 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>18220</v>
+        <v>18210</v>
       </c>
       <c r="B221" t="s">
-        <v>327</v>
+        <v>124</v>
       </c>
       <c r="C221" t="s">
         <v>115</v>
@@ -7540,9 +7543,9 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>18230</v>
-      </c>
-      <c r="B222" s="2" t="s">
+        <v>18220</v>
+      </c>
+      <c r="B222" t="s">
         <v>328</v>
       </c>
       <c r="C222" t="s">
@@ -7551,9 +7554,9 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>18300</v>
-      </c>
-      <c r="B223" t="s">
+        <v>18230</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>329</v>
       </c>
       <c r="C223" t="s">
@@ -7562,9 +7565,9 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>18310</v>
-      </c>
-      <c r="B224" s="4" t="s">
+        <v>18300</v>
+      </c>
+      <c r="B224" t="s">
         <v>330</v>
       </c>
       <c r="C224" t="s">
@@ -7573,9 +7576,9 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>18320</v>
-      </c>
-      <c r="B225" t="s">
+        <v>18310</v>
+      </c>
+      <c r="B225" s="4" t="s">
         <v>331</v>
       </c>
       <c r="C225" t="s">
@@ -7584,7 +7587,7 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>18340</v>
+        <v>18320</v>
       </c>
       <c r="B226" t="s">
         <v>332</v>
@@ -7595,7 +7598,7 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>18400</v>
+        <v>18340</v>
       </c>
       <c r="B227" t="s">
         <v>333</v>
@@ -7606,7 +7609,7 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>18410</v>
+        <v>18400</v>
       </c>
       <c r="B228" t="s">
         <v>334</v>
@@ -7617,7 +7620,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>18420</v>
+        <v>18410</v>
       </c>
       <c r="B229" t="s">
         <v>335</v>
@@ -7628,7 +7631,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>18430</v>
+        <v>18420</v>
       </c>
       <c r="B230" t="s">
         <v>336</v>
@@ -7639,10 +7642,10 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="B231" t="s">
-        <v>116</v>
+        <v>337</v>
       </c>
       <c r="C231" t="s">
         <v>115</v>
@@ -7650,10 +7653,10 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>18450</v>
+        <v>18440</v>
       </c>
       <c r="B232" t="s">
-        <v>337</v>
+        <v>116</v>
       </c>
       <c r="C232" t="s">
         <v>115</v>
@@ -7661,7 +7664,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>18500</v>
+        <v>18450</v>
       </c>
       <c r="B233" t="s">
         <v>338</v>
@@ -7672,7 +7675,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>18510</v>
+        <v>18500</v>
       </c>
       <c r="B234" t="s">
         <v>339</v>
@@ -7683,7 +7686,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>18800</v>
+        <v>18510</v>
       </c>
       <c r="B235" t="s">
         <v>340</v>
@@ -7694,7 +7697,7 @@
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>18801</v>
+        <v>18800</v>
       </c>
       <c r="B236" t="s">
         <v>341</v>
@@ -7705,7 +7708,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>18802</v>
+        <v>18801</v>
       </c>
       <c r="B237" t="s">
         <v>342</v>
@@ -7716,7 +7719,7 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>18803</v>
+        <v>18802</v>
       </c>
       <c r="B238" t="s">
         <v>343</v>
@@ -7727,7 +7730,7 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>18804</v>
+        <v>18803</v>
       </c>
       <c r="B239" t="s">
         <v>344</v>
@@ -7738,7 +7741,7 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>18805</v>
+        <v>18804</v>
       </c>
       <c r="B240" t="s">
         <v>345</v>
@@ -7749,7 +7752,7 @@
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>18806</v>
+        <v>18805</v>
       </c>
       <c r="B241" t="s">
         <v>346</v>
@@ -7760,7 +7763,7 @@
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>18811</v>
+        <v>18806</v>
       </c>
       <c r="B242" t="s">
         <v>347</v>
@@ -7771,7 +7774,7 @@
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>18812</v>
+        <v>18811</v>
       </c>
       <c r="B243" t="s">
         <v>348</v>
@@ -7780,35 +7783,35 @@
         <v>115</v>
       </c>
     </row>
-    <row r="244" ht="14" spans="1:7">
+    <row r="244" spans="1:3">
       <c r="A244">
+        <v>18812</v>
+      </c>
+      <c r="B244" t="s">
+        <v>349</v>
+      </c>
+      <c r="C244" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="245" ht="14" spans="1:7">
+      <c r="A245">
         <v>19000</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C244" t="s">
-        <v>115</v>
-      </c>
-      <c r="D244" t="s">
+      <c r="B245" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="G244" s="1"/>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>19001</v>
-      </c>
-      <c r="B245" s="2" t="s">
+      <c r="C245" t="s">
+        <v>115</v>
+      </c>
+      <c r="D245" t="s">
         <v>351</v>
       </c>
-      <c r="C245" t="s">
-        <v>115</v>
-      </c>
+      <c r="G245" s="1"/>
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>19002</v>
+        <v>19001</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>352</v>
@@ -7819,7 +7822,7 @@
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>19003</v>
+        <v>19002</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>353</v>
@@ -7830,10 +7833,10 @@
     </row>
     <row r="248" spans="1:3">
       <c r="A248">
-        <v>19004</v>
+        <v>19003</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C248" t="s">
         <v>115</v>
@@ -7841,7 +7844,7 @@
     </row>
     <row r="249" spans="1:3">
       <c r="A249">
-        <v>19005</v>
+        <v>19004</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>354</v>
@@ -7852,7 +7855,7 @@
     </row>
     <row r="250" spans="1:3">
       <c r="A250">
-        <v>19006</v>
+        <v>19005</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>355</v>
@@ -7863,7 +7866,7 @@
     </row>
     <row r="251" spans="1:3">
       <c r="A251">
-        <v>19007</v>
+        <v>19006</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>356</v>
@@ -7874,7 +7877,7 @@
     </row>
     <row r="252" spans="1:3">
       <c r="A252">
-        <v>19008</v>
+        <v>19007</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>357</v>
@@ -7885,7 +7888,7 @@
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
-        <v>19009</v>
+        <v>19008</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>358</v>
@@ -7896,7 +7899,7 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254">
-        <v>19010</v>
+        <v>19009</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>359</v>
@@ -7907,7 +7910,7 @@
     </row>
     <row r="255" spans="1:3">
       <c r="A255">
-        <v>19011</v>
+        <v>19010</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>360</v>
@@ -7918,7 +7921,7 @@
     </row>
     <row r="256" spans="1:3">
       <c r="A256">
-        <v>19012</v>
+        <v>19011</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>361</v>
@@ -7929,7 +7932,7 @@
     </row>
     <row r="257" spans="1:3">
       <c r="A257">
-        <v>19013</v>
+        <v>19012</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>362</v>
@@ -7940,7 +7943,7 @@
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
-        <v>19014</v>
+        <v>19013</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>363</v>
@@ -7951,9 +7954,9 @@
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
-        <v>19100</v>
-      </c>
-      <c r="B259" t="s">
+        <v>19014</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>364</v>
       </c>
       <c r="C259" t="s">
@@ -7962,7 +7965,7 @@
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
-        <v>19110</v>
+        <v>19100</v>
       </c>
       <c r="B260" t="s">
         <v>365</v>
@@ -7973,9 +7976,9 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
-        <v>19200</v>
-      </c>
-      <c r="B261" s="3" t="s">
+        <v>19110</v>
+      </c>
+      <c r="B261" t="s">
         <v>366</v>
       </c>
       <c r="C261" t="s">
@@ -7984,7 +7987,7 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>367</v>
@@ -7995,7 +7998,7 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
-        <v>19220</v>
+        <v>19210</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>368</v>
@@ -8006,7 +8009,7 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
-        <v>19230</v>
+        <v>19220</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>369</v>
@@ -8017,9 +8020,9 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265">
-        <v>19240</v>
-      </c>
-      <c r="B265" s="4" t="s">
+        <v>19230</v>
+      </c>
+      <c r="B265" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C265" t="s">
@@ -8028,9 +8031,9 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
-        <v>19250</v>
-      </c>
-      <c r="B266" s="3" t="s">
+        <v>19240</v>
+      </c>
+      <c r="B266" s="4" t="s">
         <v>371</v>
       </c>
       <c r="C266" t="s">
@@ -8039,9 +8042,9 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267">
-        <v>19260</v>
-      </c>
-      <c r="B267" s="4" t="s">
+        <v>19250</v>
+      </c>
+      <c r="B267" s="3" t="s">
         <v>372</v>
       </c>
       <c r="C267" t="s">
@@ -8050,9 +8053,9 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
-        <v>19270</v>
-      </c>
-      <c r="B268" s="3" t="s">
+        <v>19260</v>
+      </c>
+      <c r="B268" s="4" t="s">
         <v>373</v>
       </c>
       <c r="C268" t="s">
@@ -8061,9 +8064,9 @@
     </row>
     <row r="269" spans="1:3">
       <c r="A269">
-        <v>19280</v>
-      </c>
-      <c r="B269" s="4" t="s">
+        <v>19270</v>
+      </c>
+      <c r="B269" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C269" t="s">
@@ -8072,29 +8075,29 @@
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
+        <v>19280</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C270" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271">
         <v>19300</v>
       </c>
-      <c r="B270" t="s">
-        <v>375</v>
-      </c>
-      <c r="C270" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="271" ht="26" spans="1:3">
-      <c r="A271">
+      <c r="B271" t="s">
+        <v>376</v>
+      </c>
+      <c r="C271" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="272" ht="26" spans="1:3">
+      <c r="A272">
         <v>19310</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C271" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272">
-        <v>19320</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>377</v>
@@ -8105,9 +8108,9 @@
     </row>
     <row r="273" spans="1:3">
       <c r="A273">
-        <v>19330</v>
-      </c>
-      <c r="B273" t="s">
+        <v>19320</v>
+      </c>
+      <c r="B273" s="3" t="s">
         <v>378</v>
       </c>
       <c r="C273" t="s">
@@ -8116,7 +8119,7 @@
     </row>
     <row r="274" spans="1:3">
       <c r="A274">
-        <v>19340</v>
+        <v>19330</v>
       </c>
       <c r="B274" t="s">
         <v>379</v>
@@ -8127,7 +8130,7 @@
     </row>
     <row r="275" spans="1:3">
       <c r="A275">
-        <v>19350</v>
+        <v>19340</v>
       </c>
       <c r="B275" t="s">
         <v>380</v>
@@ -8138,7 +8141,7 @@
     </row>
     <row r="276" spans="1:3">
       <c r="A276">
-        <v>19360</v>
+        <v>19350</v>
       </c>
       <c r="B276" t="s">
         <v>381</v>
@@ -8149,9 +8152,9 @@
     </row>
     <row r="277" spans="1:3">
       <c r="A277">
-        <v>19400</v>
-      </c>
-      <c r="B277" s="3" t="s">
+        <v>19360</v>
+      </c>
+      <c r="B277" t="s">
         <v>382</v>
       </c>
       <c r="C277" t="s">
@@ -8160,7 +8163,7 @@
     </row>
     <row r="278" spans="1:3">
       <c r="A278">
-        <v>19401</v>
+        <v>19400</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>383</v>
@@ -8171,9 +8174,9 @@
     </row>
     <row r="279" spans="1:3">
       <c r="A279">
-        <v>19410</v>
-      </c>
-      <c r="B279" s="4" t="s">
+        <v>19401</v>
+      </c>
+      <c r="B279" s="3" t="s">
         <v>384</v>
       </c>
       <c r="C279" t="s">
@@ -8182,9 +8185,9 @@
     </row>
     <row r="280" spans="1:3">
       <c r="A280">
-        <v>19420</v>
-      </c>
-      <c r="B280" s="3" t="s">
+        <v>19410</v>
+      </c>
+      <c r="B280" s="4" t="s">
         <v>385</v>
       </c>
       <c r="C280" t="s">
@@ -8193,9 +8196,9 @@
     </row>
     <row r="281" spans="1:3">
       <c r="A281">
-        <v>19500</v>
-      </c>
-      <c r="B281" t="s">
+        <v>19420</v>
+      </c>
+      <c r="B281" s="3" t="s">
         <v>386</v>
       </c>
       <c r="C281" t="s">
@@ -8204,10 +8207,10 @@
     </row>
     <row r="282" spans="1:3">
       <c r="A282">
-        <v>19510</v>
-      </c>
-      <c r="B282" s="4" t="s">
-        <v>372</v>
+        <v>19500</v>
+      </c>
+      <c r="B282" t="s">
+        <v>387</v>
       </c>
       <c r="C282" t="s">
         <v>115</v>
@@ -8215,10 +8218,10 @@
     </row>
     <row r="283" spans="1:3">
       <c r="A283">
-        <v>19520</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>387</v>
+        <v>19510</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="C283" t="s">
         <v>115</v>
@@ -8226,7 +8229,7 @@
     </row>
     <row r="284" spans="1:3">
       <c r="A284">
-        <v>19600</v>
+        <v>19520</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>388</v>
@@ -8237,7 +8240,7 @@
     </row>
     <row r="285" spans="1:3">
       <c r="A285">
-        <v>19601</v>
+        <v>19600</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>389</v>
@@ -8248,7 +8251,7 @@
     </row>
     <row r="286" spans="1:3">
       <c r="A286">
-        <v>19602</v>
+        <v>19601</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>390</v>
@@ -8259,7 +8262,7 @@
     </row>
     <row r="287" spans="1:3">
       <c r="A287">
-        <v>19603</v>
+        <v>19602</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>391</v>
@@ -8270,7 +8273,7 @@
     </row>
     <row r="288" spans="1:3">
       <c r="A288">
-        <v>19604</v>
+        <v>19603</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>392</v>
@@ -8279,39 +8282,38 @@
         <v>115</v>
       </c>
     </row>
-    <row r="289" ht="14" spans="1:7">
+    <row r="289" spans="1:3">
       <c r="A289">
-        <v>19611</v>
-      </c>
-      <c r="B289" t="s">
-        <v>354</v>
+        <v>19604</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>393</v>
       </c>
       <c r="C289" t="s">
         <v>115</v>
       </c>
-      <c r="D289" t="s">
-        <v>393</v>
-      </c>
-      <c r="G289" s="1"/>
     </row>
     <row r="290" ht="14" spans="1:7">
       <c r="A290">
-        <v>19612</v>
+        <v>19611</v>
       </c>
       <c r="B290" t="s">
+        <v>355</v>
+      </c>
+      <c r="C290" t="s">
+        <v>115</v>
+      </c>
+      <c r="D290" t="s">
         <v>394</v>
-      </c>
-      <c r="C290" t="s">
-        <v>115</v>
       </c>
       <c r="G290" s="1"/>
     </row>
     <row r="291" ht="14" spans="1:7">
       <c r="A291">
-        <v>19613</v>
+        <v>19612</v>
       </c>
       <c r="B291" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="C291" t="s">
         <v>115</v>
@@ -8320,10 +8322,10 @@
     </row>
     <row r="292" ht="14" spans="1:7">
       <c r="A292">
-        <v>19614</v>
+        <v>19613</v>
       </c>
       <c r="B292" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="C292" t="s">
         <v>115</v>
@@ -8332,7 +8334,7 @@
     </row>
     <row r="293" ht="14" spans="1:7">
       <c r="A293">
-        <v>19615</v>
+        <v>19614</v>
       </c>
       <c r="B293" t="s">
         <v>396</v>
@@ -8344,7 +8346,7 @@
     </row>
     <row r="294" ht="14" spans="1:7">
       <c r="A294">
-        <v>19616</v>
+        <v>19615</v>
       </c>
       <c r="B294" t="s">
         <v>397</v>
@@ -8356,7 +8358,7 @@
     </row>
     <row r="295" ht="14" spans="1:7">
       <c r="A295">
-        <v>19617</v>
+        <v>19616</v>
       </c>
       <c r="B295" t="s">
         <v>398</v>
@@ -8368,7 +8370,7 @@
     </row>
     <row r="296" ht="14" spans="1:7">
       <c r="A296">
-        <v>19618</v>
+        <v>19617</v>
       </c>
       <c r="B296" t="s">
         <v>399</v>
@@ -8380,7 +8382,7 @@
     </row>
     <row r="297" ht="14" spans="1:7">
       <c r="A297">
-        <v>19619</v>
+        <v>19618</v>
       </c>
       <c r="B297" t="s">
         <v>400</v>
@@ -8390,9 +8392,9 @@
       </c>
       <c r="G297" s="1"/>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" ht="14" spans="1:7">
       <c r="A298">
-        <v>19631</v>
+        <v>19619</v>
       </c>
       <c r="B298" t="s">
         <v>401</v>
@@ -8400,24 +8402,25 @@
       <c r="C298" t="s">
         <v>115</v>
       </c>
-      <c r="D298" t="s">
+      <c r="G298" s="1"/>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299">
+        <v>19631</v>
+      </c>
+      <c r="B299" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="299" spans="1:3">
-      <c r="A299">
-        <v>19632</v>
-      </c>
-      <c r="B299" t="s">
+      <c r="C299" t="s">
+        <v>115</v>
+      </c>
+      <c r="D299" t="s">
         <v>403</v>
-      </c>
-      <c r="C299" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
-        <v>19633</v>
+        <v>19632</v>
       </c>
       <c r="B300" t="s">
         <v>404</v>
@@ -8428,7 +8431,7 @@
     </row>
     <row r="301" spans="1:3">
       <c r="A301">
-        <v>19634</v>
+        <v>19633</v>
       </c>
       <c r="B301" t="s">
         <v>405</v>
@@ -8439,9 +8442,9 @@
     </row>
     <row r="302" spans="1:3">
       <c r="A302">
-        <v>19700</v>
-      </c>
-      <c r="B302" s="3" t="s">
+        <v>19634</v>
+      </c>
+      <c r="B302" t="s">
         <v>406</v>
       </c>
       <c r="C302" t="s">
@@ -8450,10 +8453,10 @@
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
-        <v>19710</v>
+        <v>19700</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="C303" t="s">
         <v>115</v>
@@ -8461,10 +8464,10 @@
     </row>
     <row r="304" spans="1:3">
       <c r="A304">
-        <v>19720</v>
+        <v>19710</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>407</v>
+        <v>357</v>
       </c>
       <c r="C304" t="s">
         <v>115</v>
@@ -8472,7 +8475,7 @@
     </row>
     <row r="305" spans="1:3">
       <c r="A305">
-        <v>19730</v>
+        <v>19720</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>408</v>
@@ -8483,7 +8486,7 @@
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
-        <v>19740</v>
+        <v>19730</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>409</v>
@@ -8494,29 +8497,29 @@
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
-        <v>19800</v>
-      </c>
-      <c r="B307" t="s">
+        <v>19740</v>
+      </c>
+      <c r="B307" s="3" t="s">
         <v>410</v>
       </c>
       <c r="C307" t="s">
-        <v>411</v>
+        <v>115</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308">
+        <v>19800</v>
+      </c>
+      <c r="B308" t="s">
+        <v>411</v>
+      </c>
+      <c r="C308" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309">
         <v>19810</v>
-      </c>
-      <c r="B308" t="s">
-        <v>412</v>
-      </c>
-      <c r="C308" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
-      <c r="A309">
-        <v>20010</v>
       </c>
       <c r="B309" t="s">
         <v>413</v>
@@ -8524,26 +8527,26 @@
       <c r="C309" t="s">
         <v>115</v>
       </c>
-      <c r="D309" t="s">
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310">
+        <v>20010</v>
+      </c>
+      <c r="B310" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="310" spans="1:3">
-      <c r="A310">
-        <v>20020</v>
-      </c>
-      <c r="B310" t="s">
+      <c r="C310" t="s">
+        <v>115</v>
+      </c>
+      <c r="D310" t="s">
         <v>415</v>
-      </c>
-      <c r="C310" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311">
-        <v>20030</v>
-      </c>
-      <c r="B311" s="3" t="s">
+        <v>20020</v>
+      </c>
+      <c r="B311" t="s">
         <v>416</v>
       </c>
       <c r="C311" t="s">
@@ -8552,9 +8555,9 @@
     </row>
     <row r="312" spans="1:3">
       <c r="A312">
-        <v>20040</v>
-      </c>
-      <c r="B312" t="s">
+        <v>20030</v>
+      </c>
+      <c r="B312" s="3" t="s">
         <v>417</v>
       </c>
       <c r="C312" t="s">
@@ -8563,7 +8566,7 @@
     </row>
     <row r="313" spans="1:3">
       <c r="A313">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B313" t="s">
         <v>418</v>
@@ -8574,7 +8577,7 @@
     </row>
     <row r="314" spans="1:3">
       <c r="A314">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B314" t="s">
         <v>419</v>
@@ -8585,7 +8588,7 @@
     </row>
     <row r="315" spans="1:3">
       <c r="A315">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B315" t="s">
         <v>420</v>
@@ -8596,7 +8599,7 @@
     </row>
     <row r="316" spans="1:3">
       <c r="A316">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B316" t="s">
         <v>421</v>
@@ -8607,7 +8610,7 @@
     </row>
     <row r="317" spans="1:3">
       <c r="A317">
-        <v>20200</v>
+        <v>20120</v>
       </c>
       <c r="B317" t="s">
         <v>422</v>
@@ -8618,10 +8621,10 @@
     </row>
     <row r="318" spans="1:3">
       <c r="A318">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B318" t="s">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="C318" t="s">
         <v>115</v>
@@ -8629,10 +8632,10 @@
     </row>
     <row r="319" spans="1:3">
       <c r="A319">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B319" t="s">
-        <v>423</v>
+        <v>338</v>
       </c>
       <c r="C319" t="s">
         <v>115</v>
@@ -8640,7 +8643,7 @@
     </row>
     <row r="320" spans="1:3">
       <c r="A320">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B320" t="s">
         <v>424</v>
@@ -8651,9 +8654,9 @@
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
-        <v>20230</v>
-      </c>
-      <c r="B321" s="3" t="s">
+        <v>20220</v>
+      </c>
+      <c r="B321" t="s">
         <v>425</v>
       </c>
       <c r="C321" t="s">
@@ -8662,7 +8665,7 @@
     </row>
     <row r="322" spans="1:3">
       <c r="A322">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>426</v>
@@ -8673,7 +8676,7 @@
     </row>
     <row r="323" spans="1:3">
       <c r="A323">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>427</v>
@@ -8684,9 +8687,9 @@
     </row>
     <row r="324" spans="1:3">
       <c r="A324">
-        <v>20260</v>
-      </c>
-      <c r="B324" t="s">
+        <v>20250</v>
+      </c>
+      <c r="B324" s="3" t="s">
         <v>428</v>
       </c>
       <c r="C324" t="s">
@@ -8695,7 +8698,7 @@
     </row>
     <row r="325" spans="1:3">
       <c r="A325">
-        <v>20270</v>
+        <v>20260</v>
       </c>
       <c r="B325" t="s">
         <v>429</v>
@@ -8706,7 +8709,7 @@
     </row>
     <row r="326" spans="1:3">
       <c r="A326">
-        <v>20280</v>
+        <v>20270</v>
       </c>
       <c r="B326" t="s">
         <v>430</v>
@@ -8717,7 +8720,7 @@
     </row>
     <row r="327" spans="1:3">
       <c r="A327">
-        <v>20290</v>
+        <v>20280</v>
       </c>
       <c r="B327" t="s">
         <v>431</v>
@@ -8728,7 +8731,7 @@
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
-        <v>20300</v>
+        <v>20290</v>
       </c>
       <c r="B328" t="s">
         <v>432</v>
@@ -8739,7 +8742,7 @@
     </row>
     <row r="329" spans="1:3">
       <c r="A329">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B329" t="s">
         <v>433</v>
@@ -8750,7 +8753,7 @@
     </row>
     <row r="330" spans="1:3">
       <c r="A330">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B330" t="s">
         <v>434</v>
@@ -8761,7 +8764,7 @@
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
-        <v>20330</v>
+        <v>20320</v>
       </c>
       <c r="B331" t="s">
         <v>435</v>
@@ -8772,7 +8775,7 @@
     </row>
     <row r="332" spans="1:3">
       <c r="A332">
-        <v>20340</v>
+        <v>20330</v>
       </c>
       <c r="B332" t="s">
         <v>436</v>
@@ -8783,7 +8786,7 @@
     </row>
     <row r="333" spans="1:3">
       <c r="A333">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B333" t="s">
         <v>437</v>
@@ -8794,7 +8797,7 @@
     </row>
     <row r="334" spans="1:3">
       <c r="A334">
-        <v>23010</v>
+        <v>20350</v>
       </c>
       <c r="B334" t="s">
         <v>438</v>
@@ -8805,10 +8808,10 @@
     </row>
     <row r="335" spans="1:3">
       <c r="A335">
-        <v>23020</v>
+        <v>23010</v>
       </c>
       <c r="B335" t="s">
-        <v>119</v>
+        <v>439</v>
       </c>
       <c r="C335" t="s">
         <v>115</v>
@@ -8816,10 +8819,10 @@
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
-        <v>23030</v>
+        <v>23020</v>
       </c>
       <c r="B336" t="s">
-        <v>439</v>
+        <v>119</v>
       </c>
       <c r="C336" t="s">
         <v>115</v>
@@ -8827,7 +8830,7 @@
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
-        <v>23031</v>
+        <v>23030</v>
       </c>
       <c r="B337" t="s">
         <v>440</v>
@@ -8838,7 +8841,7 @@
     </row>
     <row r="338" spans="1:3">
       <c r="A338">
-        <v>23032</v>
+        <v>23031</v>
       </c>
       <c r="B338" t="s">
         <v>441</v>
@@ -8849,7 +8852,7 @@
     </row>
     <row r="339" spans="1:3">
       <c r="A339">
-        <v>23040</v>
+        <v>23032</v>
       </c>
       <c r="B339" t="s">
         <v>442</v>
@@ -8860,7 +8863,7 @@
     </row>
     <row r="340" spans="1:3">
       <c r="A340">
-        <v>24010</v>
+        <v>23040</v>
       </c>
       <c r="B340" t="s">
         <v>443</v>
@@ -8871,7 +8874,7 @@
     </row>
     <row r="341" spans="1:3">
       <c r="A341">
-        <v>24020</v>
+        <v>24010</v>
       </c>
       <c r="B341" t="s">
         <v>444</v>
@@ -8882,7 +8885,7 @@
     </row>
     <row r="342" spans="1:3">
       <c r="A342">
-        <v>24030</v>
+        <v>24020</v>
       </c>
       <c r="B342" t="s">
         <v>445</v>
@@ -8893,7 +8896,7 @@
     </row>
     <row r="343" spans="1:3">
       <c r="A343">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="B343" t="s">
         <v>446</v>
@@ -8904,7 +8907,7 @@
     </row>
     <row r="344" spans="1:3">
       <c r="A344">
-        <v>24110</v>
+        <v>24040</v>
       </c>
       <c r="B344" t="s">
         <v>447</v>
@@ -8915,7 +8918,7 @@
     </row>
     <row r="345" spans="1:3">
       <c r="A345">
-        <v>24111</v>
+        <v>24110</v>
       </c>
       <c r="B345" t="s">
         <v>448</v>
@@ -8926,7 +8929,7 @@
     </row>
     <row r="346" spans="1:3">
       <c r="A346">
-        <v>24112</v>
+        <v>24111</v>
       </c>
       <c r="B346" t="s">
         <v>449</v>
@@ -8937,7 +8940,7 @@
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
-        <v>24113</v>
+        <v>24112</v>
       </c>
       <c r="B347" t="s">
         <v>450</v>
@@ -8948,7 +8951,7 @@
     </row>
     <row r="348" spans="1:3">
       <c r="A348">
-        <v>24114</v>
+        <v>24113</v>
       </c>
       <c r="B348" t="s">
         <v>451</v>
@@ -8959,7 +8962,7 @@
     </row>
     <row r="349" spans="1:3">
       <c r="A349">
-        <v>24115</v>
+        <v>24114</v>
       </c>
       <c r="B349" t="s">
         <v>452</v>
@@ -8970,7 +8973,7 @@
     </row>
     <row r="350" spans="1:3">
       <c r="A350">
-        <v>24116</v>
+        <v>24115</v>
       </c>
       <c r="B350" t="s">
         <v>453</v>
@@ -8981,7 +8984,7 @@
     </row>
     <row r="351" spans="1:3">
       <c r="A351">
-        <v>24117</v>
+        <v>24116</v>
       </c>
       <c r="B351" t="s">
         <v>454</v>
@@ -8992,7 +8995,7 @@
     </row>
     <row r="352" spans="1:3">
       <c r="A352">
-        <v>24118</v>
+        <v>24117</v>
       </c>
       <c r="B352" t="s">
         <v>455</v>
@@ -9003,7 +9006,7 @@
     </row>
     <row r="353" spans="1:3">
       <c r="A353">
-        <v>24119</v>
+        <v>24118</v>
       </c>
       <c r="B353" t="s">
         <v>456</v>
@@ -9014,7 +9017,7 @@
     </row>
     <row r="354" spans="1:3">
       <c r="A354">
-        <v>24120</v>
+        <v>24119</v>
       </c>
       <c r="B354" t="s">
         <v>457</v>
@@ -9025,7 +9028,7 @@
     </row>
     <row r="355" spans="1:3">
       <c r="A355">
-        <v>24121</v>
+        <v>24120</v>
       </c>
       <c r="B355" t="s">
         <v>458</v>
@@ -9036,7 +9039,7 @@
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
-        <v>24122</v>
+        <v>24121</v>
       </c>
       <c r="B356" t="s">
         <v>459</v>
@@ -9047,10 +9050,10 @@
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
-        <v>30000</v>
+        <v>24122</v>
       </c>
       <c r="B357" t="s">
-        <v>358</v>
+        <v>460</v>
       </c>
       <c r="C357" t="s">
         <v>115</v>
@@ -9058,10 +9061,10 @@
     </row>
     <row r="358" spans="1:3">
       <c r="A358">
-        <v>30010</v>
+        <v>30000</v>
       </c>
       <c r="B358" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="C358" t="s">
         <v>115</v>
@@ -9069,10 +9072,10 @@
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B359" t="s">
-        <v>117</v>
+        <v>461</v>
       </c>
       <c r="C359" t="s">
         <v>115</v>
@@ -9080,10 +9083,10 @@
     </row>
     <row r="360" spans="1:3">
       <c r="A360">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B360" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C360" t="s">
         <v>115</v>
@@ -9091,10 +9094,10 @@
     </row>
     <row r="361" spans="1:3">
       <c r="A361">
-        <v>30040</v>
+        <v>30030</v>
       </c>
       <c r="B361" t="s">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="C361" t="s">
         <v>115</v>
@@ -9102,7 +9105,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <v>31010</v>
+        <v>30040</v>
       </c>
       <c r="B362" t="s">
         <v>462</v>
@@ -9113,7 +9116,7 @@
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
-        <v>31020</v>
+        <v>31010</v>
       </c>
       <c r="B363" t="s">
         <v>463</v>
@@ -9122,9 +9125,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="364" spans="1:4">
+    <row r="364" spans="1:3">
       <c r="A364">
-        <v>102000</v>
+        <v>31020</v>
       </c>
       <c r="B364" t="s">
         <v>464</v>
@@ -9132,27 +9135,27 @@
       <c r="C364" t="s">
         <v>115</v>
       </c>
-      <c r="D364" t="s">
+    </row>
+    <row r="365" spans="1:4">
+      <c r="A365">
+        <v>102000</v>
+      </c>
+      <c r="B365" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="365" spans="1:3">
-      <c r="A365">
-        <v>102010</v>
-      </c>
-      <c r="B365" t="s">
+      <c r="C365" t="s">
+        <v>115</v>
+      </c>
+      <c r="D365" t="s">
         <v>466</v>
-      </c>
-      <c r="C365" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366">
-        <v>102020</v>
+        <v>102010</v>
       </c>
       <c r="B366" t="s">
-        <v>354</v>
+        <v>467</v>
       </c>
       <c r="C366" t="s">
         <v>115</v>
@@ -9160,18 +9163,18 @@
     </row>
     <row r="367" spans="1:3">
       <c r="A367">
+        <v>102020</v>
+      </c>
+      <c r="B367" t="s">
+        <v>355</v>
+      </c>
+      <c r="C367" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368">
         <v>102030</v>
-      </c>
-      <c r="B367" t="s">
-        <v>467</v>
-      </c>
-      <c r="C367" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4">
-      <c r="A368">
-        <v>113000</v>
       </c>
       <c r="B368" t="s">
         <v>468</v>
@@ -9179,24 +9182,24 @@
       <c r="C368" t="s">
         <v>115</v>
       </c>
-      <c r="D368" t="s">
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369">
+        <v>113000</v>
+      </c>
+      <c r="B369" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="369" spans="1:3">
-      <c r="A369">
-        <v>113010</v>
-      </c>
-      <c r="B369" t="s">
+      <c r="C369" t="s">
+        <v>115</v>
+      </c>
+      <c r="D369" t="s">
         <v>470</v>
-      </c>
-      <c r="C369" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370">
-        <v>113020</v>
+        <v>113010</v>
       </c>
       <c r="B370" t="s">
         <v>471</v>
@@ -9207,7 +9210,7 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371">
-        <v>113030</v>
+        <v>113020</v>
       </c>
       <c r="B371" t="s">
         <v>472</v>
@@ -9218,7 +9221,7 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372">
-        <v>113040</v>
+        <v>113030</v>
       </c>
       <c r="B372" t="s">
         <v>473</v>
@@ -9227,9 +9230,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="373" spans="1:4">
+    <row r="373" spans="1:3">
       <c r="A373">
-        <v>121010</v>
+        <v>113040</v>
       </c>
       <c r="B373" t="s">
         <v>474</v>
@@ -9237,24 +9240,24 @@
       <c r="C373" t="s">
         <v>115</v>
       </c>
-      <c r="D373" t="s">
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374">
+        <v>121010</v>
+      </c>
+      <c r="B374" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="374" spans="1:3">
-      <c r="A374">
-        <v>121011</v>
-      </c>
-      <c r="B374" t="s">
+      <c r="C374" t="s">
+        <v>115</v>
+      </c>
+      <c r="D374" t="s">
         <v>476</v>
-      </c>
-      <c r="C374" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375">
-        <v>121012</v>
+        <v>121011</v>
       </c>
       <c r="B375" t="s">
         <v>477</v>
@@ -9265,7 +9268,7 @@
     </row>
     <row r="376" spans="1:3">
       <c r="A376">
-        <v>121013</v>
+        <v>121012</v>
       </c>
       <c r="B376" t="s">
         <v>478</v>
@@ -9276,7 +9279,7 @@
     </row>
     <row r="377" spans="1:3">
       <c r="A377">
-        <v>121014</v>
+        <v>121013</v>
       </c>
       <c r="B377" t="s">
         <v>479</v>
@@ -9287,7 +9290,7 @@
     </row>
     <row r="378" spans="1:3">
       <c r="A378">
-        <v>121015</v>
+        <v>121014</v>
       </c>
       <c r="B378" t="s">
         <v>480</v>
@@ -9298,7 +9301,7 @@
     </row>
     <row r="379" spans="1:3">
       <c r="A379">
-        <v>121016</v>
+        <v>121015</v>
       </c>
       <c r="B379" t="s">
         <v>481</v>
@@ -9309,7 +9312,7 @@
     </row>
     <row r="380" spans="1:3">
       <c r="A380">
-        <v>121017</v>
+        <v>121016</v>
       </c>
       <c r="B380" t="s">
         <v>482</v>
@@ -9320,7 +9323,7 @@
     </row>
     <row r="381" spans="1:3">
       <c r="A381">
-        <v>121018</v>
+        <v>121017</v>
       </c>
       <c r="B381" t="s">
         <v>483</v>
@@ -9331,7 +9334,7 @@
     </row>
     <row r="382" spans="1:3">
       <c r="A382">
-        <v>121019</v>
+        <v>121018</v>
       </c>
       <c r="B382" t="s">
         <v>484</v>
@@ -9342,7 +9345,7 @@
     </row>
     <row r="383" spans="1:3">
       <c r="A383">
-        <v>121020</v>
+        <v>121019</v>
       </c>
       <c r="B383" t="s">
         <v>485</v>
@@ -9353,12 +9356,23 @@
     </row>
     <row r="384" spans="1:3">
       <c r="A384">
-        <v>121030</v>
+        <v>121020</v>
       </c>
       <c r="B384" t="s">
         <v>486</v>
       </c>
       <c r="C384" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385">
+        <v>121030</v>
+      </c>
+      <c r="B385" t="s">
+        <v>487</v>
+      </c>
+      <c r="C385" t="s">
         <v>115</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="491">
   <si>
     <t>Id</t>
   </si>
@@ -34,10 +34,19 @@
     <t>Departure</t>
   </si>
   <si>
+    <t>DeckEdit</t>
+  </si>
+  <si>
     <t>TurnEnd</t>
   </si>
   <si>
+    <t>Mission</t>
+  </si>
+  <si>
     <t>MoveBattler</t>
+  </si>
+  <si>
+    <t>Transfer</t>
   </si>
   <si>
     <t>Wait</t>
@@ -879,7 +888,8 @@
     <t>Boot</t>
   </si>
   <si>
-    <t>橋梁戦場のエインフェリア</t>
+    <t>終末時計と
+エインフェリアの物語</t>
   </si>
   <si>
     <t>Title</t>
@@ -1083,10 +1093,13 @@
     <t>Tactics</t>
   </si>
   <si>
-    <t>ターン終了</t>
-  </si>
-  <si>
-    <t>移動</t>
+    <t>編成</t>
+  </si>
+  <si>
+    <t>報告</t>
+  </si>
+  <si>
+    <t>神界転送</t>
   </si>
   <si>
     <t>待機</t>
@@ -1102,9 +1115,6 @@
   </si>
   <si>
     <t>制圧</t>
-  </si>
-  <si>
-    <t>編成</t>
   </si>
   <si>
     <t>帰還</t>
@@ -1499,8 +1509,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1525,13 +1535,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -1539,7 +1542,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1554,22 +1564,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1584,8 +1594,62 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1600,53 +1664,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1655,14 +1673,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1683,97 +1693,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1791,7 +1717,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1803,7 +1831,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1815,37 +1843,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1857,7 +1855,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1895,11 +1905,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1911,6 +1927,24 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1944,30 +1978,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1985,7 +1995,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1994,131 +2004,131 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2129,6 +2139,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2485,8 +2498,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="11.3636363636364" customWidth="1"/>
   </cols>
@@ -2502,7 +2515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2512,8 +2525,17 @@
       <c r="C2">
         <v>19000</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2523,147 +2545,194 @@
       <c r="C3">
         <v>19001</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>19001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>19002</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>19002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>19003</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>19003</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="2"/>
+      <c r="C6"/>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>19004</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="2"/>
+      <c r="C7"/>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>19005</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="2"/>
+      <c r="C8"/>
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>19004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>19006</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="2"/>
+      <c r="C9"/>
+      <c r="E9">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>19005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>19007</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="2"/>
+      <c r="C10"/>
+      <c r="E10">
         <v>9</v>
       </c>
-      <c r="C8">
-        <v>19006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>19008</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="2"/>
+      <c r="C11"/>
+      <c r="E11">
         <v>10</v>
       </c>
-      <c r="C9">
-        <v>19007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>19009</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="2"/>
+      <c r="C12"/>
+      <c r="E12">
         <v>11</v>
       </c>
-      <c r="C10">
-        <v>19008</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>19010</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="2"/>
+      <c r="C13"/>
+      <c r="E13">
         <v>12</v>
       </c>
-      <c r="C11">
-        <v>19009</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>19011</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="2"/>
+      <c r="C14"/>
+      <c r="E14">
         <v>13</v>
       </c>
-      <c r="C12">
-        <v>19010</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14">
+        <v>19012</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="2"/>
+      <c r="C15"/>
+      <c r="E15">
         <v>14</v>
       </c>
-      <c r="C13">
-        <v>19011</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15">
+        <v>19013</v>
+      </c>
+    </row>
+    <row r="16" spans="5:7">
+      <c r="E16">
         <v>15</v>
       </c>
-      <c r="C14">
-        <v>19012</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>19013</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16">
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16">
         <v>19014</v>
       </c>
     </row>
@@ -2699,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>13210</v>
@@ -2710,7 +2779,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>13220</v>
@@ -2721,7 +2790,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -2732,7 +2801,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>13230</v>
@@ -2769,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2780,7 +2849,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>18110</v>
@@ -2791,7 +2860,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>18120</v>
@@ -2802,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>18130</v>
@@ -2835,25 +2904,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2861,7 +2930,7 @@
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>6010</v>
@@ -2893,7 +2962,7 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>6020</v>
@@ -2925,7 +2994,7 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>6030</v>
@@ -2957,7 +3026,7 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>6040</v>
@@ -2989,7 +3058,7 @@
         <v>2030</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>6210</v>
@@ -3021,7 +3090,7 @@
         <v>2040</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>6220</v>
@@ -3053,7 +3122,7 @@
         <v>2050</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8">
         <v>6230</v>
@@ -3085,7 +3154,7 @@
         <v>2060</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>6240</v>
@@ -3117,7 +3186,7 @@
         <v>2070</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10">
         <v>6250</v>
@@ -3149,7 +3218,7 @@
         <v>2080</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>6260</v>
@@ -3181,7 +3250,7 @@
         <v>2090</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C12">
         <v>6270</v>
@@ -3213,7 +3282,7 @@
         <v>2100</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>6280</v>
@@ -3260,15 +3329,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3277,12 +3346,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -3291,12 +3360,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -3305,12 +3374,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -3319,12 +3388,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -3333,12 +3402,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3347,12 +3416,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3361,12 +3430,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3375,12 +3444,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3389,12 +3458,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3403,12 +3472,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3417,12 +3486,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -3431,12 +3500,12 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3445,12 +3514,12 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -3459,12 +3528,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3473,12 +3542,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3487,12 +3556,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -3501,12 +3570,12 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -3515,12 +3584,12 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3529,12 +3598,12 @@
         <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -3543,12 +3612,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3557,12 +3626,12 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -3571,12 +3640,12 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -3585,12 +3654,12 @@
         <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3599,12 +3668,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -3613,12 +3682,12 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3627,12 +3696,12 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3641,12 +3710,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3655,12 +3724,12 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -3669,12 +3738,12 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3683,12 +3752,12 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -3697,12 +3766,12 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -3711,12 +3780,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3725,12 +3794,12 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -3739,12 +3808,12 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3753,12 +3822,12 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3767,12 +3836,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -3781,12 +3850,12 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -3795,12 +3864,12 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -3809,12 +3878,12 @@
         <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -3823,12 +3892,12 @@
         <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -3837,12 +3906,12 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -3851,12 +3920,12 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3865,12 +3934,12 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -3879,12 +3948,12 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -3893,12 +3962,12 @@
         <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B47">
         <v>11</v>
@@ -3907,12 +3976,12 @@
         <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -3921,12 +3990,12 @@
         <v>210</v>
       </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -3935,12 +4004,12 @@
         <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -3949,12 +4018,12 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -3963,12 +4032,12 @@
         <v>802</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -3977,12 +4046,12 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -3991,12 +4060,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -4005,12 +4074,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -4019,12 +4088,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4033,12 +4102,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -4047,12 +4116,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -4061,12 +4130,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -4075,12 +4144,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -4089,12 +4158,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -4103,12 +4172,12 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -4117,12 +4186,12 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -4133,7 +4202,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -4142,12 +4211,12 @@
         <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -4156,12 +4225,12 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4172,7 +4241,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -4183,7 +4252,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -4194,7 +4263,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4205,7 +4274,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -4214,12 +4283,12 @@
         <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -4228,12 +4297,12 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -4242,12 +4311,12 @@
         <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B73">
         <v>8</v>
@@ -4256,12 +4325,12 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -4270,12 +4339,12 @@
         <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -4284,12 +4353,12 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B76">
         <v>11</v>
@@ -4298,12 +4367,12 @@
         <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B77">
         <v>7</v>
@@ -4312,12 +4381,12 @@
         <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -4326,12 +4395,12 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -4340,12 +4409,12 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -4354,12 +4423,12 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4368,12 +4437,12 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -4382,12 +4451,12 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -4396,12 +4465,12 @@
         <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B84">
         <v>9</v>
@@ -4410,12 +4479,12 @@
         <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B85">
         <v>8</v>
@@ -4424,12 +4493,12 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -4438,12 +4507,12 @@
         <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4452,12 +4521,12 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -4466,12 +4535,12 @@
         <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -4480,12 +4549,12 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B90">
         <v>9</v>
@@ -4494,12 +4563,12 @@
         <v>813</v>
       </c>
       <c r="D90" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -4508,12 +4577,12 @@
         <v>800</v>
       </c>
       <c r="D91" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -4522,12 +4591,12 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -4536,12 +4605,12 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -4550,12 +4619,12 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B95">
         <v>9</v>
@@ -4564,12 +4633,12 @@
         <v>814</v>
       </c>
       <c r="D95" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -4578,12 +4647,12 @@
         <v>800</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -4592,12 +4661,12 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4606,12 +4675,12 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -4620,12 +4689,12 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -4634,12 +4703,12 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4648,12 +4717,12 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -4662,12 +4731,12 @@
         <v>818</v>
       </c>
       <c r="D102" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -4676,12 +4745,12 @@
         <v>800</v>
       </c>
       <c r="D103" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -4690,12 +4759,12 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B105">
         <v>9</v>
@@ -4704,12 +4773,12 @@
         <v>817</v>
       </c>
       <c r="D105" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -4718,12 +4787,12 @@
         <v>816</v>
       </c>
       <c r="D106" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -4732,12 +4801,12 @@
         <v>817</v>
       </c>
       <c r="D107" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B108">
         <v>4</v>
@@ -4746,12 +4815,12 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -4760,12 +4829,12 @@
         <v>801</v>
       </c>
       <c r="D109" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -4774,12 +4843,12 @@
         <v>800</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -4788,12 +4857,12 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -4802,12 +4871,12 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -4816,12 +4885,12 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -4830,12 +4899,12 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -4844,12 +4913,12 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -4858,12 +4927,12 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -4872,7 +4941,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4895,34 +4964,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="5">
+        <v>101</v>
+      </c>
+      <c r="B2" s="6">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -4930,7 +4999,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -4938,7 +5007,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -4946,7 +5015,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -4954,40 +5023,40 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B10">
         <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5014,10 +5083,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5025,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" ht="14" spans="1:7">
@@ -5036,10 +5105,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -5048,10 +5117,10 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5059,10 +5128,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5070,10 +5139,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5081,10 +5150,10 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5092,10 +5161,10 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5103,10 +5172,10 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5114,10 +5183,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5125,10 +5194,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5136,10 +5205,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5147,10 +5216,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5158,10 +5227,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5169,10 +5238,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5180,10 +5249,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5191,10 +5260,10 @@
         <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5202,10 +5271,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5213,10 +5282,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5224,10 +5293,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5235,10 +5304,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5246,10 +5315,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5257,10 +5326,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5268,10 +5337,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5279,10 +5348,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -5290,10 +5359,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5301,10 +5370,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5312,10 +5381,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5323,10 +5392,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5334,10 +5403,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5345,10 +5414,10 @@
         <v>342</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5356,13 +5425,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5370,13 +5439,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5384,13 +5453,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5398,13 +5467,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5412,13 +5481,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5426,13 +5495,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5440,10 +5509,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5451,10 +5520,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5462,10 +5531,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5473,10 +5542,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5484,10 +5553,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5495,10 +5564,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5506,10 +5575,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5517,10 +5586,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -5528,10 +5597,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5539,10 +5608,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -5550,10 +5619,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5561,10 +5630,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5572,10 +5641,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5583,10 +5652,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5594,10 +5663,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5605,10 +5674,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5616,10 +5685,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5627,10 +5696,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5638,10 +5707,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5649,10 +5718,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C57" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5660,10 +5729,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5671,10 +5740,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5682,10 +5751,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5693,10 +5762,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5704,10 +5773,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5715,10 +5784,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5726,10 +5795,10 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5737,10 +5806,10 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5748,10 +5817,10 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5759,10 +5828,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5770,10 +5839,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C68" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5781,10 +5850,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C69" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5792,10 +5861,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5803,10 +5872,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C71" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5814,10 +5883,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5825,10 +5894,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5836,10 +5905,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5847,10 +5916,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5858,10 +5927,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5869,10 +5938,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C77" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5880,10 +5949,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C78" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5891,10 +5960,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C79" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5902,10 +5971,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C80" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5913,10 +5982,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C81" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -5924,10 +5993,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C82" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -5935,10 +6004,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -5946,10 +6015,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -5957,10 +6026,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -5968,10 +6037,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C86" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -5979,10 +6048,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -5990,10 +6059,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -6001,10 +6070,10 @@
         <v>1000</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C89" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -6012,10 +6081,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C90" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -6023,10 +6092,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -6034,10 +6103,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C92" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -6045,10 +6114,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C93" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -6056,10 +6125,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C94" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -6067,10 +6136,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C95" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6078,13 +6147,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C96" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D96" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -6092,10 +6161,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C97" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -6103,10 +6172,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C98" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -6114,10 +6183,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C99" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -6125,10 +6194,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C100" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -6136,10 +6205,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -6147,10 +6216,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C102" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -6158,10 +6227,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6169,13 +6238,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6183,13 +6252,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D105" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6197,13 +6266,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D106" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6211,13 +6280,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C107" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6225,13 +6294,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C108" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D108" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -6239,10 +6308,10 @@
         <v>2101</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -6250,10 +6319,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C110" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -6261,10 +6330,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C111" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -6272,10 +6341,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -6283,10 +6352,10 @@
         <v>2105</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C113" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -6294,10 +6363,10 @@
         <v>2106</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C114" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6305,13 +6374,13 @@
         <v>2200</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C115" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D115" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6319,13 +6388,13 @@
         <v>2210</v>
       </c>
       <c r="B116" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D116" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="117" ht="29" customHeight="1" spans="1:4">
@@ -6333,13 +6402,13 @@
         <v>2220</v>
       </c>
       <c r="B117" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C117" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D117" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6347,13 +6416,13 @@
         <v>2300</v>
       </c>
       <c r="B118" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C118" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D118" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6361,13 +6430,13 @@
         <v>2310</v>
       </c>
       <c r="B119" t="s">
+        <v>226</v>
+      </c>
+      <c r="C119" t="s">
+        <v>118</v>
+      </c>
+      <c r="D119" t="s">
         <v>223</v>
-      </c>
-      <c r="C119" t="s">
-        <v>115</v>
-      </c>
-      <c r="D119" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6375,13 +6444,13 @@
         <v>2320</v>
       </c>
       <c r="B120" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C120" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D120" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6389,13 +6458,13 @@
         <v>2330</v>
       </c>
       <c r="B121" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C121" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D121" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6403,13 +6472,13 @@
         <v>2340</v>
       </c>
       <c r="B122" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C122" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D122" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6417,13 +6486,13 @@
         <v>2400</v>
       </c>
       <c r="B123" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C123" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D123" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -6431,10 +6500,10 @@
         <v>3000</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C124" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -6442,10 +6511,10 @@
         <v>3010</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C125" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -6453,10 +6522,10 @@
         <v>3011</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C126" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -6464,10 +6533,10 @@
         <v>3040</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C127" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -6475,10 +6544,10 @@
         <v>3050</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C128" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -6486,10 +6555,10 @@
         <v>3051</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C129" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -6497,10 +6566,10 @@
         <v>3052</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C130" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -6508,10 +6577,10 @@
         <v>3053</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -6519,10 +6588,10 @@
         <v>3054</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C132" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -6530,10 +6599,10 @@
         <v>3070</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C133" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -6541,10 +6610,10 @@
         <v>3071</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C134" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -6552,10 +6621,10 @@
         <v>3072</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C135" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -6563,10 +6632,10 @@
         <v>3073</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C136" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -6574,10 +6643,10 @@
         <v>3090</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C137" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -6585,10 +6654,10 @@
         <v>3211</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C138" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -6596,10 +6665,10 @@
         <v>3230</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C139" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6607,10 +6676,10 @@
         <v>5000</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C140" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6618,10 +6687,10 @@
         <v>5001</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C141" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6629,10 +6698,10 @@
         <v>5002</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C142" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6640,10 +6709,10 @@
         <v>6001</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C143" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6651,10 +6720,10 @@
         <v>6002</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C144" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6662,10 +6731,10 @@
         <v>6100</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C145" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6673,10 +6742,10 @@
         <v>6010</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C146" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6684,10 +6753,10 @@
         <v>6011</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C147" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6695,10 +6764,10 @@
         <v>6012</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C148" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6706,10 +6775,10 @@
         <v>6020</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C149" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6717,10 +6786,10 @@
         <v>6030</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C150" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6728,10 +6797,10 @@
         <v>6040</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C151" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6739,10 +6808,10 @@
         <v>6210</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C152" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6750,10 +6819,10 @@
         <v>6220</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C153" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6761,10 +6830,10 @@
         <v>6230</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C154" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6772,10 +6841,10 @@
         <v>6240</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C155" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6783,10 +6852,10 @@
         <v>6250</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6794,10 +6863,10 @@
         <v>6260</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C157" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6805,10 +6874,10 @@
         <v>6270</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C158" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6816,10 +6885,10 @@
         <v>6280</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C159" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6827,10 +6896,10 @@
         <v>6810</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C160" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6838,10 +6907,10 @@
         <v>6820</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C161" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6849,10 +6918,10 @@
         <v>6830</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C162" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6860,10 +6929,10 @@
         <v>6840</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C163" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -6871,10 +6940,10 @@
         <v>6850</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C164" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -6882,10 +6951,10 @@
         <v>6860</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C165" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6893,10 +6962,10 @@
         <v>6870</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C166" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6904,10 +6973,10 @@
         <v>6880</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C167" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6915,10 +6984,10 @@
         <v>6890</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C168" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="169" ht="130" spans="1:4">
@@ -6926,36 +6995,36 @@
         <v>12010</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C169" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D169" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="170" ht="26" spans="1:4">
       <c r="A170">
         <v>13010</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>284</v>
+      <c r="B170" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="C170" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D170" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
         <v>13020</v>
       </c>
-      <c r="B171" s="4"/>
+      <c r="B171" s="5"/>
       <c r="C171" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -6963,10 +7032,10 @@
         <v>13110</v>
       </c>
       <c r="B172" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C172" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -6974,10 +7043,10 @@
         <v>13120</v>
       </c>
       <c r="B173" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C173" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -6985,10 +7054,10 @@
         <v>13130</v>
       </c>
       <c r="B174" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C174" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -6996,10 +7065,10 @@
         <v>13140</v>
       </c>
       <c r="B175" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C175" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -7007,10 +7076,10 @@
         <v>13210</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C176" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -7018,10 +7087,10 @@
         <v>13220</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C177" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -7029,10 +7098,10 @@
         <v>13230</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C178" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -7040,10 +7109,10 @@
         <v>13240</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C179" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -7051,10 +7120,10 @@
         <v>13300</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C180" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -7062,10 +7131,10 @@
         <v>13301</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C181" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -7073,10 +7142,10 @@
         <v>13310</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C182" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -7084,10 +7153,10 @@
         <v>13320</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C183" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="184" ht="26" spans="1:3">
@@ -7095,10 +7164,10 @@
         <v>13330</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C184" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -7106,10 +7175,10 @@
         <v>13400</v>
       </c>
       <c r="B185" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C185" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -7117,10 +7186,10 @@
         <v>13410</v>
       </c>
       <c r="B186" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C186" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -7128,10 +7197,10 @@
         <v>13420</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C187" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -7139,10 +7208,10 @@
         <v>13421</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C188" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -7150,10 +7219,10 @@
         <v>13430</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C189" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -7161,10 +7230,10 @@
         <v>14090</v>
       </c>
       <c r="B190" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C190" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -7172,10 +7241,10 @@
         <v>14110</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C191" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="192" ht="14" spans="1:7">
@@ -7183,13 +7252,13 @@
         <v>15010</v>
       </c>
       <c r="B192" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C192" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D192" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -7198,13 +7267,13 @@
         <v>16010</v>
       </c>
       <c r="B193" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C193" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D193" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G193" s="1"/>
     </row>
@@ -7213,10 +7282,10 @@
         <v>16020</v>
       </c>
       <c r="B194" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C194" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G194" s="1"/>
     </row>
@@ -7225,10 +7294,10 @@
         <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C195" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -7236,10 +7305,10 @@
         <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C196" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -7247,10 +7316,10 @@
         <v>16200</v>
       </c>
       <c r="B197" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C197" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -7258,10 +7327,10 @@
         <v>16210</v>
       </c>
       <c r="B198" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C198" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -7269,10 +7338,10 @@
         <v>16220</v>
       </c>
       <c r="B199" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C199" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -7280,10 +7349,10 @@
         <v>16230</v>
       </c>
       <c r="B200" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C200" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -7291,10 +7360,10 @@
         <v>16300</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C201" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -7302,10 +7371,10 @@
         <v>16310</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C202" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -7313,10 +7382,10 @@
         <v>16320</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C203" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -7324,10 +7393,10 @@
         <v>16400</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C204" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -7335,10 +7404,10 @@
         <v>16410</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C205" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7346,13 +7415,13 @@
         <v>16800</v>
       </c>
       <c r="B206" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C206" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D206" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7360,13 +7429,13 @@
         <v>16801</v>
       </c>
       <c r="B207" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C207" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D207" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7374,13 +7443,13 @@
         <v>16802</v>
       </c>
       <c r="B208" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C208" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D208" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7388,13 +7457,13 @@
         <v>16803</v>
       </c>
       <c r="B209" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C209" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D209" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7402,13 +7471,13 @@
         <v>16804</v>
       </c>
       <c r="B210" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C210" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D210" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7416,13 +7485,13 @@
         <v>16805</v>
       </c>
       <c r="B211" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C211" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D211" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -7430,13 +7499,13 @@
         <v>16806</v>
       </c>
       <c r="B212" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C212" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D212" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -7444,10 +7513,10 @@
         <v>17010</v>
       </c>
       <c r="B213" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C213" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -7455,13 +7524,13 @@
         <v>18010</v>
       </c>
       <c r="B214" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C214" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D214" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -7469,10 +7538,10 @@
         <v>18020</v>
       </c>
       <c r="B215" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C215" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -7480,10 +7549,10 @@
         <v>18100</v>
       </c>
       <c r="B216" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C216" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -7491,10 +7560,10 @@
         <v>18110</v>
       </c>
       <c r="B217" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C217" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -7502,10 +7571,10 @@
         <v>18120</v>
       </c>
       <c r="B218" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C218" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -7513,10 +7582,10 @@
         <v>18130</v>
       </c>
       <c r="B219" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C219" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -7524,10 +7593,10 @@
         <v>18200</v>
       </c>
       <c r="B220" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C220" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -7535,10 +7604,10 @@
         <v>18210</v>
       </c>
       <c r="B221" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C221" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -7546,10 +7615,10 @@
         <v>18220</v>
       </c>
       <c r="B222" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C222" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -7557,10 +7626,10 @@
         <v>18230</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C223" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -7568,21 +7637,21 @@
         <v>18300</v>
       </c>
       <c r="B224" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C224" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
         <v>18310</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>331</v>
+      <c r="B225" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="C225" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -7590,10 +7659,10 @@
         <v>18320</v>
       </c>
       <c r="B226" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C226" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -7601,10 +7670,10 @@
         <v>18340</v>
       </c>
       <c r="B227" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C227" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -7612,10 +7681,10 @@
         <v>18400</v>
       </c>
       <c r="B228" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C228" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -7623,10 +7692,10 @@
         <v>18410</v>
       </c>
       <c r="B229" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C229" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -7634,10 +7703,10 @@
         <v>18420</v>
       </c>
       <c r="B230" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C230" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -7645,10 +7714,10 @@
         <v>18430</v>
       </c>
       <c r="B231" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C231" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -7656,10 +7725,10 @@
         <v>18440</v>
       </c>
       <c r="B232" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C232" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -7667,10 +7736,10 @@
         <v>18450</v>
       </c>
       <c r="B233" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C233" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -7678,10 +7747,10 @@
         <v>18500</v>
       </c>
       <c r="B234" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C234" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -7689,10 +7758,10 @@
         <v>18510</v>
       </c>
       <c r="B235" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C235" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7700,10 +7769,10 @@
         <v>18800</v>
       </c>
       <c r="B236" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C236" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7711,10 +7780,10 @@
         <v>18801</v>
       </c>
       <c r="B237" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C237" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -7722,10 +7791,10 @@
         <v>18802</v>
       </c>
       <c r="B238" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C238" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -7733,10 +7802,10 @@
         <v>18803</v>
       </c>
       <c r="B239" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C239" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7744,10 +7813,10 @@
         <v>18804</v>
       </c>
       <c r="B240" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C240" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7755,10 +7824,10 @@
         <v>18805</v>
       </c>
       <c r="B241" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C241" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7766,10 +7835,10 @@
         <v>18806</v>
       </c>
       <c r="B242" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C242" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7777,10 +7846,10 @@
         <v>18811</v>
       </c>
       <c r="B243" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C243" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7788,10 +7857,10 @@
         <v>18812</v>
       </c>
       <c r="B244" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C244" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="245" ht="14" spans="1:7">
@@ -7799,13 +7868,13 @@
         <v>19000</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C245" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D245" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G245" s="1"/>
     </row>
@@ -7814,10 +7883,10 @@
         <v>19001</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C246" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -7825,10 +7894,10 @@
         <v>19002</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C247" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -7836,10 +7905,10 @@
         <v>19003</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C248" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -7847,10 +7916,10 @@
         <v>19004</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C249" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -7858,10 +7927,10 @@
         <v>19005</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C250" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -7869,10 +7938,10 @@
         <v>19006</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C251" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -7880,10 +7949,10 @@
         <v>19007</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C252" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -7891,10 +7960,10 @@
         <v>19008</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C253" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -7902,10 +7971,10 @@
         <v>19009</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C254" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -7913,10 +7982,10 @@
         <v>19010</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C255" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -7924,10 +7993,10 @@
         <v>19011</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C256" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -7935,10 +8004,10 @@
         <v>19012</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C257" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -7946,10 +8015,10 @@
         <v>19013</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C258" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -7957,10 +8026,10 @@
         <v>19014</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C259" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -7968,10 +8037,10 @@
         <v>19100</v>
       </c>
       <c r="B260" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C260" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -7979,10 +8048,10 @@
         <v>19110</v>
       </c>
       <c r="B261" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C261" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -7990,10 +8059,10 @@
         <v>19200</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C262" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -8001,10 +8070,10 @@
         <v>19210</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C263" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -8012,10 +8081,10 @@
         <v>19220</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C264" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -8023,21 +8092,21 @@
         <v>19230</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C265" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
         <v>19240</v>
       </c>
-      <c r="B266" s="4" t="s">
-        <v>371</v>
+      <c r="B266" s="5" t="s">
+        <v>374</v>
       </c>
       <c r="C266" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -8045,21 +8114,21 @@
         <v>19250</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C267" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
         <v>19260</v>
       </c>
-      <c r="B268" s="4" t="s">
-        <v>373</v>
+      <c r="B268" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="C268" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -8067,21 +8136,21 @@
         <v>19270</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C269" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
         <v>19280</v>
       </c>
-      <c r="B270" s="4" t="s">
-        <v>375</v>
+      <c r="B270" s="5" t="s">
+        <v>378</v>
       </c>
       <c r="C270" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -8089,10 +8158,10 @@
         <v>19300</v>
       </c>
       <c r="B271" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C271" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="272" ht="26" spans="1:3">
@@ -8100,10 +8169,10 @@
         <v>19310</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C272" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -8111,10 +8180,10 @@
         <v>19320</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C273" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -8122,10 +8191,10 @@
         <v>19330</v>
       </c>
       <c r="B274" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C274" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -8133,10 +8202,10 @@
         <v>19340</v>
       </c>
       <c r="B275" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C275" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -8144,10 +8213,10 @@
         <v>19350</v>
       </c>
       <c r="B276" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C276" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -8155,10 +8224,10 @@
         <v>19360</v>
       </c>
       <c r="B277" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C277" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -8166,10 +8235,10 @@
         <v>19400</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C278" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -8177,21 +8246,21 @@
         <v>19401</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C279" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280">
         <v>19410</v>
       </c>
-      <c r="B280" s="4" t="s">
-        <v>385</v>
+      <c r="B280" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="C280" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -8199,10 +8268,10 @@
         <v>19420</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C281" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -8210,21 +8279,21 @@
         <v>19500</v>
       </c>
       <c r="B282" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C282" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283">
         <v>19510</v>
       </c>
-      <c r="B283" s="4" t="s">
-        <v>373</v>
+      <c r="B283" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="C283" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -8232,10 +8301,10 @@
         <v>19520</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C284" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -8243,10 +8312,10 @@
         <v>19600</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C285" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -8254,10 +8323,10 @@
         <v>19601</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C286" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -8265,10 +8334,10 @@
         <v>19602</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C287" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -8276,10 +8345,10 @@
         <v>19603</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C288" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -8287,10 +8356,10 @@
         <v>19604</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C289" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="290" ht="14" spans="1:7">
@@ -8298,13 +8367,13 @@
         <v>19611</v>
       </c>
       <c r="B290" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C290" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D290" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G290" s="1"/>
     </row>
@@ -8313,10 +8382,10 @@
         <v>19612</v>
       </c>
       <c r="B291" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C291" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G291" s="1"/>
     </row>
@@ -8325,10 +8394,10 @@
         <v>19613</v>
       </c>
       <c r="B292" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C292" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G292" s="1"/>
     </row>
@@ -8337,10 +8406,10 @@
         <v>19614</v>
       </c>
       <c r="B293" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C293" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G293" s="1"/>
     </row>
@@ -8349,10 +8418,10 @@
         <v>19615</v>
       </c>
       <c r="B294" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C294" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G294" s="1"/>
     </row>
@@ -8361,10 +8430,10 @@
         <v>19616</v>
       </c>
       <c r="B295" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C295" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G295" s="1"/>
     </row>
@@ -8373,10 +8442,10 @@
         <v>19617</v>
       </c>
       <c r="B296" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C296" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G296" s="1"/>
     </row>
@@ -8385,10 +8454,10 @@
         <v>19618</v>
       </c>
       <c r="B297" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C297" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G297" s="1"/>
     </row>
@@ -8397,10 +8466,10 @@
         <v>19619</v>
       </c>
       <c r="B298" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C298" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G298" s="1"/>
     </row>
@@ -8409,13 +8478,13 @@
         <v>19631</v>
       </c>
       <c r="B299" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C299" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D299" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -8423,10 +8492,10 @@
         <v>19632</v>
       </c>
       <c r="B300" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C300" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -8434,10 +8503,10 @@
         <v>19633</v>
       </c>
       <c r="B301" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C301" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -8445,10 +8514,10 @@
         <v>19634</v>
       </c>
       <c r="B302" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C302" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -8456,10 +8525,10 @@
         <v>19700</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C303" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -8467,10 +8536,10 @@
         <v>19710</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C304" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -8478,10 +8547,10 @@
         <v>19720</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C305" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -8489,10 +8558,10 @@
         <v>19730</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C306" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -8500,10 +8569,10 @@
         <v>19740</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C307" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -8511,10 +8580,10 @@
         <v>19800</v>
       </c>
       <c r="B308" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C308" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -8522,10 +8591,10 @@
         <v>19810</v>
       </c>
       <c r="B309" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C309" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -8533,13 +8602,13 @@
         <v>20010</v>
       </c>
       <c r="B310" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C310" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D310" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -8547,10 +8616,10 @@
         <v>20020</v>
       </c>
       <c r="B311" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C311" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -8558,10 +8627,10 @@
         <v>20030</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C312" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -8569,10 +8638,10 @@
         <v>20040</v>
       </c>
       <c r="B313" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C313" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -8580,10 +8649,10 @@
         <v>20050</v>
       </c>
       <c r="B314" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C314" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -8591,10 +8660,10 @@
         <v>20100</v>
       </c>
       <c r="B315" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C315" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -8602,10 +8671,10 @@
         <v>20110</v>
       </c>
       <c r="B316" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C316" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -8613,10 +8682,10 @@
         <v>20120</v>
       </c>
       <c r="B317" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C317" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -8624,10 +8693,10 @@
         <v>20200</v>
       </c>
       <c r="B318" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C318" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -8635,10 +8704,10 @@
         <v>20201</v>
       </c>
       <c r="B319" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C319" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -8646,10 +8715,10 @@
         <v>20210</v>
       </c>
       <c r="B320" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C320" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -8657,10 +8726,10 @@
         <v>20220</v>
       </c>
       <c r="B321" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C321" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -8668,10 +8737,10 @@
         <v>20230</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C322" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -8679,10 +8748,10 @@
         <v>20240</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C323" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -8690,10 +8759,10 @@
         <v>20250</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C324" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -8701,10 +8770,10 @@
         <v>20260</v>
       </c>
       <c r="B325" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C325" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -8712,10 +8781,10 @@
         <v>20270</v>
       </c>
       <c r="B326" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C326" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -8723,10 +8792,10 @@
         <v>20280</v>
       </c>
       <c r="B327" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C327" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -8734,10 +8803,10 @@
         <v>20290</v>
       </c>
       <c r="B328" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C328" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -8745,10 +8814,10 @@
         <v>20300</v>
       </c>
       <c r="B329" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C329" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -8756,10 +8825,10 @@
         <v>20310</v>
       </c>
       <c r="B330" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C330" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -8767,10 +8836,10 @@
         <v>20320</v>
       </c>
       <c r="B331" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C331" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -8778,10 +8847,10 @@
         <v>20330</v>
       </c>
       <c r="B332" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C332" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -8789,10 +8858,10 @@
         <v>20340</v>
       </c>
       <c r="B333" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C333" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -8800,10 +8869,10 @@
         <v>20350</v>
       </c>
       <c r="B334" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C334" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -8811,10 +8880,10 @@
         <v>23010</v>
       </c>
       <c r="B335" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C335" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -8822,10 +8891,10 @@
         <v>23020</v>
       </c>
       <c r="B336" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C336" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -8833,10 +8902,10 @@
         <v>23030</v>
       </c>
       <c r="B337" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C337" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -8844,10 +8913,10 @@
         <v>23031</v>
       </c>
       <c r="B338" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C338" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -8855,10 +8924,10 @@
         <v>23032</v>
       </c>
       <c r="B339" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C339" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -8866,10 +8935,10 @@
         <v>23040</v>
       </c>
       <c r="B340" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C340" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -8877,10 +8946,10 @@
         <v>24010</v>
       </c>
       <c r="B341" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C341" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -8888,10 +8957,10 @@
         <v>24020</v>
       </c>
       <c r="B342" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C342" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -8899,10 +8968,10 @@
         <v>24030</v>
       </c>
       <c r="B343" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C343" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -8910,10 +8979,10 @@
         <v>24040</v>
       </c>
       <c r="B344" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C344" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -8921,10 +8990,10 @@
         <v>24110</v>
       </c>
       <c r="B345" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C345" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -8932,10 +9001,10 @@
         <v>24111</v>
       </c>
       <c r="B346" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C346" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -8943,10 +9012,10 @@
         <v>24112</v>
       </c>
       <c r="B347" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C347" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -8954,10 +9023,10 @@
         <v>24113</v>
       </c>
       <c r="B348" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C348" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -8965,10 +9034,10 @@
         <v>24114</v>
       </c>
       <c r="B349" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C349" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -8976,10 +9045,10 @@
         <v>24115</v>
       </c>
       <c r="B350" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C350" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -8987,10 +9056,10 @@
         <v>24116</v>
       </c>
       <c r="B351" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C351" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -8998,10 +9067,10 @@
         <v>24117</v>
       </c>
       <c r="B352" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C352" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -9009,10 +9078,10 @@
         <v>24118</v>
       </c>
       <c r="B353" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C353" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -9020,10 +9089,10 @@
         <v>24119</v>
       </c>
       <c r="B354" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C354" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -9031,10 +9100,10 @@
         <v>24120</v>
       </c>
       <c r="B355" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C355" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -9042,10 +9111,10 @@
         <v>24121</v>
       </c>
       <c r="B356" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C356" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -9053,10 +9122,10 @@
         <v>24122</v>
       </c>
       <c r="B357" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C357" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -9064,10 +9133,10 @@
         <v>30000</v>
       </c>
       <c r="B358" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C358" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -9075,10 +9144,10 @@
         <v>30010</v>
       </c>
       <c r="B359" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C359" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -9086,10 +9155,10 @@
         <v>30020</v>
       </c>
       <c r="B360" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C360" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -9097,10 +9166,10 @@
         <v>30030</v>
       </c>
       <c r="B361" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C361" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -9108,10 +9177,10 @@
         <v>30040</v>
       </c>
       <c r="B362" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C362" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -9119,10 +9188,10 @@
         <v>31010</v>
       </c>
       <c r="B363" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C363" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -9130,10 +9199,10 @@
         <v>31020</v>
       </c>
       <c r="B364" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C364" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -9141,13 +9210,13 @@
         <v>102000</v>
       </c>
       <c r="B365" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C365" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D365" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -9155,10 +9224,10 @@
         <v>102010</v>
       </c>
       <c r="B366" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C366" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -9166,10 +9235,10 @@
         <v>102020</v>
       </c>
       <c r="B367" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C367" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -9177,10 +9246,10 @@
         <v>102030</v>
       </c>
       <c r="B368" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C368" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9188,13 +9257,13 @@
         <v>113000</v>
       </c>
       <c r="B369" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C369" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D369" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -9202,10 +9271,10 @@
         <v>113010</v>
       </c>
       <c r="B370" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C370" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -9213,10 +9282,10 @@
         <v>113020</v>
       </c>
       <c r="B371" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C371" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -9224,10 +9293,10 @@
         <v>113030</v>
       </c>
       <c r="B372" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C372" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -9235,10 +9304,10 @@
         <v>113040</v>
       </c>
       <c r="B373" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C373" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9246,13 +9315,13 @@
         <v>121010</v>
       </c>
       <c r="B374" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C374" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D374" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -9260,10 +9329,10 @@
         <v>121011</v>
       </c>
       <c r="B375" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C375" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -9271,10 +9340,10 @@
         <v>121012</v>
       </c>
       <c r="B376" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C376" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -9282,10 +9351,10 @@
         <v>121013</v>
       </c>
       <c r="B377" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C377" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -9293,10 +9362,10 @@
         <v>121014</v>
       </c>
       <c r="B378" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C378" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -9304,10 +9373,10 @@
         <v>121015</v>
       </c>
       <c r="B379" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C379" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -9315,10 +9384,10 @@
         <v>121016</v>
       </c>
       <c r="B380" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C380" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -9326,10 +9395,10 @@
         <v>121017</v>
       </c>
       <c r="B381" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C381" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -9337,10 +9406,10 @@
         <v>121018</v>
       </c>
       <c r="B382" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C382" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -9348,10 +9417,10 @@
         <v>121019</v>
       </c>
       <c r="B383" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C383" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -9359,10 +9428,10 @@
         <v>121020</v>
       </c>
       <c r="B384" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C384" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -9370,10 +9439,10 @@
         <v>121030</v>
       </c>
       <c r="B385" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C385" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="491">
   <si>
     <t>Id</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Wait</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>UnitActEnd</t>
@@ -1009,9 +1012,6 @@
     <t>仲間にするキャラを選んでください</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>仲間決定！</t>
   </si>
   <si>
@@ -1102,7 +1102,7 @@
     <t>神界転送</t>
   </si>
   <si>
-    <t>待機</t>
+    <t>仲間確認</t>
   </si>
   <si>
     <t>バトル</t>
@@ -1507,8 +1507,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -1535,28 +1535,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1578,16 +1571,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1601,23 +1632,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1631,11 +1648,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1647,24 +1663,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1672,7 +1672,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1687,19 +1687,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1711,31 +1741,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1747,37 +1759,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1795,7 +1783,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1807,67 +1855,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1878,15 +1878,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1920,13 +1911,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1943,23 +1938,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1978,6 +1967,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1986,149 +1986,149 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2139,9 +2139,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2595,14 +2592,21 @@
         <v>19003</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="2"/>
-      <c r="C6"/>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>19004</v>
+      </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>19004</v>
@@ -2610,12 +2614,11 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="2"/>
-      <c r="C7"/>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>19005</v>
@@ -2623,12 +2626,11 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="2"/>
-      <c r="C8"/>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>19006</v>
@@ -2636,12 +2638,11 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="2"/>
-      <c r="C9"/>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>19007</v>
@@ -2649,12 +2650,11 @@
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="2"/>
-      <c r="C10"/>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>19008</v>
@@ -2662,12 +2662,11 @@
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="2"/>
-      <c r="C11"/>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11">
         <v>19009</v>
@@ -2675,12 +2674,11 @@
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="2"/>
-      <c r="C12"/>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>19010</v>
@@ -2688,12 +2686,11 @@
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="2"/>
-      <c r="C13"/>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13">
         <v>19011</v>
@@ -2701,12 +2698,11 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="2"/>
-      <c r="C14"/>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14">
         <v>19012</v>
@@ -2714,12 +2710,11 @@
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="2"/>
-      <c r="C15"/>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>19013</v>
@@ -2730,7 +2725,7 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16">
         <v>19014</v>
@@ -2768,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>13210</v>
@@ -2779,7 +2774,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>13220</v>
@@ -2790,7 +2785,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -2801,7 +2796,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>13230</v>
@@ -2838,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2849,7 +2844,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>18110</v>
@@ -2860,7 +2855,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>18120</v>
@@ -2871,7 +2866,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>18130</v>
@@ -2904,25 +2899,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2930,7 +2925,7 @@
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>6010</v>
@@ -2962,7 +2957,7 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>6020</v>
@@ -2994,7 +2989,7 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>6030</v>
@@ -3026,7 +3021,7 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>6040</v>
@@ -3058,7 +3053,7 @@
         <v>2030</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>6210</v>
@@ -3090,7 +3085,7 @@
         <v>2040</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>6220</v>
@@ -3122,7 +3117,7 @@
         <v>2050</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>6230</v>
@@ -3154,7 +3149,7 @@
         <v>2060</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>6240</v>
@@ -3186,7 +3181,7 @@
         <v>2070</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>6250</v>
@@ -3218,7 +3213,7 @@
         <v>2080</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11">
         <v>6260</v>
@@ -3250,7 +3245,7 @@
         <v>2090</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>6270</v>
@@ -3282,7 +3277,7 @@
         <v>2100</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>6280</v>
@@ -3329,15 +3324,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3346,12 +3341,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -3360,12 +3355,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -3374,12 +3369,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -3388,12 +3383,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -3402,12 +3397,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3416,12 +3411,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3430,12 +3425,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3444,12 +3439,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3458,12 +3453,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3472,12 +3467,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3486,12 +3481,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -3500,12 +3495,12 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3514,12 +3509,12 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -3528,12 +3523,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3542,12 +3537,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3556,12 +3551,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -3570,12 +3565,12 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -3584,12 +3579,12 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3598,12 +3593,12 @@
         <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -3612,12 +3607,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3626,12 +3621,12 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -3640,12 +3635,12 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -3654,12 +3649,12 @@
         <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3668,12 +3663,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -3682,12 +3677,12 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3696,12 +3691,12 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3710,12 +3705,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3724,12 +3719,12 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -3738,12 +3733,12 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3752,12 +3747,12 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -3766,12 +3761,12 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -3780,12 +3775,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3794,12 +3789,12 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -3808,12 +3803,12 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3822,12 +3817,12 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3836,12 +3831,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -3850,12 +3845,12 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -3864,12 +3859,12 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -3878,12 +3873,12 @@
         <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -3892,12 +3887,12 @@
         <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -3906,12 +3901,12 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -3920,12 +3915,12 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3934,12 +3929,12 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -3948,12 +3943,12 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -3962,12 +3957,12 @@
         <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B47">
         <v>11</v>
@@ -3976,12 +3971,12 @@
         <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -3990,12 +3985,12 @@
         <v>210</v>
       </c>
       <c r="D48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -4004,12 +3999,12 @@
         <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -4018,12 +4013,12 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -4032,12 +4027,12 @@
         <v>802</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -4046,12 +4041,12 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -4060,12 +4055,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -4074,12 +4069,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -4088,12 +4083,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4102,12 +4097,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -4116,12 +4111,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -4130,12 +4125,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -4144,12 +4139,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -4158,12 +4153,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -4172,12 +4167,12 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -4186,12 +4181,12 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -4202,7 +4197,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -4211,12 +4206,12 @@
         <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -4225,12 +4220,12 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4241,7 +4236,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -4252,7 +4247,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -4263,7 +4258,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4274,7 +4269,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -4283,12 +4278,12 @@
         <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -4297,12 +4292,12 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -4311,12 +4306,12 @@
         <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B73">
         <v>8</v>
@@ -4325,12 +4320,12 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -4339,12 +4334,12 @@
         <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -4353,12 +4348,12 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B76">
         <v>11</v>
@@ -4367,12 +4362,12 @@
         <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B77">
         <v>7</v>
@@ -4381,12 +4376,12 @@
         <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -4395,12 +4390,12 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -4409,12 +4404,12 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -4423,12 +4418,12 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4437,12 +4432,12 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -4451,12 +4446,12 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -4465,12 +4460,12 @@
         <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B84">
         <v>9</v>
@@ -4479,12 +4474,12 @@
         <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B85">
         <v>8</v>
@@ -4493,12 +4488,12 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -4507,12 +4502,12 @@
         <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4521,12 +4516,12 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -4535,12 +4530,12 @@
         <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -4549,12 +4544,12 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B90">
         <v>9</v>
@@ -4563,12 +4558,12 @@
         <v>813</v>
       </c>
       <c r="D90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -4577,12 +4572,12 @@
         <v>800</v>
       </c>
       <c r="D91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -4591,12 +4586,12 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -4605,12 +4600,12 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -4619,12 +4614,12 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B95">
         <v>9</v>
@@ -4633,12 +4628,12 @@
         <v>814</v>
       </c>
       <c r="D95" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -4647,12 +4642,12 @@
         <v>800</v>
       </c>
       <c r="D96" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -4661,12 +4656,12 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4675,12 +4670,12 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -4689,12 +4684,12 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -4703,12 +4698,12 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4717,12 +4712,12 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -4731,12 +4726,12 @@
         <v>818</v>
       </c>
       <c r="D102" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -4745,12 +4740,12 @@
         <v>800</v>
       </c>
       <c r="D103" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -4759,12 +4754,12 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B105">
         <v>9</v>
@@ -4773,12 +4768,12 @@
         <v>817</v>
       </c>
       <c r="D105" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -4787,12 +4782,12 @@
         <v>816</v>
       </c>
       <c r="D106" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -4801,12 +4796,12 @@
         <v>817</v>
       </c>
       <c r="D107" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B108">
         <v>4</v>
@@ -4815,12 +4810,12 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -4829,12 +4824,12 @@
         <v>801</v>
       </c>
       <c r="D109" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -4843,12 +4838,12 @@
         <v>800</v>
       </c>
       <c r="D110" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -4857,12 +4852,12 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -4871,12 +4866,12 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -4885,12 +4880,12 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -4899,12 +4894,12 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -4913,12 +4908,12 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -4927,12 +4922,12 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -4941,7 +4936,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4964,34 +4959,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="6">
+        <v>102</v>
+      </c>
+      <c r="B2" s="5">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -4999,7 +4994,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -5007,7 +5002,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -5015,7 +5010,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -5023,40 +5018,40 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10">
         <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5083,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5094,10 +5089,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" ht="14" spans="1:7">
@@ -5105,10 +5100,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -5117,10 +5112,10 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5128,10 +5123,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5139,10 +5134,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5150,10 +5145,10 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5161,10 +5156,10 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5172,10 +5167,10 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5183,10 +5178,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5194,10 +5189,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5205,10 +5200,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5216,10 +5211,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5227,10 +5222,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5238,10 +5233,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5249,10 +5244,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5260,10 +5255,10 @@
         <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5271,10 +5266,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5282,10 +5277,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5293,10 +5288,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5304,10 +5299,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5315,10 +5310,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5326,10 +5321,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5337,10 +5332,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5348,10 +5343,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -5359,10 +5354,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5370,10 +5365,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5381,10 +5376,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5392,10 +5387,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5403,10 +5398,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5414,10 +5409,10 @@
         <v>342</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5425,13 +5420,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5439,13 +5434,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5453,13 +5448,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" t="s">
         <v>147</v>
-      </c>
-      <c r="C34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5467,13 +5462,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5481,13 +5476,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" t="s">
         <v>150</v>
-      </c>
-      <c r="C36" t="s">
-        <v>118</v>
-      </c>
-      <c r="D36" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5495,13 +5490,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5509,10 +5504,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5520,10 +5515,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5531,10 +5526,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5542,10 +5537,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5553,10 +5548,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5564,10 +5559,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5575,10 +5570,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5586,10 +5581,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -5597,10 +5592,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5608,10 +5603,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -5619,10 +5614,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5630,10 +5625,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5641,10 +5636,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5652,10 +5647,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5663,10 +5658,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5674,10 +5669,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5685,10 +5680,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5696,10 +5691,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5707,10 +5702,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5718,10 +5713,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5729,10 +5724,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5740,10 +5735,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5751,10 +5746,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5762,10 +5757,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5773,10 +5768,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5784,10 +5779,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5795,10 +5790,10 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5806,10 +5801,10 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5817,10 +5812,10 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5828,10 +5823,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5839,10 +5834,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5850,10 +5845,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5861,10 +5856,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5872,10 +5867,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5883,10 +5878,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5894,10 +5889,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5905,10 +5900,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5916,10 +5911,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5927,10 +5922,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5938,10 +5933,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C77" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5949,10 +5944,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5960,10 +5955,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C79" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5971,10 +5966,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C80" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5982,10 +5977,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -5993,10 +5988,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -6004,10 +5999,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C83" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -6015,10 +6010,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -6026,10 +6021,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -6037,10 +6032,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -6048,10 +6043,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -6059,10 +6054,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -6070,10 +6065,10 @@
         <v>1000</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -6081,10 +6076,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C90" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -6092,10 +6087,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C91" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -6103,10 +6098,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C92" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -6114,10 +6109,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C93" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -6125,10 +6120,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C94" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -6136,10 +6131,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C95" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6147,13 +6142,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C96" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -6161,10 +6156,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C97" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -6172,10 +6167,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C98" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -6183,10 +6178,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -6194,10 +6189,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C100" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -6205,10 +6200,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -6216,10 +6211,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C102" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -6227,10 +6222,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C103" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6238,13 +6233,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C104" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6252,13 +6247,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
+        <v>214</v>
+      </c>
+      <c r="C105" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105" t="s">
         <v>213</v>
-      </c>
-      <c r="C105" t="s">
-        <v>118</v>
-      </c>
-      <c r="D105" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6266,13 +6261,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C106" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6280,13 +6275,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
+        <v>214</v>
+      </c>
+      <c r="C107" t="s">
+        <v>119</v>
+      </c>
+      <c r="D107" t="s">
         <v>213</v>
-      </c>
-      <c r="C107" t="s">
-        <v>118</v>
-      </c>
-      <c r="D107" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6294,13 +6289,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C108" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -6308,10 +6303,10 @@
         <v>2101</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C109" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -6319,10 +6314,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C110" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -6330,10 +6325,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C111" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -6341,10 +6336,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C112" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -6352,10 +6347,10 @@
         <v>2105</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C113" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -6363,10 +6358,10 @@
         <v>2106</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C114" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6374,13 +6369,13 @@
         <v>2200</v>
       </c>
       <c r="B115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C115" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6388,13 +6383,13 @@
         <v>2210</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C116" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D116" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" ht="29" customHeight="1" spans="1:4">
@@ -6402,13 +6397,13 @@
         <v>2220</v>
       </c>
       <c r="B117" t="s">
+        <v>225</v>
+      </c>
+      <c r="C117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D117" t="s">
         <v>224</v>
-      </c>
-      <c r="C117" t="s">
-        <v>118</v>
-      </c>
-      <c r="D117" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6416,13 +6411,13 @@
         <v>2300</v>
       </c>
       <c r="B118" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C118" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D118" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6430,13 +6425,13 @@
         <v>2310</v>
       </c>
       <c r="B119" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C119" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D119" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6444,13 +6439,13 @@
         <v>2320</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C120" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D120" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6458,13 +6453,13 @@
         <v>2330</v>
       </c>
       <c r="B121" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C121" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D121" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6472,13 +6467,13 @@
         <v>2340</v>
       </c>
       <c r="B122" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C122" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D122" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6486,13 +6481,13 @@
         <v>2400</v>
       </c>
       <c r="B123" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C123" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D123" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -6500,10 +6495,10 @@
         <v>3000</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C124" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -6511,10 +6506,10 @@
         <v>3010</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C125" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -6522,10 +6517,10 @@
         <v>3011</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C126" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -6533,10 +6528,10 @@
         <v>3040</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -6544,10 +6539,10 @@
         <v>3050</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C128" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -6555,10 +6550,10 @@
         <v>3051</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C129" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -6566,10 +6561,10 @@
         <v>3052</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C130" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -6577,10 +6572,10 @@
         <v>3053</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C131" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -6588,10 +6583,10 @@
         <v>3054</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C132" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -6599,10 +6594,10 @@
         <v>3070</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C133" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -6610,10 +6605,10 @@
         <v>3071</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C134" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -6621,10 +6616,10 @@
         <v>3072</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C135" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -6632,10 +6627,10 @@
         <v>3073</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C136" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -6643,10 +6638,10 @@
         <v>3090</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C137" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -6654,10 +6649,10 @@
         <v>3211</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C138" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -6665,10 +6660,10 @@
         <v>3230</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C139" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6676,10 +6671,10 @@
         <v>5000</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C140" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6687,10 +6682,10 @@
         <v>5001</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C141" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6698,10 +6693,10 @@
         <v>5002</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C142" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6709,10 +6704,10 @@
         <v>6001</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C143" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6720,10 +6715,10 @@
         <v>6002</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C144" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6731,10 +6726,10 @@
         <v>6100</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6742,10 +6737,10 @@
         <v>6010</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C146" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6753,10 +6748,10 @@
         <v>6011</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C147" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6764,10 +6759,10 @@
         <v>6012</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C148" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6775,10 +6770,10 @@
         <v>6020</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6786,10 +6781,10 @@
         <v>6030</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C150" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6797,10 +6792,10 @@
         <v>6040</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6808,10 +6803,10 @@
         <v>6210</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C152" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6819,10 +6814,10 @@
         <v>6220</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C153" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6830,10 +6825,10 @@
         <v>6230</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C154" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6841,10 +6836,10 @@
         <v>6240</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C155" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6852,10 +6847,10 @@
         <v>6250</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6863,10 +6858,10 @@
         <v>6260</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C157" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6874,10 +6869,10 @@
         <v>6270</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C158" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6885,10 +6880,10 @@
         <v>6280</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C159" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6896,10 +6891,10 @@
         <v>6810</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C160" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6907,10 +6902,10 @@
         <v>6820</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C161" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6918,10 +6913,10 @@
         <v>6830</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C162" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6929,10 +6924,10 @@
         <v>6840</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C163" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -6940,10 +6935,10 @@
         <v>6850</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C164" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -6951,10 +6946,10 @@
         <v>6860</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C165" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6962,10 +6957,10 @@
         <v>6870</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C166" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6973,10 +6968,10 @@
         <v>6880</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C167" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6984,10 +6979,10 @@
         <v>6890</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C168" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="169" ht="130" spans="1:4">
@@ -6995,13 +6990,13 @@
         <v>12010</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C169" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D169" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" ht="26" spans="1:4">
@@ -7009,22 +7004,22 @@
         <v>13010</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C170" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
         <v>13020</v>
       </c>
-      <c r="B171" s="5"/>
+      <c r="B171" s="4"/>
       <c r="C171" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -7032,10 +7027,10 @@
         <v>13110</v>
       </c>
       <c r="B172" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C172" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -7043,10 +7038,10 @@
         <v>13120</v>
       </c>
       <c r="B173" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C173" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -7054,10 +7049,10 @@
         <v>13130</v>
       </c>
       <c r="B174" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C174" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -7065,10 +7060,10 @@
         <v>13140</v>
       </c>
       <c r="B175" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C175" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -7076,10 +7071,10 @@
         <v>13210</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C176" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -7087,10 +7082,10 @@
         <v>13220</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C177" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -7098,10 +7093,10 @@
         <v>13230</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C178" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -7109,10 +7104,10 @@
         <v>13240</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C179" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -7120,10 +7115,10 @@
         <v>13300</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C180" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -7131,10 +7126,10 @@
         <v>13301</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C181" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -7142,10 +7137,10 @@
         <v>13310</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C182" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -7153,10 +7148,10 @@
         <v>13320</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C183" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="184" ht="26" spans="1:3">
@@ -7164,10 +7159,10 @@
         <v>13330</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C184" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -7175,10 +7170,10 @@
         <v>13400</v>
       </c>
       <c r="B185" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C185" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -7186,10 +7181,10 @@
         <v>13410</v>
       </c>
       <c r="B186" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C186" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -7197,10 +7192,10 @@
         <v>13420</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C187" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -7208,10 +7203,10 @@
         <v>13421</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C188" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -7219,10 +7214,10 @@
         <v>13430</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C189" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -7230,10 +7225,10 @@
         <v>14090</v>
       </c>
       <c r="B190" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C190" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -7241,10 +7236,10 @@
         <v>14110</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C191" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="192" ht="14" spans="1:7">
@@ -7252,13 +7247,13 @@
         <v>15010</v>
       </c>
       <c r="B192" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C192" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D192" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -7267,13 +7262,13 @@
         <v>16010</v>
       </c>
       <c r="B193" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C193" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D193" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G193" s="1"/>
     </row>
@@ -7282,10 +7277,10 @@
         <v>16020</v>
       </c>
       <c r="B194" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C194" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G194" s="1"/>
     </row>
@@ -7294,10 +7289,10 @@
         <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C195" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -7305,10 +7300,10 @@
         <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C196" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -7316,10 +7311,10 @@
         <v>16200</v>
       </c>
       <c r="B197" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C197" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -7327,10 +7322,10 @@
         <v>16210</v>
       </c>
       <c r="B198" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C198" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -7338,10 +7333,10 @@
         <v>16220</v>
       </c>
       <c r="B199" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C199" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -7349,10 +7344,10 @@
         <v>16230</v>
       </c>
       <c r="B200" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C200" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -7360,10 +7355,10 @@
         <v>16300</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C201" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -7371,10 +7366,10 @@
         <v>16310</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C202" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -7382,10 +7377,10 @@
         <v>16320</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C203" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -7393,10 +7388,10 @@
         <v>16400</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C204" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -7404,10 +7399,10 @@
         <v>16410</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C205" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7415,13 +7410,13 @@
         <v>16800</v>
       </c>
       <c r="B206" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C206" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D206" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7429,13 +7424,13 @@
         <v>16801</v>
       </c>
       <c r="B207" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C207" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D207" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7443,13 +7438,13 @@
         <v>16802</v>
       </c>
       <c r="B208" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C208" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D208" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7457,13 +7452,13 @@
         <v>16803</v>
       </c>
       <c r="B209" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C209" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D209" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7471,13 +7466,13 @@
         <v>16804</v>
       </c>
       <c r="B210" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C210" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D210" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7485,13 +7480,13 @@
         <v>16805</v>
       </c>
       <c r="B211" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C211" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D211" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -7499,13 +7494,13 @@
         <v>16806</v>
       </c>
       <c r="B212" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C212" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D212" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -7513,10 +7508,10 @@
         <v>17010</v>
       </c>
       <c r="B213" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C213" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -7524,13 +7519,13 @@
         <v>18010</v>
       </c>
       <c r="B214" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C214" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D214" t="s">
-        <v>327</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -7541,7 +7536,7 @@
         <v>328</v>
       </c>
       <c r="C215" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -7549,10 +7544,10 @@
         <v>18100</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C216" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -7563,7 +7558,7 @@
         <v>329</v>
       </c>
       <c r="C217" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -7574,7 +7569,7 @@
         <v>330</v>
       </c>
       <c r="C218" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -7582,10 +7577,10 @@
         <v>18130</v>
       </c>
       <c r="B219" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C219" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -7593,10 +7588,10 @@
         <v>18200</v>
       </c>
       <c r="B220" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C220" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -7604,10 +7599,10 @@
         <v>18210</v>
       </c>
       <c r="B221" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C221" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -7618,7 +7613,7 @@
         <v>331</v>
       </c>
       <c r="C222" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -7629,7 +7624,7 @@
         <v>332</v>
       </c>
       <c r="C223" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -7640,18 +7635,18 @@
         <v>333</v>
       </c>
       <c r="C224" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
         <v>18310</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" s="4" t="s">
         <v>334</v>
       </c>
       <c r="C225" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -7662,7 +7657,7 @@
         <v>335</v>
       </c>
       <c r="C226" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -7673,7 +7668,7 @@
         <v>336</v>
       </c>
       <c r="C227" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -7684,7 +7679,7 @@
         <v>337</v>
       </c>
       <c r="C228" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -7695,7 +7690,7 @@
         <v>338</v>
       </c>
       <c r="C229" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -7706,7 +7701,7 @@
         <v>339</v>
       </c>
       <c r="C230" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -7717,7 +7712,7 @@
         <v>340</v>
       </c>
       <c r="C231" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -7725,10 +7720,10 @@
         <v>18440</v>
       </c>
       <c r="B232" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C232" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -7739,7 +7734,7 @@
         <v>341</v>
       </c>
       <c r="C233" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -7750,7 +7745,7 @@
         <v>342</v>
       </c>
       <c r="C234" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -7761,7 +7756,7 @@
         <v>343</v>
       </c>
       <c r="C235" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7772,7 +7767,7 @@
         <v>344</v>
       </c>
       <c r="C236" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7783,7 +7778,7 @@
         <v>345</v>
       </c>
       <c r="C237" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -7794,7 +7789,7 @@
         <v>346</v>
       </c>
       <c r="C238" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -7805,7 +7800,7 @@
         <v>347</v>
       </c>
       <c r="C239" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7816,7 +7811,7 @@
         <v>348</v>
       </c>
       <c r="C240" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7827,7 +7822,7 @@
         <v>349</v>
       </c>
       <c r="C241" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7838,7 +7833,7 @@
         <v>350</v>
       </c>
       <c r="C242" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7849,7 +7844,7 @@
         <v>351</v>
       </c>
       <c r="C243" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7860,7 +7855,7 @@
         <v>352</v>
       </c>
       <c r="C244" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="245" ht="14" spans="1:7">
@@ -7871,7 +7866,7 @@
         <v>353</v>
       </c>
       <c r="C245" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D245" t="s">
         <v>354</v>
@@ -7886,7 +7881,7 @@
         <v>355</v>
       </c>
       <c r="C246" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -7897,7 +7892,7 @@
         <v>356</v>
       </c>
       <c r="C247" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -7908,7 +7903,7 @@
         <v>357</v>
       </c>
       <c r="C248" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -7919,7 +7914,7 @@
         <v>358</v>
       </c>
       <c r="C249" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -7930,7 +7925,7 @@
         <v>359</v>
       </c>
       <c r="C250" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -7941,7 +7936,7 @@
         <v>360</v>
       </c>
       <c r="C251" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -7952,7 +7947,7 @@
         <v>361</v>
       </c>
       <c r="C252" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -7963,7 +7958,7 @@
         <v>362</v>
       </c>
       <c r="C253" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -7974,7 +7969,7 @@
         <v>355</v>
       </c>
       <c r="C254" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -7985,7 +7980,7 @@
         <v>363</v>
       </c>
       <c r="C255" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -7996,7 +7991,7 @@
         <v>364</v>
       </c>
       <c r="C256" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -8007,7 +8002,7 @@
         <v>365</v>
       </c>
       <c r="C257" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -8018,7 +8013,7 @@
         <v>366</v>
       </c>
       <c r="C258" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -8029,7 +8024,7 @@
         <v>367</v>
       </c>
       <c r="C259" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -8040,7 +8035,7 @@
         <v>368</v>
       </c>
       <c r="C260" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -8051,7 +8046,7 @@
         <v>369</v>
       </c>
       <c r="C261" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -8062,7 +8057,7 @@
         <v>370</v>
       </c>
       <c r="C262" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -8073,7 +8068,7 @@
         <v>371</v>
       </c>
       <c r="C263" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -8084,7 +8079,7 @@
         <v>372</v>
       </c>
       <c r="C264" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -8095,18 +8090,18 @@
         <v>373</v>
       </c>
       <c r="C265" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266">
         <v>19240</v>
       </c>
-      <c r="B266" s="5" t="s">
+      <c r="B266" s="4" t="s">
         <v>374</v>
       </c>
       <c r="C266" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -8117,18 +8112,18 @@
         <v>375</v>
       </c>
       <c r="C267" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268">
         <v>19260</v>
       </c>
-      <c r="B268" s="5" t="s">
+      <c r="B268" s="4" t="s">
         <v>376</v>
       </c>
       <c r="C268" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -8139,18 +8134,18 @@
         <v>377</v>
       </c>
       <c r="C269" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270">
         <v>19280</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="B270" s="4" t="s">
         <v>378</v>
       </c>
       <c r="C270" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -8161,7 +8156,7 @@
         <v>379</v>
       </c>
       <c r="C271" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="272" ht="26" spans="1:3">
@@ -8172,7 +8167,7 @@
         <v>380</v>
       </c>
       <c r="C272" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -8183,7 +8178,7 @@
         <v>381</v>
       </c>
       <c r="C273" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -8194,7 +8189,7 @@
         <v>382</v>
       </c>
       <c r="C274" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -8205,7 +8200,7 @@
         <v>383</v>
       </c>
       <c r="C275" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -8216,7 +8211,7 @@
         <v>384</v>
       </c>
       <c r="C276" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -8227,7 +8222,7 @@
         <v>385</v>
       </c>
       <c r="C277" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -8238,7 +8233,7 @@
         <v>386</v>
       </c>
       <c r="C278" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -8249,18 +8244,18 @@
         <v>387</v>
       </c>
       <c r="C279" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280">
         <v>19410</v>
       </c>
-      <c r="B280" s="5" t="s">
+      <c r="B280" s="4" t="s">
         <v>388</v>
       </c>
       <c r="C280" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -8271,7 +8266,7 @@
         <v>389</v>
       </c>
       <c r="C281" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -8282,18 +8277,18 @@
         <v>390</v>
       </c>
       <c r="C282" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283">
         <v>19510</v>
       </c>
-      <c r="B283" s="5" t="s">
+      <c r="B283" s="4" t="s">
         <v>376</v>
       </c>
       <c r="C283" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -8304,7 +8299,7 @@
         <v>391</v>
       </c>
       <c r="C284" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -8315,7 +8310,7 @@
         <v>392</v>
       </c>
       <c r="C285" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -8326,7 +8321,7 @@
         <v>393</v>
       </c>
       <c r="C286" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -8337,7 +8332,7 @@
         <v>394</v>
       </c>
       <c r="C287" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -8348,7 +8343,7 @@
         <v>395</v>
       </c>
       <c r="C288" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -8359,7 +8354,7 @@
         <v>396</v>
       </c>
       <c r="C289" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="290" ht="14" spans="1:7">
@@ -8370,7 +8365,7 @@
         <v>359</v>
       </c>
       <c r="C290" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D290" t="s">
         <v>397</v>
@@ -8385,7 +8380,7 @@
         <v>398</v>
       </c>
       <c r="C291" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G291" s="1"/>
     </row>
@@ -8397,7 +8392,7 @@
         <v>364</v>
       </c>
       <c r="C292" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G292" s="1"/>
     </row>
@@ -8409,7 +8404,7 @@
         <v>399</v>
       </c>
       <c r="C293" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G293" s="1"/>
     </row>
@@ -8421,7 +8416,7 @@
         <v>400</v>
       </c>
       <c r="C294" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G294" s="1"/>
     </row>
@@ -8433,7 +8428,7 @@
         <v>401</v>
       </c>
       <c r="C295" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G295" s="1"/>
     </row>
@@ -8445,7 +8440,7 @@
         <v>402</v>
       </c>
       <c r="C296" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G296" s="1"/>
     </row>
@@ -8457,7 +8452,7 @@
         <v>403</v>
       </c>
       <c r="C297" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G297" s="1"/>
     </row>
@@ -8469,7 +8464,7 @@
         <v>404</v>
       </c>
       <c r="C298" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G298" s="1"/>
     </row>
@@ -8481,7 +8476,7 @@
         <v>405</v>
       </c>
       <c r="C299" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D299" t="s">
         <v>406</v>
@@ -8495,7 +8490,7 @@
         <v>407</v>
       </c>
       <c r="C300" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -8506,7 +8501,7 @@
         <v>408</v>
       </c>
       <c r="C301" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -8517,7 +8512,7 @@
         <v>409</v>
       </c>
       <c r="C302" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -8528,7 +8523,7 @@
         <v>410</v>
       </c>
       <c r="C303" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -8539,7 +8534,7 @@
         <v>361</v>
       </c>
       <c r="C304" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -8550,7 +8545,7 @@
         <v>411</v>
       </c>
       <c r="C305" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -8561,7 +8556,7 @@
         <v>412</v>
       </c>
       <c r="C306" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -8572,7 +8567,7 @@
         <v>413</v>
       </c>
       <c r="C307" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -8594,7 +8589,7 @@
         <v>416</v>
       </c>
       <c r="C309" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -8605,7 +8600,7 @@
         <v>417</v>
       </c>
       <c r="C310" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D310" t="s">
         <v>418</v>
@@ -8619,7 +8614,7 @@
         <v>419</v>
       </c>
       <c r="C311" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -8630,7 +8625,7 @@
         <v>420</v>
       </c>
       <c r="C312" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -8641,7 +8636,7 @@
         <v>421</v>
       </c>
       <c r="C313" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -8652,7 +8647,7 @@
         <v>422</v>
       </c>
       <c r="C314" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -8663,7 +8658,7 @@
         <v>423</v>
       </c>
       <c r="C315" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -8674,7 +8669,7 @@
         <v>424</v>
       </c>
       <c r="C316" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -8685,7 +8680,7 @@
         <v>425</v>
       </c>
       <c r="C317" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -8696,7 +8691,7 @@
         <v>426</v>
       </c>
       <c r="C318" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -8707,7 +8702,7 @@
         <v>341</v>
       </c>
       <c r="C319" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -8718,7 +8713,7 @@
         <v>427</v>
       </c>
       <c r="C320" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -8729,7 +8724,7 @@
         <v>428</v>
       </c>
       <c r="C321" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -8740,7 +8735,7 @@
         <v>429</v>
       </c>
       <c r="C322" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -8751,7 +8746,7 @@
         <v>430</v>
       </c>
       <c r="C323" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -8762,7 +8757,7 @@
         <v>431</v>
       </c>
       <c r="C324" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -8773,7 +8768,7 @@
         <v>432</v>
       </c>
       <c r="C325" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -8784,7 +8779,7 @@
         <v>433</v>
       </c>
       <c r="C326" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -8795,7 +8790,7 @@
         <v>434</v>
       </c>
       <c r="C327" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -8806,7 +8801,7 @@
         <v>435</v>
       </c>
       <c r="C328" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -8817,7 +8812,7 @@
         <v>436</v>
       </c>
       <c r="C329" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -8828,7 +8823,7 @@
         <v>437</v>
       </c>
       <c r="C330" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -8839,7 +8834,7 @@
         <v>438</v>
       </c>
       <c r="C331" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -8850,7 +8845,7 @@
         <v>439</v>
       </c>
       <c r="C332" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -8861,7 +8856,7 @@
         <v>440</v>
       </c>
       <c r="C333" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -8872,7 +8867,7 @@
         <v>441</v>
       </c>
       <c r="C334" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -8883,7 +8878,7 @@
         <v>442</v>
       </c>
       <c r="C335" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -8891,10 +8886,10 @@
         <v>23020</v>
       </c>
       <c r="B336" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C336" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -8905,7 +8900,7 @@
         <v>443</v>
       </c>
       <c r="C337" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -8916,7 +8911,7 @@
         <v>444</v>
       </c>
       <c r="C338" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -8927,7 +8922,7 @@
         <v>445</v>
       </c>
       <c r="C339" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -8938,7 +8933,7 @@
         <v>446</v>
       </c>
       <c r="C340" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -8949,7 +8944,7 @@
         <v>447</v>
       </c>
       <c r="C341" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -8960,7 +8955,7 @@
         <v>448</v>
       </c>
       <c r="C342" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -8971,7 +8966,7 @@
         <v>449</v>
       </c>
       <c r="C343" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -8982,7 +8977,7 @@
         <v>450</v>
       </c>
       <c r="C344" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -8993,7 +8988,7 @@
         <v>451</v>
       </c>
       <c r="C345" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -9004,7 +8999,7 @@
         <v>452</v>
       </c>
       <c r="C346" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -9015,7 +9010,7 @@
         <v>453</v>
       </c>
       <c r="C347" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -9026,7 +9021,7 @@
         <v>454</v>
       </c>
       <c r="C348" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -9037,7 +9032,7 @@
         <v>455</v>
       </c>
       <c r="C349" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -9048,7 +9043,7 @@
         <v>456</v>
       </c>
       <c r="C350" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -9059,7 +9054,7 @@
         <v>457</v>
       </c>
       <c r="C351" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -9070,7 +9065,7 @@
         <v>458</v>
       </c>
       <c r="C352" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -9081,7 +9076,7 @@
         <v>459</v>
       </c>
       <c r="C353" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -9092,7 +9087,7 @@
         <v>460</v>
       </c>
       <c r="C354" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -9103,7 +9098,7 @@
         <v>461</v>
       </c>
       <c r="C355" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -9114,7 +9109,7 @@
         <v>462</v>
       </c>
       <c r="C356" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -9125,7 +9120,7 @@
         <v>463</v>
       </c>
       <c r="C357" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -9136,7 +9131,7 @@
         <v>355</v>
       </c>
       <c r="C358" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -9147,7 +9142,7 @@
         <v>464</v>
       </c>
       <c r="C359" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -9155,10 +9150,10 @@
         <v>30020</v>
       </c>
       <c r="B360" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C360" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -9166,10 +9161,10 @@
         <v>30030</v>
       </c>
       <c r="B361" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C361" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -9180,7 +9175,7 @@
         <v>465</v>
       </c>
       <c r="C362" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -9191,7 +9186,7 @@
         <v>466</v>
       </c>
       <c r="C363" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -9202,7 +9197,7 @@
         <v>467</v>
       </c>
       <c r="C364" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -9213,7 +9208,7 @@
         <v>468</v>
       </c>
       <c r="C365" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D365" t="s">
         <v>469</v>
@@ -9227,7 +9222,7 @@
         <v>470</v>
       </c>
       <c r="C366" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -9238,7 +9233,7 @@
         <v>359</v>
       </c>
       <c r="C367" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -9249,7 +9244,7 @@
         <v>471</v>
       </c>
       <c r="C368" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9260,7 +9255,7 @@
         <v>472</v>
       </c>
       <c r="C369" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D369" t="s">
         <v>473</v>
@@ -9274,7 +9269,7 @@
         <v>474</v>
       </c>
       <c r="C370" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -9285,7 +9280,7 @@
         <v>475</v>
       </c>
       <c r="C371" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -9296,7 +9291,7 @@
         <v>476</v>
       </c>
       <c r="C372" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -9307,7 +9302,7 @@
         <v>477</v>
       </c>
       <c r="C373" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9318,7 +9313,7 @@
         <v>478</v>
       </c>
       <c r="C374" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D374" t="s">
         <v>479</v>
@@ -9332,7 +9327,7 @@
         <v>480</v>
       </c>
       <c r="C375" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -9343,7 +9338,7 @@
         <v>481</v>
       </c>
       <c r="C376" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -9354,7 +9349,7 @@
         <v>482</v>
       </c>
       <c r="C377" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -9365,7 +9360,7 @@
         <v>483</v>
       </c>
       <c r="C378" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -9376,7 +9371,7 @@
         <v>484</v>
       </c>
       <c r="C379" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -9387,7 +9382,7 @@
         <v>485</v>
       </c>
       <c r="C380" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -9398,7 +9393,7 @@
         <v>486</v>
       </c>
       <c r="C381" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -9409,7 +9404,7 @@
         <v>487</v>
       </c>
       <c r="C382" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -9420,7 +9415,7 @@
         <v>488</v>
       </c>
       <c r="C383" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -9431,7 +9426,7 @@
         <v>489</v>
       </c>
       <c r="C384" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -9442,7 +9437,7 @@
         <v>490</v>
       </c>
       <c r="C385" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="493">
   <si>
     <t>Id</t>
   </si>
@@ -46,16 +46,19 @@
     <t>MoveBattler</t>
   </si>
   <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Wait</t>
+  </si>
+  <si>
     <t>Transfer</t>
   </si>
   <si>
-    <t>Wait</t>
+    <t>UnitActEnd</t>
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>UnitActEnd</t>
   </si>
   <si>
     <t>Battle</t>
@@ -1099,13 +1102,13 @@
     <t>報告</t>
   </si>
   <si>
-    <t>神界転送</t>
+    <t>献上</t>
+  </si>
+  <si>
+    <t>転送</t>
   </si>
   <si>
     <t>仲間確認</t>
-  </si>
-  <si>
-    <t>バトル</t>
   </si>
   <si>
     <t>部隊</t>
@@ -1218,6 +1221,9 @@
   </si>
   <si>
     <t>5th</t>
+  </si>
+  <si>
+    <t>バトル</t>
   </si>
   <si>
     <t>シンボルタイトル</t>
@@ -1507,9 +1513,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -1535,7 +1541,67 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1549,40 +1615,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1594,22 +1637,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1625,14 +1654,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1642,29 +1663,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1673,6 +1672,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1687,43 +1693,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1735,7 +1711,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1747,13 +1741,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1765,61 +1759,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1837,19 +1777,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1861,13 +1855,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1896,17 +1902,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1930,16 +1945,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1948,21 +1954,21 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1986,7 +1992,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1995,7 +2001,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2004,127 +2010,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2612,13 +2618,21 @@
         <v>19004</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="2"/>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>19005</v>
+      </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>19005</v>
@@ -2630,7 +2644,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>19006</v>
@@ -2642,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>19007</v>
@@ -2654,7 +2668,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>19008</v>
@@ -2666,7 +2680,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11">
         <v>19009</v>
@@ -2678,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12">
         <v>19010</v>
@@ -2690,7 +2704,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13">
         <v>19011</v>
@@ -2702,7 +2716,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14">
         <v>19012</v>
@@ -2714,7 +2728,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15">
         <v>19013</v>
@@ -2725,7 +2739,7 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16">
         <v>19014</v>
@@ -2763,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>13210</v>
@@ -2774,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>13220</v>
@@ -2785,7 +2799,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -2796,7 +2810,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>13230</v>
@@ -2833,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2844,7 +2858,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>18110</v>
@@ -2855,7 +2869,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>18120</v>
@@ -2866,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>18130</v>
@@ -2899,25 +2913,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2925,7 +2939,7 @@
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>6010</v>
@@ -2957,7 +2971,7 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>6020</v>
@@ -2989,7 +3003,7 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4">
         <v>6030</v>
@@ -3021,7 +3035,7 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5">
         <v>6040</v>
@@ -3053,7 +3067,7 @@
         <v>2030</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6">
         <v>6210</v>
@@ -3085,7 +3099,7 @@
         <v>2040</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>6220</v>
@@ -3117,7 +3131,7 @@
         <v>2050</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>6230</v>
@@ -3149,7 +3163,7 @@
         <v>2060</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>6240</v>
@@ -3181,7 +3195,7 @@
         <v>2070</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>6250</v>
@@ -3213,7 +3227,7 @@
         <v>2080</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11">
         <v>6260</v>
@@ -3245,7 +3259,7 @@
         <v>2090</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>6270</v>
@@ -3277,7 +3291,7 @@
         <v>2100</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13">
         <v>6280</v>
@@ -3324,15 +3338,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3341,12 +3355,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -3355,12 +3369,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -3369,12 +3383,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -3383,12 +3397,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -3397,12 +3411,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3411,12 +3425,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3425,12 +3439,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3439,12 +3453,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3453,12 +3467,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3467,12 +3481,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3481,12 +3495,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -3495,12 +3509,12 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3509,12 +3523,12 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -3523,12 +3537,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3537,12 +3551,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3551,12 +3565,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -3565,12 +3579,12 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -3579,12 +3593,12 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3593,12 +3607,12 @@
         <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -3607,12 +3621,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3621,12 +3635,12 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -3635,12 +3649,12 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -3649,12 +3663,12 @@
         <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3663,12 +3677,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -3677,12 +3691,12 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3691,12 +3705,12 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3705,12 +3719,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3719,12 +3733,12 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -3733,12 +3747,12 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3747,12 +3761,12 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -3761,12 +3775,12 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -3775,12 +3789,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3789,12 +3803,12 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -3803,12 +3817,12 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3817,12 +3831,12 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3831,12 +3845,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -3845,12 +3859,12 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -3859,12 +3873,12 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -3873,12 +3887,12 @@
         <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -3887,12 +3901,12 @@
         <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -3901,12 +3915,12 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -3915,12 +3929,12 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3929,12 +3943,12 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -3943,12 +3957,12 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -3957,12 +3971,12 @@
         <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B47">
         <v>11</v>
@@ -3971,12 +3985,12 @@
         <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -3985,12 +3999,12 @@
         <v>210</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -3999,12 +4013,12 @@
         <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -4013,12 +4027,12 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -4027,12 +4041,12 @@
         <v>802</v>
       </c>
       <c r="D51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -4041,12 +4055,12 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -4055,12 +4069,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -4069,12 +4083,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -4083,12 +4097,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4097,12 +4111,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -4111,12 +4125,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -4125,12 +4139,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -4139,12 +4153,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -4153,12 +4167,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -4167,12 +4181,12 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -4181,12 +4195,12 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -4197,7 +4211,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -4206,12 +4220,12 @@
         <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -4220,12 +4234,12 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4236,7 +4250,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -4247,7 +4261,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -4258,7 +4272,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4269,7 +4283,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -4278,12 +4292,12 @@
         <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -4292,12 +4306,12 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -4306,12 +4320,12 @@
         <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B73">
         <v>8</v>
@@ -4320,12 +4334,12 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -4334,12 +4348,12 @@
         <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -4348,12 +4362,12 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B76">
         <v>11</v>
@@ -4362,12 +4376,12 @@
         <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B77">
         <v>7</v>
@@ -4376,12 +4390,12 @@
         <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -4390,12 +4404,12 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -4404,12 +4418,12 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -4418,12 +4432,12 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4432,12 +4446,12 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -4446,12 +4460,12 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -4460,12 +4474,12 @@
         <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B84">
         <v>9</v>
@@ -4474,12 +4488,12 @@
         <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B85">
         <v>8</v>
@@ -4488,12 +4502,12 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -4502,12 +4516,12 @@
         <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4516,12 +4530,12 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -4530,12 +4544,12 @@
         <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -4544,12 +4558,12 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>9</v>
@@ -4558,12 +4572,12 @@
         <v>813</v>
       </c>
       <c r="D90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -4572,12 +4586,12 @@
         <v>800</v>
       </c>
       <c r="D91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -4586,12 +4600,12 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -4600,12 +4614,12 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -4614,12 +4628,12 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B95">
         <v>9</v>
@@ -4628,12 +4642,12 @@
         <v>814</v>
       </c>
       <c r="D95" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -4642,12 +4656,12 @@
         <v>800</v>
       </c>
       <c r="D96" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -4656,12 +4670,12 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4670,12 +4684,12 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -4684,12 +4698,12 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -4698,12 +4712,12 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4712,12 +4726,12 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -4726,12 +4740,12 @@
         <v>818</v>
       </c>
       <c r="D102" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -4740,12 +4754,12 @@
         <v>800</v>
       </c>
       <c r="D103" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -4754,12 +4768,12 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B105">
         <v>9</v>
@@ -4768,12 +4782,12 @@
         <v>817</v>
       </c>
       <c r="D105" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -4782,12 +4796,12 @@
         <v>816</v>
       </c>
       <c r="D106" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -4796,12 +4810,12 @@
         <v>817</v>
       </c>
       <c r="D107" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B108">
         <v>4</v>
@@ -4810,12 +4824,12 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -4824,12 +4838,12 @@
         <v>801</v>
       </c>
       <c r="D109" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -4838,12 +4852,12 @@
         <v>800</v>
       </c>
       <c r="D110" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -4852,12 +4866,12 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -4866,12 +4880,12 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -4880,12 +4894,12 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -4894,12 +4908,12 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -4908,12 +4922,12 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -4922,12 +4936,12 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -4936,7 +4950,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4959,34 +4973,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -4994,7 +5008,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -5002,7 +5016,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -5010,7 +5024,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -5018,40 +5032,40 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10">
         <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5078,10 +5092,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5089,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" ht="14" spans="1:7">
@@ -5100,10 +5114,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -5112,10 +5126,10 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5123,10 +5137,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5134,10 +5148,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5145,10 +5159,10 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5156,10 +5170,10 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5167,10 +5181,10 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5178,10 +5192,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5189,10 +5203,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5200,10 +5214,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5211,10 +5225,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5222,10 +5236,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5233,10 +5247,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5244,10 +5258,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5255,10 +5269,10 @@
         <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5266,10 +5280,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5277,10 +5291,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5288,10 +5302,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5299,10 +5313,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5310,10 +5324,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5321,10 +5335,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5332,10 +5346,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5343,10 +5357,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -5354,10 +5368,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5365,10 +5379,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5376,10 +5390,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5387,10 +5401,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5398,10 +5412,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5409,10 +5423,10 @@
         <v>342</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5420,13 +5434,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5434,13 +5448,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5448,13 +5462,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
         <v>148</v>
-      </c>
-      <c r="C34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5462,13 +5476,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5476,13 +5490,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" t="s">
         <v>151</v>
-      </c>
-      <c r="C36" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5490,13 +5504,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5504,10 +5518,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5515,10 +5529,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5526,10 +5540,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5537,10 +5551,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5548,10 +5562,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5559,10 +5573,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5570,10 +5584,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5581,10 +5595,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -5592,10 +5606,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5603,10 +5617,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -5614,10 +5628,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5625,10 +5639,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5636,10 +5650,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5647,10 +5661,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5658,10 +5672,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5669,10 +5683,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5680,10 +5694,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5691,10 +5705,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5702,10 +5716,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5713,10 +5727,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5724,10 +5738,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5735,10 +5749,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5746,10 +5760,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5757,10 +5771,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5768,10 +5782,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5779,10 +5793,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5790,10 +5804,10 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5801,10 +5815,10 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5812,10 +5826,10 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5823,10 +5837,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5834,10 +5848,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5845,10 +5859,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C69" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5856,10 +5870,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5867,10 +5881,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5878,10 +5892,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5889,10 +5903,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5900,10 +5914,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5911,10 +5925,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5922,10 +5936,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5933,10 +5947,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C77" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5944,10 +5958,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5955,10 +5969,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5966,10 +5980,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C80" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5977,10 +5991,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -5988,10 +6002,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -5999,10 +6013,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -6010,10 +6024,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -6021,10 +6035,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -6032,10 +6046,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C86" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -6043,10 +6057,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C87" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -6054,10 +6068,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -6065,10 +6079,10 @@
         <v>1000</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -6076,10 +6090,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -6087,10 +6101,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C91" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -6098,10 +6112,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C92" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -6109,10 +6123,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -6120,10 +6134,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -6131,10 +6145,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C95" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6142,13 +6156,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -6156,10 +6170,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -6167,10 +6181,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -6178,10 +6192,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -6189,10 +6203,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -6200,10 +6214,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -6211,10 +6225,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C102" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -6222,10 +6236,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C103" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6233,13 +6247,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6247,13 +6261,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
+        <v>215</v>
+      </c>
+      <c r="C105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105" t="s">
         <v>214</v>
-      </c>
-      <c r="C105" t="s">
-        <v>119</v>
-      </c>
-      <c r="D105" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6261,13 +6275,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C106" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6275,13 +6289,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" t="s">
+        <v>120</v>
+      </c>
+      <c r="D107" t="s">
         <v>214</v>
-      </c>
-      <c r="C107" t="s">
-        <v>119</v>
-      </c>
-      <c r="D107" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6289,13 +6303,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C108" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -6303,10 +6317,10 @@
         <v>2101</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C109" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -6314,10 +6328,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C110" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -6325,10 +6339,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C111" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -6336,10 +6350,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C112" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -6347,10 +6361,10 @@
         <v>2105</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C113" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -6358,10 +6372,10 @@
         <v>2106</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C114" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6369,13 +6383,13 @@
         <v>2200</v>
       </c>
       <c r="B115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C115" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D115" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6383,13 +6397,13 @@
         <v>2210</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D116" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" ht="29" customHeight="1" spans="1:4">
@@ -6397,13 +6411,13 @@
         <v>2220</v>
       </c>
       <c r="B117" t="s">
+        <v>226</v>
+      </c>
+      <c r="C117" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" t="s">
         <v>225</v>
-      </c>
-      <c r="C117" t="s">
-        <v>119</v>
-      </c>
-      <c r="D117" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6411,13 +6425,13 @@
         <v>2300</v>
       </c>
       <c r="B118" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C118" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6425,13 +6439,13 @@
         <v>2310</v>
       </c>
       <c r="B119" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C119" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D119" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6439,13 +6453,13 @@
         <v>2320</v>
       </c>
       <c r="B120" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C120" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6453,13 +6467,13 @@
         <v>2330</v>
       </c>
       <c r="B121" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C121" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6467,13 +6481,13 @@
         <v>2340</v>
       </c>
       <c r="B122" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C122" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D122" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6481,13 +6495,13 @@
         <v>2400</v>
       </c>
       <c r="B123" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C123" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D123" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -6495,10 +6509,10 @@
         <v>3000</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C124" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -6506,10 +6520,10 @@
         <v>3010</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C125" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -6517,10 +6531,10 @@
         <v>3011</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C126" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -6528,10 +6542,10 @@
         <v>3040</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C127" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -6539,10 +6553,10 @@
         <v>3050</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C128" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -6550,10 +6564,10 @@
         <v>3051</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C129" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -6561,10 +6575,10 @@
         <v>3052</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C130" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -6572,10 +6586,10 @@
         <v>3053</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C131" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -6583,10 +6597,10 @@
         <v>3054</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -6594,10 +6608,10 @@
         <v>3070</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -6605,10 +6619,10 @@
         <v>3071</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C134" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -6616,10 +6630,10 @@
         <v>3072</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C135" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -6627,10 +6641,10 @@
         <v>3073</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C136" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -6638,10 +6652,10 @@
         <v>3090</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C137" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -6649,10 +6663,10 @@
         <v>3211</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C138" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -6660,10 +6674,10 @@
         <v>3230</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C139" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6671,10 +6685,10 @@
         <v>5000</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C140" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6682,10 +6696,10 @@
         <v>5001</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C141" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6693,10 +6707,10 @@
         <v>5002</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C142" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6704,10 +6718,10 @@
         <v>6001</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C143" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6715,10 +6729,10 @@
         <v>6002</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C144" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6726,10 +6740,10 @@
         <v>6100</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C145" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6737,10 +6751,10 @@
         <v>6010</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C146" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6748,10 +6762,10 @@
         <v>6011</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C147" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6759,10 +6773,10 @@
         <v>6012</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C148" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6770,10 +6784,10 @@
         <v>6020</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6781,10 +6795,10 @@
         <v>6030</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C150" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6792,10 +6806,10 @@
         <v>6040</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C151" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6803,10 +6817,10 @@
         <v>6210</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6814,10 +6828,10 @@
         <v>6220</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C153" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6825,10 +6839,10 @@
         <v>6230</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6836,10 +6850,10 @@
         <v>6240</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C155" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6847,10 +6861,10 @@
         <v>6250</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6858,10 +6872,10 @@
         <v>6260</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C157" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6869,10 +6883,10 @@
         <v>6270</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C158" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6880,10 +6894,10 @@
         <v>6280</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C159" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6891,10 +6905,10 @@
         <v>6810</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C160" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6902,10 +6916,10 @@
         <v>6820</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C161" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6913,10 +6927,10 @@
         <v>6830</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C162" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6924,10 +6938,10 @@
         <v>6840</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C163" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -6935,10 +6949,10 @@
         <v>6850</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C164" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -6946,10 +6960,10 @@
         <v>6860</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C165" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6957,10 +6971,10 @@
         <v>6870</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C166" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6968,10 +6982,10 @@
         <v>6880</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C167" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6979,10 +6993,10 @@
         <v>6890</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C168" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="169" ht="130" spans="1:4">
@@ -6990,13 +7004,13 @@
         <v>12010</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C169" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" ht="26" spans="1:4">
@@ -7004,13 +7018,13 @@
         <v>13010</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C170" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -7019,7 +7033,7 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -7027,10 +7041,10 @@
         <v>13110</v>
       </c>
       <c r="B172" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C172" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -7038,10 +7052,10 @@
         <v>13120</v>
       </c>
       <c r="B173" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C173" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -7049,10 +7063,10 @@
         <v>13130</v>
       </c>
       <c r="B174" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C174" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -7060,10 +7074,10 @@
         <v>13140</v>
       </c>
       <c r="B175" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C175" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -7071,10 +7085,10 @@
         <v>13210</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C176" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -7082,10 +7096,10 @@
         <v>13220</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C177" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -7093,10 +7107,10 @@
         <v>13230</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C178" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -7104,10 +7118,10 @@
         <v>13240</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C179" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -7115,10 +7129,10 @@
         <v>13300</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C180" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -7126,10 +7140,10 @@
         <v>13301</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C181" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -7137,10 +7151,10 @@
         <v>13310</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C182" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -7148,10 +7162,10 @@
         <v>13320</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C183" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="184" ht="26" spans="1:3">
@@ -7159,10 +7173,10 @@
         <v>13330</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C184" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -7170,10 +7184,10 @@
         <v>13400</v>
       </c>
       <c r="B185" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C185" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -7181,10 +7195,10 @@
         <v>13410</v>
       </c>
       <c r="B186" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C186" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -7192,10 +7206,10 @@
         <v>13420</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C187" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -7203,10 +7217,10 @@
         <v>13421</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C188" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -7214,10 +7228,10 @@
         <v>13430</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C189" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -7225,10 +7239,10 @@
         <v>14090</v>
       </c>
       <c r="B190" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C190" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -7236,10 +7250,10 @@
         <v>14110</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C191" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="192" ht="14" spans="1:7">
@@ -7247,13 +7261,13 @@
         <v>15010</v>
       </c>
       <c r="B192" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C192" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D192" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -7262,13 +7276,13 @@
         <v>16010</v>
       </c>
       <c r="B193" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C193" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D193" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G193" s="1"/>
     </row>
@@ -7277,10 +7291,10 @@
         <v>16020</v>
       </c>
       <c r="B194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C194" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G194" s="1"/>
     </row>
@@ -7289,10 +7303,10 @@
         <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C195" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -7300,10 +7314,10 @@
         <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C196" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -7311,10 +7325,10 @@
         <v>16200</v>
       </c>
       <c r="B197" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C197" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -7322,10 +7336,10 @@
         <v>16210</v>
       </c>
       <c r="B198" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C198" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -7333,10 +7347,10 @@
         <v>16220</v>
       </c>
       <c r="B199" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C199" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -7344,10 +7358,10 @@
         <v>16230</v>
       </c>
       <c r="B200" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C200" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -7355,10 +7369,10 @@
         <v>16300</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C201" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -7366,10 +7380,10 @@
         <v>16310</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C202" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -7377,10 +7391,10 @@
         <v>16320</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C203" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -7388,10 +7402,10 @@
         <v>16400</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C204" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -7399,10 +7413,10 @@
         <v>16410</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C205" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7410,13 +7424,13 @@
         <v>16800</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C206" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D206" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7424,13 +7438,13 @@
         <v>16801</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C207" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D207" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7438,13 +7452,13 @@
         <v>16802</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C208" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D208" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7452,13 +7466,13 @@
         <v>16803</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C209" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D209" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7466,13 +7480,13 @@
         <v>16804</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C210" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D210" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7480,13 +7494,13 @@
         <v>16805</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C211" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D211" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -7494,13 +7508,13 @@
         <v>16806</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C212" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D212" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -7508,10 +7522,10 @@
         <v>17010</v>
       </c>
       <c r="B213" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C213" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -7519,13 +7533,13 @@
         <v>18010</v>
       </c>
       <c r="B214" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C214" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D214" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -7533,10 +7547,10 @@
         <v>18020</v>
       </c>
       <c r="B215" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C215" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -7544,10 +7558,10 @@
         <v>18100</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C216" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -7555,10 +7569,10 @@
         <v>18110</v>
       </c>
       <c r="B217" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C217" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -7566,10 +7580,10 @@
         <v>18120</v>
       </c>
       <c r="B218" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C218" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -7577,10 +7591,10 @@
         <v>18130</v>
       </c>
       <c r="B219" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C219" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -7588,10 +7602,10 @@
         <v>18200</v>
       </c>
       <c r="B220" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C220" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -7599,10 +7613,10 @@
         <v>18210</v>
       </c>
       <c r="B221" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C221" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -7610,10 +7624,10 @@
         <v>18220</v>
       </c>
       <c r="B222" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C222" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -7621,10 +7635,10 @@
         <v>18230</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C223" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -7632,10 +7646,10 @@
         <v>18300</v>
       </c>
       <c r="B224" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C224" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -7643,10 +7657,10 @@
         <v>18310</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C225" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -7654,10 +7668,10 @@
         <v>18320</v>
       </c>
       <c r="B226" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C226" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -7665,10 +7679,10 @@
         <v>18340</v>
       </c>
       <c r="B227" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C227" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -7676,10 +7690,10 @@
         <v>18400</v>
       </c>
       <c r="B228" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C228" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -7687,10 +7701,10 @@
         <v>18410</v>
       </c>
       <c r="B229" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C229" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -7698,10 +7712,10 @@
         <v>18420</v>
       </c>
       <c r="B230" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C230" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -7709,10 +7723,10 @@
         <v>18430</v>
       </c>
       <c r="B231" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C231" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -7720,10 +7734,10 @@
         <v>18440</v>
       </c>
       <c r="B232" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C232" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -7731,10 +7745,10 @@
         <v>18450</v>
       </c>
       <c r="B233" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C233" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -7742,10 +7756,10 @@
         <v>18500</v>
       </c>
       <c r="B234" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C234" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -7753,10 +7767,10 @@
         <v>18510</v>
       </c>
       <c r="B235" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C235" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7764,10 +7778,10 @@
         <v>18800</v>
       </c>
       <c r="B236" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C236" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7775,10 +7789,10 @@
         <v>18801</v>
       </c>
       <c r="B237" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C237" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -7786,10 +7800,10 @@
         <v>18802</v>
       </c>
       <c r="B238" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C238" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -7797,10 +7811,10 @@
         <v>18803</v>
       </c>
       <c r="B239" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C239" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7808,10 +7822,10 @@
         <v>18804</v>
       </c>
       <c r="B240" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C240" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7819,10 +7833,10 @@
         <v>18805</v>
       </c>
       <c r="B241" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C241" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7830,10 +7844,10 @@
         <v>18806</v>
       </c>
       <c r="B242" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C242" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7841,10 +7855,10 @@
         <v>18811</v>
       </c>
       <c r="B243" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C243" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7852,10 +7866,10 @@
         <v>18812</v>
       </c>
       <c r="B244" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C244" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="245" ht="14" spans="1:7">
@@ -7863,13 +7877,13 @@
         <v>19000</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C245" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D245" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G245" s="1"/>
     </row>
@@ -7878,10 +7892,10 @@
         <v>19001</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C246" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -7889,10 +7903,10 @@
         <v>19002</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C247" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -7900,10 +7914,10 @@
         <v>19003</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C248" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -7911,10 +7925,10 @@
         <v>19004</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C249" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -7922,10 +7936,10 @@
         <v>19005</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C250" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -7933,10 +7947,10 @@
         <v>19006</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C251" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -7944,10 +7958,10 @@
         <v>19007</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C252" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -7955,10 +7969,10 @@
         <v>19008</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C253" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -7966,10 +7980,10 @@
         <v>19009</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C254" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -7977,10 +7991,10 @@
         <v>19010</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C255" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -7988,10 +8002,10 @@
         <v>19011</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C256" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -7999,10 +8013,10 @@
         <v>19012</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C257" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -8010,10 +8024,10 @@
         <v>19013</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C258" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -8021,10 +8035,10 @@
         <v>19014</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C259" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -8032,10 +8046,10 @@
         <v>19100</v>
       </c>
       <c r="B260" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C260" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -8043,10 +8057,10 @@
         <v>19110</v>
       </c>
       <c r="B261" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C261" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -8054,10 +8068,10 @@
         <v>19200</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C262" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -8065,10 +8079,10 @@
         <v>19210</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C263" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -8076,10 +8090,10 @@
         <v>19220</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C264" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -8087,10 +8101,10 @@
         <v>19230</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C265" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -8098,10 +8112,10 @@
         <v>19240</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C266" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -8109,10 +8123,10 @@
         <v>19250</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C267" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -8120,10 +8134,10 @@
         <v>19260</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C268" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -8131,10 +8145,10 @@
         <v>19270</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C269" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -8142,10 +8156,10 @@
         <v>19280</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C270" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -8153,10 +8167,10 @@
         <v>19300</v>
       </c>
       <c r="B271" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C271" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="272" ht="26" spans="1:3">
@@ -8164,10 +8178,10 @@
         <v>19310</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C272" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -8175,10 +8189,10 @@
         <v>19320</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C273" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -8186,10 +8200,10 @@
         <v>19330</v>
       </c>
       <c r="B274" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C274" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -8197,10 +8211,10 @@
         <v>19340</v>
       </c>
       <c r="B275" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C275" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -8208,10 +8222,10 @@
         <v>19350</v>
       </c>
       <c r="B276" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C276" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -8219,10 +8233,10 @@
         <v>19360</v>
       </c>
       <c r="B277" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C277" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -8230,10 +8244,10 @@
         <v>19400</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C278" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -8241,10 +8255,10 @@
         <v>19401</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C279" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -8252,10 +8266,10 @@
         <v>19410</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C280" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -8263,10 +8277,10 @@
         <v>19420</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C281" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -8274,10 +8288,10 @@
         <v>19500</v>
       </c>
       <c r="B282" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C282" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -8285,10 +8299,10 @@
         <v>19510</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C283" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -8296,10 +8310,10 @@
         <v>19520</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C284" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -8307,10 +8321,10 @@
         <v>19600</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C285" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -8318,10 +8332,10 @@
         <v>19601</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C286" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -8329,10 +8343,10 @@
         <v>19602</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C287" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -8340,10 +8354,10 @@
         <v>19603</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C288" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -8351,10 +8365,10 @@
         <v>19604</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C289" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="290" ht="14" spans="1:7">
@@ -8362,13 +8376,13 @@
         <v>19611</v>
       </c>
       <c r="B290" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="C290" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D290" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G290" s="1"/>
     </row>
@@ -8377,10 +8391,10 @@
         <v>19612</v>
       </c>
       <c r="B291" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C291" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G291" s="1"/>
     </row>
@@ -8389,10 +8403,10 @@
         <v>19613</v>
       </c>
       <c r="B292" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C292" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G292" s="1"/>
     </row>
@@ -8401,10 +8415,10 @@
         <v>19614</v>
       </c>
       <c r="B293" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C293" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G293" s="1"/>
     </row>
@@ -8413,10 +8427,10 @@
         <v>19615</v>
       </c>
       <c r="B294" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C294" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G294" s="1"/>
     </row>
@@ -8425,10 +8439,10 @@
         <v>19616</v>
       </c>
       <c r="B295" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C295" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G295" s="1"/>
     </row>
@@ -8437,10 +8451,10 @@
         <v>19617</v>
       </c>
       <c r="B296" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C296" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G296" s="1"/>
     </row>
@@ -8449,10 +8463,10 @@
         <v>19618</v>
       </c>
       <c r="B297" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C297" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G297" s="1"/>
     </row>
@@ -8461,10 +8475,10 @@
         <v>19619</v>
       </c>
       <c r="B298" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C298" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G298" s="1"/>
     </row>
@@ -8473,13 +8487,13 @@
         <v>19631</v>
       </c>
       <c r="B299" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C299" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D299" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -8487,10 +8501,10 @@
         <v>19632</v>
       </c>
       <c r="B300" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C300" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -8498,10 +8512,10 @@
         <v>19633</v>
       </c>
       <c r="B301" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C301" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -8509,10 +8523,10 @@
         <v>19634</v>
       </c>
       <c r="B302" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C302" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -8520,10 +8534,10 @@
         <v>19700</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C303" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -8531,10 +8545,10 @@
         <v>19710</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C304" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -8542,10 +8556,10 @@
         <v>19720</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C305" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -8553,10 +8567,10 @@
         <v>19730</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C306" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -8564,10 +8578,10 @@
         <v>19740</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C307" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -8575,10 +8589,10 @@
         <v>19800</v>
       </c>
       <c r="B308" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C308" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -8586,10 +8600,10 @@
         <v>19810</v>
       </c>
       <c r="B309" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C309" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -8597,13 +8611,13 @@
         <v>20010</v>
       </c>
       <c r="B310" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C310" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D310" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -8611,10 +8625,10 @@
         <v>20020</v>
       </c>
       <c r="B311" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C311" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -8622,10 +8636,10 @@
         <v>20030</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C312" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -8633,10 +8647,10 @@
         <v>20040</v>
       </c>
       <c r="B313" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C313" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -8644,10 +8658,10 @@
         <v>20050</v>
       </c>
       <c r="B314" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C314" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -8655,10 +8669,10 @@
         <v>20100</v>
       </c>
       <c r="B315" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C315" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -8666,10 +8680,10 @@
         <v>20110</v>
       </c>
       <c r="B316" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C316" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -8677,10 +8691,10 @@
         <v>20120</v>
       </c>
       <c r="B317" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C317" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -8688,10 +8702,10 @@
         <v>20200</v>
       </c>
       <c r="B318" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C318" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -8699,10 +8713,10 @@
         <v>20201</v>
       </c>
       <c r="B319" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -8710,10 +8724,10 @@
         <v>20210</v>
       </c>
       <c r="B320" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C320" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -8721,10 +8735,10 @@
         <v>20220</v>
       </c>
       <c r="B321" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C321" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -8732,10 +8746,10 @@
         <v>20230</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C322" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -8743,10 +8757,10 @@
         <v>20240</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C323" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -8754,10 +8768,10 @@
         <v>20250</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C324" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -8765,10 +8779,10 @@
         <v>20260</v>
       </c>
       <c r="B325" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C325" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -8776,10 +8790,10 @@
         <v>20270</v>
       </c>
       <c r="B326" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C326" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -8787,10 +8801,10 @@
         <v>20280</v>
       </c>
       <c r="B327" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C327" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -8798,10 +8812,10 @@
         <v>20290</v>
       </c>
       <c r="B328" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C328" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -8809,10 +8823,10 @@
         <v>20300</v>
       </c>
       <c r="B329" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C329" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -8820,10 +8834,10 @@
         <v>20310</v>
       </c>
       <c r="B330" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C330" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -8831,10 +8845,10 @@
         <v>20320</v>
       </c>
       <c r="B331" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C331" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -8842,10 +8856,10 @@
         <v>20330</v>
       </c>
       <c r="B332" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C332" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -8853,10 +8867,10 @@
         <v>20340</v>
       </c>
       <c r="B333" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C333" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -8864,10 +8878,10 @@
         <v>20350</v>
       </c>
       <c r="B334" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C334" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -8875,10 +8889,10 @@
         <v>23010</v>
       </c>
       <c r="B335" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C335" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -8886,10 +8900,10 @@
         <v>23020</v>
       </c>
       <c r="B336" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C336" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -8897,10 +8911,10 @@
         <v>23030</v>
       </c>
       <c r="B337" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C337" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -8908,10 +8922,10 @@
         <v>23031</v>
       </c>
       <c r="B338" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C338" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -8919,10 +8933,10 @@
         <v>23032</v>
       </c>
       <c r="B339" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C339" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -8930,10 +8944,10 @@
         <v>23040</v>
       </c>
       <c r="B340" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C340" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -8941,10 +8955,10 @@
         <v>24010</v>
       </c>
       <c r="B341" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C341" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -8952,10 +8966,10 @@
         <v>24020</v>
       </c>
       <c r="B342" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C342" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -8963,10 +8977,10 @@
         <v>24030</v>
       </c>
       <c r="B343" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C343" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -8974,10 +8988,10 @@
         <v>24040</v>
       </c>
       <c r="B344" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C344" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -8985,10 +8999,10 @@
         <v>24110</v>
       </c>
       <c r="B345" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C345" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -8996,10 +9010,10 @@
         <v>24111</v>
       </c>
       <c r="B346" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C346" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -9007,10 +9021,10 @@
         <v>24112</v>
       </c>
       <c r="B347" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C347" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -9018,10 +9032,10 @@
         <v>24113</v>
       </c>
       <c r="B348" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C348" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -9029,10 +9043,10 @@
         <v>24114</v>
       </c>
       <c r="B349" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C349" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -9040,10 +9054,10 @@
         <v>24115</v>
       </c>
       <c r="B350" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C350" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -9051,10 +9065,10 @@
         <v>24116</v>
       </c>
       <c r="B351" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C351" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -9062,10 +9076,10 @@
         <v>24117</v>
       </c>
       <c r="B352" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C352" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -9073,10 +9087,10 @@
         <v>24118</v>
       </c>
       <c r="B353" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C353" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -9084,10 +9098,10 @@
         <v>24119</v>
       </c>
       <c r="B354" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C354" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -9095,10 +9109,10 @@
         <v>24120</v>
       </c>
       <c r="B355" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C355" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -9106,10 +9120,10 @@
         <v>24121</v>
       </c>
       <c r="B356" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C356" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -9117,10 +9131,10 @@
         <v>24122</v>
       </c>
       <c r="B357" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C357" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -9128,10 +9142,10 @@
         <v>30000</v>
       </c>
       <c r="B358" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C358" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -9139,10 +9153,10 @@
         <v>30010</v>
       </c>
       <c r="B359" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C359" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -9150,10 +9164,10 @@
         <v>30020</v>
       </c>
       <c r="B360" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C360" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -9161,10 +9175,10 @@
         <v>30030</v>
       </c>
       <c r="B361" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C361" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -9172,10 +9186,10 @@
         <v>30040</v>
       </c>
       <c r="B362" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C362" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -9183,10 +9197,10 @@
         <v>31010</v>
       </c>
       <c r="B363" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C363" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -9194,10 +9208,10 @@
         <v>31020</v>
       </c>
       <c r="B364" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C364" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -9205,13 +9219,13 @@
         <v>102000</v>
       </c>
       <c r="B365" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C365" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D365" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -9219,10 +9233,10 @@
         <v>102010</v>
       </c>
       <c r="B366" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C366" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -9230,10 +9244,10 @@
         <v>102020</v>
       </c>
       <c r="B367" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="C367" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -9241,10 +9255,10 @@
         <v>102030</v>
       </c>
       <c r="B368" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C368" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9252,13 +9266,13 @@
         <v>113000</v>
       </c>
       <c r="B369" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C369" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D369" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -9266,10 +9280,10 @@
         <v>113010</v>
       </c>
       <c r="B370" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C370" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -9277,10 +9291,10 @@
         <v>113020</v>
       </c>
       <c r="B371" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C371" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -9288,10 +9302,10 @@
         <v>113030</v>
       </c>
       <c r="B372" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C372" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -9299,10 +9313,10 @@
         <v>113040</v>
       </c>
       <c r="B373" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C373" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9310,13 +9324,13 @@
         <v>121010</v>
       </c>
       <c r="B374" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C374" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D374" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -9324,10 +9338,10 @@
         <v>121011</v>
       </c>
       <c r="B375" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C375" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -9335,10 +9349,10 @@
         <v>121012</v>
       </c>
       <c r="B376" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C376" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -9346,10 +9360,10 @@
         <v>121013</v>
       </c>
       <c r="B377" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C377" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -9357,10 +9371,10 @@
         <v>121014</v>
       </c>
       <c r="B378" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C378" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -9368,10 +9382,10 @@
         <v>121015</v>
       </c>
       <c r="B379" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C379" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -9379,10 +9393,10 @@
         <v>121016</v>
       </c>
       <c r="B380" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C380" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -9390,10 +9404,10 @@
         <v>121017</v>
       </c>
       <c r="B381" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C381" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -9401,10 +9415,10 @@
         <v>121018</v>
       </c>
       <c r="B382" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C382" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -9412,10 +9426,10 @@
         <v>121019</v>
       </c>
       <c r="B383" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C383" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -9423,10 +9437,10 @@
         <v>121020</v>
       </c>
       <c r="B384" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C384" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -9434,10 +9448,10 @@
         <v>121030</v>
       </c>
       <c r="B385" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C385" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -894,8 +894,7 @@
     <t>Boot</t>
   </si>
   <si>
-    <t>終末時計と
-エインフェリアの物語</t>
+    <t>エインフェリアと終末時計</t>
   </si>
   <si>
     <t>Title</t>
@@ -1513,10 +1512,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1541,14 +1540,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1563,21 +1586,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1591,24 +1630,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1622,26 +1653,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1653,34 +1668,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1693,25 +1692,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1723,43 +1716,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1777,6 +1734,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1789,25 +1782,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1819,19 +1806,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1849,7 +1836,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1861,19 +1872,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1884,45 +1883,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1945,15 +1905,32 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1976,11 +1953,33 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1992,16 +1991,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2010,127 +2009,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7013,7 +7012,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="170" ht="26" spans="1:4">
+    <row r="170" spans="1:4">
       <c r="A170">
         <v>13010</v>
       </c>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="711" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="766"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="494">
   <si>
     <t>Id</t>
   </si>
@@ -46,22 +46,25 @@
     <t>MoveBattler</t>
   </si>
   <si>
+    <t>Relief</t>
+  </si>
+  <si>
+    <t>Wait</t>
+  </si>
+  <si>
     <t>Present</t>
   </si>
   <si>
-    <t>Wait</t>
+    <t>UnitActEnd</t>
   </si>
   <si>
     <t>Transfer</t>
   </si>
   <si>
-    <t>UnitActEnd</t>
+    <t>Battle</t>
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Battle</t>
   </si>
   <si>
     <t>Units</t>
@@ -1101,6 +1104,9 @@
     <t>報告</t>
   </si>
   <si>
+    <t>救済</t>
+  </si>
+  <si>
     <t>献上</t>
   </si>
   <si>
@@ -1108,12 +1114,6 @@
   </si>
   <si>
     <t>仲間確認</t>
-  </si>
-  <si>
-    <t>部隊</t>
-  </si>
-  <si>
-    <t>セーブ</t>
   </si>
   <si>
     <t>制圧</t>
@@ -1265,6 +1265,9 @@
   </si>
   <si>
     <t>ヘルプ</t>
+  </si>
+  <si>
+    <t>セーブ</t>
   </si>
   <si>
     <t>タイトルへ</t>
@@ -1512,10 +1515,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1540,7 +1543,35 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1555,36 +1586,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1593,30 +1594,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1630,31 +1617,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1669,7 +1640,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1692,7 +1695,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1704,13 +1773,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1722,43 +1857,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1770,109 +1875,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1883,30 +1886,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1936,17 +1915,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1956,15 +1953,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1983,6 +1971,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1991,16 +1994,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2009,127 +2012,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2637,13 +2640,21 @@
         <v>19005</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="2"/>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>19006</v>
+      </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>19006</v>
@@ -2655,7 +2666,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9">
         <v>19007</v>
@@ -2667,7 +2678,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10">
         <v>19008</v>
@@ -2679,19 +2690,18 @@
         <v>10</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11">
         <v>19009</v>
       </c>
     </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="2"/>
+    <row r="12" spans="5:7">
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12">
         <v>19010</v>
@@ -2703,7 +2713,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13">
         <v>19011</v>
@@ -2715,7 +2725,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14">
         <v>19012</v>
@@ -2727,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15">
         <v>19013</v>
@@ -2738,7 +2748,7 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16">
         <v>19014</v>
@@ -2776,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>13210</v>
@@ -2787,7 +2797,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>13220</v>
@@ -2798,7 +2808,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>13240</v>
@@ -2809,7 +2819,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>13230</v>
@@ -2846,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>18100</v>
@@ -2857,7 +2867,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>18110</v>
@@ -2868,7 +2878,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>18120</v>
@@ -2879,7 +2889,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>18130</v>
@@ -2912,25 +2922,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2938,7 +2948,7 @@
         <v>1010</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>6010</v>
@@ -2970,7 +2980,7 @@
         <v>1020</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>6020</v>
@@ -3002,7 +3012,7 @@
         <v>1030</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>6030</v>
@@ -3034,7 +3044,7 @@
         <v>1040</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>6040</v>
@@ -3066,7 +3076,7 @@
         <v>2030</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>6210</v>
@@ -3098,7 +3108,7 @@
         <v>2040</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>6220</v>
@@ -3130,7 +3140,7 @@
         <v>2050</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>6230</v>
@@ -3162,7 +3172,7 @@
         <v>2060</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9">
         <v>6240</v>
@@ -3194,7 +3204,7 @@
         <v>2070</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10">
         <v>6250</v>
@@ -3226,7 +3236,7 @@
         <v>2080</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>6260</v>
@@ -3258,7 +3268,7 @@
         <v>2090</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>6270</v>
@@ -3290,7 +3300,7 @@
         <v>2100</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>6280</v>
@@ -3337,15 +3347,15 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3354,12 +3364,12 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -3368,12 +3378,12 @@
         <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -3382,12 +3392,12 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -3396,12 +3406,12 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -3410,12 +3420,12 @@
         <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3424,12 +3434,12 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -3438,12 +3448,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3452,12 +3462,12 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3466,12 +3476,12 @@
         <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -3480,12 +3490,12 @@
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3494,12 +3504,12 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -3508,12 +3518,12 @@
         <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3522,12 +3532,12 @@
         <v>141</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -3536,12 +3546,12 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -3550,12 +3560,12 @@
         <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3564,12 +3574,12 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -3578,12 +3588,12 @@
         <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -3592,12 +3602,12 @@
         <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3606,12 +3616,12 @@
         <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -3620,12 +3630,12 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -3634,12 +3644,12 @@
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23">
         <v>6</v>
@@ -3648,12 +3658,12 @@
         <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -3662,12 +3672,12 @@
         <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3676,12 +3686,12 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -3690,12 +3700,12 @@
         <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3704,12 +3714,12 @@
         <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3718,12 +3728,12 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -3732,12 +3742,12 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -3746,12 +3756,12 @@
         <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3760,12 +3770,12 @@
         <v>190</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -3774,12 +3784,12 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -3788,12 +3798,12 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -3802,12 +3812,12 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -3816,12 +3826,12 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3830,12 +3840,12 @@
         <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3844,12 +3854,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38">
         <v>12</v>
@@ -3858,12 +3868,12 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -3872,12 +3882,12 @@
         <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -3886,12 +3896,12 @@
         <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -3900,12 +3910,12 @@
         <v>240</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B42">
         <v>11</v>
@@ -3914,12 +3924,12 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B43">
         <v>7</v>
@@ -3928,12 +3938,12 @@
         <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3942,12 +3952,12 @@
         <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -3956,12 +3966,12 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B46">
         <v>9</v>
@@ -3970,12 +3980,12 @@
         <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B47">
         <v>11</v>
@@ -3984,12 +3994,12 @@
         <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -3998,12 +4008,12 @@
         <v>210</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B49">
         <v>7</v>
@@ -4012,12 +4022,12 @@
         <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B50">
         <v>6</v>
@@ -4026,12 +4036,12 @@
         <v>160</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B51">
         <v>12</v>
@@ -4040,12 +4050,12 @@
         <v>802</v>
       </c>
       <c r="D51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -4054,12 +4064,12 @@
         <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B53">
         <v>6</v>
@@ -4068,12 +4078,12 @@
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B54">
         <v>7</v>
@@ -4082,12 +4092,12 @@
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -4096,12 +4106,12 @@
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -4110,12 +4120,12 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -4124,12 +4134,12 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -4138,12 +4148,12 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -4152,12 +4162,12 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -4166,12 +4176,12 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -4180,12 +4190,12 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -4194,12 +4204,12 @@
         <v>802</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -4210,7 +4220,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -4219,12 +4229,12 @@
         <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -4233,12 +4243,12 @@
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4249,7 +4259,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -4260,7 +4270,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -4271,7 +4281,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -4282,7 +4292,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -4291,12 +4301,12 @@
         <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B71">
         <v>5</v>
@@ -4305,12 +4315,12 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -4319,12 +4329,12 @@
         <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B73">
         <v>8</v>
@@ -4333,12 +4343,12 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -4347,12 +4357,12 @@
         <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -4361,12 +4371,12 @@
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B76">
         <v>11</v>
@@ -4375,12 +4385,12 @@
         <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B77">
         <v>7</v>
@@ -4389,12 +4399,12 @@
         <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -4403,12 +4413,12 @@
         <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -4417,12 +4427,12 @@
         <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -4431,12 +4441,12 @@
         <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4445,12 +4455,12 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -4459,12 +4469,12 @@
         <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B83">
         <v>12</v>
@@ -4473,12 +4483,12 @@
         <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B84">
         <v>9</v>
@@ -4487,12 +4497,12 @@
         <v>150</v>
       </c>
       <c r="D84" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B85">
         <v>8</v>
@@ -4501,12 +4511,12 @@
         <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -4515,12 +4525,12 @@
         <v>140</v>
       </c>
       <c r="D86" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -4529,12 +4539,12 @@
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -4543,12 +4553,12 @@
         <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -4557,12 +4567,12 @@
         <v>804</v>
       </c>
       <c r="D89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B90">
         <v>9</v>
@@ -4571,12 +4581,12 @@
         <v>813</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -4585,12 +4595,12 @@
         <v>800</v>
       </c>
       <c r="D91" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -4599,12 +4609,12 @@
         <v>801</v>
       </c>
       <c r="D92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -4613,12 +4623,12 @@
         <v>800</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -4627,12 +4637,12 @@
         <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95">
         <v>9</v>
@@ -4641,12 +4651,12 @@
         <v>814</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -4655,12 +4665,12 @@
         <v>800</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -4669,12 +4679,12 @@
         <v>801</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -4683,12 +4693,12 @@
         <v>800</v>
       </c>
       <c r="D98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -4697,12 +4707,12 @@
         <v>804</v>
       </c>
       <c r="D99" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -4711,12 +4721,12 @@
         <v>801</v>
       </c>
       <c r="D100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4725,12 +4735,12 @@
         <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -4739,12 +4749,12 @@
         <v>818</v>
       </c>
       <c r="D102" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -4753,12 +4763,12 @@
         <v>800</v>
       </c>
       <c r="D103" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -4767,12 +4777,12 @@
         <v>825</v>
       </c>
       <c r="D104" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B105">
         <v>9</v>
@@ -4781,12 +4791,12 @@
         <v>817</v>
       </c>
       <c r="D105" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -4795,12 +4805,12 @@
         <v>816</v>
       </c>
       <c r="D106" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -4809,12 +4819,12 @@
         <v>817</v>
       </c>
       <c r="D107" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B108">
         <v>4</v>
@@ -4823,12 +4833,12 @@
         <v>802</v>
       </c>
       <c r="D108" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -4837,12 +4847,12 @@
         <v>801</v>
       </c>
       <c r="D109" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -4851,12 +4861,12 @@
         <v>800</v>
       </c>
       <c r="D110" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -4865,12 +4875,12 @@
         <v>804</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -4879,12 +4889,12 @@
         <v>801</v>
       </c>
       <c r="D112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -4893,12 +4903,12 @@
         <v>800</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -4907,12 +4917,12 @@
         <v>804</v>
       </c>
       <c r="D114" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B115">
         <v>4</v>
@@ -4921,12 +4931,12 @@
         <v>802</v>
       </c>
       <c r="D115" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -4935,12 +4945,12 @@
         <v>801</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -4949,7 +4959,7 @@
         <v>800</v>
       </c>
       <c r="D117" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4972,34 +4982,34 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -5007,7 +5017,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -5015,7 +5025,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -5023,7 +5033,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -5031,40 +5041,40 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10">
         <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -5091,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5102,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" ht="14" spans="1:7">
@@ -5113,10 +5123,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -5125,10 +5135,10 @@
         <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5136,10 +5146,10 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5147,10 +5157,10 @@
         <v>102</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5158,10 +5168,10 @@
         <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5169,10 +5179,10 @@
         <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5180,10 +5190,10 @@
         <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5191,10 +5201,10 @@
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5202,10 +5212,10 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5213,10 +5223,10 @@
         <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5224,10 +5234,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5235,10 +5245,10 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5246,10 +5256,10 @@
         <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5257,10 +5267,10 @@
         <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5268,10 +5278,10 @@
         <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5279,10 +5289,10 @@
         <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5290,10 +5300,10 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5301,10 +5311,10 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5312,10 +5322,10 @@
         <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5323,10 +5333,10 @@
         <v>240</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5334,10 +5344,10 @@
         <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5345,10 +5355,10 @@
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5356,10 +5366,10 @@
         <v>270</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -5367,10 +5377,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5378,10 +5388,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5389,10 +5399,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5400,10 +5410,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5411,10 +5421,10 @@
         <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -5422,10 +5432,10 @@
         <v>342</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5433,13 +5443,13 @@
         <v>371</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5447,13 +5457,13 @@
         <v>380</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5461,13 +5471,13 @@
         <v>381</v>
       </c>
       <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" t="s">
         <v>149</v>
-      </c>
-      <c r="C34" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5475,13 +5485,13 @@
         <v>390</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5489,13 +5499,13 @@
         <v>391</v>
       </c>
       <c r="B36" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
         <v>152</v>
-      </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5503,13 +5513,13 @@
         <v>400</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -5517,10 +5527,10 @@
         <v>401</v>
       </c>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5528,10 +5538,10 @@
         <v>402</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -5539,10 +5549,10 @@
         <v>403</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -5550,10 +5560,10 @@
         <v>404</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -5561,10 +5571,10 @@
         <v>405</v>
       </c>
       <c r="B42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -5572,10 +5582,10 @@
         <v>420</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -5583,10 +5593,10 @@
         <v>421</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -5594,10 +5604,10 @@
         <v>422</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -5605,10 +5615,10 @@
         <v>600</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -5616,10 +5626,10 @@
         <v>601</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -5627,10 +5637,10 @@
         <v>602</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -5638,10 +5648,10 @@
         <v>603</v>
       </c>
       <c r="B49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -5649,10 +5659,10 @@
         <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -5660,10 +5670,10 @@
         <v>611</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C51" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -5671,10 +5681,10 @@
         <v>620</v>
       </c>
       <c r="B52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -5682,10 +5692,10 @@
         <v>621</v>
       </c>
       <c r="B53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -5693,10 +5703,10 @@
         <v>622</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -5704,10 +5714,10 @@
         <v>623</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -5715,10 +5725,10 @@
         <v>624</v>
       </c>
       <c r="B56" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -5726,10 +5736,10 @@
         <v>625</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -5737,10 +5747,10 @@
         <v>651</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -5748,10 +5758,10 @@
         <v>652</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -5759,10 +5769,10 @@
         <v>702</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -5770,10 +5780,10 @@
         <v>706</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -5781,10 +5791,10 @@
         <v>800</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -5792,10 +5802,10 @@
         <v>801</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -5803,10 +5813,10 @@
         <v>802</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -5814,10 +5824,10 @@
         <v>803</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -5825,10 +5835,10 @@
         <v>804</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -5836,10 +5846,10 @@
         <v>805</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -5847,10 +5857,10 @@
         <v>806</v>
       </c>
       <c r="B68" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -5858,10 +5868,10 @@
         <v>807</v>
       </c>
       <c r="B69" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C69" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -5869,10 +5879,10 @@
         <v>808</v>
       </c>
       <c r="B70" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -5880,10 +5890,10 @@
         <v>810</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C71" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -5891,10 +5901,10 @@
         <v>811</v>
       </c>
       <c r="B72" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -5902,10 +5912,10 @@
         <v>812</v>
       </c>
       <c r="B73" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C73" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -5913,10 +5923,10 @@
         <v>813</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -5924,10 +5934,10 @@
         <v>814</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -5935,10 +5945,10 @@
         <v>815</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C76" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -5946,10 +5956,10 @@
         <v>816</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -5957,10 +5967,10 @@
         <v>817</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -5968,10 +5978,10 @@
         <v>818</v>
       </c>
       <c r="B79" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -5979,10 +5989,10 @@
         <v>819</v>
       </c>
       <c r="B80" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -5990,10 +6000,10 @@
         <v>820</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C81" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -6001,10 +6011,10 @@
         <v>821</v>
       </c>
       <c r="B82" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -6012,10 +6022,10 @@
         <v>822</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C83" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -6023,10 +6033,10 @@
         <v>823</v>
       </c>
       <c r="B84" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C84" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -6034,10 +6044,10 @@
         <v>824</v>
       </c>
       <c r="B85" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C85" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -6045,10 +6055,10 @@
         <v>825</v>
       </c>
       <c r="B86" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C86" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -6056,10 +6066,10 @@
         <v>826</v>
       </c>
       <c r="B87" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C87" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -6067,10 +6077,10 @@
         <v>827</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C88" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -6078,10 +6088,10 @@
         <v>1000</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -6089,10 +6099,10 @@
         <v>1001</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -6100,10 +6110,10 @@
         <v>1010</v>
       </c>
       <c r="B91" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -6111,10 +6121,10 @@
         <v>1020</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C92" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -6122,10 +6132,10 @@
         <v>1060</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C93" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -6133,10 +6143,10 @@
         <v>1110</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C94" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -6144,10 +6154,10 @@
         <v>1120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -6155,13 +6165,13 @@
         <v>2000</v>
       </c>
       <c r="B96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C96" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D96" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -6169,10 +6179,10 @@
         <v>2001</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C97" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -6180,10 +6190,10 @@
         <v>2002</v>
       </c>
       <c r="B98" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C98" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -6191,10 +6201,10 @@
         <v>2003</v>
       </c>
       <c r="B99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -6202,10 +6212,10 @@
         <v>2004</v>
       </c>
       <c r="B100" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -6213,10 +6223,10 @@
         <v>2005</v>
       </c>
       <c r="B101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -6224,10 +6234,10 @@
         <v>2006</v>
       </c>
       <c r="B102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C102" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -6235,10 +6245,10 @@
         <v>2007</v>
       </c>
       <c r="B103" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C103" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -6246,13 +6256,13 @@
         <v>2010</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C104" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -6260,13 +6270,13 @@
         <v>2011</v>
       </c>
       <c r="B105" t="s">
+        <v>216</v>
+      </c>
+      <c r="C105" t="s">
+        <v>121</v>
+      </c>
+      <c r="D105" t="s">
         <v>215</v>
-      </c>
-      <c r="C105" t="s">
-        <v>120</v>
-      </c>
-      <c r="D105" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -6274,13 +6284,13 @@
         <v>2012</v>
       </c>
       <c r="B106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -6288,13 +6298,13 @@
         <v>2013</v>
       </c>
       <c r="B107" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" t="s">
+        <v>121</v>
+      </c>
+      <c r="D107" t="s">
         <v>215</v>
-      </c>
-      <c r="C107" t="s">
-        <v>120</v>
-      </c>
-      <c r="D107" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -6302,13 +6312,13 @@
         <v>2100</v>
       </c>
       <c r="B108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C108" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -6316,10 +6326,10 @@
         <v>2101</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C109" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -6327,10 +6337,10 @@
         <v>2102</v>
       </c>
       <c r="B110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C110" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -6338,10 +6348,10 @@
         <v>2103</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C111" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -6349,10 +6359,10 @@
         <v>2104</v>
       </c>
       <c r="B112" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C112" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -6360,10 +6370,10 @@
         <v>2105</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C113" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -6371,10 +6381,10 @@
         <v>2106</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C114" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -6382,13 +6392,13 @@
         <v>2200</v>
       </c>
       <c r="B115" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C115" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D115" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -6396,13 +6406,13 @@
         <v>2210</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D116" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="117" ht="29" customHeight="1" spans="1:4">
@@ -6410,13 +6420,13 @@
         <v>2220</v>
       </c>
       <c r="B117" t="s">
+        <v>227</v>
+      </c>
+      <c r="C117" t="s">
+        <v>121</v>
+      </c>
+      <c r="D117" t="s">
         <v>226</v>
-      </c>
-      <c r="C117" t="s">
-        <v>120</v>
-      </c>
-      <c r="D117" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -6424,13 +6434,13 @@
         <v>2300</v>
       </c>
       <c r="B118" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C118" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D118" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -6438,13 +6448,13 @@
         <v>2310</v>
       </c>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D119" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -6452,13 +6462,13 @@
         <v>2320</v>
       </c>
       <c r="B120" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C120" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D120" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -6466,13 +6476,13 @@
         <v>2330</v>
       </c>
       <c r="B121" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C121" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D121" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -6480,13 +6490,13 @@
         <v>2340</v>
       </c>
       <c r="B122" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C122" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D122" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -6494,13 +6504,13 @@
         <v>2400</v>
       </c>
       <c r="B123" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C123" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D123" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -6508,10 +6518,10 @@
         <v>3000</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C124" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -6519,10 +6529,10 @@
         <v>3010</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C125" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -6530,10 +6540,10 @@
         <v>3011</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -6541,10 +6551,10 @@
         <v>3040</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C127" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -6552,10 +6562,10 @@
         <v>3050</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -6563,10 +6573,10 @@
         <v>3051</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C129" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -6574,10 +6584,10 @@
         <v>3052</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C130" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -6585,10 +6595,10 @@
         <v>3053</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C131" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -6596,10 +6606,10 @@
         <v>3054</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C132" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -6607,10 +6617,10 @@
         <v>3070</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C133" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -6618,10 +6628,10 @@
         <v>3071</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C134" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -6629,10 +6639,10 @@
         <v>3072</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C135" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -6640,10 +6650,10 @@
         <v>3073</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C136" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -6651,10 +6661,10 @@
         <v>3090</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C137" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -6662,10 +6672,10 @@
         <v>3211</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C138" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -6673,10 +6683,10 @@
         <v>3230</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C139" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -6684,10 +6694,10 @@
         <v>5000</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C140" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -6695,10 +6705,10 @@
         <v>5001</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C141" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -6706,10 +6716,10 @@
         <v>5002</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C142" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -6717,10 +6727,10 @@
         <v>6001</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C143" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -6728,10 +6738,10 @@
         <v>6002</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C144" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -6739,10 +6749,10 @@
         <v>6100</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C145" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -6750,10 +6760,10 @@
         <v>6010</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -6761,10 +6771,10 @@
         <v>6011</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C147" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -6772,10 +6782,10 @@
         <v>6012</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C148" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -6783,10 +6793,10 @@
         <v>6020</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C149" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -6794,10 +6804,10 @@
         <v>6030</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -6805,10 +6815,10 @@
         <v>6040</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C151" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -6816,10 +6826,10 @@
         <v>6210</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C152" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -6827,10 +6837,10 @@
         <v>6220</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C153" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -6838,10 +6848,10 @@
         <v>6230</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C154" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -6849,10 +6859,10 @@
         <v>6240</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -6860,10 +6870,10 @@
         <v>6250</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -6871,10 +6881,10 @@
         <v>6260</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -6882,10 +6892,10 @@
         <v>6270</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C158" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -6893,10 +6903,10 @@
         <v>6280</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -6904,10 +6914,10 @@
         <v>6810</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C160" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -6915,10 +6925,10 @@
         <v>6820</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C161" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -6926,10 +6936,10 @@
         <v>6830</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C162" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -6937,10 +6947,10 @@
         <v>6840</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C163" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -6948,10 +6958,10 @@
         <v>6850</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C164" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -6959,10 +6969,10 @@
         <v>6860</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C165" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -6970,10 +6980,10 @@
         <v>6870</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C166" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -6981,10 +6991,10 @@
         <v>6880</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C167" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -6992,10 +7002,10 @@
         <v>6890</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C168" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="169" ht="130" spans="1:4">
@@ -7003,13 +7013,13 @@
         <v>12010</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C169" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -7017,13 +7027,13 @@
         <v>13010</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C170" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -7032,7 +7042,7 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -7040,10 +7050,10 @@
         <v>13110</v>
       </c>
       <c r="B172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C172" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -7051,10 +7061,10 @@
         <v>13120</v>
       </c>
       <c r="B173" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C173" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -7062,10 +7072,10 @@
         <v>13130</v>
       </c>
       <c r="B174" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C174" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -7073,10 +7083,10 @@
         <v>13140</v>
       </c>
       <c r="B175" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C175" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -7084,10 +7094,10 @@
         <v>13210</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C176" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -7095,10 +7105,10 @@
         <v>13220</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C177" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -7106,10 +7116,10 @@
         <v>13230</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C178" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -7117,10 +7127,10 @@
         <v>13240</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C179" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -7128,10 +7138,10 @@
         <v>13300</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C180" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -7139,10 +7149,10 @@
         <v>13301</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C181" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -7150,10 +7160,10 @@
         <v>13310</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C182" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -7161,10 +7171,10 @@
         <v>13320</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C183" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184" ht="26" spans="1:3">
@@ -7172,10 +7182,10 @@
         <v>13330</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C184" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -7183,10 +7193,10 @@
         <v>13400</v>
       </c>
       <c r="B185" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C185" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -7194,10 +7204,10 @@
         <v>13410</v>
       </c>
       <c r="B186" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C186" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -7205,10 +7215,10 @@
         <v>13420</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C187" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -7216,10 +7226,10 @@
         <v>13421</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C188" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -7227,10 +7237,10 @@
         <v>13430</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C189" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -7238,10 +7248,10 @@
         <v>14090</v>
       </c>
       <c r="B190" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C190" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -7249,10 +7259,10 @@
         <v>14110</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C191" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="192" ht="14" spans="1:7">
@@ -7260,13 +7270,13 @@
         <v>15010</v>
       </c>
       <c r="B192" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C192" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D192" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G192" s="1"/>
     </row>
@@ -7275,10 +7285,10 @@
         <v>16010</v>
       </c>
       <c r="B193" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C193" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D193" t="s">
         <v>13</v>
@@ -7290,10 +7300,10 @@
         <v>16020</v>
       </c>
       <c r="B194" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C194" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G194" s="1"/>
     </row>
@@ -7302,10 +7312,10 @@
         <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C195" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -7313,10 +7323,10 @@
         <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C196" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -7324,10 +7334,10 @@
         <v>16200</v>
       </c>
       <c r="B197" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C197" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -7335,10 +7345,10 @@
         <v>16210</v>
       </c>
       <c r="B198" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C198" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -7346,10 +7356,10 @@
         <v>16220</v>
       </c>
       <c r="B199" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C199" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -7357,10 +7367,10 @@
         <v>16230</v>
       </c>
       <c r="B200" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C200" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -7368,10 +7378,10 @@
         <v>16300</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C201" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -7379,10 +7389,10 @@
         <v>16310</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C202" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -7390,10 +7400,10 @@
         <v>16320</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C203" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -7401,10 +7411,10 @@
         <v>16400</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C204" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -7412,10 +7422,10 @@
         <v>16410</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C205" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -7423,13 +7433,13 @@
         <v>16800</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C206" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7437,13 +7447,13 @@
         <v>16801</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C207" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D207" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -7451,13 +7461,13 @@
         <v>16802</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C208" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D208" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -7465,13 +7475,13 @@
         <v>16803</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C209" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D209" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -7479,13 +7489,13 @@
         <v>16804</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C210" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D210" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -7493,13 +7503,13 @@
         <v>16805</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C211" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D211" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -7507,13 +7517,13 @@
         <v>16806</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C212" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D212" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -7521,10 +7531,10 @@
         <v>17010</v>
       </c>
       <c r="B213" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C213" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -7532,13 +7542,13 @@
         <v>18010</v>
       </c>
       <c r="B214" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C214" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D214" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -7546,10 +7556,10 @@
         <v>18020</v>
       </c>
       <c r="B215" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C215" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -7557,10 +7567,10 @@
         <v>18100</v>
       </c>
       <c r="B216" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C216" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -7568,10 +7578,10 @@
         <v>18110</v>
       </c>
       <c r="B217" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C217" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -7579,10 +7589,10 @@
         <v>18120</v>
       </c>
       <c r="B218" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C218" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -7590,10 +7600,10 @@
         <v>18130</v>
       </c>
       <c r="B219" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C219" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -7601,10 +7611,10 @@
         <v>18200</v>
       </c>
       <c r="B220" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C220" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -7612,10 +7622,10 @@
         <v>18210</v>
       </c>
       <c r="B221" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C221" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -7623,10 +7633,10 @@
         <v>18220</v>
       </c>
       <c r="B222" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C222" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -7634,10 +7644,10 @@
         <v>18230</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C223" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -7645,10 +7655,10 @@
         <v>18300</v>
       </c>
       <c r="B224" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C224" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -7656,10 +7666,10 @@
         <v>18310</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C225" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -7667,10 +7677,10 @@
         <v>18320</v>
       </c>
       <c r="B226" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C226" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -7678,10 +7688,10 @@
         <v>18340</v>
       </c>
       <c r="B227" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C227" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -7689,10 +7699,10 @@
         <v>18400</v>
       </c>
       <c r="B228" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C228" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -7700,10 +7710,10 @@
         <v>18410</v>
       </c>
       <c r="B229" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C229" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -7711,10 +7721,10 @@
         <v>18420</v>
       </c>
       <c r="B230" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C230" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -7722,10 +7732,10 @@
         <v>18430</v>
       </c>
       <c r="B231" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C231" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -7733,10 +7743,10 @@
         <v>18440</v>
       </c>
       <c r="B232" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C232" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -7744,10 +7754,10 @@
         <v>18450</v>
       </c>
       <c r="B233" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C233" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -7755,10 +7765,10 @@
         <v>18500</v>
       </c>
       <c r="B234" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C234" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -7766,10 +7776,10 @@
         <v>18510</v>
       </c>
       <c r="B235" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C235" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -7777,10 +7787,10 @@
         <v>18800</v>
       </c>
       <c r="B236" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C236" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -7788,10 +7798,10 @@
         <v>18801</v>
       </c>
       <c r="B237" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C237" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -7799,10 +7809,10 @@
         <v>18802</v>
       </c>
       <c r="B238" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C238" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -7810,10 +7820,10 @@
         <v>18803</v>
       </c>
       <c r="B239" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C239" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -7821,10 +7831,10 @@
         <v>18804</v>
       </c>
       <c r="B240" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C240" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -7832,10 +7842,10 @@
         <v>18805</v>
       </c>
       <c r="B241" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C241" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -7843,10 +7853,10 @@
         <v>18806</v>
       </c>
       <c r="B242" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C242" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -7854,10 +7864,10 @@
         <v>18811</v>
       </c>
       <c r="B243" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C243" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -7865,10 +7875,10 @@
         <v>18812</v>
       </c>
       <c r="B244" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C244" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="245" ht="14" spans="1:7">
@@ -7876,13 +7886,13 @@
         <v>19000</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C245" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D245" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G245" s="1"/>
     </row>
@@ -7891,10 +7901,10 @@
         <v>19001</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C246" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -7902,10 +7912,10 @@
         <v>19002</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C247" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -7913,10 +7923,10 @@
         <v>19003</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C248" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -7924,10 +7934,10 @@
         <v>19004</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C249" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -7935,10 +7945,10 @@
         <v>19005</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C250" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -7946,10 +7956,10 @@
         <v>19006</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C251" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -7960,7 +7970,7 @@
         <v>362</v>
       </c>
       <c r="C252" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -7971,7 +7981,7 @@
         <v>363</v>
       </c>
       <c r="C253" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -7979,10 +7989,10 @@
         <v>19009</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C254" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -7993,7 +8003,7 @@
         <v>364</v>
       </c>
       <c r="C255" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -8004,7 +8014,7 @@
         <v>365</v>
       </c>
       <c r="C256" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -8015,7 +8025,7 @@
         <v>366</v>
       </c>
       <c r="C257" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -8026,7 +8036,7 @@
         <v>367</v>
       </c>
       <c r="C258" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -8037,7 +8047,7 @@
         <v>368</v>
       </c>
       <c r="C259" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -8048,7 +8058,7 @@
         <v>369</v>
       </c>
       <c r="C260" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -8059,7 +8069,7 @@
         <v>370</v>
       </c>
       <c r="C261" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -8070,7 +8080,7 @@
         <v>371</v>
       </c>
       <c r="C262" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -8081,7 +8091,7 @@
         <v>372</v>
       </c>
       <c r="C263" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -8092,7 +8102,7 @@
         <v>373</v>
       </c>
       <c r="C264" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -8103,7 +8113,7 @@
         <v>374</v>
       </c>
       <c r="C265" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -8114,7 +8124,7 @@
         <v>375</v>
       </c>
       <c r="C266" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -8125,7 +8135,7 @@
         <v>376</v>
       </c>
       <c r="C267" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -8136,7 +8146,7 @@
         <v>377</v>
       </c>
       <c r="C268" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -8147,7 +8157,7 @@
         <v>378</v>
       </c>
       <c r="C269" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -8158,7 +8168,7 @@
         <v>379</v>
       </c>
       <c r="C270" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -8169,7 +8179,7 @@
         <v>380</v>
       </c>
       <c r="C271" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="272" ht="26" spans="1:3">
@@ -8180,7 +8190,7 @@
         <v>381</v>
       </c>
       <c r="C272" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -8191,7 +8201,7 @@
         <v>382</v>
       </c>
       <c r="C273" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -8202,7 +8212,7 @@
         <v>383</v>
       </c>
       <c r="C274" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -8213,7 +8223,7 @@
         <v>384</v>
       </c>
       <c r="C275" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -8224,7 +8234,7 @@
         <v>385</v>
       </c>
       <c r="C276" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -8235,7 +8245,7 @@
         <v>386</v>
       </c>
       <c r="C277" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -8246,7 +8256,7 @@
         <v>387</v>
       </c>
       <c r="C278" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -8257,7 +8267,7 @@
         <v>388</v>
       </c>
       <c r="C279" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -8268,7 +8278,7 @@
         <v>389</v>
       </c>
       <c r="C280" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -8279,7 +8289,7 @@
         <v>390</v>
       </c>
       <c r="C281" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -8290,7 +8300,7 @@
         <v>391</v>
       </c>
       <c r="C282" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -8301,7 +8311,7 @@
         <v>377</v>
       </c>
       <c r="C283" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -8312,7 +8322,7 @@
         <v>392</v>
       </c>
       <c r="C284" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -8323,7 +8333,7 @@
         <v>393</v>
       </c>
       <c r="C285" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -8334,7 +8344,7 @@
         <v>394</v>
       </c>
       <c r="C286" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -8345,7 +8355,7 @@
         <v>395</v>
       </c>
       <c r="C287" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -8356,7 +8366,7 @@
         <v>396</v>
       </c>
       <c r="C288" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -8367,7 +8377,7 @@
         <v>397</v>
       </c>
       <c r="C289" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="290" ht="14" spans="1:7">
@@ -8378,7 +8388,7 @@
         <v>398</v>
       </c>
       <c r="C290" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D290" t="s">
         <v>399</v>
@@ -8393,7 +8403,7 @@
         <v>400</v>
       </c>
       <c r="C291" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G291" s="1"/>
     </row>
@@ -8405,7 +8415,7 @@
         <v>365</v>
       </c>
       <c r="C292" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G292" s="1"/>
     </row>
@@ -8417,7 +8427,7 @@
         <v>401</v>
       </c>
       <c r="C293" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G293" s="1"/>
     </row>
@@ -8429,7 +8439,7 @@
         <v>402</v>
       </c>
       <c r="C294" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G294" s="1"/>
     </row>
@@ -8441,7 +8451,7 @@
         <v>403</v>
       </c>
       <c r="C295" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G295" s="1"/>
     </row>
@@ -8453,7 +8463,7 @@
         <v>404</v>
       </c>
       <c r="C296" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G296" s="1"/>
     </row>
@@ -8465,7 +8475,7 @@
         <v>405</v>
       </c>
       <c r="C297" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G297" s="1"/>
     </row>
@@ -8477,7 +8487,7 @@
         <v>406</v>
       </c>
       <c r="C298" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G298" s="1"/>
     </row>
@@ -8489,7 +8499,7 @@
         <v>407</v>
       </c>
       <c r="C299" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D299" t="s">
         <v>408</v>
@@ -8503,7 +8513,7 @@
         <v>409</v>
       </c>
       <c r="C300" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -8514,7 +8524,7 @@
         <v>410</v>
       </c>
       <c r="C301" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -8525,7 +8535,7 @@
         <v>411</v>
       </c>
       <c r="C302" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -8536,7 +8546,7 @@
         <v>412</v>
       </c>
       <c r="C303" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -8544,10 +8554,10 @@
         <v>19710</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="C304" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -8555,10 +8565,10 @@
         <v>19720</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C305" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -8566,10 +8576,10 @@
         <v>19730</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C306" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -8577,10 +8587,10 @@
         <v>19740</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C307" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -8588,10 +8598,10 @@
         <v>19800</v>
       </c>
       <c r="B308" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C308" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -8599,10 +8609,10 @@
         <v>19810</v>
       </c>
       <c r="B309" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C309" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -8610,13 +8620,13 @@
         <v>20010</v>
       </c>
       <c r="B310" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C310" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D310" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -8624,10 +8634,10 @@
         <v>20020</v>
       </c>
       <c r="B311" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C311" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -8635,10 +8645,10 @@
         <v>20030</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C312" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -8646,10 +8656,10 @@
         <v>20040</v>
       </c>
       <c r="B313" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C313" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -8657,10 +8667,10 @@
         <v>20050</v>
       </c>
       <c r="B314" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C314" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -8668,10 +8678,10 @@
         <v>20100</v>
       </c>
       <c r="B315" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C315" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -8679,10 +8689,10 @@
         <v>20110</v>
       </c>
       <c r="B316" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C316" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -8690,10 +8700,10 @@
         <v>20120</v>
       </c>
       <c r="B317" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C317" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -8701,10 +8711,10 @@
         <v>20200</v>
       </c>
       <c r="B318" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C318" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -8712,10 +8722,10 @@
         <v>20201</v>
       </c>
       <c r="B319" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C319" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -8723,10 +8733,10 @@
         <v>20210</v>
       </c>
       <c r="B320" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C320" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -8734,10 +8744,10 @@
         <v>20220</v>
       </c>
       <c r="B321" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C321" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -8745,10 +8755,10 @@
         <v>20230</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C322" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -8756,10 +8766,10 @@
         <v>20240</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C323" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -8767,10 +8777,10 @@
         <v>20250</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C324" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -8778,10 +8788,10 @@
         <v>20260</v>
       </c>
       <c r="B325" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C325" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -8789,10 +8799,10 @@
         <v>20270</v>
       </c>
       <c r="B326" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C326" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -8800,10 +8810,10 @@
         <v>20280</v>
       </c>
       <c r="B327" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C327" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -8811,10 +8821,10 @@
         <v>20290</v>
       </c>
       <c r="B328" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C328" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -8822,10 +8832,10 @@
         <v>20300</v>
       </c>
       <c r="B329" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C329" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -8833,10 +8843,10 @@
         <v>20310</v>
       </c>
       <c r="B330" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C330" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -8844,10 +8854,10 @@
         <v>20320</v>
       </c>
       <c r="B331" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C331" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -8855,10 +8865,10 @@
         <v>20330</v>
       </c>
       <c r="B332" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C332" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -8866,10 +8876,10 @@
         <v>20340</v>
       </c>
       <c r="B333" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C333" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -8877,10 +8887,10 @@
         <v>20350</v>
       </c>
       <c r="B334" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C334" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -8888,10 +8898,10 @@
         <v>23010</v>
       </c>
       <c r="B335" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C335" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -8899,10 +8909,10 @@
         <v>23020</v>
       </c>
       <c r="B336" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C336" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -8910,10 +8920,10 @@
         <v>23030</v>
       </c>
       <c r="B337" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C337" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -8921,10 +8931,10 @@
         <v>23031</v>
       </c>
       <c r="B338" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C338" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -8932,10 +8942,10 @@
         <v>23032</v>
       </c>
       <c r="B339" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C339" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -8943,10 +8953,10 @@
         <v>23040</v>
       </c>
       <c r="B340" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C340" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -8954,10 +8964,10 @@
         <v>24010</v>
       </c>
       <c r="B341" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C341" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -8965,10 +8975,10 @@
         <v>24020</v>
       </c>
       <c r="B342" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C342" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -8976,10 +8986,10 @@
         <v>24030</v>
       </c>
       <c r="B343" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C343" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -8987,10 +8997,10 @@
         <v>24040</v>
       </c>
       <c r="B344" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C344" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -8998,10 +9008,10 @@
         <v>24110</v>
       </c>
       <c r="B345" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C345" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -9009,10 +9019,10 @@
         <v>24111</v>
       </c>
       <c r="B346" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C346" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -9020,10 +9030,10 @@
         <v>24112</v>
       </c>
       <c r="B347" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C347" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -9031,10 +9041,10 @@
         <v>24113</v>
       </c>
       <c r="B348" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C348" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -9042,10 +9052,10 @@
         <v>24114</v>
       </c>
       <c r="B349" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C349" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -9053,10 +9063,10 @@
         <v>24115</v>
       </c>
       <c r="B350" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C350" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -9064,10 +9074,10 @@
         <v>24116</v>
       </c>
       <c r="B351" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C351" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -9075,10 +9085,10 @@
         <v>24117</v>
       </c>
       <c r="B352" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C352" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -9086,10 +9096,10 @@
         <v>24118</v>
       </c>
       <c r="B353" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C353" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -9097,10 +9107,10 @@
         <v>24119</v>
       </c>
       <c r="B354" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C354" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -9108,10 +9118,10 @@
         <v>24120</v>
       </c>
       <c r="B355" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C355" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -9119,10 +9129,10 @@
         <v>24121</v>
       </c>
       <c r="B356" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C356" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -9130,10 +9140,10 @@
         <v>24122</v>
       </c>
       <c r="B357" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C357" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -9141,10 +9151,10 @@
         <v>30000</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C358" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -9152,10 +9162,10 @@
         <v>30010</v>
       </c>
       <c r="B359" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C359" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -9163,10 +9173,10 @@
         <v>30020</v>
       </c>
       <c r="B360" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C360" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -9174,10 +9184,10 @@
         <v>30030</v>
       </c>
       <c r="B361" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C361" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -9185,10 +9195,10 @@
         <v>30040</v>
       </c>
       <c r="B362" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C362" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -9196,10 +9206,10 @@
         <v>31010</v>
       </c>
       <c r="B363" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C363" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -9207,10 +9217,10 @@
         <v>31020</v>
       </c>
       <c r="B364" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C364" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -9218,13 +9228,13 @@
         <v>102000</v>
       </c>
       <c r="B365" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C365" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D365" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -9232,10 +9242,10 @@
         <v>102010</v>
       </c>
       <c r="B366" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C366" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -9246,7 +9256,7 @@
         <v>398</v>
       </c>
       <c r="C367" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -9254,10 +9264,10 @@
         <v>102030</v>
       </c>
       <c r="B368" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C368" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9265,13 +9275,13 @@
         <v>113000</v>
       </c>
       <c r="B369" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C369" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D369" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -9279,10 +9289,10 @@
         <v>113010</v>
       </c>
       <c r="B370" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C370" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -9290,10 +9300,10 @@
         <v>113020</v>
       </c>
       <c r="B371" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C371" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -9301,10 +9311,10 @@
         <v>113030</v>
       </c>
       <c r="B372" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C372" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -9312,10 +9322,10 @@
         <v>113040</v>
       </c>
       <c r="B373" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C373" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9323,13 +9333,13 @@
         <v>121010</v>
       </c>
       <c r="B374" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C374" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D374" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -9337,10 +9347,10 @@
         <v>121011</v>
       </c>
       <c r="B375" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C375" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -9348,10 +9358,10 @@
         <v>121012</v>
       </c>
       <c r="B376" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C376" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -9359,10 +9369,10 @@
         <v>121013</v>
       </c>
       <c r="B377" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C377" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -9370,10 +9380,10 @@
         <v>121014</v>
       </c>
       <c r="B378" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C378" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -9381,10 +9391,10 @@
         <v>121015</v>
       </c>
       <c r="B379" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C379" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -9392,10 +9402,10 @@
         <v>121016</v>
       </c>
       <c r="B380" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C380" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -9403,10 +9413,10 @@
         <v>121017</v>
       </c>
       <c r="B381" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C381" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -9414,10 +9424,10 @@
         <v>121018</v>
       </c>
       <c r="B382" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C382" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -9425,10 +9435,10 @@
         <v>121019</v>
       </c>
       <c r="B383" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C383" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -9436,10 +9446,10 @@
         <v>121020</v>
       </c>
       <c r="B384" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C384" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -9447,10 +9457,10 @@
         <v>121030</v>
       </c>
       <c r="B385" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C385" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="766"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="766" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -1515,10 +1515,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1543,6 +1543,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -1550,14 +1557,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1565,13 +1573,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1585,9 +1586,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1601,14 +1648,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -1618,29 +1657,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1655,34 +1672,17 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1695,19 +1695,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1719,37 +1731,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1773,7 +1767,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1785,37 +1833,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1827,19 +1845,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1851,31 +1875,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1906,11 +1906,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1939,11 +1937,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1951,8 +1955,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1972,17 +1976,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1994,19 +1994,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2015,103 +2015,97 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2120,19 +2114,25 @@
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -999,7 +999,7 @@
     <t>x2</t>
   </si>
   <si>
-    <t>x4</t>
+    <t>x3</t>
   </si>
   <si>
     <t>マニュアル</t>
@@ -1515,10 +1515,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1542,8 +1542,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1557,22 +1579,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1586,6 +1593,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1602,15 +1610,30 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1641,7 +1664,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1650,30 +1673,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1695,25 +1695,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1725,31 +1755,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1767,7 +1785,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1779,25 +1803,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1809,43 +1857,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1857,25 +1875,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1886,6 +1886,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1907,17 +1916,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1937,6 +1937,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1948,15 +1968,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1975,17 +1986,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1994,145 +1994,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="766" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="19200" windowHeight="8270" tabRatio="766"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -1515,10 +1515,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1543,6 +1543,14 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1550,22 +1558,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1585,9 +1603,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1603,7 +1635,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1611,15 +1643,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1627,13 +1651,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1647,9 +1664,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1657,30 +1680,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1695,19 +1695,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1719,13 +1755,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1737,61 +1779,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1809,7 +1803,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1821,61 +1875,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1898,6 +1898,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1913,11 +1937,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1939,50 +1969,20 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1994,16 +1994,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2012,127 +2012,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="528">
   <si>
     <t>Id</t>
   </si>
@@ -1463,6 +1463,9 @@
     <t>収集率</t>
   </si>
   <si>
+    <t>スキルScope</t>
+  </si>
+  <si>
     <t>共通</t>
   </si>
   <si>
@@ -1511,6 +1514,9 @@
     <t>アーティファクトを入手し評価値が\d減少しました</t>
   </si>
   <si>
+    <t>全滅してしまった…</t>
+  </si>
+  <si>
     <t>エインフェリアを召喚しますか？</t>
   </si>
   <si>
@@ -1535,6 +1541,15 @@
     <t>ロード</t>
   </si>
   <si>
+    <t>\dを入手！</t>
+  </si>
+  <si>
+    <t>\dを会得！</t>
+  </si>
+  <si>
+    <t>神格等級アップ</t>
+  </si>
+  <si>
     <t>FileList</t>
   </si>
   <si>
@@ -1587,6 +1602,15 @@
   </si>
   <si>
     <t>ヒロインは派遣できません！</t>
+  </si>
+  <si>
+    <t>課題を達成！</t>
+  </si>
+  <si>
+    <t>MissionClear</t>
+  </si>
+  <si>
+    <t>を獲得！</t>
   </si>
 </sst>
 </file>
@@ -1594,10 +1618,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1621,8 +1645,32 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1630,6 +1678,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1650,14 +1705,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -1667,7 +1714,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1675,7 +1722,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1695,29 +1742,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -1727,18 +1751,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1752,6 +1768,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -1759,7 +1783,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1774,7 +1798,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1786,13 +1810,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1804,13 +1852,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1822,13 +1864,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1846,13 +1894,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1864,25 +1942,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1894,67 +1978,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1983,17 +2007,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2022,15 +2040,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2055,6 +2064,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2073,145 +2097,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -9385,7 +9409,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -9416,161 +9440,158 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" customFormat="1" spans="1:4">
       <c r="A3">
-        <v>1000</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>600</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
       </c>
       <c r="C3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:3">
       <c r="A4">
-        <v>2000</v>
+        <v>601</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" customFormat="1" spans="1:3">
       <c r="A5">
-        <v>2001</v>
+        <v>602</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" customFormat="1" spans="1:3">
       <c r="A6">
-        <v>2002</v>
+        <v>603</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" customFormat="1" spans="1:3">
       <c r="A7">
-        <v>2003</v>
+        <v>606</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" customFormat="1" spans="1:3">
       <c r="A8">
-        <v>2004</v>
+        <v>611</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" customFormat="1" spans="1:3">
       <c r="A9">
-        <v>2005</v>
+        <v>620</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" customFormat="1" spans="1:3">
       <c r="A10">
-        <v>2006</v>
+        <v>621</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" customFormat="1" spans="1:3">
       <c r="A11">
-        <v>2007</v>
+        <v>622</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" customFormat="1" spans="1:3">
       <c r="A12">
-        <v>2100</v>
+        <v>623</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
         <v>104</v>
       </c>
-      <c r="D12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+    </row>
+    <row r="13" customFormat="1" spans="1:3">
       <c r="A13">
-        <v>2101</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>202</v>
+        <v>624</v>
+      </c>
+      <c r="B13" t="s">
+        <v>156</v>
       </c>
       <c r="C13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" customFormat="1" spans="1:3">
       <c r="A14">
-        <v>2102</v>
+        <v>625</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" customFormat="1" spans="1:3">
       <c r="A15">
-        <v>2103</v>
+        <v>651</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" customFormat="1" spans="1:3">
       <c r="A16">
-        <v>2104</v>
+        <v>652</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
         <v>104</v>
@@ -9578,172 +9599,148 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2105</v>
+        <v>1000</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18">
-        <v>2106</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>207</v>
+        <v>2000</v>
+      </c>
+      <c r="B18" t="s">
+        <v>188</v>
       </c>
       <c r="C18" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
-        <v>2200</v>
+        <v>2001</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s">
         <v>104</v>
       </c>
-      <c r="D19" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
-        <v>2210</v>
+        <v>2002</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s">
         <v>104</v>
       </c>
-      <c r="D20" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" ht="29" customHeight="1" spans="1:4">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
-        <v>2220</v>
+        <v>2003</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="D21" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
-        <v>2300</v>
+        <v>2004</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
         <v>104</v>
       </c>
-      <c r="D22" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
-        <v>2310</v>
+        <v>2005</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
-        <v>2320</v>
+        <v>2006</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
         <v>104</v>
       </c>
-      <c r="D24" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
-        <v>2330</v>
+        <v>2007</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="C25" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>2340</v>
+        <v>2100</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C26" t="s">
         <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
-        <v>2400</v>
-      </c>
-      <c r="B27" t="s">
-        <v>216</v>
+        <v>2101</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="C27" t="s">
         <v>104</v>
       </c>
-      <c r="D27" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
-        <v>3010</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>328</v>
+        <v>2102</v>
+      </c>
+      <c r="B28" t="s">
+        <v>203</v>
       </c>
       <c r="C28" t="s">
         <v>104</v>
-      </c>
-      <c r="D28" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>3020</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>329</v>
+        <v>2103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>204</v>
       </c>
       <c r="C29" t="s">
         <v>104</v>
@@ -9751,10 +9748,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>3040</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>220</v>
+        <v>2104</v>
+      </c>
+      <c r="B30" t="s">
+        <v>205</v>
       </c>
       <c r="C30" t="s">
         <v>104</v>
@@ -9762,10 +9759,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>3050</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>36</v>
+        <v>2105</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="C31" t="s">
         <v>104</v>
@@ -9773,145 +9770,172 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>3051</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>221</v>
+        <v>2106</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:4">
       <c r="A33">
-        <v>3052</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>222</v>
+        <v>2200</v>
+      </c>
+      <c r="B33" t="s">
+        <v>208</v>
       </c>
       <c r="C33" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
-        <v>3100</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>479</v>
+        <v>2210</v>
+      </c>
+      <c r="B34" t="s">
+        <v>188</v>
       </c>
       <c r="C34" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" ht="29" customHeight="1" spans="1:4">
       <c r="A35">
-        <v>3110</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>480</v>
+        <v>2220</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
       </c>
       <c r="C35" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36">
-        <v>3120</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>481</v>
+        <v>2300</v>
+      </c>
+      <c r="B36" t="s">
+        <v>211</v>
       </c>
       <c r="C36" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37">
-        <v>3130</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>482</v>
+        <v>2310</v>
+      </c>
+      <c r="B37" t="s">
+        <v>212</v>
       </c>
       <c r="C37" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38">
-        <v>3200</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>483</v>
+        <v>2320</v>
+      </c>
+      <c r="B38" t="s">
+        <v>213</v>
       </c>
       <c r="C38" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:3">
+      <c r="D38" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39">
-        <v>3210</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>484</v>
+        <v>2330</v>
+      </c>
+      <c r="B39" t="s">
+        <v>214</v>
       </c>
       <c r="C39" t="s">
         <v>104</v>
+      </c>
+      <c r="D39" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>6001</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>233</v>
+        <v>2340</v>
+      </c>
+      <c r="B40" t="s">
+        <v>215</v>
       </c>
       <c r="C40" t="s">
         <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41">
-        <v>6002</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>234</v>
+        <v>2400</v>
+      </c>
+      <c r="B41" t="s">
+        <v>216</v>
       </c>
       <c r="C41" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42">
-        <v>6100</v>
+        <v>3010</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>104</v>
+        <v>328</v>
       </c>
       <c r="C42" t="s">
-        <v>235</v>
+        <v>104</v>
+      </c>
+      <c r="D42" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>6010</v>
+        <v>3020</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>236</v>
+        <v>329</v>
       </c>
       <c r="C43" t="s">
-        <v>237</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>6011</v>
+        <v>3040</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
@@ -9919,10 +9943,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>6012</v>
+        <v>3050</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>239</v>
+        <v>36</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
@@ -9930,142 +9954,145 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>6020</v>
+        <v>3051</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>6030</v>
+        <v>3052</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>6040</v>
+        <v>3100</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>244</v>
+        <v>480</v>
       </c>
       <c r="C48" t="s">
-        <v>245</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>6210</v>
+        <v>3110</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>246</v>
+        <v>481</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>6220</v>
+        <v>3120</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>248</v>
+        <v>482</v>
       </c>
       <c r="C50" t="s">
-        <v>249</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>6230</v>
+        <v>3130</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>250</v>
+        <v>483</v>
       </c>
       <c r="C51" t="s">
-        <v>251</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>6240</v>
+        <v>3200</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>252</v>
+        <v>484</v>
       </c>
       <c r="C52" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:3">
       <c r="A53">
-        <v>6250</v>
+        <v>3210</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>254</v>
+        <v>485</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54">
-        <v>6260</v>
+        <v>6001</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="C54" t="s">
-        <v>257</v>
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6270</v>
+        <v>6002</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6280</v>
+        <v>6100</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6810</v>
+        <v>6010</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="C57" t="s">
-        <v>104</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6820</v>
+        <v>6011</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="C58" t="s">
         <v>104</v>
@@ -10073,10 +10100,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>6830</v>
+        <v>6012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="C59" t="s">
         <v>104</v>
@@ -10084,265 +10111,255 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>6840</v>
+        <v>6020</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>6850</v>
+        <v>6030</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>6860</v>
+        <v>6040</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>6870</v>
+        <v>6210</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>6880</v>
+        <v>6220</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>6890</v>
+        <v>6230</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
-        <v>10010</v>
+        <v>6240</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="67" ht="26" spans="1:3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
-        <v>10100</v>
+        <v>6250</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>487</v>
+        <v>254</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>255</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>10101</v>
+        <v>6260</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>488</v>
+        <v>256</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>10110</v>
+        <v>6270</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>489</v>
+        <v>258</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" customFormat="1" spans="1:3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
-        <v>10120</v>
+        <v>6280</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>490</v>
+        <v>260</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" customFormat="1" spans="1:3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
-        <v>10130</v>
+        <v>6810</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>491</v>
+        <v>262</v>
       </c>
       <c r="C71" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="72" customFormat="1" spans="1:3">
+    <row r="72" spans="1:3">
       <c r="A72">
-        <v>10140</v>
+        <v>6820</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>492</v>
+        <v>263</v>
       </c>
       <c r="C72" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="73" customFormat="1" spans="1:3">
+    <row r="73" spans="1:3">
       <c r="A73">
-        <v>10141</v>
+        <v>6830</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>493</v>
+        <v>264</v>
       </c>
       <c r="C73" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="74" customFormat="1" spans="1:4">
+    <row r="74" spans="1:3">
       <c r="A74">
-        <v>11010</v>
+        <v>6840</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>494</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
         <v>104</v>
       </c>
-      <c r="D74" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" spans="1:3">
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
-        <v>11011</v>
+        <v>6850</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>495</v>
+        <v>266</v>
       </c>
       <c r="C75" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="76" customFormat="1" spans="1:3">
+    <row r="76" spans="1:3">
       <c r="A76">
-        <v>11020</v>
+        <v>6860</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>496</v>
+        <v>267</v>
       </c>
       <c r="C76" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" ht="130" spans="1:4">
+    <row r="77" spans="1:3">
       <c r="A77">
-        <v>12010</v>
+        <v>6870</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C77" t="s">
         <v>104</v>
       </c>
-      <c r="D77" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
-        <v>13010</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>273</v>
+        <v>6880</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="C78" t="s">
         <v>104</v>
-      </c>
-      <c r="D78" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>13020</v>
-      </c>
-      <c r="B79" s="3"/>
+        <v>6890</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="C79" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:4">
       <c r="A80">
-        <v>13110</v>
-      </c>
-      <c r="B80" t="s">
-        <v>275</v>
+        <v>10010</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="C80" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="D80" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
-        <v>13210</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>279</v>
+        <v>10100</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>488</v>
       </c>
       <c r="C81" t="s">
         <v>104</v>
-      </c>
-      <c r="D81" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>13220</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>280</v>
+        <v>10101</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="C82" t="s">
         <v>104</v>
@@ -10350,46 +10367,43 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>13230</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>281</v>
+        <v>10110</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="C83" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" customFormat="1" spans="1:3">
       <c r="A84">
-        <v>13240</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>282</v>
+        <v>10120</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="C84" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" customFormat="1" spans="1:3">
       <c r="A85">
-        <v>14010</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>497</v>
+        <v>10121</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="C85" t="s">
         <v>104</v>
       </c>
-      <c r="D85" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+    </row>
+    <row r="86" customFormat="1" spans="1:3">
       <c r="A86">
-        <v>14020</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>217</v>
+        <v>10130</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="C86" t="s">
         <v>104</v>
@@ -10397,10 +10411,10 @@
     </row>
     <row r="87" customFormat="1" spans="1:3">
       <c r="A87">
-        <v>14021</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>498</v>
+        <v>10140</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="C87" t="s">
         <v>104</v>
@@ -10408,10 +10422,10 @@
     </row>
     <row r="88" customFormat="1" spans="1:3">
       <c r="A88">
-        <v>14030</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>321</v>
+        <v>10141</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>494</v>
       </c>
       <c r="C88" t="s">
         <v>104</v>
@@ -10419,32 +10433,35 @@
     </row>
     <row r="89" customFormat="1" spans="1:3">
       <c r="A89">
-        <v>14040</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>324</v>
+        <v>10150</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="C89" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="90" customFormat="1" spans="1:3">
+    <row r="90" customFormat="1" spans="1:4">
       <c r="A90">
-        <v>14050</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>325</v>
+        <v>11010</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="C90" t="s">
         <v>104</v>
+      </c>
+      <c r="D90" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:3">
       <c r="A91">
-        <v>14060</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>317</v>
+        <v>11011</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>497</v>
       </c>
       <c r="C91" t="s">
         <v>104</v>
@@ -10452,80 +10469,83 @@
     </row>
     <row r="92" customFormat="1" spans="1:3">
       <c r="A92">
-        <v>14070</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>112</v>
+        <v>11020</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="C92" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="93" ht="14" spans="1:7">
+    <row r="93" ht="130" spans="1:4">
       <c r="A93">
-        <v>19000</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>339</v>
+        <v>12010</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="C93" t="s">
         <v>104</v>
       </c>
       <c r="D93" t="s">
-        <v>499</v>
-      </c>
-      <c r="G93" s="4"/>
-    </row>
-    <row r="94" spans="1:3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94">
-        <v>19001</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>341</v>
+        <v>13010</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="C94" t="s">
         <v>104</v>
+      </c>
+      <c r="D94" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>19002</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>342</v>
-      </c>
+        <v>13020</v>
+      </c>
+      <c r="B95" s="3"/>
       <c r="C95" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>19003</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>343</v>
+        <v>13110</v>
+      </c>
+      <c r="B96" t="s">
+        <v>275</v>
       </c>
       <c r="C96" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:4">
       <c r="A97">
-        <v>19004</v>
+        <v>13210</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>344</v>
+        <v>279</v>
       </c>
       <c r="C97" t="s">
         <v>104</v>
+      </c>
+      <c r="D97" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>19005</v>
+        <v>13220</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>345</v>
+        <v>280</v>
       </c>
       <c r="C98" t="s">
         <v>104</v>
@@ -10533,43 +10553,46 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>19006</v>
+        <v>13230</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>346</v>
+        <v>281</v>
       </c>
       <c r="C99" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="100" customFormat="1" spans="1:3">
+    <row r="100" spans="1:3">
       <c r="A100">
-        <v>19100</v>
+        <v>13240</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>500</v>
+        <v>282</v>
       </c>
       <c r="C100" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="101" customFormat="1" spans="1:3">
+    <row r="101" spans="1:4">
       <c r="A101">
-        <v>19101</v>
-      </c>
-      <c r="B101" t="s">
-        <v>38</v>
+        <v>14010</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="C101" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="102" customFormat="1" spans="1:3">
+        <v>104</v>
+      </c>
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102">
-        <v>19102</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>396</v>
+        <v>14020</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="C102" t="s">
         <v>104</v>
@@ -10577,10 +10600,10 @@
     </row>
     <row r="103" customFormat="1" spans="1:3">
       <c r="A103">
-        <v>19103</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>399</v>
+        <v>14021</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>500</v>
       </c>
       <c r="C103" t="s">
         <v>104</v>
@@ -10588,10 +10611,10 @@
     </row>
     <row r="104" customFormat="1" spans="1:3">
       <c r="A104">
-        <v>19104</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>397</v>
+        <v>14030</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="C104" t="s">
         <v>104</v>
@@ -10599,10 +10622,10 @@
     </row>
     <row r="105" customFormat="1" spans="1:3">
       <c r="A105">
-        <v>19105</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>501</v>
+        <v>14040</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="C105" t="s">
         <v>104</v>
@@ -10610,10 +10633,10 @@
     </row>
     <row r="106" customFormat="1" spans="1:3">
       <c r="A106">
-        <v>19106</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>398</v>
+        <v>14050</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="C106" t="s">
         <v>104</v>
@@ -10621,10 +10644,10 @@
     </row>
     <row r="107" customFormat="1" spans="1:3">
       <c r="A107">
-        <v>19107</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>288</v>
+        <v>14060</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="C107" t="s">
         <v>104</v>
@@ -10632,71 +10655,70 @@
     </row>
     <row r="108" customFormat="1" spans="1:3">
       <c r="A108">
-        <v>19108</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>291</v>
+        <v>14070</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C108" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="109" customFormat="1" spans="1:3">
+    <row r="109" customFormat="1" ht="14" spans="1:7">
       <c r="A109">
-        <v>19109</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>292</v>
+        <v>16010</v>
+      </c>
+      <c r="B109" t="s">
+        <v>297</v>
       </c>
       <c r="C109" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="D109" t="s">
+        <v>298</v>
+      </c>
+      <c r="G109" s="4"/>
+    </row>
+    <row r="110" customFormat="1" ht="14" spans="1:7">
       <c r="A110">
-        <v>31010</v>
+        <v>16020</v>
       </c>
       <c r="B110" t="s">
-        <v>453</v>
+        <v>161</v>
       </c>
       <c r="C110" t="s">
         <v>104</v>
       </c>
-      <c r="D110" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="G110" s="4"/>
+    </row>
+    <row r="111" customFormat="1" spans="1:3">
       <c r="A111">
-        <v>31020</v>
+        <v>16100</v>
       </c>
       <c r="B111" t="s">
-        <v>454</v>
+        <v>300</v>
       </c>
       <c r="C111" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" customFormat="1" spans="1:3">
       <c r="A112">
-        <v>32010</v>
+        <v>16110</v>
       </c>
       <c r="B112" t="s">
-        <v>503</v>
+        <v>301</v>
       </c>
       <c r="C112" t="s">
         <v>104</v>
       </c>
-      <c r="D112" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
+    </row>
+    <row r="113" customFormat="1" spans="1:3">
       <c r="A113">
-        <v>32020</v>
+        <v>16200</v>
       </c>
       <c r="B113" t="s">
-        <v>505</v>
+        <v>302</v>
       </c>
       <c r="C113" t="s">
         <v>104</v>
@@ -10704,10 +10726,10 @@
     </row>
     <row r="114" customFormat="1" spans="1:3">
       <c r="A114">
-        <v>32030</v>
+        <v>16210</v>
       </c>
       <c r="B114" t="s">
-        <v>506</v>
+        <v>303</v>
       </c>
       <c r="C114" t="s">
         <v>104</v>
@@ -10715,142 +10737,894 @@
     </row>
     <row r="115" customFormat="1" spans="1:3">
       <c r="A115">
+        <v>16220</v>
+      </c>
+      <c r="B115" t="s">
+        <v>304</v>
+      </c>
+      <c r="C115" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" customFormat="1" spans="1:3">
+      <c r="A116">
+        <v>16230</v>
+      </c>
+      <c r="B116" t="s">
+        <v>305</v>
+      </c>
+      <c r="C116" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" spans="1:3">
+      <c r="A117">
+        <v>16300</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C117" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" spans="1:3">
+      <c r="A118">
+        <v>16310</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C118" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" customFormat="1" spans="1:3">
+      <c r="A119">
+        <v>16320</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C119" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" spans="1:3">
+      <c r="A120">
+        <v>16400</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C120" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" spans="1:3">
+      <c r="A121">
+        <v>16410</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" customFormat="1" spans="1:4">
+      <c r="A122">
+        <v>16800</v>
+      </c>
+      <c r="B122" t="s">
+        <v>190</v>
+      </c>
+      <c r="C122" t="s">
+        <v>104</v>
+      </c>
+      <c r="D122" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" spans="1:4">
+      <c r="A123">
+        <v>16801</v>
+      </c>
+      <c r="B123" t="s">
+        <v>191</v>
+      </c>
+      <c r="C123" t="s">
+        <v>104</v>
+      </c>
+      <c r="D123" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" spans="1:4">
+      <c r="A124">
+        <v>16802</v>
+      </c>
+      <c r="B124" t="s">
+        <v>192</v>
+      </c>
+      <c r="C124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D124" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="125" customFormat="1" spans="1:4">
+      <c r="A125">
+        <v>16803</v>
+      </c>
+      <c r="B125" t="s">
+        <v>193</v>
+      </c>
+      <c r="C125" t="s">
+        <v>104</v>
+      </c>
+      <c r="D125" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" spans="1:4">
+      <c r="A126">
+        <v>16804</v>
+      </c>
+      <c r="B126" t="s">
+        <v>194</v>
+      </c>
+      <c r="C126" t="s">
+        <v>104</v>
+      </c>
+      <c r="D126" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" spans="1:4">
+      <c r="A127">
+        <v>16805</v>
+      </c>
+      <c r="B127" t="s">
+        <v>195</v>
+      </c>
+      <c r="C127" t="s">
+        <v>104</v>
+      </c>
+      <c r="D127" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" spans="1:4">
+      <c r="A128">
+        <v>16806</v>
+      </c>
+      <c r="B128" t="s">
+        <v>196</v>
+      </c>
+      <c r="C128" t="s">
+        <v>104</v>
+      </c>
+      <c r="D128" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="129" ht="14" spans="1:7">
+      <c r="A129">
+        <v>19000</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D129" t="s">
+        <v>501</v>
+      </c>
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
+        <v>19001</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C130" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <v>19002</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C131" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132">
+        <v>19003</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C132" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133">
+        <v>19004</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C133" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>19005</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C134" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>19006</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C135" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" customFormat="1" spans="1:3">
+      <c r="A136">
+        <v>19100</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C136" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" customFormat="1" spans="1:3">
+      <c r="A137">
+        <v>19101</v>
+      </c>
+      <c r="B137" t="s">
+        <v>38</v>
+      </c>
+      <c r="C137" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="138" customFormat="1" spans="1:3">
+      <c r="A138">
+        <v>19102</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C138" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" spans="1:3">
+      <c r="A139">
+        <v>19103</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C139" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" customFormat="1" spans="1:3">
+      <c r="A140">
+        <v>19104</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C140" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="141" customFormat="1" spans="1:3">
+      <c r="A141">
+        <v>19105</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C141" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" spans="1:3">
+      <c r="A142">
+        <v>19106</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C142" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" spans="1:3">
+      <c r="A143">
+        <v>19107</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C143" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" customFormat="1" spans="1:3">
+      <c r="A144">
+        <v>19108</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C144" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" spans="1:3">
+      <c r="A145">
+        <v>19109</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C145" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="146" customFormat="1" spans="1:4">
+      <c r="A146">
+        <v>20010</v>
+      </c>
+      <c r="B146" t="s">
+        <v>404</v>
+      </c>
+      <c r="C146" t="s">
+        <v>104</v>
+      </c>
+      <c r="D146" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="147" customFormat="1" spans="1:3">
+      <c r="A147">
+        <v>20020</v>
+      </c>
+      <c r="B147" t="s">
+        <v>406</v>
+      </c>
+      <c r="C147" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" spans="1:3">
+      <c r="A148">
+        <v>20030</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C148" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:3">
+      <c r="A149">
+        <v>20040</v>
+      </c>
+      <c r="B149" t="s">
+        <v>408</v>
+      </c>
+      <c r="C149" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:3">
+      <c r="A150">
+        <v>20050</v>
+      </c>
+      <c r="B150" t="s">
+        <v>409</v>
+      </c>
+      <c r="C150" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:3">
+      <c r="A151">
+        <v>20100</v>
+      </c>
+      <c r="B151" t="s">
+        <v>504</v>
+      </c>
+      <c r="C151" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:3">
+      <c r="A152">
+        <v>20110</v>
+      </c>
+      <c r="B152" t="s">
+        <v>217</v>
+      </c>
+      <c r="C152" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:3">
+      <c r="A153">
+        <v>20111</v>
+      </c>
+      <c r="B153" t="s">
+        <v>505</v>
+      </c>
+      <c r="C153" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" spans="1:3">
+      <c r="A154">
+        <v>20120</v>
+      </c>
+      <c r="B154" t="s">
+        <v>506</v>
+      </c>
+      <c r="C154" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" spans="1:3">
+      <c r="A155">
+        <v>20200</v>
+      </c>
+      <c r="B155" t="s">
+        <v>413</v>
+      </c>
+      <c r="C155" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" spans="1:3">
+      <c r="A156">
+        <v>20201</v>
+      </c>
+      <c r="B156" t="s">
+        <v>327</v>
+      </c>
+      <c r="C156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" spans="1:3">
+      <c r="A157">
+        <v>20210</v>
+      </c>
+      <c r="B157" t="s">
+        <v>414</v>
+      </c>
+      <c r="C157" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" spans="1:3">
+      <c r="A158">
+        <v>20220</v>
+      </c>
+      <c r="B158" t="s">
+        <v>415</v>
+      </c>
+      <c r="C158" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" spans="1:3">
+      <c r="A159">
+        <v>20230</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C159" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" spans="1:3">
+      <c r="A160">
+        <v>20240</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C160" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:3">
+      <c r="A161">
+        <v>20250</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" spans="1:3">
+      <c r="A162">
+        <v>20260</v>
+      </c>
+      <c r="B162" t="s">
+        <v>419</v>
+      </c>
+      <c r="C162" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" spans="1:3">
+      <c r="A163">
+        <v>20270</v>
+      </c>
+      <c r="B163" t="s">
+        <v>420</v>
+      </c>
+      <c r="C163" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:3">
+      <c r="A164">
+        <v>20280</v>
+      </c>
+      <c r="B164" t="s">
+        <v>421</v>
+      </c>
+      <c r="C164" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" spans="1:3">
+      <c r="A165">
+        <v>20290</v>
+      </c>
+      <c r="B165" t="s">
+        <v>422</v>
+      </c>
+      <c r="C165" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" spans="1:3">
+      <c r="A166">
+        <v>20300</v>
+      </c>
+      <c r="B166" t="s">
+        <v>423</v>
+      </c>
+      <c r="C166" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:3">
+      <c r="A167">
+        <v>20301</v>
+      </c>
+      <c r="B167" t="s">
+        <v>216</v>
+      </c>
+      <c r="C167" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:3">
+      <c r="A168">
+        <v>20310</v>
+      </c>
+      <c r="B168" t="s">
+        <v>424</v>
+      </c>
+      <c r="C168" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" spans="1:3">
+      <c r="A169">
+        <v>20320</v>
+      </c>
+      <c r="B169" t="s">
+        <v>425</v>
+      </c>
+      <c r="C169" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" spans="1:3">
+      <c r="A170">
+        <v>20330</v>
+      </c>
+      <c r="B170" t="s">
+        <v>426</v>
+      </c>
+      <c r="C170" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:3">
+      <c r="A171">
+        <v>20340</v>
+      </c>
+      <c r="B171" t="s">
+        <v>427</v>
+      </c>
+      <c r="C171" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:3">
+      <c r="A172">
+        <v>20350</v>
+      </c>
+      <c r="B172" t="s">
+        <v>428</v>
+      </c>
+      <c r="C172" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173">
+        <v>31010</v>
+      </c>
+      <c r="B173" t="s">
+        <v>453</v>
+      </c>
+      <c r="C173" t="s">
+        <v>104</v>
+      </c>
+      <c r="D173" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174">
+        <v>31020</v>
+      </c>
+      <c r="B174" t="s">
+        <v>454</v>
+      </c>
+      <c r="C174" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175">
+        <v>32010</v>
+      </c>
+      <c r="B175" t="s">
+        <v>508</v>
+      </c>
+      <c r="C175" t="s">
+        <v>104</v>
+      </c>
+      <c r="D175" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176">
+        <v>32020</v>
+      </c>
+      <c r="B176" t="s">
+        <v>510</v>
+      </c>
+      <c r="C176" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177" customFormat="1" spans="1:3">
+      <c r="A177">
+        <v>32030</v>
+      </c>
+      <c r="B177" t="s">
+        <v>511</v>
+      </c>
+      <c r="C177" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="178" customFormat="1" spans="1:3">
+      <c r="A178">
         <v>32040</v>
       </c>
-      <c r="B115" t="s">
-        <v>507</v>
-      </c>
-      <c r="C115" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116">
+      <c r="B178" t="s">
+        <v>512</v>
+      </c>
+      <c r="C178" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179">
         <v>33010</v>
       </c>
-      <c r="B116" t="s">
-        <v>508</v>
-      </c>
-      <c r="C116" t="s">
-        <v>104</v>
-      </c>
-      <c r="D116" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117">
+      <c r="B179" t="s">
+        <v>513</v>
+      </c>
+      <c r="C179" t="s">
+        <v>104</v>
+      </c>
+      <c r="D179" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180">
         <v>33020</v>
       </c>
-      <c r="B117" t="s">
-        <v>510</v>
-      </c>
-      <c r="C117" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118">
+      <c r="B180" t="s">
+        <v>515</v>
+      </c>
+      <c r="C180" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181">
         <v>33030</v>
       </c>
-      <c r="B118" t="s">
-        <v>511</v>
-      </c>
-      <c r="C118" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119">
+      <c r="B181" t="s">
+        <v>516</v>
+      </c>
+      <c r="C181" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182">
         <v>33040</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B182" t="s">
         <v>424</v>
       </c>
-      <c r="C119" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120">
+      <c r="C182" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183">
         <v>34010</v>
       </c>
-      <c r="B120" t="s">
-        <v>512</v>
-      </c>
-      <c r="C120" t="s">
-        <v>104</v>
-      </c>
-      <c r="D120" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121">
+      <c r="B183" t="s">
+        <v>517</v>
+      </c>
+      <c r="C183" t="s">
+        <v>104</v>
+      </c>
+      <c r="D183" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184">
         <v>34020</v>
       </c>
-      <c r="B121" t="s">
-        <v>514</v>
-      </c>
-      <c r="C121" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="122" customFormat="1" spans="1:3">
-      <c r="A122">
+      <c r="B184" t="s">
+        <v>519</v>
+      </c>
+      <c r="C184" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="185" customFormat="1" spans="1:3">
+      <c r="A185">
         <v>34030</v>
       </c>
-      <c r="B122" t="s">
-        <v>515</v>
-      </c>
-      <c r="C122" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="123" customFormat="1" spans="1:3">
-      <c r="A123">
+      <c r="B185" t="s">
+        <v>520</v>
+      </c>
+      <c r="C185" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="186" customFormat="1" spans="1:3">
+      <c r="A186">
         <v>34040</v>
       </c>
-      <c r="B123" t="s">
-        <v>516</v>
-      </c>
-      <c r="C123" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="124" customFormat="1" spans="1:3">
-      <c r="A124">
+      <c r="B186" t="s">
+        <v>521</v>
+      </c>
+      <c r="C186" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:3">
+      <c r="A187">
         <v>34050</v>
       </c>
-      <c r="B124" t="s">
-        <v>517</v>
-      </c>
-      <c r="C124" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125">
+      <c r="B187" t="s">
+        <v>522</v>
+      </c>
+      <c r="C187" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188">
         <v>35010</v>
       </c>
-      <c r="B125" t="s">
-        <v>518</v>
-      </c>
-      <c r="C125" t="s">
-        <v>104</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="B188" t="s">
+        <v>523</v>
+      </c>
+      <c r="C188" t="s">
+        <v>104</v>
+      </c>
+      <c r="D188" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126">
+    <row r="189" spans="1:3">
+      <c r="A189">
         <v>35020</v>
       </c>
-      <c r="B126" t="s">
-        <v>519</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="B189" t="s">
+        <v>524</v>
+      </c>
+      <c r="C189" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190">
+        <v>36010</v>
+      </c>
+      <c r="B190" t="s">
+        <v>525</v>
+      </c>
+      <c r="C190" t="s">
+        <v>104</v>
+      </c>
+      <c r="D190" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="191" customFormat="1" spans="1:3">
+      <c r="A191">
+        <v>36011</v>
+      </c>
+      <c r="B191" t="s">
+        <v>527</v>
+      </c>
+      <c r="C191" t="s">
         <v>104</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="528">
   <si>
     <t>Id</t>
   </si>
@@ -1619,8 +1619,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -1645,14 +1645,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -1661,16 +1653,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1678,6 +1669,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1697,9 +1696,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1714,10 +1719,26 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1728,15 +1749,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1751,7 +1766,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1759,7 +1774,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1767,25 +1782,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1804,7 +1804,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1816,19 +1840,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1846,37 +1942,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1888,97 +1978,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2020,6 +2020,17 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -2036,6 +2047,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2059,32 +2085,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -2097,7 +2097,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2115,127 +2115,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -9409,7 +9409,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -9907,35 +9907,38 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
+        <v>2500</v>
+      </c>
+      <c r="B42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
         <v>3010</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" t="s">
         <v>479</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43">
-        <v>3020</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3040</v>
+        <v>3020</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>220</v>
+        <v>329</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
@@ -9943,10 +9946,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
         <v>104</v>
@@ -9954,10 +9957,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>221</v>
+        <v>36</v>
       </c>
       <c r="C46" t="s">
         <v>104</v>
@@ -9965,10 +9968,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C47" t="s">
         <v>104</v>
@@ -9976,10 +9979,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3100</v>
+        <v>3052</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>480</v>
+        <v>222</v>
       </c>
       <c r="C48" t="s">
         <v>104</v>
@@ -9987,10 +9990,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3110</v>
+        <v>3100</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C49" t="s">
         <v>104</v>
@@ -9998,10 +10001,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3120</v>
+        <v>3110</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C50" t="s">
         <v>104</v>
@@ -10009,10 +10012,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3130</v>
+        <v>3120</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C51" t="s">
         <v>104</v>
@@ -10020,90 +10023,90 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
+        <v>3130</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>3200</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:3">
-      <c r="A53">
+      <c r="C53" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:3">
+      <c r="A54">
         <v>3210</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54">
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
         <v>6001</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" t="s">
         <v>486</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
-        <v>6002</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C55" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6100</v>
+        <v>6002</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="C56" t="s">
-        <v>235</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6010</v>
+        <v>6100</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" t="s">
         <v>104</v>
@@ -10111,142 +10114,142 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>6020</v>
+        <v>6012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C62" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>6210</v>
+        <v>6040</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C63" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C64" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>6240</v>
+        <v>6230</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C66" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C67" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6260</v>
+        <v>6250</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C68" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>6270</v>
+        <v>6260</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6280</v>
+        <v>6270</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6810</v>
+        <v>6280</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>261</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6820</v>
+        <v>6810</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C72" t="s">
         <v>104</v>
@@ -10254,10 +10257,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6830</v>
+        <v>6820</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C73" t="s">
         <v>104</v>
@@ -10265,10 +10268,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6840</v>
+        <v>6830</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C74" t="s">
         <v>104</v>
@@ -10276,10 +10279,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6850</v>
+        <v>6840</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C75" t="s">
         <v>104</v>
@@ -10287,10 +10290,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6860</v>
+        <v>6850</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C76" t="s">
         <v>104</v>
@@ -10298,10 +10301,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6870</v>
+        <v>6860</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C77" t="s">
         <v>104</v>
@@ -10309,10 +10312,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6880</v>
+        <v>6870</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C78" t="s">
         <v>104</v>
@@ -10320,46 +10323,46 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
+        <v>6880</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
         <v>6890</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80">
+      <c r="C80" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81">
         <v>10010</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C80" t="s">
-        <v>104</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C81" t="s">
+        <v>104</v>
+      </c>
+      <c r="D81" t="s">
         <v>487</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81">
-        <v>10100</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C81" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>10101</v>
+        <v>10100</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C82" t="s">
         <v>104</v>
@@ -10367,21 +10370,21 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
+        <v>10101</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C83" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
         <v>10110</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C83" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="84" customFormat="1" spans="1:3">
-      <c r="A84">
-        <v>10120</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="C84" t="s">
         <v>104</v>
@@ -10389,10 +10392,10 @@
     </row>
     <row r="85" customFormat="1" spans="1:3">
       <c r="A85">
-        <v>10121</v>
+        <v>10120</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>314</v>
+        <v>491</v>
       </c>
       <c r="C85" t="s">
         <v>104</v>
@@ -10400,10 +10403,10 @@
     </row>
     <row r="86" customFormat="1" spans="1:3">
       <c r="A86">
-        <v>10130</v>
+        <v>10121</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>492</v>
+        <v>314</v>
       </c>
       <c r="C86" t="s">
         <v>104</v>
@@ -10411,10 +10414,10 @@
     </row>
     <row r="87" customFormat="1" spans="1:3">
       <c r="A87">
-        <v>10140</v>
+        <v>10130</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C87" t="s">
         <v>104</v>
@@ -10422,10 +10425,10 @@
     </row>
     <row r="88" customFormat="1" spans="1:3">
       <c r="A88">
-        <v>10141</v>
+        <v>10140</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C88" t="s">
         <v>104</v>
@@ -10433,130 +10436,130 @@
     </row>
     <row r="89" customFormat="1" spans="1:3">
       <c r="A89">
+        <v>10141</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C89" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:3">
+      <c r="A90">
         <v>10150</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C89" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" customFormat="1" spans="1:4">
-      <c r="A90">
+      <c r="C90" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:4">
+      <c r="A91">
         <v>11010</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C90" t="s">
-        <v>104</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C91" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" t="s">
         <v>296</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" spans="1:3">
-      <c r="A91">
-        <v>11011</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C91" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:3">
       <c r="A92">
+        <v>11011</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C92" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:3">
+      <c r="A93">
         <v>11020</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C92" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="93" ht="130" spans="1:4">
-      <c r="A93">
+      <c r="C93" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" ht="130" spans="1:4">
+      <c r="A94">
         <v>12010</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C93" t="s">
-        <v>104</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C94" t="s">
+        <v>104</v>
+      </c>
+      <c r="D94" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94">
+    <row r="95" spans="1:4">
+      <c r="A95">
         <v>13010</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B95" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C94" t="s">
-        <v>104</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C95" t="s">
+        <v>104</v>
+      </c>
+      <c r="D95" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95">
-        <v>13020</v>
-      </c>
-      <c r="B95" s="3"/>
-      <c r="C95" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
+        <v>13020</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
         <v>13110</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>275</v>
       </c>
-      <c r="C96" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97">
+      <c r="C97" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98">
         <v>13210</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C97" t="s">
-        <v>104</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C98" t="s">
+        <v>104</v>
+      </c>
+      <c r="D98" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98">
-        <v>13220</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C98" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>13230</v>
+        <v>13220</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C99" t="s">
         <v>104</v>
@@ -10564,57 +10567,57 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
+        <v>13230</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C100" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
         <v>13240</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C100" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101">
+      <c r="C101" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:3">
+      <c r="A102">
+        <v>13320</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103">
         <v>14010</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="C101" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C103" t="s">
+        <v>104</v>
+      </c>
+      <c r="D103" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
-      <c r="A102">
+    <row r="104" spans="1:3">
+      <c r="A104">
         <v>14020</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C102" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="103" customFormat="1" spans="1:3">
-      <c r="A103">
-        <v>14021</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="C103" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="104" customFormat="1" spans="1:3">
-      <c r="A104">
-        <v>14030</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="C104" t="s">
         <v>104</v>
@@ -10622,10 +10625,10 @@
     </row>
     <row r="105" customFormat="1" spans="1:3">
       <c r="A105">
-        <v>14040</v>
+        <v>14021</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>324</v>
+        <v>500</v>
       </c>
       <c r="C105" t="s">
         <v>104</v>
@@ -10633,10 +10636,10 @@
     </row>
     <row r="106" customFormat="1" spans="1:3">
       <c r="A106">
-        <v>14050</v>
+        <v>14030</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C106" t="s">
         <v>104</v>
@@ -10644,10 +10647,10 @@
     </row>
     <row r="107" customFormat="1" spans="1:3">
       <c r="A107">
-        <v>14060</v>
+        <v>14040</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C107" t="s">
         <v>104</v>
@@ -10655,70 +10658,70 @@
     </row>
     <row r="108" customFormat="1" spans="1:3">
       <c r="A108">
+        <v>14050</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C108" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" spans="1:3">
+      <c r="A109">
+        <v>14060</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C109" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" spans="1:3">
+      <c r="A110">
         <v>14070</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B110" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C108" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="109" customFormat="1" ht="14" spans="1:7">
-      <c r="A109">
+      <c r="C110" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" ht="14" spans="1:7">
+      <c r="A111">
         <v>16010</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B111" t="s">
         <v>297</v>
       </c>
-      <c r="C109" t="s">
-        <v>104</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C111" t="s">
+        <v>104</v>
+      </c>
+      <c r="D111" t="s">
         <v>298</v>
       </c>
-      <c r="G109" s="4"/>
-    </row>
-    <row r="110" customFormat="1" ht="14" spans="1:7">
-      <c r="A110">
+      <c r="G111" s="4"/>
+    </row>
+    <row r="112" customFormat="1" ht="14" spans="1:7">
+      <c r="A112">
         <v>16020</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B112" t="s">
         <v>161</v>
       </c>
-      <c r="C110" t="s">
-        <v>104</v>
-      </c>
-      <c r="G110" s="4"/>
-    </row>
-    <row r="111" customFormat="1" spans="1:3">
-      <c r="A111">
-        <v>16100</v>
-      </c>
-      <c r="B111" t="s">
-        <v>300</v>
-      </c>
-      <c r="C111" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="112" customFormat="1" spans="1:3">
-      <c r="A112">
-        <v>16110</v>
-      </c>
-      <c r="B112" t="s">
-        <v>301</v>
-      </c>
       <c r="C112" t="s">
         <v>104</v>
       </c>
+      <c r="G112" s="4"/>
     </row>
     <row r="113" customFormat="1" spans="1:3">
       <c r="A113">
-        <v>16200</v>
+        <v>16100</v>
       </c>
       <c r="B113" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C113" t="s">
         <v>104</v>
@@ -10726,10 +10729,10 @@
     </row>
     <row r="114" customFormat="1" spans="1:3">
       <c r="A114">
-        <v>16210</v>
+        <v>16110</v>
       </c>
       <c r="B114" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C114" t="s">
         <v>104</v>
@@ -10737,10 +10740,10 @@
     </row>
     <row r="115" customFormat="1" spans="1:3">
       <c r="A115">
-        <v>16220</v>
+        <v>16200</v>
       </c>
       <c r="B115" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C115" t="s">
         <v>104</v>
@@ -10748,10 +10751,10 @@
     </row>
     <row r="116" customFormat="1" spans="1:3">
       <c r="A116">
-        <v>16230</v>
+        <v>16210</v>
       </c>
       <c r="B116" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C116" t="s">
         <v>104</v>
@@ -10759,10 +10762,10 @@
     </row>
     <row r="117" customFormat="1" spans="1:3">
       <c r="A117">
-        <v>16300</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>306</v>
+        <v>16220</v>
+      </c>
+      <c r="B117" t="s">
+        <v>304</v>
       </c>
       <c r="C117" t="s">
         <v>104</v>
@@ -10770,10 +10773,10 @@
     </row>
     <row r="118" customFormat="1" spans="1:3">
       <c r="A118">
-        <v>16310</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>307</v>
+        <v>16230</v>
+      </c>
+      <c r="B118" t="s">
+        <v>305</v>
       </c>
       <c r="C118" t="s">
         <v>104</v>
@@ -10781,10 +10784,10 @@
     </row>
     <row r="119" customFormat="1" spans="1:3">
       <c r="A119">
-        <v>16320</v>
+        <v>16300</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C119" t="s">
         <v>104</v>
@@ -10792,10 +10795,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:3">
       <c r="A120">
-        <v>16400</v>
+        <v>16310</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C120" t="s">
         <v>104</v>
@@ -10803,49 +10806,43 @@
     </row>
     <row r="121" customFormat="1" spans="1:3">
       <c r="A121">
+        <v>16320</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C121" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" customFormat="1" spans="1:3">
+      <c r="A122">
+        <v>16400</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C122" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" spans="1:3">
+      <c r="A123">
         <v>16410</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B123" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C121" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="122" customFormat="1" spans="1:4">
-      <c r="A122">
-        <v>16800</v>
-      </c>
-      <c r="B122" t="s">
-        <v>190</v>
-      </c>
-      <c r="C122" t="s">
-        <v>104</v>
-      </c>
-      <c r="D122" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="123" customFormat="1" spans="1:4">
-      <c r="A123">
-        <v>16801</v>
-      </c>
-      <c r="B123" t="s">
-        <v>191</v>
-      </c>
       <c r="C123" t="s">
         <v>104</v>
-      </c>
-      <c r="D123" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:4">
       <c r="A124">
-        <v>16802</v>
+        <v>16800</v>
       </c>
       <c r="B124" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C124" t="s">
         <v>104</v>
@@ -10856,10 +10853,10 @@
     </row>
     <row r="125" customFormat="1" spans="1:4">
       <c r="A125">
-        <v>16803</v>
+        <v>16801</v>
       </c>
       <c r="B125" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C125" t="s">
         <v>104</v>
@@ -10870,10 +10867,10 @@
     </row>
     <row r="126" customFormat="1" spans="1:4">
       <c r="A126">
-        <v>16804</v>
+        <v>16802</v>
       </c>
       <c r="B126" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C126" t="s">
         <v>104</v>
@@ -10884,10 +10881,10 @@
     </row>
     <row r="127" customFormat="1" spans="1:4">
       <c r="A127">
-        <v>16805</v>
+        <v>16803</v>
       </c>
       <c r="B127" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C127" t="s">
         <v>104</v>
@@ -10898,10 +10895,10 @@
     </row>
     <row r="128" customFormat="1" spans="1:4">
       <c r="A128">
-        <v>16806</v>
+        <v>16804</v>
       </c>
       <c r="B128" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C128" t="s">
         <v>104</v>
@@ -10910,49 +10907,55 @@
         <v>311</v>
       </c>
     </row>
-    <row r="129" ht="14" spans="1:7">
+    <row r="129" customFormat="1" spans="1:4">
       <c r="A129">
+        <v>16805</v>
+      </c>
+      <c r="B129" t="s">
+        <v>195</v>
+      </c>
+      <c r="C129" t="s">
+        <v>104</v>
+      </c>
+      <c r="D129" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" spans="1:4">
+      <c r="A130">
+        <v>16806</v>
+      </c>
+      <c r="B130" t="s">
+        <v>196</v>
+      </c>
+      <c r="C130" t="s">
+        <v>104</v>
+      </c>
+      <c r="D130" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="131" ht="14" spans="1:7">
+      <c r="A131">
         <v>19000</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C129" t="s">
-        <v>104</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="C131" t="s">
+        <v>104</v>
+      </c>
+      <c r="D131" t="s">
         <v>501</v>
       </c>
-      <c r="G129" s="4"/>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130">
-        <v>19001</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C130" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131">
-        <v>19002</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C131" t="s">
-        <v>104</v>
-      </c>
+      <c r="G131" s="4"/>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>19003</v>
+        <v>19001</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C132" t="s">
         <v>104</v>
@@ -10960,10 +10963,10 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>19004</v>
+        <v>19002</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C133" t="s">
         <v>104</v>
@@ -10971,10 +10974,10 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19005</v>
+        <v>19003</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C134" t="s">
         <v>104</v>
@@ -10982,43 +10985,43 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
+        <v>19004</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C135" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>19005</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C136" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
         <v>19006</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C135" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="136" customFormat="1" spans="1:3">
-      <c r="A136">
-        <v>19100</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C136" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="137" customFormat="1" spans="1:3">
-      <c r="A137">
-        <v>19101</v>
-      </c>
-      <c r="B137" t="s">
-        <v>38</v>
-      </c>
       <c r="C137" t="s">
-        <v>289</v>
+        <v>104</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:3">
       <c r="A138">
-        <v>19102</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>396</v>
+        <v>19100</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="C138" t="s">
         <v>104</v>
@@ -11026,21 +11029,21 @@
     </row>
     <row r="139" customFormat="1" spans="1:3">
       <c r="A139">
-        <v>19103</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>399</v>
+        <v>19101</v>
+      </c>
+      <c r="B139" t="s">
+        <v>38</v>
       </c>
       <c r="C139" t="s">
-        <v>104</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140" customFormat="1" spans="1:3">
       <c r="A140">
-        <v>19104</v>
+        <v>19102</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C140" t="s">
         <v>104</v>
@@ -11048,10 +11051,10 @@
     </row>
     <row r="141" customFormat="1" spans="1:3">
       <c r="A141">
-        <v>19105</v>
+        <v>19103</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="C141" t="s">
         <v>104</v>
@@ -11059,10 +11062,10 @@
     </row>
     <row r="142" customFormat="1" spans="1:3">
       <c r="A142">
-        <v>19106</v>
+        <v>19104</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C142" t="s">
         <v>104</v>
@@ -11070,10 +11073,10 @@
     </row>
     <row r="143" customFormat="1" spans="1:3">
       <c r="A143">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>288</v>
+        <v>503</v>
       </c>
       <c r="C143" t="s">
         <v>104</v>
@@ -11081,10 +11084,10 @@
     </row>
     <row r="144" customFormat="1" spans="1:3">
       <c r="A144">
-        <v>19108</v>
+        <v>19106</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>291</v>
+        <v>398</v>
       </c>
       <c r="C144" t="s">
         <v>104</v>
@@ -11092,57 +11095,57 @@
     </row>
     <row r="145" customFormat="1" spans="1:3">
       <c r="A145">
-        <v>19109</v>
+        <v>19107</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C145" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="146" customFormat="1" spans="1:4">
+    <row r="146" customFormat="1" spans="1:3">
       <c r="A146">
-        <v>20010</v>
-      </c>
-      <c r="B146" t="s">
-        <v>404</v>
+        <v>19108</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="C146" t="s">
         <v>104</v>
-      </c>
-      <c r="D146" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="147" customFormat="1" spans="1:3">
       <c r="A147">
-        <v>20020</v>
-      </c>
-      <c r="B147" t="s">
-        <v>406</v>
+        <v>19109</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="C147" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="148" customFormat="1" spans="1:3">
+    <row r="148" customFormat="1" spans="1:4">
       <c r="A148">
-        <v>20030</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>407</v>
+        <v>20010</v>
+      </c>
+      <c r="B148" t="s">
+        <v>404</v>
       </c>
       <c r="C148" t="s">
         <v>104</v>
+      </c>
+      <c r="D148" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:3">
       <c r="A149">
-        <v>20040</v>
+        <v>20020</v>
       </c>
       <c r="B149" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C149" t="s">
         <v>104</v>
@@ -11150,10 +11153,10 @@
     </row>
     <row r="150" customFormat="1" spans="1:3">
       <c r="A150">
-        <v>20050</v>
-      </c>
-      <c r="B150" t="s">
-        <v>409</v>
+        <v>20030</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="C150" t="s">
         <v>104</v>
@@ -11161,10 +11164,10 @@
     </row>
     <row r="151" customFormat="1" spans="1:3">
       <c r="A151">
-        <v>20100</v>
+        <v>20040</v>
       </c>
       <c r="B151" t="s">
-        <v>504</v>
+        <v>408</v>
       </c>
       <c r="C151" t="s">
         <v>104</v>
@@ -11172,10 +11175,10 @@
     </row>
     <row r="152" customFormat="1" spans="1:3">
       <c r="A152">
-        <v>20110</v>
+        <v>20050</v>
       </c>
       <c r="B152" t="s">
-        <v>217</v>
+        <v>409</v>
       </c>
       <c r="C152" t="s">
         <v>104</v>
@@ -11183,10 +11186,10 @@
     </row>
     <row r="153" customFormat="1" spans="1:3">
       <c r="A153">
-        <v>20111</v>
+        <v>20100</v>
       </c>
       <c r="B153" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C153" t="s">
         <v>104</v>
@@ -11194,10 +11197,10 @@
     </row>
     <row r="154" customFormat="1" spans="1:3">
       <c r="A154">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="B154" t="s">
-        <v>506</v>
+        <v>217</v>
       </c>
       <c r="C154" t="s">
         <v>104</v>
@@ -11205,10 +11208,10 @@
     </row>
     <row r="155" customFormat="1" spans="1:3">
       <c r="A155">
-        <v>20200</v>
+        <v>20111</v>
       </c>
       <c r="B155" t="s">
-        <v>413</v>
+        <v>505</v>
       </c>
       <c r="C155" t="s">
         <v>104</v>
@@ -11216,10 +11219,10 @@
     </row>
     <row r="156" customFormat="1" spans="1:3">
       <c r="A156">
-        <v>20201</v>
+        <v>20120</v>
       </c>
       <c r="B156" t="s">
-        <v>327</v>
+        <v>506</v>
       </c>
       <c r="C156" t="s">
         <v>104</v>
@@ -11227,10 +11230,10 @@
     </row>
     <row r="157" customFormat="1" spans="1:3">
       <c r="A157">
-        <v>20210</v>
+        <v>20200</v>
       </c>
       <c r="B157" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C157" t="s">
         <v>104</v>
@@ -11238,10 +11241,10 @@
     </row>
     <row r="158" customFormat="1" spans="1:3">
       <c r="A158">
-        <v>20220</v>
+        <v>20201</v>
       </c>
       <c r="B158" t="s">
-        <v>415</v>
+        <v>327</v>
       </c>
       <c r="C158" t="s">
         <v>104</v>
@@ -11249,10 +11252,10 @@
     </row>
     <row r="159" customFormat="1" spans="1:3">
       <c r="A159">
-        <v>20230</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>416</v>
+        <v>20210</v>
+      </c>
+      <c r="B159" t="s">
+        <v>414</v>
       </c>
       <c r="C159" t="s">
         <v>104</v>
@@ -11260,10 +11263,10 @@
     </row>
     <row r="160" customFormat="1" spans="1:3">
       <c r="A160">
-        <v>20240</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>417</v>
+        <v>20220</v>
+      </c>
+      <c r="B160" t="s">
+        <v>415</v>
       </c>
       <c r="C160" t="s">
         <v>104</v>
@@ -11271,10 +11274,10 @@
     </row>
     <row r="161" customFormat="1" spans="1:3">
       <c r="A161">
-        <v>20250</v>
+        <v>20230</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C161" t="s">
         <v>104</v>
@@ -11282,10 +11285,10 @@
     </row>
     <row r="162" customFormat="1" spans="1:3">
       <c r="A162">
-        <v>20260</v>
-      </c>
-      <c r="B162" t="s">
-        <v>419</v>
+        <v>20240</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="C162" t="s">
         <v>104</v>
@@ -11293,10 +11296,10 @@
     </row>
     <row r="163" customFormat="1" spans="1:3">
       <c r="A163">
-        <v>20270</v>
-      </c>
-      <c r="B163" t="s">
-        <v>420</v>
+        <v>20250</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="C163" t="s">
         <v>104</v>
@@ -11304,10 +11307,10 @@
     </row>
     <row r="164" customFormat="1" spans="1:3">
       <c r="A164">
-        <v>20280</v>
+        <v>20260</v>
       </c>
       <c r="B164" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C164" t="s">
         <v>104</v>
@@ -11315,10 +11318,10 @@
     </row>
     <row r="165" customFormat="1" spans="1:3">
       <c r="A165">
-        <v>20290</v>
+        <v>20270</v>
       </c>
       <c r="B165" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C165" t="s">
         <v>104</v>
@@ -11326,10 +11329,10 @@
     </row>
     <row r="166" customFormat="1" spans="1:3">
       <c r="A166">
-        <v>20300</v>
+        <v>20280</v>
       </c>
       <c r="B166" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C166" t="s">
         <v>104</v>
@@ -11337,10 +11340,10 @@
     </row>
     <row r="167" customFormat="1" spans="1:3">
       <c r="A167">
-        <v>20301</v>
+        <v>20290</v>
       </c>
       <c r="B167" t="s">
-        <v>216</v>
+        <v>422</v>
       </c>
       <c r="C167" t="s">
         <v>104</v>
@@ -11348,10 +11351,10 @@
     </row>
     <row r="168" customFormat="1" spans="1:3">
       <c r="A168">
-        <v>20310</v>
+        <v>20300</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C168" t="s">
         <v>104</v>
@@ -11359,10 +11362,10 @@
     </row>
     <row r="169" customFormat="1" spans="1:3">
       <c r="A169">
-        <v>20320</v>
+        <v>20301</v>
       </c>
       <c r="B169" t="s">
-        <v>425</v>
+        <v>216</v>
       </c>
       <c r="C169" t="s">
         <v>104</v>
@@ -11370,10 +11373,10 @@
     </row>
     <row r="170" customFormat="1" spans="1:3">
       <c r="A170">
-        <v>20330</v>
+        <v>20310</v>
       </c>
       <c r="B170" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C170" t="s">
         <v>104</v>
@@ -11381,10 +11384,10 @@
     </row>
     <row r="171" customFormat="1" spans="1:3">
       <c r="A171">
-        <v>20340</v>
+        <v>20320</v>
       </c>
       <c r="B171" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C171" t="s">
         <v>104</v>
@@ -11392,35 +11395,32 @@
     </row>
     <row r="172" customFormat="1" spans="1:3">
       <c r="A172">
+        <v>20330</v>
+      </c>
+      <c r="B172" t="s">
+        <v>426</v>
+      </c>
+      <c r="C172" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:3">
+      <c r="A173">
+        <v>20340</v>
+      </c>
+      <c r="B173" t="s">
+        <v>427</v>
+      </c>
+      <c r="C173" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="174" customFormat="1" spans="1:3">
+      <c r="A174">
         <v>20350</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B174" t="s">
         <v>428</v>
-      </c>
-      <c r="C172" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
-      <c r="A173">
-        <v>31010</v>
-      </c>
-      <c r="B173" t="s">
-        <v>453</v>
-      </c>
-      <c r="C173" t="s">
-        <v>104</v>
-      </c>
-      <c r="D173" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174">
-        <v>31020</v>
-      </c>
-      <c r="B174" t="s">
-        <v>454</v>
       </c>
       <c r="C174" t="s">
         <v>104</v>
@@ -11428,140 +11428,143 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175">
-        <v>32010</v>
+        <v>31010</v>
       </c>
       <c r="B175" t="s">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="C175" t="s">
         <v>104</v>
       </c>
       <c r="D175" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
+        <v>31020</v>
+      </c>
+      <c r="B176" t="s">
+        <v>454</v>
+      </c>
+      <c r="C176" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177">
+        <v>32010</v>
+      </c>
+      <c r="B177" t="s">
+        <v>508</v>
+      </c>
+      <c r="C177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D177" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
         <v>32020</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B178" t="s">
         <v>510</v>
       </c>
-      <c r="C176" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="177" customFormat="1" spans="1:3">
-      <c r="A177">
+      <c r="C178" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="179" customFormat="1" spans="1:3">
+      <c r="A179">
         <v>32030</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B179" t="s">
         <v>511</v>
       </c>
-      <c r="C177" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="178" customFormat="1" spans="1:3">
-      <c r="A178">
+      <c r="C179" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="180" customFormat="1" spans="1:3">
+      <c r="A180">
         <v>32040</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B180" t="s">
         <v>512</v>
       </c>
-      <c r="C178" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
-      <c r="A179">
+      <c r="C180" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181">
         <v>33010</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B181" t="s">
         <v>513</v>
       </c>
-      <c r="C179" t="s">
-        <v>104</v>
-      </c>
-      <c r="D179" t="s">
+      <c r="C181" t="s">
+        <v>104</v>
+      </c>
+      <c r="D181" t="s">
         <v>514</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180">
-        <v>33020</v>
-      </c>
-      <c r="B180" t="s">
-        <v>515</v>
-      </c>
-      <c r="C180" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181">
-        <v>33030</v>
-      </c>
-      <c r="B181" t="s">
-        <v>516</v>
-      </c>
-      <c r="C181" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>33040</v>
+        <v>33020</v>
       </c>
       <c r="B182" t="s">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="C182" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:3">
       <c r="A183">
-        <v>34010</v>
+        <v>33030</v>
       </c>
       <c r="B183" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C183" t="s">
         <v>104</v>
-      </c>
-      <c r="D183" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
+        <v>33040</v>
+      </c>
+      <c r="B184" t="s">
+        <v>424</v>
+      </c>
+      <c r="C184" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185">
+        <v>34010</v>
+      </c>
+      <c r="B185" t="s">
+        <v>517</v>
+      </c>
+      <c r="C185" t="s">
+        <v>104</v>
+      </c>
+      <c r="D185" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186">
         <v>34020</v>
       </c>
-      <c r="B184" t="s">
+      <c r="B186" t="s">
         <v>519</v>
-      </c>
-      <c r="C184" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="185" customFormat="1" spans="1:3">
-      <c r="A185">
-        <v>34030</v>
-      </c>
-      <c r="B185" t="s">
-        <v>520</v>
-      </c>
-      <c r="C185" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="186" customFormat="1" spans="1:3">
-      <c r="A186">
-        <v>34040</v>
-      </c>
-      <c r="B186" t="s">
-        <v>521</v>
       </c>
       <c r="C186" t="s">
         <v>104</v>
@@ -11569,35 +11572,32 @@
     </row>
     <row r="187" customFormat="1" spans="1:3">
       <c r="A187">
+        <v>34030</v>
+      </c>
+      <c r="B187" t="s">
+        <v>520</v>
+      </c>
+      <c r="C187" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="188" customFormat="1" spans="1:3">
+      <c r="A188">
+        <v>34040</v>
+      </c>
+      <c r="B188" t="s">
+        <v>521</v>
+      </c>
+      <c r="C188" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="189" customFormat="1" spans="1:3">
+      <c r="A189">
         <v>34050</v>
       </c>
-      <c r="B187" t="s">
+      <c r="B189" t="s">
         <v>522</v>
-      </c>
-      <c r="C187" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
-      <c r="A188">
-        <v>35010</v>
-      </c>
-      <c r="B188" t="s">
-        <v>523</v>
-      </c>
-      <c r="C188" t="s">
-        <v>104</v>
-      </c>
-      <c r="D188" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189">
-        <v>35020</v>
-      </c>
-      <c r="B189" t="s">
-        <v>524</v>
       </c>
       <c r="C189" t="s">
         <v>104</v>
@@ -11605,26 +11605,51 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190">
+        <v>35010</v>
+      </c>
+      <c r="B190" t="s">
+        <v>523</v>
+      </c>
+      <c r="C190" t="s">
+        <v>104</v>
+      </c>
+      <c r="D190" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191">
+        <v>35020</v>
+      </c>
+      <c r="B191" t="s">
+        <v>524</v>
+      </c>
+      <c r="C191" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192">
         <v>36010</v>
       </c>
-      <c r="B190" t="s">
+      <c r="B192" t="s">
         <v>525</v>
       </c>
-      <c r="C190" t="s">
-        <v>104</v>
-      </c>
-      <c r="D190" t="s">
+      <c r="C192" t="s">
+        <v>104</v>
+      </c>
+      <c r="D192" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="191" customFormat="1" spans="1:3">
-      <c r="A191">
+    <row r="193" customFormat="1" spans="1:3">
+      <c r="A193">
         <v>36011</v>
       </c>
-      <c r="B191" t="s">
+      <c r="B193" t="s">
         <v>527</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C193" t="s">
         <v>104</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="530">
   <si>
     <t>Id</t>
   </si>
@@ -1508,13 +1508,19 @@
     <t>帰還しますか？</t>
   </si>
   <si>
+    <t>呪いが解けるまで帰還できない！</t>
+  </si>
+  <si>
     <t>アーティファクトを献上しますか？</t>
   </si>
   <si>
     <t>アーティファクトを入手し評価値が\d減少しました</t>
   </si>
   <si>
-    <t>全滅してしまった…</t>
+    <t>エンフェリア達は力尽きた…</t>
+  </si>
+  <si>
+    <t>呪いが解けたようだ…</t>
   </si>
   <si>
     <t>エインフェリアを召喚しますか？</t>
@@ -1618,10 +1624,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1645,18 +1651,34 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1667,8 +1689,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1683,7 +1714,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1697,29 +1735,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1734,24 +1757,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1772,22 +1794,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1798,7 +1804,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1810,43 +1894,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1864,19 +1918,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1894,49 +1948,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1954,31 +1966,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1989,6 +1995,50 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2016,26 +2066,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2047,21 +2077,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2080,15 +2095,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2097,145 +2103,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -9409,7 +9415,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -10425,7 +10431,7 @@
     </row>
     <row r="88" customFormat="1" spans="1:3">
       <c r="A88">
-        <v>10140</v>
+        <v>10131</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>493</v>
@@ -10436,7 +10442,7 @@
     </row>
     <row r="89" customFormat="1" spans="1:3">
       <c r="A89">
-        <v>10141</v>
+        <v>10140</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>494</v>
@@ -10447,7 +10453,7 @@
     </row>
     <row r="90" customFormat="1" spans="1:3">
       <c r="A90">
-        <v>10150</v>
+        <v>10141</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>495</v>
@@ -10456,9 +10462,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="91" customFormat="1" spans="1:4">
+    <row r="91" customFormat="1" spans="1:3">
       <c r="A91">
-        <v>11010</v>
+        <v>10150</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>496</v>
@@ -10466,16 +10472,13 @@
       <c r="C91" t="s">
         <v>104</v>
       </c>
-      <c r="D91" t="s">
-        <v>296</v>
-      </c>
     </row>
     <row r="92" customFormat="1" spans="1:3">
       <c r="A92">
-        <v>11011</v>
+        <v>10160</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C92" t="s">
         <v>104</v>
@@ -10483,69 +10486,71 @@
     </row>
     <row r="93" customFormat="1" spans="1:3">
       <c r="A93">
+        <v>10161</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C93" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:4">
+      <c r="A94">
+        <v>11010</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C94" t="s">
+        <v>104</v>
+      </c>
+      <c r="D94" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:3">
+      <c r="A95">
+        <v>11011</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C95" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:3">
+      <c r="A96">
         <v>11020</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C93" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="94" ht="130" spans="1:4">
-      <c r="A94">
+      <c r="B96" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C96" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97" ht="130" spans="1:4">
+      <c r="A97">
         <v>12010</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C94" t="s">
-        <v>104</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C97" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95">
-        <v>13010</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C95" t="s">
-        <v>104</v>
-      </c>
-      <c r="D95" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96">
-        <v>13020</v>
-      </c>
-      <c r="B96" s="3"/>
-      <c r="C96" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97">
-        <v>13110</v>
-      </c>
-      <c r="B97" t="s">
-        <v>275</v>
-      </c>
-      <c r="C97" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>13210</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>279</v>
+        <v>13010</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="C98" t="s">
         <v>104</v>
@@ -10556,68 +10561,66 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>13220</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>280</v>
-      </c>
+        <v>13020</v>
+      </c>
+      <c r="B99" s="3"/>
       <c r="C99" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
+        <v>13110</v>
+      </c>
+      <c r="B100" t="s">
+        <v>275</v>
+      </c>
+      <c r="C100" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101">
+        <v>13210</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C101" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>13220</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
         <v>13230</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C100" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101">
-        <v>13240</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C101" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="102" customFormat="1" spans="1:3">
-      <c r="A102">
-        <v>13320</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C102" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103">
-        <v>14010</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C103" t="s">
         <v>104</v>
-      </c>
-      <c r="D103" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>14020</v>
+        <v>13240</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="C104" t="s">
         <v>104</v>
@@ -10625,32 +10628,35 @@
     </row>
     <row r="105" customFormat="1" spans="1:3">
       <c r="A105">
-        <v>14021</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>500</v>
+        <v>13320</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="C105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" customFormat="1" spans="1:3">
+    <row r="106" spans="1:4">
       <c r="A106">
-        <v>14030</v>
+        <v>14010</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>321</v>
+        <v>501</v>
       </c>
       <c r="C106" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="107" customFormat="1" spans="1:3">
+      <c r="D106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107">
-        <v>14040</v>
+        <v>14020</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>324</v>
+        <v>217</v>
       </c>
       <c r="C107" t="s">
         <v>104</v>
@@ -10658,10 +10664,10 @@
     </row>
     <row r="108" customFormat="1" spans="1:3">
       <c r="A108">
-        <v>14050</v>
+        <v>14021</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>325</v>
+        <v>502</v>
       </c>
       <c r="C108" t="s">
         <v>104</v>
@@ -10669,10 +10675,10 @@
     </row>
     <row r="109" customFormat="1" spans="1:3">
       <c r="A109">
-        <v>14060</v>
+        <v>14030</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C109" t="s">
         <v>104</v>
@@ -10680,81 +10686,81 @@
     </row>
     <row r="110" customFormat="1" spans="1:3">
       <c r="A110">
-        <v>14070</v>
+        <v>14040</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>112</v>
+        <v>324</v>
       </c>
       <c r="C110" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="111" customFormat="1" ht="14" spans="1:7">
+    <row r="111" customFormat="1" spans="1:3">
       <c r="A111">
-        <v>16010</v>
-      </c>
-      <c r="B111" t="s">
-        <v>297</v>
+        <v>14050</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="C111" t="s">
         <v>104</v>
       </c>
-      <c r="D111" t="s">
-        <v>298</v>
-      </c>
-      <c r="G111" s="4"/>
-    </row>
-    <row r="112" customFormat="1" ht="14" spans="1:7">
+    </row>
+    <row r="112" customFormat="1" spans="1:3">
       <c r="A112">
-        <v>16020</v>
-      </c>
-      <c r="B112" t="s">
-        <v>161</v>
+        <v>14060</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="C112" t="s">
         <v>104</v>
       </c>
-      <c r="G112" s="4"/>
     </row>
     <row r="113" customFormat="1" spans="1:3">
       <c r="A113">
-        <v>16100</v>
-      </c>
-      <c r="B113" t="s">
-        <v>300</v>
+        <v>14070</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C113" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="114" customFormat="1" spans="1:3">
+    <row r="114" customFormat="1" ht="14" spans="1:7">
       <c r="A114">
-        <v>16110</v>
+        <v>16010</v>
       </c>
       <c r="B114" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C114" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="115" customFormat="1" spans="1:3">
+      <c r="D114" t="s">
+        <v>298</v>
+      </c>
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" customFormat="1" ht="14" spans="1:7">
       <c r="A115">
-        <v>16200</v>
+        <v>16020</v>
       </c>
       <c r="B115" t="s">
-        <v>302</v>
+        <v>161</v>
       </c>
       <c r="C115" t="s">
         <v>104</v>
       </c>
+      <c r="G115" s="4"/>
     </row>
     <row r="116" customFormat="1" spans="1:3">
       <c r="A116">
-        <v>16210</v>
+        <v>16100</v>
       </c>
       <c r="B116" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C116" t="s">
         <v>104</v>
@@ -10762,10 +10768,10 @@
     </row>
     <row r="117" customFormat="1" spans="1:3">
       <c r="A117">
-        <v>16220</v>
+        <v>16110</v>
       </c>
       <c r="B117" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C117" t="s">
         <v>104</v>
@@ -10773,10 +10779,10 @@
     </row>
     <row r="118" customFormat="1" spans="1:3">
       <c r="A118">
-        <v>16230</v>
+        <v>16200</v>
       </c>
       <c r="B118" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C118" t="s">
         <v>104</v>
@@ -10784,10 +10790,10 @@
     </row>
     <row r="119" customFormat="1" spans="1:3">
       <c r="A119">
-        <v>16300</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>306</v>
+        <v>16210</v>
+      </c>
+      <c r="B119" t="s">
+        <v>303</v>
       </c>
       <c r="C119" t="s">
         <v>104</v>
@@ -10795,10 +10801,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:3">
       <c r="A120">
-        <v>16310</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>307</v>
+        <v>16220</v>
+      </c>
+      <c r="B120" t="s">
+        <v>304</v>
       </c>
       <c r="C120" t="s">
         <v>104</v>
@@ -10806,10 +10812,10 @@
     </row>
     <row r="121" customFormat="1" spans="1:3">
       <c r="A121">
-        <v>16320</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>308</v>
+        <v>16230</v>
+      </c>
+      <c r="B121" t="s">
+        <v>305</v>
       </c>
       <c r="C121" t="s">
         <v>104</v>
@@ -10817,10 +10823,10 @@
     </row>
     <row r="122" customFormat="1" spans="1:3">
       <c r="A122">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C122" t="s">
         <v>104</v>
@@ -10828,63 +10834,54 @@
     </row>
     <row r="123" customFormat="1" spans="1:3">
       <c r="A123">
+        <v>16310</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C123" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" spans="1:3">
+      <c r="A124">
+        <v>16320</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C124" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" customFormat="1" spans="1:3">
+      <c r="A125">
+        <v>16400</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C125" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" spans="1:3">
+      <c r="A126">
         <v>16410</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B126" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C123" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="124" customFormat="1" spans="1:4">
-      <c r="A124">
-        <v>16800</v>
-      </c>
-      <c r="B124" t="s">
-        <v>190</v>
-      </c>
-      <c r="C124" t="s">
-        <v>104</v>
-      </c>
-      <c r="D124" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="125" customFormat="1" spans="1:4">
-      <c r="A125">
-        <v>16801</v>
-      </c>
-      <c r="B125" t="s">
-        <v>191</v>
-      </c>
-      <c r="C125" t="s">
-        <v>104</v>
-      </c>
-      <c r="D125" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="126" customFormat="1" spans="1:4">
-      <c r="A126">
-        <v>16802</v>
-      </c>
-      <c r="B126" t="s">
-        <v>192</v>
-      </c>
       <c r="C126" t="s">
         <v>104</v>
-      </c>
-      <c r="D126" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:4">
       <c r="A127">
-        <v>16803</v>
+        <v>16800</v>
       </c>
       <c r="B127" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C127" t="s">
         <v>104</v>
@@ -10895,10 +10892,10 @@
     </row>
     <row r="128" customFormat="1" spans="1:4">
       <c r="A128">
-        <v>16804</v>
+        <v>16801</v>
       </c>
       <c r="B128" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C128" t="s">
         <v>104</v>
@@ -10909,10 +10906,10 @@
     </row>
     <row r="129" customFormat="1" spans="1:4">
       <c r="A129">
-        <v>16805</v>
+        <v>16802</v>
       </c>
       <c r="B129" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C129" t="s">
         <v>104</v>
@@ -10923,10 +10920,10 @@
     </row>
     <row r="130" customFormat="1" spans="1:4">
       <c r="A130">
-        <v>16806</v>
+        <v>16803</v>
       </c>
       <c r="B130" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C130" t="s">
         <v>104</v>
@@ -10935,60 +10932,69 @@
         <v>311</v>
       </c>
     </row>
-    <row r="131" ht="14" spans="1:7">
+    <row r="131" customFormat="1" spans="1:4">
       <c r="A131">
+        <v>16804</v>
+      </c>
+      <c r="B131" t="s">
+        <v>194</v>
+      </c>
+      <c r="C131" t="s">
+        <v>104</v>
+      </c>
+      <c r="D131" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" spans="1:4">
+      <c r="A132">
+        <v>16805</v>
+      </c>
+      <c r="B132" t="s">
+        <v>195</v>
+      </c>
+      <c r="C132" t="s">
+        <v>104</v>
+      </c>
+      <c r="D132" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" spans="1:4">
+      <c r="A133">
+        <v>16806</v>
+      </c>
+      <c r="B133" t="s">
+        <v>196</v>
+      </c>
+      <c r="C133" t="s">
+        <v>104</v>
+      </c>
+      <c r="D133" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="134" ht="14" spans="1:7">
+      <c r="A134">
         <v>19000</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C131" t="s">
-        <v>104</v>
-      </c>
-      <c r="D131" t="s">
-        <v>501</v>
-      </c>
-      <c r="G131" s="4"/>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132">
-        <v>19001</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C132" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133">
-        <v>19002</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C133" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134">
-        <v>19003</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C134" t="s">
         <v>104</v>
       </c>
+      <c r="D134" t="s">
+        <v>503</v>
+      </c>
+      <c r="G134" s="4"/>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19004</v>
+        <v>19001</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C135" t="s">
         <v>104</v>
@@ -10996,10 +11002,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19005</v>
+        <v>19002</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C136" t="s">
         <v>104</v>
@@ -11007,43 +11013,43 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
+        <v>19003</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C137" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>19004</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C138" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>19005</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C139" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
         <v>19006</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C137" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="138" customFormat="1" spans="1:3">
-      <c r="A138">
-        <v>19100</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C138" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="139" customFormat="1" spans="1:3">
-      <c r="A139">
-        <v>19101</v>
-      </c>
-      <c r="B139" t="s">
-        <v>38</v>
-      </c>
-      <c r="C139" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="140" customFormat="1" spans="1:3">
-      <c r="A140">
-        <v>19102</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="C140" t="s">
         <v>104</v>
@@ -11051,10 +11057,10 @@
     </row>
     <row r="141" customFormat="1" spans="1:3">
       <c r="A141">
-        <v>19103</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>399</v>
+        <v>19100</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="C141" t="s">
         <v>104</v>
@@ -11062,21 +11068,21 @@
     </row>
     <row r="142" customFormat="1" spans="1:3">
       <c r="A142">
-        <v>19104</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>397</v>
+        <v>19101</v>
+      </c>
+      <c r="B142" t="s">
+        <v>38</v>
       </c>
       <c r="C142" t="s">
-        <v>104</v>
+        <v>289</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:3">
       <c r="A143">
-        <v>19105</v>
+        <v>19102</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>503</v>
+        <v>396</v>
       </c>
       <c r="C143" t="s">
         <v>104</v>
@@ -11084,10 +11090,10 @@
     </row>
     <row r="144" customFormat="1" spans="1:3">
       <c r="A144">
-        <v>19106</v>
+        <v>19103</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C144" t="s">
         <v>104</v>
@@ -11095,10 +11101,10 @@
     </row>
     <row r="145" customFormat="1" spans="1:3">
       <c r="A145">
-        <v>19107</v>
+        <v>19104</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>288</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
         <v>104</v>
@@ -11106,10 +11112,10 @@
     </row>
     <row r="146" customFormat="1" spans="1:3">
       <c r="A146">
-        <v>19108</v>
+        <v>19105</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>291</v>
+        <v>505</v>
       </c>
       <c r="C146" t="s">
         <v>104</v>
@@ -11117,35 +11123,32 @@
     </row>
     <row r="147" customFormat="1" spans="1:3">
       <c r="A147">
-        <v>19109</v>
+        <v>19106</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>292</v>
+        <v>398</v>
       </c>
       <c r="C147" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="148" customFormat="1" spans="1:4">
+    <row r="148" customFormat="1" spans="1:3">
       <c r="A148">
-        <v>20010</v>
-      </c>
-      <c r="B148" t="s">
-        <v>404</v>
+        <v>19107</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="C148" t="s">
         <v>104</v>
-      </c>
-      <c r="D148" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:3">
       <c r="A149">
-        <v>20020</v>
-      </c>
-      <c r="B149" t="s">
-        <v>406</v>
+        <v>19108</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="C149" t="s">
         <v>104</v>
@@ -11153,32 +11156,35 @@
     </row>
     <row r="150" customFormat="1" spans="1:3">
       <c r="A150">
-        <v>20030</v>
+        <v>19109</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>407</v>
+        <v>292</v>
       </c>
       <c r="C150" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="151" customFormat="1" spans="1:3">
+    <row r="151" customFormat="1" spans="1:4">
       <c r="A151">
-        <v>20040</v>
+        <v>20010</v>
       </c>
       <c r="B151" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C151" t="s">
         <v>104</v>
+      </c>
+      <c r="D151" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="152" customFormat="1" spans="1:3">
       <c r="A152">
-        <v>20050</v>
+        <v>20020</v>
       </c>
       <c r="B152" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C152" t="s">
         <v>104</v>
@@ -11186,10 +11192,10 @@
     </row>
     <row r="153" customFormat="1" spans="1:3">
       <c r="A153">
-        <v>20100</v>
-      </c>
-      <c r="B153" t="s">
-        <v>504</v>
+        <v>20030</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="C153" t="s">
         <v>104</v>
@@ -11197,10 +11203,10 @@
     </row>
     <row r="154" customFormat="1" spans="1:3">
       <c r="A154">
-        <v>20110</v>
+        <v>20040</v>
       </c>
       <c r="B154" t="s">
-        <v>217</v>
+        <v>408</v>
       </c>
       <c r="C154" t="s">
         <v>104</v>
@@ -11208,10 +11214,10 @@
     </row>
     <row r="155" customFormat="1" spans="1:3">
       <c r="A155">
-        <v>20111</v>
+        <v>20050</v>
       </c>
       <c r="B155" t="s">
-        <v>505</v>
+        <v>409</v>
       </c>
       <c r="C155" t="s">
         <v>104</v>
@@ -11219,7 +11225,7 @@
     </row>
     <row r="156" customFormat="1" spans="1:3">
       <c r="A156">
-        <v>20120</v>
+        <v>20100</v>
       </c>
       <c r="B156" t="s">
         <v>506</v>
@@ -11230,10 +11236,10 @@
     </row>
     <row r="157" customFormat="1" spans="1:3">
       <c r="A157">
-        <v>20200</v>
+        <v>20110</v>
       </c>
       <c r="B157" t="s">
-        <v>413</v>
+        <v>217</v>
       </c>
       <c r="C157" t="s">
         <v>104</v>
@@ -11241,10 +11247,10 @@
     </row>
     <row r="158" customFormat="1" spans="1:3">
       <c r="A158">
-        <v>20201</v>
+        <v>20111</v>
       </c>
       <c r="B158" t="s">
-        <v>327</v>
+        <v>507</v>
       </c>
       <c r="C158" t="s">
         <v>104</v>
@@ -11252,10 +11258,10 @@
     </row>
     <row r="159" customFormat="1" spans="1:3">
       <c r="A159">
-        <v>20210</v>
+        <v>20120</v>
       </c>
       <c r="B159" t="s">
-        <v>414</v>
+        <v>508</v>
       </c>
       <c r="C159" t="s">
         <v>104</v>
@@ -11263,10 +11269,10 @@
     </row>
     <row r="160" customFormat="1" spans="1:3">
       <c r="A160">
-        <v>20220</v>
+        <v>20200</v>
       </c>
       <c r="B160" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C160" t="s">
         <v>104</v>
@@ -11274,10 +11280,10 @@
     </row>
     <row r="161" customFormat="1" spans="1:3">
       <c r="A161">
-        <v>20230</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>416</v>
+        <v>20201</v>
+      </c>
+      <c r="B161" t="s">
+        <v>327</v>
       </c>
       <c r="C161" t="s">
         <v>104</v>
@@ -11285,10 +11291,10 @@
     </row>
     <row r="162" customFormat="1" spans="1:3">
       <c r="A162">
-        <v>20240</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>417</v>
+        <v>20210</v>
+      </c>
+      <c r="B162" t="s">
+        <v>414</v>
       </c>
       <c r="C162" t="s">
         <v>104</v>
@@ -11296,10 +11302,10 @@
     </row>
     <row r="163" customFormat="1" spans="1:3">
       <c r="A163">
-        <v>20250</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>418</v>
+        <v>20220</v>
+      </c>
+      <c r="B163" t="s">
+        <v>415</v>
       </c>
       <c r="C163" t="s">
         <v>104</v>
@@ -11307,10 +11313,10 @@
     </row>
     <row r="164" customFormat="1" spans="1:3">
       <c r="A164">
-        <v>20260</v>
-      </c>
-      <c r="B164" t="s">
-        <v>419</v>
+        <v>20230</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>416</v>
       </c>
       <c r="C164" t="s">
         <v>104</v>
@@ -11318,10 +11324,10 @@
     </row>
     <row r="165" customFormat="1" spans="1:3">
       <c r="A165">
-        <v>20270</v>
-      </c>
-      <c r="B165" t="s">
-        <v>420</v>
+        <v>20240</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>417</v>
       </c>
       <c r="C165" t="s">
         <v>104</v>
@@ -11329,10 +11335,10 @@
     </row>
     <row r="166" customFormat="1" spans="1:3">
       <c r="A166">
-        <v>20280</v>
-      </c>
-      <c r="B166" t="s">
-        <v>421</v>
+        <v>20250</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="C166" t="s">
         <v>104</v>
@@ -11340,10 +11346,10 @@
     </row>
     <row r="167" customFormat="1" spans="1:3">
       <c r="A167">
-        <v>20290</v>
+        <v>20260</v>
       </c>
       <c r="B167" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C167" t="s">
         <v>104</v>
@@ -11351,10 +11357,10 @@
     </row>
     <row r="168" customFormat="1" spans="1:3">
       <c r="A168">
-        <v>20300</v>
+        <v>20270</v>
       </c>
       <c r="B168" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C168" t="s">
         <v>104</v>
@@ -11362,10 +11368,10 @@
     </row>
     <row r="169" customFormat="1" spans="1:3">
       <c r="A169">
-        <v>20301</v>
+        <v>20280</v>
       </c>
       <c r="B169" t="s">
-        <v>216</v>
+        <v>421</v>
       </c>
       <c r="C169" t="s">
         <v>104</v>
@@ -11373,10 +11379,10 @@
     </row>
     <row r="170" customFormat="1" spans="1:3">
       <c r="A170">
-        <v>20310</v>
+        <v>20290</v>
       </c>
       <c r="B170" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C170" t="s">
         <v>104</v>
@@ -11384,10 +11390,10 @@
     </row>
     <row r="171" customFormat="1" spans="1:3">
       <c r="A171">
-        <v>20320</v>
+        <v>20300</v>
       </c>
       <c r="B171" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C171" t="s">
         <v>104</v>
@@ -11395,10 +11401,10 @@
     </row>
     <row r="172" customFormat="1" spans="1:3">
       <c r="A172">
-        <v>20330</v>
+        <v>20301</v>
       </c>
       <c r="B172" t="s">
-        <v>426</v>
+        <v>216</v>
       </c>
       <c r="C172" t="s">
         <v>104</v>
@@ -11406,10 +11412,10 @@
     </row>
     <row r="173" customFormat="1" spans="1:3">
       <c r="A173">
-        <v>20340</v>
+        <v>20310</v>
       </c>
       <c r="B173" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C173" t="s">
         <v>104</v>
@@ -11417,137 +11423,137 @@
     </row>
     <row r="174" customFormat="1" spans="1:3">
       <c r="A174">
+        <v>20320</v>
+      </c>
+      <c r="B174" t="s">
+        <v>425</v>
+      </c>
+      <c r="C174" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="175" customFormat="1" spans="1:3">
+      <c r="A175">
+        <v>20330</v>
+      </c>
+      <c r="B175" t="s">
+        <v>426</v>
+      </c>
+      <c r="C175" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="176" customFormat="1" spans="1:3">
+      <c r="A176">
+        <v>20340</v>
+      </c>
+      <c r="B176" t="s">
+        <v>427</v>
+      </c>
+      <c r="C176" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="177" customFormat="1" spans="1:3">
+      <c r="A177">
         <v>20350</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B177" t="s">
         <v>428</v>
       </c>
-      <c r="C174" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175">
+      <c r="C177" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178">
         <v>31010</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B178" t="s">
         <v>453</v>
       </c>
-      <c r="C175" t="s">
-        <v>104</v>
-      </c>
-      <c r="D175" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176">
+      <c r="C178" t="s">
+        <v>104</v>
+      </c>
+      <c r="D178" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179">
         <v>31020</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B179" t="s">
         <v>454</v>
       </c>
-      <c r="C176" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
-      <c r="A177">
+      <c r="C179" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180">
         <v>32010</v>
       </c>
-      <c r="B177" t="s">
-        <v>508</v>
-      </c>
-      <c r="C177" t="s">
-        <v>104</v>
-      </c>
-      <c r="D177" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178">
+      <c r="B180" t="s">
+        <v>510</v>
+      </c>
+      <c r="C180" t="s">
+        <v>104</v>
+      </c>
+      <c r="D180" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181">
         <v>32020</v>
       </c>
-      <c r="B178" t="s">
-        <v>510</v>
-      </c>
-      <c r="C178" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="179" customFormat="1" spans="1:3">
-      <c r="A179">
+      <c r="B181" t="s">
+        <v>512</v>
+      </c>
+      <c r="C181" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="182" customFormat="1" spans="1:3">
+      <c r="A182">
         <v>32030</v>
       </c>
-      <c r="B179" t="s">
-        <v>511</v>
-      </c>
-      <c r="C179" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="180" customFormat="1" spans="1:3">
-      <c r="A180">
+      <c r="B182" t="s">
+        <v>513</v>
+      </c>
+      <c r="C182" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="183" customFormat="1" spans="1:3">
+      <c r="A183">
         <v>32040</v>
       </c>
-      <c r="B180" t="s">
-        <v>512</v>
-      </c>
-      <c r="C180" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
-      <c r="A181">
+      <c r="B183" t="s">
+        <v>514</v>
+      </c>
+      <c r="C183" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184">
         <v>33010</v>
       </c>
-      <c r="B181" t="s">
-        <v>513</v>
-      </c>
-      <c r="C181" t="s">
-        <v>104</v>
-      </c>
-      <c r="D181" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182">
+      <c r="B184" t="s">
+        <v>515</v>
+      </c>
+      <c r="C184" t="s">
+        <v>104</v>
+      </c>
+      <c r="D184" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185">
         <v>33020</v>
-      </c>
-      <c r="B182" t="s">
-        <v>515</v>
-      </c>
-      <c r="C182" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183">
-        <v>33030</v>
-      </c>
-      <c r="B183" t="s">
-        <v>516</v>
-      </c>
-      <c r="C183" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184">
-        <v>33040</v>
-      </c>
-      <c r="B184" t="s">
-        <v>424</v>
-      </c>
-      <c r="C184" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
-      <c r="A185">
-        <v>34010</v>
       </c>
       <c r="B185" t="s">
         <v>517</v>
@@ -11555,101 +11561,134 @@
       <c r="C185" t="s">
         <v>104</v>
       </c>
-      <c r="D185" t="s">
-        <v>518</v>
-      </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
+        <v>33030</v>
+      </c>
+      <c r="B186" t="s">
+        <v>518</v>
+      </c>
+      <c r="C186" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187">
+        <v>33040</v>
+      </c>
+      <c r="B187" t="s">
+        <v>424</v>
+      </c>
+      <c r="C187" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188">
+        <v>34010</v>
+      </c>
+      <c r="B188" t="s">
+        <v>519</v>
+      </c>
+      <c r="C188" t="s">
+        <v>104</v>
+      </c>
+      <c r="D188" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189">
         <v>34020</v>
       </c>
-      <c r="B186" t="s">
-        <v>519</v>
-      </c>
-      <c r="C186" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="187" customFormat="1" spans="1:3">
-      <c r="A187">
+      <c r="B189" t="s">
+        <v>521</v>
+      </c>
+      <c r="C189" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="190" customFormat="1" spans="1:3">
+      <c r="A190">
         <v>34030</v>
       </c>
-      <c r="B187" t="s">
-        <v>520</v>
-      </c>
-      <c r="C187" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="188" customFormat="1" spans="1:3">
-      <c r="A188">
+      <c r="B190" t="s">
+        <v>522</v>
+      </c>
+      <c r="C190" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="191" customFormat="1" spans="1:3">
+      <c r="A191">
         <v>34040</v>
       </c>
-      <c r="B188" t="s">
-        <v>521</v>
-      </c>
-      <c r="C188" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="189" customFormat="1" spans="1:3">
-      <c r="A189">
+      <c r="B191" t="s">
+        <v>523</v>
+      </c>
+      <c r="C191" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="192" customFormat="1" spans="1:3">
+      <c r="A192">
         <v>34050</v>
       </c>
-      <c r="B189" t="s">
-        <v>522</v>
-      </c>
-      <c r="C189" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190">
+      <c r="B192" t="s">
+        <v>524</v>
+      </c>
+      <c r="C192" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193">
         <v>35010</v>
       </c>
-      <c r="B190" t="s">
-        <v>523</v>
-      </c>
-      <c r="C190" t="s">
-        <v>104</v>
-      </c>
-      <c r="D190" t="s">
+      <c r="B193" t="s">
+        <v>525</v>
+      </c>
+      <c r="C193" t="s">
+        <v>104</v>
+      </c>
+      <c r="D193" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
-      <c r="A191">
+    <row r="194" spans="1:3">
+      <c r="A194">
         <v>35020</v>
       </c>
-      <c r="B191" t="s">
-        <v>524</v>
-      </c>
-      <c r="C191" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
-      <c r="A192">
+      <c r="B194" t="s">
+        <v>526</v>
+      </c>
+      <c r="C194" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195">
         <v>36010</v>
       </c>
-      <c r="B192" t="s">
-        <v>525</v>
-      </c>
-      <c r="C192" t="s">
-        <v>104</v>
-      </c>
-      <c r="D192" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="193" customFormat="1" spans="1:3">
-      <c r="A193">
+      <c r="B195" t="s">
+        <v>527</v>
+      </c>
+      <c r="C195" t="s">
+        <v>104</v>
+      </c>
+      <c r="D195" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="196" customFormat="1" spans="1:3">
+      <c r="A196">
         <v>36011</v>
       </c>
-      <c r="B193" t="s">
-        <v>527</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="B196" t="s">
+        <v>529</v>
+      </c>
+      <c r="C196" t="s">
         <v>104</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="531">
   <si>
     <t>Id</t>
   </si>
@@ -1511,6 +1511,9 @@
     <t>呪いが解けるまで帰還できない！</t>
   </si>
   <si>
+    <t>呪いが解けるまで帰還できない！\n残りターン不足により経験値ボーナスが減算！</t>
+  </si>
+  <si>
     <t>アーティファクトを献上しますか？</t>
   </si>
   <si>
@@ -1520,9 +1523,6 @@
     <t>エンフェリア達は力尽きた…</t>
   </si>
   <si>
-    <t>呪いが解けたようだ…</t>
-  </si>
-  <si>
     <t>エインフェリアを召喚しますか？</t>
   </si>
   <si>
@@ -1530,6 +1530,9 @@
   </si>
   <si>
     <t>Periodが終了しヘイムダルから定期報告が入りました。</t>
+  </si>
+  <si>
+    <t>未編成の仲間がいますが出撃しますか？</t>
   </si>
   <si>
     <t>固有スキルははずすことができません！</t>
@@ -1624,10 +1627,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1651,13 +1654,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -1666,24 +1662,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1699,6 +1708,67 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -1713,55 +1783,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1769,29 +1795,6 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1804,19 +1807,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1834,13 +1873,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1864,37 +1933,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1912,25 +1951,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1942,43 +1969,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2003,6 +2006,62 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2033,65 +2092,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <c